--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.04770422987439053</v>
+        <v>0.04770771590472154</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7305704836709384</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.233775352556562</v>
+        <v>3.231033916110257</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.086534596643042</v>
+        <v>3.083907722603894</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.452054794520548</v>
+        <v>3.449315068493151</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003092360757865938</v>
+        <v>0.003094984534250477</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01494610376195347</v>
+        <v>-0.01502736314795285</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1767134960461636</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.929023246441133</v>
+        <v>1.926286958732681</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.95829208311153</v>
+        <v>1.955675606267657</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.947945205479452</v>
+        <v>1.945205479452055</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005183970705614389</v>
+        <v>0.005191334528153105</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03379411750143876</v>
+        <v>0.03378771524738287</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3143492769744161</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.564516005987335</v>
+        <v>4.561782913533029</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.415304680799736</v>
+        <v>4.412688259157157</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.947945205479452</v>
+        <v>4.945205479452055</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002190812779905442</v>
+        <v>0.002192125357463615</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0352410698033251</v>
+        <v>0.03537391376349239</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.940800144170121</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4767123287671233</v>
+        <v>0.473972602739726</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4604843670447589</v>
+        <v>0.4577791621356169</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4493150684931507</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02097701149425288</v>
+        <v>0.02109826589595376</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.128600336267571</v>
+        <v>-0.1286540991621506</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02444889779559123</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.66521302666907</v>
+        <v>6.662594167889294</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.648858846376239</v>
+        <v>7.646325255541829</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.123287671232877</v>
+        <v>7.120547945205479</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.0015003271403311</v>
+        <v>0.001500916872319119</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08378037884397396</v>
+        <v>-0.08389100991922925</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1783567134268538</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.12613607492174</v>
+        <v>2.123400097043723</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.320552873817656</v>
+        <v>2.317846588162516</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.120547945205479</v>
+        <v>2.117808219178082</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004703367822009269</v>
+        <v>0.004709428060176871</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0418503263608811</v>
+        <v>0.0419542326979498</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.547561525646646</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.057682574902438</v>
+        <v>1.054942591098275</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.015196279293646</v>
+        <v>1.012465382828471</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.032876712328767</v>
+        <v>1.03013698630137</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009454632455226385</v>
+        <v>0.009479188805515227</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1521377081046303</v>
+        <v>0.152288325142402</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.631926061159288</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.840086979166798</v>
+        <v>1.837341328569348</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.597106809561772</v>
+        <v>1.594515268860583</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.868493150684932</v>
+        <v>1.865753424657534</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005434525711674814</v>
+        <v>0.005442646853095355</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01763849166425767</v>
+        <v>-0.01766016642743377</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.3745985401459855</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.303774131954452</v>
+        <v>4.301045124640604</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.381049232319421</v>
+        <v>4.378367829184524</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.457534246575342</v>
+        <v>4.454794520547945</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002323542010662801</v>
+        <v>0.002325016294925667</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02666858191700478</v>
+        <v>0.02664415042841769</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.3594612861736335</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.827911065153962</v>
+        <v>2.82517668961387</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.754453691252206</v>
+        <v>2.751855828950009</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.947945205479452</v>
+        <v>2.945205479452055</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003536179098141321</v>
+        <v>0.0035396016244799</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.247438344803789</v>
+        <v>-3.310120331512438</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>0.07677910324969162</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1232876712328767</v>
+        <v>0.1205479452054795</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1394510225892944</v>
+        <v>-0.1395428624150412</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.004524886877828038</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.432559010178015</v>
+        <v>4.429899145044603</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.150850360098135</v>
+        <v>5.148308906447078</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.698630136986301</v>
+        <v>4.695890410958904</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002256033135044127</v>
+        <v>0.002257387735607086</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2575023764537924</v>
+        <v>-0.2576902006071873</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2310461497890295</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.365781733849452</v>
+        <v>3.363099441991152</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.533053880730691</v>
+        <v>4.530587424202222</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.452054794520548</v>
+        <v>3.449315068493151</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002971077981507428</v>
+        <v>0.002973447610600362</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1360373760499006</v>
+        <v>-0.1362518441747599</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.04513317191283295</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.087908011640671</v>
+        <v>2.08522001196124</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.416664741924373</v>
+        <v>2.414152780411999</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.213698630136986</v>
+        <v>2.210958904109589</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004789483034811497</v>
+        <v>0.004795657025463977</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02389697814209089</v>
+        <v>-0.02396140668949964</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.224082087781732</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.94934896075208</v>
+        <v>1.946610733921423</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.997072969861009</v>
+        <v>1.994399347795217</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.947945205479452</v>
+        <v>1.945205479452055</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005129917834794387</v>
+        <v>0.005137133904453062</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04894539402200596</v>
+        <v>0.04894467992692561</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.7197455752212389</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.200539154542192</v>
+        <v>3.197799820219215</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.051197109765895</v>
+        <v>3.048587672366086</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.452054794520548</v>
+        <v>3.449315068493151</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003124473570588268</v>
+        <v>0.003127150091375789</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1109301865179349</v>
+        <v>0.1110087460934481</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.175173210161663</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.922359254845625</v>
+        <v>1.91961615436935</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.730405094915108</v>
+        <v>1.72781371984617</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.947945205479452</v>
+        <v>1.945205479452055</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005201941299366048</v>
+        <v>0.00520937478945383</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03265017489340829</v>
+        <v>0.03263981184985146</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4631718646317187</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.382189515418394</v>
+        <v>3.379455174735999</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.275251965911407</v>
+        <v>3.272636921369618</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.613698630136986</v>
+        <v>3.610958904109589</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002956664596827877</v>
+        <v>0.002959056854713628</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4676913652846474</v>
+        <v>-0.4682668093259846</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.002376657021276651</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.624064693068692</v>
+        <v>1.621340196054113</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.050983183726009</v>
+        <v>3.04916116671019</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.610958904109589</v>
+        <v>1.608219178082192</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006157390184442019</v>
+        <v>0.006167737051321615</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03809293366369107</v>
+        <v>0.038094954831697</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.3336288486776695</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9753424657534246</v>
+        <v>0.9726027397260275</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9395521673682873</v>
+        <v>0.9369111517199432</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.947945205479452</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01025280898876405</v>
+        <v>0.01028169014084507</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.144681726878572</v>
+        <v>0.1447736314298172</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1546720835751594</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.015157840210544</v>
+        <v>2.012392830148</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.760452528324768</v>
+        <v>1.757895862463682</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.213698630136986</v>
+        <v>2.210958904109589</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004962390439329159</v>
+        <v>0.004969208720180422</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02917400353193243</v>
+        <v>0.02918850550555913</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8634300690223793</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.514003637926878</v>
+        <v>4.511261684779196</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.386045141478179</v>
+        <v>4.383319149647098</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.53972602739726</v>
+        <v>4.536986301369863</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002215328298803199</v>
+        <v>0.002216674779416936</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1359298852555417</v>
+        <v>0.1359896465325489</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2214315298076921</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.125067022807023</v>
+        <v>3.122289365238812</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.751109081089103</v>
+        <v>2.748519209456854</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.452054794520548</v>
+        <v>3.449315068493151</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003199931370117534</v>
+        <v>0.003202778099727838</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1244189890338069</v>
+        <v>0.1244743345233301</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.4990619136960601</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.157574487293613</v>
+        <v>3.154802126416977</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.80818317556773</v>
+        <v>2.805579486840233</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.452054794520548</v>
+        <v>3.449315068493151</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003166987838368017</v>
+        <v>0.003169770907742274</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>44.74164038513754</v>
+        <v>44.9717455807639</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4767123287671233</v>
+        <v>0.473972602739726</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.01042184593191847</v>
+        <v>0.01031008496092547</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4493150684931507</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02097701149425288</v>
+        <v>0.02109826589595376</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05717836334815342</v>
+        <v>0.05734768962015328</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.3815760722891566</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4712328767123288</v>
+        <v>0.4684931506849316</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4457458580781991</v>
+        <v>0.4430833445649608</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4493150684931507</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02122093023255814</v>
+        <v>0.02134502923976608</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.646828664088222</v>
+        <v>-1.65636062069093</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.02934219644012948</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4493150684931507</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.196772095026254</v>
+        <v>-0.1969572778094497</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.1574511910322278</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.882080684850172</v>
+        <v>2.879373704777326</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.58812320513737</v>
+        <v>3.585579727219161</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.947945205479452</v>
+        <v>2.945205479452055</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003469715491507782</v>
+        <v>0.003472977468471166</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05498689052555032</v>
+        <v>0.05498546217907816</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.4448192592592592</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.821665091806581</v>
+        <v>2.8189256830298</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.67459730272188</v>
+        <v>2.672004292085024</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.947945205479452</v>
+        <v>2.945205479452055</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003544006703360201</v>
+        <v>0.00354745073990455</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.09439034035591985</v>
+        <v>0.09442108642170288</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>2.079282229181495</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.362098408121448</v>
+        <v>2.359350948720198</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.158369204312641</v>
+        <v>2.155798145697544</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.520547945205479</v>
+        <v>2.517808219178082</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004233523872509993</v>
+        <v>0.00423845380248512</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2481920283414377</v>
+        <v>-0.248540597565487</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.07753572915221318</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.818472270985312</v>
+        <v>1.815745208691625</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.418798868245017</v>
+        <v>2.416291822032077</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.821917808219178</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005499121520605672</v>
+        <v>0.005507380634756414</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.03166409437234192</v>
+        <v>-0.03173445592016275</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.01154181184668979</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.840492888612149</v>
+        <v>2.837768101346708</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.93337556947348</v>
+        <v>2.930774639970792</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.947945205479452</v>
+        <v>2.945205479452055</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003520515766855502</v>
+        <v>0.003523896119367309</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02102500061905978</v>
+        <v>0.02099155922319175</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2123870967741937</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.851034833402464</v>
+        <v>1.848296428692582</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.812918226566597</v>
+        <v>1.810295503421042</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.868493150684932</v>
+        <v>1.865753424657534</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005402383477364704</v>
+        <v>0.005410387557299797</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.04770771590472154</v>
+        <v>0.04771121230180721</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7305704836709384</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.231033916110257</v>
+        <v>3.228292474571051</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.083907722603894</v>
+        <v>3.081280830696215</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.449315068493151</v>
+        <v>3.446575342465753</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003094984534250477</v>
+        <v>0.003097612771695576</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01502736314795285</v>
+        <v>-0.01510884004672539</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1767134960461636</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.926286958732681</v>
+        <v>1.923550680252641</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.955675606267657</v>
+        <v>1.953059138376162</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.945205479452055</v>
+        <v>1.942465753424657</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005191334528153105</v>
+        <v>0.005198719276107968</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03378771524738287</v>
+        <v>0.03378130857488733</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3143492769744161</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.561782913533029</v>
+        <v>4.559049825591419</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.412688259157157</v>
+        <v>4.410071828321474</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.945205479452055</v>
+        <v>4.942465753424657</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002192125357463615</v>
+        <v>0.002193439506597794</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03537391376349239</v>
+        <v>0.03550830712927328</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.940800144170121</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.473972602739726</v>
+        <v>0.4712328767123288</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4577791621356169</v>
+        <v>0.4550739704046623</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02109826589595376</v>
+        <v>0.02122093023255814</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1286540991621506</v>
+        <v>-0.1287079018425488</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02444889779559123</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.662594167889294</v>
+        <v>6.659975373024237</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.646325255541829</v>
+        <v>7.643791774432818</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.120547945205479</v>
+        <v>7.117808219178082</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001500916872319119</v>
+        <v>0.001501507053690363</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08389100991922925</v>
+        <v>-0.08400191312126783</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1783567134268538</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.123400097043723</v>
+        <v>2.120664128044978</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.317846588162516</v>
+        <v>2.315140346276432</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.117808219178082</v>
+        <v>2.115068493150685</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004709428060176871</v>
+        <v>0.004715503915850604</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0419542326979498</v>
+        <v>0.04205869065739071</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.547561525646646</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.054942591098275</v>
+        <v>1.052202605925751</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.012465382828471</v>
+        <v>1.009734495148215</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.03013698630137</v>
+        <v>1.027397260273973</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009479188805515227</v>
+        <v>0.00950387305988639</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.152288325142402</v>
+        <v>0.1524394260221942</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.631926061159288</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.837341328569348</v>
+        <v>1.834595659013879</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.594515268860583</v>
+        <v>1.591923720751417</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.865753424657534</v>
+        <v>1.863013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005442646853095355</v>
+        <v>0.005450792358995956</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01766016642743377</v>
+        <v>-0.01768186780162668</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.3745985401459855</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.301045124640604</v>
+        <v>4.29831613001366</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.378367829184524</v>
+        <v>4.375686439172479</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.454794520547945</v>
+        <v>4.452054794520548</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002325016294925667</v>
+        <v>0.002326492444372215</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02664415042841769</v>
+        <v>0.02661967919925202</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.3594612861736335</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.82517668961387</v>
+        <v>2.822442322710318</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.751855828950009</v>
+        <v>2.749257957836714</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.945205479452055</v>
+        <v>2.942465753424658</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.0035396016244799</v>
+        <v>0.003543030771448063</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.310120331512438</v>
+        <v>-3.375260405950111</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>0.07677910324969162</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1205479452054795</v>
+        <v>0.1178082191780822</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1395428624150412</v>
+        <v>-0.1396348037014683</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.004524886877828038</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.429899145044603</v>
+        <v>4.427239353795684</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.148308906447078</v>
+        <v>5.145767602923246</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.695890410958904</v>
+        <v>4.693150684931507</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002257387735607086</v>
+        <v>0.002258743926150395</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2576902006071873</v>
+        <v>-0.2578782799149166</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2310461497890295</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.363099441991152</v>
+        <v>3.360417210142988</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.530587424202222</v>
+        <v>4.528121356908567</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.449315068493151</v>
+        <v>3.446575342465753</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002973447610600362</v>
+        <v>0.002975820969436856</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1362518441747599</v>
+        <v>-0.1364668121415052</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.04513317191283295</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.08522001196124</v>
+        <v>2.082532126264021</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.414152780411999</v>
+        <v>2.411641099085679</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.210958904109589</v>
+        <v>2.208219178082192</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004795657025463977</v>
+        <v>0.004801846691287111</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02396140668949964</v>
+        <v>-0.02402601058593325</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.224082087781732</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.946610733921423</v>
+        <v>1.943872511175607</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.994399347795217</v>
+        <v>1.991725734763306</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.945205479452055</v>
+        <v>1.942465753424657</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005137133904453062</v>
+        <v>0.005144370293066309</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04894467992692561</v>
+        <v>0.04894397042266613</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.7197455752212389</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.197799820219215</v>
+        <v>3.195060483377739</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.048587672366086</v>
+        <v>3.045978215681346</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.449315068493151</v>
+        <v>3.446575342465753</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003127150091375789</v>
+        <v>0.003129831204143042</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1110087460934481</v>
+        <v>0.1110875494249695</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.175173210161663</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.91961615436935</v>
+        <v>1.916873043446866</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.72781371984617</v>
+        <v>1.725222323334396</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.945205479452055</v>
+        <v>1.942465753424657</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00520937478945383</v>
+        <v>0.00521682958304755</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03263981184985146</v>
+        <v>0.03262943665725368</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4631718646317187</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.379455174735999</v>
+        <v>3.376720840307528</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.272636921369618</v>
+        <v>3.270021868869419</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.610958904109589</v>
+        <v>3.608219178082192</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002959056854713628</v>
+        <v>0.002961452981434281</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4682668093259846</v>
+        <v>-0.4688435705370917</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.002376657021276651</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.621340196054113</v>
+        <v>1.618615734370366</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.04916116671019</v>
+        <v>3.047342825176885</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.608219178082192</v>
+        <v>1.605479452054795</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006167737051321615</v>
+        <v>0.006178118615589732</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.038094954831697</v>
+        <v>0.03809700826460153</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.3336288486776695</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9726027397260275</v>
+        <v>0.9698630136986303</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9369111517199432</v>
+        <v>0.9342701173178037</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9452054794520548</v>
+        <v>0.9424657534246575</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01028169014084507</v>
+        <v>0.01031073446327684</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1447736314298172</v>
+        <v>0.1448658199283509</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1546720835751594</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.012392830148</v>
+        <v>2.009627741123752</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.757895862463682</v>
+        <v>1.755339102751378</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.210958904109589</v>
+        <v>2.208219178082192</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004969208720180422</v>
+        <v>0.004976045958844179</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02918850550555913</v>
+        <v>0.02920302536897958</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8634300690223793</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.511261684779196</v>
+        <v>4.508519728813297</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.383319149647098</v>
+        <v>4.380593155754616</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.536986301369863</v>
+        <v>4.534246575342466</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002216674779416936</v>
+        <v>0.002218022899199364</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1359896465325489</v>
+        <v>0.1360495291110095</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2214315298076921</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.122289365238812</v>
+        <v>3.119511628772085</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.748519209456854</v>
+        <v>2.745929247656297</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.449315068493151</v>
+        <v>3.446575342465753</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003202778099727838</v>
+        <v>0.003205629979951779</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1244743345233301</v>
+        <v>0.1245297893582096</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.4990619136960601</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.154802126416977</v>
+        <v>3.152029699436592</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.805579486840233</v>
+        <v>2.802975723066896</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.449315068493151</v>
+        <v>3.446575342465753</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003169770907742274</v>
+        <v>0.003172558939335961</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>44.9717455807639</v>
+        <v>45.20456112213172</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.473972602739726</v>
+        <v>0.4712328767123288</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.01031008496092547</v>
+        <v>0.01019883892992138</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02109826589595376</v>
+        <v>0.02122093023255814</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05734768962015328</v>
+        <v>0.05751903296551122</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.3815760722891566</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4684931506849316</v>
+        <v>0.4657534246575342</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4430833445649608</v>
+        <v>0.4404208436338599</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02134502923976608</v>
+        <v>0.02147058823529412</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.65636062069093</v>
+        <v>-1.666003413281083</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.02934219644012948</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1969572778094497</v>
+        <v>-0.1971427672764509</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.1574511910322278</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.879373704777326</v>
+        <v>2.876666774506659</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.585579727219161</v>
+        <v>3.583036506687601</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.945205479452055</v>
+        <v>2.942465753424658</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003472977468471166</v>
+        <v>0.003476245524376029</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05498546217907816</v>
+        <v>0.05498403953597301</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.4448192592592592</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.8189256830298</v>
+        <v>2.816186272986022</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.672004292085024</v>
+        <v>2.669411258794684</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.945205479452055</v>
+        <v>2.942465753424658</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00354745073990455</v>
+        <v>0.003550901478330455</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.09442108642170288</v>
+        <v>0.0944519201283625</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>2.079282229181495</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.359350948720198</v>
+        <v>2.356603467174062</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.155798145697544</v>
+        <v>2.153227038879578</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.517808219178082</v>
+        <v>2.515068493150685</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.00423845380248512</v>
+        <v>0.004243395267508272</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.248540597565487</v>
+        <v>-0.2488900539721604</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.07753572915221318</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.815745208691625</v>
+        <v>1.813018178961106</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.416291822032077</v>
+        <v>2.413785343342941</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.819178082191781</v>
+        <v>1.816438356164384</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005507380634756414</v>
+        <v>0.005515664495835441</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.03173445592016275</v>
+        <v>-0.03180494320286069</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.01154181184668979</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.837768101346708</v>
+        <v>2.835043340191982</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.930774639970792</v>
+        <v>2.928173739670304</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.945205479452055</v>
+        <v>2.942465753424658</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003523896119367309</v>
+        <v>0.003527282937171192</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02099155922319175</v>
+        <v>0.02095802730643737</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2123870967741937</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.848296428692582</v>
+        <v>1.845558027562971</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.810295503421042</v>
+        <v>1.807672772241236</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.865753424657534</v>
+        <v>1.863013698630137</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005410387557299797</v>
+        <v>0.005418415379333716</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>967.6</v>
+        <v>947</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.04771121230180721</v>
+        <v>0.04771823629820473</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7305704836709384</v>
+        <v>0.7682154171066526</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.228292474571051</v>
+        <v>3.222809576163678</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.081280830696215</v>
+        <v>3.076026993240568</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.446575342465753</v>
+        <v>3.441095890410959</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003097612771695576</v>
+        <v>0.00310288267540264</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9358</v>
+        <v>9186</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01510884004672539</v>
+        <v>-0.01527245000650752</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1767134960461636</v>
+        <v>0.1987464506858261</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.923550680252641</v>
+        <v>1.918078151131943</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.953059138376162</v>
+        <v>1.947826229848671</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.942465753424657</v>
+        <v>1.936986301369863</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005198719276107968</v>
+        <v>0.005213551905639797</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105.5</v>
+        <v>106.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>89.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03378130857488733</v>
+        <v>0.03205807634671402</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3143492769744161</v>
+        <v>0.2940869565217392</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.559049825591419</v>
+        <v>4.555353474845992</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.410071828321474</v>
+        <v>4.413853812346551</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.942465753424657</v>
+        <v>4.936986301369863</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002193439506597794</v>
+        <v>0.002195219329349207</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5549</v>
+        <v>5584</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03550830712927328</v>
+        <v>0.0357818514455945</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.940800144170121</v>
+        <v>1.922367478510029</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4712328767123288</v>
+        <v>0.4657534246575342</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4550739704046623</v>
+        <v>0.4496636275365348</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02122093023255814</v>
+        <v>0.02147058823529412</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.5</v>
+        <v>334.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24950</v>
+        <v>26640</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1287079018425488</v>
+        <v>-0.1348862519762346</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02444889779559123</v>
+        <v>0.005705705705705721</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.659975373024237</v>
+        <v>6.668213850004244</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.643791774432818</v>
+        <v>7.707904151606504</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.117808219178082</v>
+        <v>7.112328767123287</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001501507053690363</v>
+        <v>0.001499651964520249</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>122.5</v>
+        <v>123.8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24950</v>
+        <v>26640</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08400191312126783</v>
+        <v>-0.08875951547765451</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1783567134268538</v>
+        <v>0.1153153153153152</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.120664128044978</v>
+        <v>2.115345526719058</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.315140346276432</v>
+        <v>2.321391073650422</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.115068493150685</v>
+        <v>2.10958904109589</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004715503915850604</v>
+        <v>0.00472736008074775</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>96.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2281</v>
+        <v>2318</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04205869065739071</v>
+        <v>0.0402041335941396</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.547561525646646</v>
+        <v>2.498208001725625</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.052202605925751</v>
+        <v>1.046727754779499</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.009734495148215</v>
+        <v>1.006271481697365</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.027397260273973</v>
+        <v>1.021917808219178</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.00950387305988639</v>
+        <v>0.009553582537903157</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>219.1</v>
+        <v>215.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1524394260221942</v>
+        <v>0.1527430883961673</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.631926061159288</v>
+        <v>2.697746282527881</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.834595659013879</v>
+        <v>1.829104262674252</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.591923720751417</v>
+        <v>1.586740602556219</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.863013698630137</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005450792358995956</v>
+        <v>0.005467156905194373</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>117.7</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13700</v>
+        <v>13810</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01768186780162668</v>
+        <v>-0.01045381243443485</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3745985401459855</v>
+        <v>0.3207820419985519</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.29831613001366</v>
+        <v>4.289236156767093</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.375686439172479</v>
+        <v>4.334548716032417</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.452054794520548</v>
+        <v>4.446575342465754</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002326492444372215</v>
+        <v>0.002331417444624279</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>108</v>
+        <v>108.1</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1244</v>
+        <v>1233</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02661967919925202</v>
+        <v>0.02623401421643526</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3594612861736335</v>
+        <v>0.3728594793187348</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.822442322710318</v>
+        <v>2.8170473212908</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.749257957836714</v>
+        <v>2.745034058768469</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.942465753424658</v>
+        <v>2.936986301369863</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003543030771448063</v>
+        <v>0.003549816122867931</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>243.1</v>
+        <v>237.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.375260405950111</v>
+        <v>-3.513516798703747</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.07677910324969162</v>
+        <v>0.1035623946037101</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1178082191780822</v>
+        <v>0.1123287671232877</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>244.2</v>
+        <v>239.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>243.1</v>
+        <v>237.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1396348037014683</v>
+        <v>-0.1358097478239605</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.004524886877828038</v>
+        <v>0.008431703204047292</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.427239353795684</v>
+        <v>4.418422230130404</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.145767602923246</v>
+        <v>5.112788785808188</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.693150684931507</v>
+        <v>4.687671232876713</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002258743926150395</v>
+        <v>0.002263251332524837</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>284.4</v>
+        <v>288.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2578782799149166</v>
+        <v>-0.2582552060304935</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2310461497890295</v>
+        <v>0.2148144517696045</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.360417210142988</v>
+        <v>3.355052926810682</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.528121356908567</v>
+        <v>4.523190393903337</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.446575342465753</v>
+        <v>3.441095890410959</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002975820969436856</v>
+        <v>0.00298057891131572</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1364668121415052</v>
+        <v>-0.1368982545982676</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.04513317191283295</v>
+        <v>0.073731343283582</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.082532126264021</v>
+        <v>2.077156698313309</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.411641099085679</v>
+        <v>2.406618581620979</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.208219178082192</v>
+        <v>2.202739726027397</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004801846691287111</v>
+        <v>0.004814273284302621</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>108.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16860</v>
+        <v>16840</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02402601058593325</v>
+        <v>-0.01582116598591259</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.224082087781732</v>
+        <v>0.2054816437054632</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.943872511175607</v>
+        <v>1.938202175892544</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.991725734763306</v>
+        <v>1.969359743276902</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.942465753424657</v>
+        <v>1.936986301369863</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005144370293066309</v>
+        <v>0.005159420479648875</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>90.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04894397042266613</v>
+        <v>0.0489425652276808</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7197455752212389</v>
+        <v>0.7747146118721462</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.195060483377739</v>
+        <v>3.189581802116793</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.045978215681346</v>
+        <v>3.040759244453457</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.446575342465753</v>
+        <v>3.441095890410959</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003129831204143042</v>
+        <v>0.003135207252989534</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.7</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1110875494249695</v>
+        <v>0.1093105783976285</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.175173210161663</v>
+        <v>1.182448036951501</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.916873043446866</v>
+        <v>1.911469924744631</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.725222323334396</v>
+        <v>1.723115205036359</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.942465753424657</v>
+        <v>1.936986301369863</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00521682958304755</v>
+        <v>0.005231575904253886</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150.7</v>
+        <v>145</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03262943665725368</v>
+        <v>0.03260864970271204</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4631718646317187</v>
+        <v>0.5206896551724138</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.376720840307528</v>
+        <v>3.371252190275036</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.270021868869419</v>
+        <v>3.264791740070761</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.608219178082192</v>
+        <v>3.602739726027397</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002961452981434281</v>
+        <v>0.002966256878926691</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>292</v>
+        <v>288.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23500</v>
+        <v>23270</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4688435705370917</v>
+        <v>-0.4661528390305638</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.002376657021276651</v>
+        <v>-0.004247153072625687</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.618615734370366</v>
+        <v>1.613065074476706</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.047342825176885</v>
+        <v>3.021585937719461</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.605479452054795</v>
+        <v>1.6</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006178118615589732</v>
+        <v>0.006199377916135279</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>502.9</v>
+        <v>499</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03809700826460153</v>
+        <v>0.03810121300021583</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3336288486776695</v>
+        <v>0.3440519999999998</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9698630136986303</v>
+        <v>0.9643835616438354</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9342701173178037</v>
+        <v>0.9289879922755035</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9424657534246575</v>
+        <v>0.9369863013698631</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01031073446327684</v>
+        <v>0.01036931818181818</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>86.5</v>
+        <v>88.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>172.3</v>
+        <v>179</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1448658199283509</v>
+        <v>0.1316384318420239</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1546720835751594</v>
+        <v>0.1397206703910614</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.009627741123752</v>
+        <v>2.007778721032684</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.755339102751378</v>
+        <v>1.774222812285125</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.208219178082192</v>
+        <v>2.202739726027397</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004976045958844179</v>
+        <v>0.004980628540009919</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8490</v>
+        <v>8406</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02920302536897958</v>
+        <v>0.02974061024880868</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8634300690223793</v>
+        <v>0.8778594185105877</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.508519728813297</v>
+        <v>4.502957665399123</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.380593155754616</v>
+        <v>4.372904807853607</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.534246575342466</v>
+        <v>4.528767123287671</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002218022899199364</v>
+        <v>0.002220762606062307</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>78.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>41.6</v>
+        <v>38.4</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1360495291110095</v>
+        <v>0.126506548619518</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2214315298076921</v>
+        <v>0.3602541124999998</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.119511628772085</v>
+        <v>3.120065424617647</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.745929247656297</v>
+        <v>2.769682456299205</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.446575342465753</v>
+        <v>3.441095890410959</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003205629979951779</v>
+        <v>0.003205060996830047</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1245297893582096</v>
+        <v>0.1246410282423323</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.4990619136960601</v>
+        <v>0.5980000000000001</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.152029699436592</v>
+        <v>3.146484646431385</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.802975723066896</v>
+        <v>2.797767969881849</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.446575342465753</v>
+        <v>3.441095890410959</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003172558939335961</v>
+        <v>0.003178149943093348</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>45.20456112213172</v>
+        <v>45.67851430602452</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1761052631578948</v>
+        <v>0.3966249999999998</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4712328767123288</v>
+        <v>0.4657534246575343</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.01019883892992138</v>
+        <v>0.0099778973598871</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02122093023255814</v>
+        <v>0.02147058823529411</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1328</v>
+        <v>1249</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05751903296551122</v>
+        <v>0.05786791493011603</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.3815760722891566</v>
+        <v>0.4689615884707765</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4657534246575342</v>
+        <v>0.4602739726027398</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4404208436338599</v>
+        <v>0.4350958811650375</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02147058823529412</v>
+        <v>0.02172619047619048</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12360</v>
+        <v>12510</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.666003413281083</v>
+        <v>-1.685629330140723</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02934219644012948</v>
+        <v>0.0169999638689049</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>215.3</v>
+        <v>217.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21410</v>
+        <v>21280</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1971427672764509</v>
+        <v>-0.2008595253989265</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1574511910322278</v>
+        <v>0.1785850563909774</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.876666774506659</v>
+        <v>2.87184353455672</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.583036506687601</v>
+        <v>3.593665476636418</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.942465753424658</v>
+        <v>2.936986301369863</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003476245524376029</v>
+        <v>0.003482083852992199</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05498403953597301</v>
+        <v>0.05498121141622932</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4448192592592592</v>
+        <v>0.4687545180722892</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.816186272986022</v>
+        <v>2.810707449084968</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.669411258794684</v>
+        <v>2.664225124267203</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.942465753424658</v>
+        <v>2.936986301369863</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003550901478330455</v>
+        <v>0.003557823139244008</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.0944519201283625</v>
+        <v>0.09451385168872962</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>2.079282229181495</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.356603467174062</v>
+        <v>2.351108437335707</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.153227038879578</v>
+        <v>2.148084680434307</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.515068493150685</v>
+        <v>2.50958904109589</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004243395267508272</v>
+        <v>0.004253312965578088</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>72070</v>
+        <v>70030</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2488900539721604</v>
+        <v>-0.2495916417520284</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.07753572915221318</v>
+        <v>0.1089247465371983</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.813018178961106</v>
+        <v>1.807564217687294</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.413785343342941</v>
+        <v>2.408774099888139</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.816438356164384</v>
+        <v>1.810958904109589</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005515664495835441</v>
+        <v>0.005532306903482853</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>114.8</v>
+        <v>114</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.03180494320286069</v>
+        <v>-0.03194629637646113</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01154181184668979</v>
+        <v>-0.004605263157894668</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.835043340191982</v>
+        <v>2.829593896499943</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.928173739670304</v>
+        <v>2.922972027180352</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.942465753424658</v>
+        <v>2.936986301369863</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003527282937171192</v>
+        <v>0.003534076042632644</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02095802730643737</v>
+        <v>0.02089069030304371</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2123870967741937</v>
+        <v>0.2282352941176471</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.845558027562971</v>
+        <v>1.840081236108182</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.807672772241236</v>
+        <v>1.802427285885003</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.863013698630137</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005418415379333716</v>
+        <v>0.005434542673317102</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>947</v>
+        <v>921</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.04771823629820473</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7682154171066526</v>
+        <v>0.8181324647122692</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.222809576163678</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9186</v>
+        <v>9040</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.01527245000650752</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1987464506858261</v>
+        <v>0.2181067362831857</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.918078151131943</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92</v>
+        <v>91.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03205807634671402</v>
+        <v>0.03227098231645414</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2940869565217392</v>
+        <v>0.2970992366412215</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.555353474845992</v>
+        <v>4.555133428313781</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.413853812346551</v>
+        <v>4.41273028724676</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.936986301369863</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002195219329349207</v>
+        <v>0.002195325374629432</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5584</v>
+        <v>5624</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.0357818514455945</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.922367478510029</v>
+        <v>1.901582503556188</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.4657534246575342</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>334.9</v>
+        <v>338</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26640</v>
+        <v>26520</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1348862519762346</v>
+        <v>-0.1360684205021946</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.005705705705705721</v>
+        <v>0.01960784313725483</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.668213850004244</v>
+        <v>6.670800673754837</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.707904151606504</v>
+        <v>7.721445577475597</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.112328767123287</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001499651964520249</v>
+        <v>0.001499070424835709</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>123.8</v>
+        <v>122.5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26640</v>
+        <v>26520</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08875951547765451</v>
+        <v>-0.08422453992753005</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1153153153153152</v>
+        <v>0.1085972850678734</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.115345526719058</v>
+        <v>2.115192216811459</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.321391073650422</v>
+        <v>2.309727994506507</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.10958904109589</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00472736008074775</v>
+        <v>0.004727702721540113</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2318</v>
+        <v>2258</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.0402041335941396</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.498208001725625</v>
+        <v>2.591163041629761</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>1.046727754779499</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215.2</v>
+        <v>215.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1527430883961673</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.697746282527881</v>
+        <v>2.696028797027403</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.829104262674252</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>113.3</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13810</v>
+        <v>13550</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01045381243443485</v>
+        <v>-0.009044955611587014</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3207820419985519</v>
+        <v>0.3378597785977859</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.289236156767093</v>
+        <v>4.28852821925426</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.334548716032417</v>
+        <v>4.327671818756428</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.446575342465754</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002331417444624279</v>
+        <v>0.002331802308097886</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>108.1</v>
+        <v>109.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1233</v>
+        <v>1287</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02623401421643526</v>
+        <v>0.02156626172455279</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3728594793187348</v>
+        <v>0.3322908391608392</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.8170473212908</v>
+        <v>2.818068122322756</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.745034058768469</v>
+        <v>2.758575951368485</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.936986301369863</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003549816122867931</v>
+        <v>0.003548530257585693</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>237.2</v>
+        <v>233.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-3.513516798703747</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.1035623946037101</v>
+        <v>0.1224914236706691</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>239.2</v>
+        <v>239.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>237.2</v>
+        <v>233.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1358097478239605</v>
+        <v>-0.1357284911420534</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.008431703204047292</v>
+        <v>0.02530017152658659</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.418422230130404</v>
+        <v>4.418351057433957</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.112788785808188</v>
+        <v>5.112225744051648</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.687671232876713</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002263251332524837</v>
+        <v>0.002263287789949333</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>288.2</v>
+        <v>278.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.2582552060304935</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2148144517696045</v>
+        <v>0.2553227859447831</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.355052926810682</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16840</v>
+        <v>16720</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.01582116598591259</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2054816437054632</v>
+        <v>0.2141334258373206</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.938202175892544</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145</v>
+        <v>144.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.03260864970271204</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5206896551724138</v>
+        <v>0.5227900552486187</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.371252190275036</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>288.6</v>
+        <v>289</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23270</v>
+        <v>23010</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4661528390305638</v>
+        <v>-0.4666093744421836</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.004247153072625687</v>
+        <v>0.008400000869187352</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.613065074476706</v>
+        <v>1.613077155559487</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.021585937719461</v>
+        <v>3.02419479883536</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006199377916135279</v>
+        <v>0.006199331486119493</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03810121300021583</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3440519999999998</v>
+        <v>0.3631746910569105</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.9643835616438354</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>179</v>
+        <v>180.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.1316384318420239</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1397206703910614</v>
+        <v>0.1302493074792244</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>2.007778721032684</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8406</v>
+        <v>8307</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02974061024880868</v>
+        <v>0.03101795443513604</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8778594185105877</v>
+        <v>0.8896350953412784</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.502957665399123</v>
+        <v>4.502760984245428</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.372904807853607</v>
+        <v>4.367296384001728</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.528767123287671</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002220762606062307</v>
+        <v>0.002220859609246126</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>80.8</v>
+        <v>79.2</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.126506548619518</v>
+        <v>0.1334985123127973</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3602541124999998</v>
+        <v>0.3367996365535249</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.120065424617647</v>
+        <v>3.115649741189496</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.769682456299205</v>
+        <v>2.748702100042729</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.441095890410959</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003205060996830047</v>
+        <v>0.003209603399187673</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>48.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1246410282423323</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5980000000000001</v>
+        <v>0.6339468302658489</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.146484646431385</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1249</v>
+        <v>1295</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05786791493011603</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4689615884707765</v>
+        <v>0.4167822579150577</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.4602739726027398</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12510</v>
+        <v>12580</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-1.685629330140723</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0169999638689049</v>
+        <v>0.01134098155802854</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21280</v>
+        <v>20660</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.2008595253989265</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1785850563909774</v>
+        <v>0.2139540174249759</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.87184353455672</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>70030</v>
+        <v>69410</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2495916417520284</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1089247465371983</v>
+        <v>0.1188301397493157</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.807564217687294</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>127.5</v>
+        <v>125.1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>114</v>
+        <v>111.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.03194629637646113</v>
+        <v>-0.02543171412481142</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.004605263157894668</v>
+        <v>-0.003231871083258731</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.829593896499943</v>
+        <v>2.828208452696645</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.922972027180352</v>
+        <v>2.902011581627487</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.936986301369863</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003534076042632644</v>
+        <v>0.003535807267128837</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112.8</v>
+        <v>112.4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01527245000650752</v>
+        <v>-0.01344995964127526</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2181067362831857</v>
+        <v>0.2137872088495574</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.918078151131943</v>
+        <v>1.918001040577017</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.947826229848671</v>
+        <v>1.944149776609002</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.936986301369863</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005213551905639797</v>
+        <v>0.005213761509217729</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03227098231645414</v>
+        <v>0.03248414281305929</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2970992366412215</v>
+        <v>0.2958778625954199</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.555133428313781</v>
+        <v>4.554913046325039</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.41273028724676</v>
+        <v>4.411605813058717</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.936986301369863</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002195325374629432</v>
+        <v>0.002195431591843038</v>
       </c>
     </row>
     <row r="5">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>338</v>
+        <v>344.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1360684205021946</v>
+        <v>-0.1385061402373621</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01960784313725483</v>
+        <v>0.03921568627450989</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.670800673754837</v>
+        <v>6.676096692001482</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.721445577475597</v>
+        <v>7.749441991195279</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.112328767123287</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001499070424835709</v>
+        <v>0.001497881241291911</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>122.5</v>
+        <v>128.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08422453992753005</v>
+        <v>-0.105895292807102</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1085972850678734</v>
+        <v>0.1665158371040725</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.115192216811459</v>
+        <v>2.115919671826467</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.309727994506507</v>
+        <v>2.366523355491036</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.10958904109589</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004727702721540113</v>
+        <v>0.004726077333251492</v>
       </c>
     </row>
     <row r="8">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.3</v>
+        <v>113.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.009044955611587014</v>
+        <v>-0.008640427949218632</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3378597785977859</v>
+        <v>0.3354981549815499</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.28852821925426</v>
+        <v>4.288324576614654</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.327671818756428</v>
+        <v>4.325700479941489</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.446575342465754</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002331802308097886</v>
+        <v>0.002331913040009283</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>109.5</v>
+        <v>109.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02156626172455279</v>
+        <v>0.02123600547135757</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3322908391608392</v>
+        <v>0.333507543123543</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.818068122322756</v>
+        <v>2.818140254550277</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.758575951368485</v>
+        <v>2.75953867612565</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.936986301369863</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003548530257585693</v>
+        <v>0.003548439430526432</v>
       </c>
     </row>
     <row r="12">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>239.1</v>
+        <v>234.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1357284911420534</v>
+        <v>-0.1322766198448039</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02530017152658659</v>
+        <v>0.007289879931389409</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.418351057433957</v>
+        <v>4.415317195832888</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.112225744051648</v>
+        <v>5.088392564740147</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.687671232876713</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002263287789949333</v>
+        <v>0.002264842944791793</v>
       </c>
     </row>
     <row r="14">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>158.4</v>
+        <v>157</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1368982545982676</v>
+        <v>-0.1333252726983955</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.073731343283582</v>
+        <v>0.06424129353233843</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.077156698313309</v>
+        <v>2.076294426343629</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.406618581620979</v>
+        <v>2.395702056304539</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.202739726027397</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004814273284302621</v>
+        <v>0.004816272621609874</v>
       </c>
     </row>
     <row r="16">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>289</v>
+        <v>287.7</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4666093744421836</v>
+        <v>-0.465121877671337</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.008400000869187352</v>
+        <v>0.003863945501955568</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.613077155559487</v>
+        <v>1.613037793718568</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.02419479883536</v>
+        <v>3.015710918771539</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.6</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006199331486119493</v>
+        <v>0.006199482764099907</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>88.7</v>
+        <v>89.2</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1316384318420239</v>
+        <v>0.12865875224256</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1302493074792244</v>
+        <v>0.1366204986149584</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.007778721032684</v>
+        <v>2.00859409588165</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.774222812285125</v>
+        <v>1.779629220870103</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.202739726027397</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004980628540009919</v>
+        <v>0.004978606688381512</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03101795443513604</v>
+        <v>0.03025049601221911</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8896350953412784</v>
+        <v>0.8959975030697005</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.502760984245428</v>
+        <v>4.502879220774307</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.367296384001728</v>
+        <v>4.370664453163148</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.528767123287671</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002220859609246126</v>
+        <v>0.002220801293950855</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1246410282423323</v>
+        <v>0.1242085188300849</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6339468302658489</v>
+        <v>0.6359918200408998</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.146484646431385</v>
+        <v>3.146739673569725</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.797767969881849</v>
+        <v>2.799071187295752</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.441095890410959</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003178149943093348</v>
+        <v>0.003177892370313493</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>217.9</v>
+        <v>215.7</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.2008595253989265</v>
+        <v>-0.1980328396335409</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2139540174249759</v>
+        <v>0.2016974830590512</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.87184353455672</v>
+        <v>2.871344631409678</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.593665476636418</v>
+        <v>3.580376820040382</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.936986301369863</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003482083852992199</v>
+        <v>0.003482688873571589</v>
       </c>
     </row>
     <row r="30">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>104.4</v>
+        <v>104</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02089069030304371</v>
+        <v>0.02301193997878715</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2282352941176471</v>
+        <v>0.223529411764706</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.840081236108182</v>
+        <v>1.839997429010967</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.802427285885003</v>
+        <v>1.798607970351862</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.857534246575342</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005434542673317102</v>
+        <v>0.005434790202601091</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>921</v>
+        <v>939.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.04771823629820473</v>
+        <v>0.04772176394871619</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8181324647122692</v>
+        <v>0.7815725077135867</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.222809576163678</v>
+        <v>3.220068119270274</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.076026993240568</v>
+        <v>3.073400047675148</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.441095890410959</v>
+        <v>3.438356164383562</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00310288267540264</v>
+        <v>0.003105524364579648</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9040</v>
+        <v>9017</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01344995964127526</v>
+        <v>-0.01352985582001272</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2137872088495574</v>
+        <v>0.2168832613951424</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.918001040577017</v>
+        <v>1.915264694739641</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.944149776609002</v>
+        <v>1.941533361186235</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.936986301369863</v>
+        <v>1.934246575342466</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005213761509217729</v>
+        <v>0.005221210429798786</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03248414281305929</v>
+        <v>0.03247711287838592</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2958778625954199</v>
+        <v>0.2695726495726498</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.554913046325039</v>
+        <v>4.552180589548812</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.411605813058717</v>
+        <v>4.408989344914426</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.936986301369863</v>
+        <v>4.934246575342466</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002195431591843038</v>
+        <v>0.002196749404660843</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5624</v>
+        <v>5578</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0357818514455945</v>
+        <v>0.03592105869796358</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.901582503556188</v>
+        <v>1.925510935819291</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4657534246575342</v>
+        <v>0.4630136986301371</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4496636275365348</v>
+        <v>0.4469584769442696</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4356164383561644</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02147058823529412</v>
+        <v>0.02159763313609467</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>344.5</v>
+        <v>345.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26520</v>
+        <v>26960</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1385061402373621</v>
+        <v>-0.138822292943943</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03921568627450989</v>
+        <v>0.02433234421364983</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.676096692001482</v>
+        <v>6.674040059617674</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.749441991195279</v>
+        <v>7.749898778073267</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.112328767123287</v>
+        <v>7.109589041095891</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001497881241291911</v>
+        <v>0.00149834281944254</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26520</v>
+        <v>26960</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.105895292807102</v>
+        <v>-0.1060317453852639</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1665158371040725</v>
+        <v>0.1474777448071216</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.115919671826467</v>
+        <v>2.113184485022778</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.366523355491036</v>
+        <v>2.363824972659096</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.10958904109589</v>
+        <v>2.106849315068493</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004726077333251492</v>
+        <v>0.004732194501178258</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2258</v>
+        <v>2296</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0402041335941396</v>
+        <v>0.04030466221130407</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.591163041629761</v>
+        <v>2.531727416376306</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.046727754779499</v>
+        <v>1.043987779352932</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.006271481697365</v>
+        <v>1.003540421643213</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.021917808219178</v>
+        <v>1.019178082191781</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009553582537903157</v>
+        <v>0.009578656185226651</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215.3</v>
+        <v>256</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1527430883961673</v>
+        <v>0.1528956544702157</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.696028797027403</v>
+        <v>2.10841796875</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.829104262674252</v>
+        <v>1.826358535711393</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.586740602556219</v>
+        <v>1.584149032594498</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.857534246575342</v>
+        <v>1.854794520547945</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005467156905194373</v>
+        <v>0.005475376167639974</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13550</v>
+        <v>13330</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008640427949218632</v>
+        <v>-0.008657029597641558</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3354981549815499</v>
+        <v>0.3575393848462116</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.288324576614654</v>
+        <v>4.28559321125808</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.325700479941489</v>
+        <v>4.323017703468132</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.446575342465754</v>
+        <v>4.443835616438356</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002331913040009283</v>
+        <v>0.00233339925351067</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1287</v>
+        <v>1329</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02123600547135757</v>
+        <v>0.02120711072838879</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.333507543123543</v>
+        <v>0.29136509255079</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.818140254550277</v>
+        <v>2.815406838926766</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.75953867612565</v>
+        <v>2.756940104851641</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.936986301369863</v>
+        <v>2.934246575342466</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003548439430526432</v>
+        <v>0.003551884531122331</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>193.9</v>
+        <v>189.5</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>233.2</v>
+        <v>235.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.513516798703747</v>
+        <v>-3.495574901313615</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.1224914236706691</v>
+        <v>0.08676720475785893</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1123287671232877</v>
+        <v>0.1095890410958904</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>233.2</v>
+        <v>235.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1322766198448039</v>
+        <v>-0.1323655857998323</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007289879931389409</v>
+        <v>-0.002124044180118911</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.415317195832888</v>
+        <v>4.412655916746355</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.088392564740147</v>
+        <v>5.085847039405623</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.687671232876713</v>
+        <v>4.684931506849315</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002264842944791793</v>
+        <v>0.002266208874806953</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>278.9</v>
+        <v>287.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2582552060304935</v>
+        <v>-0.2584440538602029</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2553227859447831</v>
+        <v>0.2160803230288295</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.355052926810682</v>
+        <v>3.352370875493646</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.523190393903337</v>
+        <v>4.520725500138679</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.441095890410959</v>
+        <v>3.438356164383562</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00298057891131572</v>
+        <v>0.00298296351191378</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1333252726983955</v>
+        <v>-0.1335384291468409</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.06424129353233843</v>
+        <v>0.09558258642765716</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.076294426343629</v>
+        <v>2.073606192506492</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.395702056304539</v>
+        <v>2.393188875606706</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.202739726027397</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004816272621609874</v>
+        <v>0.004822516462449603</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16720</v>
+        <v>17040</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01582116598591259</v>
+        <v>-0.01587554147331286</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2141334258373206</v>
+        <v>0.1913327981220658</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.938202175892544</v>
+        <v>1.935463714648833</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.969359743276902</v>
+        <v>1.96668591851317</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.936986301369863</v>
+        <v>1.934246575342466</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005159420479648875</v>
+        <v>0.005166720473400547</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>87.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0489425652276808</v>
+        <v>0.04894186955758061</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7747146118721462</v>
+        <v>0.8077325581395349</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.189581802116793</v>
+        <v>3.186842457686018</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.040759244453457</v>
+        <v>3.038149729908441</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.441095890410959</v>
+        <v>3.438356164383562</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003135207252989534</v>
+        <v>0.003137902212857127</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1093105783976285</v>
+        <v>0.1093874963696352</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.182448036951501</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.911469924744631</v>
+        <v>1.908726894297492</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.723115205036359</v>
+        <v>1.720523172059914</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.936986301369863</v>
+        <v>1.934246575342466</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005231575904253886</v>
+        <v>0.005239094199319965</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>144.8</v>
+        <v>146.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03260864970271204</v>
+        <v>0.03259823787941077</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5227900552486187</v>
+        <v>0.5051194539249146</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.371252190275036</v>
+        <v>3.368517874702478</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.264791740070761</v>
+        <v>3.262176663810907</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.602739726027397</v>
+        <v>3.6</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002966256878926691</v>
+        <v>0.002968664668547512</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23010</v>
+        <v>23650</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.465121877671337</v>
+        <v>-0.4656998077481942</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.003863945501955568</v>
+        <v>-0.02330192871035941</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.613037793718568</v>
+        <v>1.6103133603874</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.015710918771539</v>
+        <v>3.013873818013693</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.6</v>
+        <v>1.597260273972603</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006199482764099907</v>
+        <v>0.006209971453999646</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>492</v>
+        <v>502.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03810121300021583</v>
+        <v>0.03810336484814374</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3631746910569105</v>
+        <v>0.3346904437810945</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9643835616438354</v>
+        <v>0.9616438356164385</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9289879922755035</v>
+        <v>0.926346901647034</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9369863013698631</v>
+        <v>0.9342465753424658</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01036931818181818</v>
+        <v>0.0103988603988604</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>89.2</v>
+        <v>91</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>180.5</v>
+        <v>192.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.12865875224256</v>
+        <v>0.1181934042909493</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1366204986149584</v>
+        <v>0.08727272727272717</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.00859409588165</v>
+        <v>2.008710965609329</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.779629220870103</v>
+        <v>1.796389567226127</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.202739726027397</v>
+        <v>2.2</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004978606688381512</v>
+        <v>0.004978317025797969</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8307</v>
+        <v>8376</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03025049601221911</v>
+        <v>0.0302656894358234</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8959975030697005</v>
+        <v>0.8803786124641835</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.502879220774307</v>
+        <v>4.500137155935057</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.370664453163148</v>
+        <v>4.367938486235863</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.528767123287671</v>
+        <v>4.526027397260274</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002220801293950855</v>
+        <v>0.002222154492960595</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.3</v>
+        <v>41.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1334985123127973</v>
+        <v>0.1335567296112975</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3367996365535249</v>
+        <v>0.2427045165048543</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.115649741189496</v>
+        <v>3.112873139055122</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.748702100042729</v>
+        <v>2.746111471741288</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.441095890410959</v>
+        <v>3.438356164383562</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003209603399187673</v>
+        <v>0.003212466282206216</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>48.9</v>
+        <v>52</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1242085188300849</v>
+        <v>0.1242639723976285</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6359918200408998</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.146739673569725</v>
+        <v>3.143967255146119</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.799071187295752</v>
+        <v>2.796467139688938</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.441095890410959</v>
+        <v>3.438356164383562</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003177892370313493</v>
+        <v>0.003180694704638468</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>45.67851430602452</v>
+        <v>45.91975030729211</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.3966249999999998</v>
+        <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4657534246575343</v>
+        <v>0.4630136986301369</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.0099778973598871</v>
+        <v>0.009868204660035816</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4356164383561644</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02147058823529411</v>
+        <v>0.02159763313609468</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05786791493011603</v>
+        <v>0.0580455277327699</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4167822579150577</v>
+        <v>0.4113330953846153</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4602739726027398</v>
+        <v>0.4575342465753425</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4350958811650375</v>
+        <v>0.4324334204746072</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4356164383561644</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02172619047619048</v>
+        <v>0.0218562874251497</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12580</v>
+        <v>12640</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.685629330140723</v>
+        <v>-1.695616482004173</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01134098155802854</v>
+        <v>0.006540312341772214</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4356164383561644</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>215.7</v>
+        <v>217.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20660</v>
+        <v>20860</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1980328396335409</v>
+        <v>-0.2010480998012577</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2016974830590512</v>
+        <v>0.2023149568552254</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.871344631409678</v>
+        <v>2.869137054746489</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.580376820040382</v>
+        <v>3.591126141677341</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.936986301369863</v>
+        <v>2.934246575342466</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003482688873571589</v>
+        <v>0.003485368530393742</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>664</v>
+        <v>662.2</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05498121141622932</v>
+        <v>0.05497980596791393</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4687545180722892</v>
+        <v>0.4727469042585322</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.810707449084968</v>
+        <v>2.807968035221407</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.664225124267203</v>
+        <v>2.661632023036855</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.936986301369863</v>
+        <v>2.934246575342466</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003557823139244008</v>
+        <v>0.00356129410113157</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.09451385168872962</v>
+        <v>0.09454495015829291</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>2.079282229181495</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.351108437335707</v>
+        <v>2.348360888886843</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.148084680434307</v>
+        <v>2.145513428705896</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.50958904109589</v>
+        <v>2.506849315068493</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004253312965578088</v>
+        <v>0.004258289280545864</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69410</v>
+        <v>69480</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2495916417520284</v>
+        <v>-0.2499437798761603</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1188301397493157</v>
+        <v>0.1177029360967186</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.807564217687294</v>
+        <v>1.804837286394418</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.408774099888139</v>
+        <v>2.406269340845445</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.810958904109589</v>
+        <v>1.808219178082192</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005532306903482853</v>
+        <v>0.005540665674066012</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>111.7</v>
+        <v>112.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02543171412481142</v>
+        <v>-0.02549753446378271</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.003231871083258731</v>
+        <v>-0.01295212765957443</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.828208452696645</v>
+        <v>2.825482749453424</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.902011581627487</v>
+        <v>2.899410570396771</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.936986301369863</v>
+        <v>2.934246575342466</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003535807267128837</v>
+        <v>0.00353921821038704</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1530</v>
+        <v>1443</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02301193997878715</v>
+        <v>0.0229809783786206</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.223529411764706</v>
+        <v>0.2972972972972974</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.839997429010967</v>
+        <v>1.837258926120174</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.798607970351862</v>
+        <v>1.795985423924644</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.857534246575342</v>
+        <v>1.854794520547945</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005434790202601091</v>
+        <v>0.005442890959913566</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>939.9</v>
+        <v>917.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.04772176394871619</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7815725077135867</v>
+        <v>0.8246703715811265</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.220068119270274</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9017</v>
+        <v>9123</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.01352985582001272</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2168832613951424</v>
+        <v>0.202744313054916</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.915264694739641</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.03247711287838592</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2695726495726498</v>
+        <v>0.2709304812834226</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.552180589548812</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5578</v>
+        <v>5600</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03592105869796358</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.925510935819291</v>
+        <v>1.914017857142857</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.4630136986301371</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>345.2</v>
+        <v>343.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26960</v>
+        <v>26980</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.138822292943943</v>
+        <v>-0.1382285558355758</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02433234421364983</v>
+        <v>0.01882876204595996</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.674040059617674</v>
+        <v>6.672756494701204</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.749898778073267</v>
+        <v>7.743069859051928</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.109589041095891</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00149834281944254</v>
+        <v>0.001498631039202605</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26960</v>
+        <v>26980</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1060317453852639</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1474777448071216</v>
+        <v>0.1466271312083025</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.113184485022778</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2296</v>
+        <v>2263</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04030466221130407</v>
+        <v>0.03927243767381745</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.531727416376306</v>
+        <v>2.586953292973928</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.043987779352932</v>
+        <v>1.043990340181344</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.003540421643213</v>
+        <v>1.0045396205427</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>1.019178082191781</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009578656185226651</v>
+        <v>0.00957863268951605</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>256</v>
+        <v>251.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1528956544702157</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.10841796875</v>
+        <v>2.166553919617986</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.826358535711393</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13330</v>
+        <v>13500</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008657029597641558</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3575393848462116</v>
+        <v>0.3404444444444445</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.28559321125808</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>109.6</v>
+        <v>110.3</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1329</v>
+        <v>1343</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02120711072838879</v>
+        <v>0.018905055573717</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.29136509255079</v>
+        <v>0.2860651481757259</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.815406838926766</v>
+        <v>2.815909290596953</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.756940104851641</v>
+        <v>2.763662104916531</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.934246575342466</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003551884531122331</v>
+        <v>0.00355125075704412</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>189.5</v>
+        <v>191.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>235.4</v>
+        <v>234.1</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.495574901313615</v>
+        <v>-3.535544158045473</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.08676720475785893</v>
+        <v>0.103759077317386</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>234.9</v>
+        <v>234.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>235.4</v>
+        <v>234.1</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1323655857998323</v>
+        <v>-0.1321159490963616</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002124044180118911</v>
+        <v>0.002135839384878269</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.412655916746355</v>
+        <v>4.412435762062105</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.085847039405623</v>
+        <v>5.084130486633427</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.684931506849315</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002266208874806953</v>
+        <v>0.002266321945348074</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>287.9</v>
+        <v>287.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.2584440538602029</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2160803230288295</v>
+        <v>0.2194689132706371</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.352370875493646</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1335384291468409</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.09558258642765716</v>
+        <v>0.1112337662337664</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.073606192506492</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.2</v>
+        <v>108.4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17040</v>
+        <v>17000</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01587554147331286</v>
+        <v>-0.01681320155533107</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1913327981220658</v>
+        <v>0.196343209411765</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.935463714648833</v>
+        <v>1.935485525307556</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.96668591851317</v>
+        <v>1.968583720173375</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005166720473400547</v>
+        <v>0.005166662250502214</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>146.5</v>
+        <v>146.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.03259823787941077</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5051194539249146</v>
+        <v>0.5061475409836065</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.368517874702478</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>287.7</v>
+        <v>293.4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23650</v>
+        <v>23470</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4656998077481942</v>
+        <v>-0.4721462253634601</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.02330192871035941</v>
+        <v>0.003687772134639777</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.6103133603874</v>
+        <v>1.610483972204213</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.013873818013693</v>
+        <v>3.051003989339911</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.597260273972603</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006209971453999646</v>
+        <v>0.006209313580633371</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>91</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>192.5</v>
+        <v>189.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1181934042909493</v>
+        <v>0.1205083062349554</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08727272727272717</v>
+        <v>0.09963060686015823</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.008710965609329</v>
+        <v>2.008080065765282</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.796389567226127</v>
+        <v>1.792115287848848</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004978317025797969</v>
+        <v>0.004979881116537546</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8376</v>
+        <v>8412</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0302656894358234</v>
+        <v>0.03001041652294599</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8803786124641835</v>
+        <v>0.8744256734427009</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.500137155935057</v>
+        <v>4.500176441262276</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.367938486235863</v>
+        <v>4.369059156172159</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.526027397260274</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002222154492960595</v>
+        <v>0.002222135094150898</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.1335567296112975</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2427045165048543</v>
+        <v>0.3061078081632653</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>3.112873139055122</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1300</v>
+        <v>1260</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0580455277327699</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4113330953846153</v>
+        <v>0.4561373206349206</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.4575342465753425</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12640</v>
+        <v>12430</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-1.695616482004173</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.006540312341772214</v>
+        <v>0.02354541818181821</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>217.9</v>
+        <v>217.8</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20860</v>
+        <v>20710</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.2010480998012577</v>
+        <v>-0.200920377703702</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2023149568552254</v>
+        <v>0.2104674070497343</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.869137054746489</v>
+        <v>2.869114537470215</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.591126141677341</v>
+        <v>3.590523969595548</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.934246575342466</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003485368530393742</v>
+        <v>0.003485395884131312</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>662.2</v>
+        <v>671</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05497980596791393</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4727469042585322</v>
+        <v>0.4534321907600596</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.807968035221407</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69480</v>
+        <v>69620</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2499437798761603</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1177029360967186</v>
+        <v>0.1154553289284688</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.804837286394418</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>112.8</v>
+        <v>110</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02549753446378271</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01295212765957443</v>
+        <v>0.01217272727272722</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.825482749453424</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1443</v>
+        <v>1540</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.0229809783786206</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2972972972972974</v>
+        <v>0.2155844155844155</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.837258926120174</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917.7</v>
+        <v>917.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.04772176394871619</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8246703715811265</v>
+        <v>0.8250681198910081</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.220068119270274</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9123</v>
+        <v>8912</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.01352985582001272</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.202744313054916</v>
+        <v>0.2312204183123878</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.915264694739641</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106.1</v>
+        <v>106.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.5</v>
+        <v>92.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03247711287838592</v>
+        <v>0.03141334543056142</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2709304812834226</v>
+        <v>0.2907243243243245</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.552180589548812</v>
+        <v>4.553279662294862</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.408989344914426</v>
+        <v>4.414602237276759</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.934246575342466</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002196749404660843</v>
+        <v>0.00219621915227583</v>
       </c>
     </row>
     <row r="5">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5600</v>
+        <v>5578</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,16 +1272,16 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03592105869796358</v>
+        <v>0.029323739067205</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.914017857142857</v>
+        <v>1.934385084259591</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4630136986301371</v>
+        <v>0.463013698630137</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4469584769442696</v>
+        <v>0.4498232004730891</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.4356164383561644</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>343.6</v>
+        <v>353.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26980</v>
+        <v>27580</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1382285558355758</v>
+        <v>-0.1419949107893225</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01882876204595996</v>
+        <v>0.02654097171863667</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.672756494701204</v>
+        <v>6.680847422271937</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.743069859051928</v>
+        <v>7.786489271780413</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.109589041095891</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001498631039202605</v>
+        <v>0.001496816102499663</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>128.9</v>
+        <v>128.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26980</v>
+        <v>27580</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1060317453852639</v>
+        <v>-0.1037367523153655</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1466271312083025</v>
+        <v>0.1155910079767946</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.113184485022778</v>
+        <v>2.113108071128417</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.363824972659096</v>
+        <v>2.357686847683785</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.106849315068493</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004732194501178258</v>
+        <v>0.004732365626079842</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2263</v>
+        <v>2347</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03927243767381745</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.586953292973928</v>
+        <v>2.458574904985087</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>1.043990340181344</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>251.3</v>
+        <v>241.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1528956544702157</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.166553919617986</v>
+        <v>2.292325196524617</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.826358535711393</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13500</v>
+        <v>13450</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008657029597641558</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3404444444444445</v>
+        <v>0.3454275092936803</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.28559321125808</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110.3</v>
+        <v>110.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.018905055573717</v>
+        <v>0.01825102720097358</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2860651481757259</v>
+        <v>0.2807677942264988</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.815909290596953</v>
+        <v>2.816051931868021</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.763662104916531</v>
+        <v>2.765577305243625</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.934246575342466</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.00355125075704412</v>
+        <v>0.003551070875801116</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>234.1</v>
+        <v>235</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-3.535544158045473</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.103759077317386</v>
+        <v>0.09953191489361712</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>234.6</v>
+        <v>235.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>234.1</v>
+        <v>235</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1321159490963616</v>
+        <v>-0.1329465156556612</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002135839384878269</v>
+        <v>0.002553191489361728</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.412435762062105</v>
+        <v>4.413167828470048</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.084130486633427</v>
+        <v>5.089844984369403</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.684931506849315</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002266321945348074</v>
+        <v>0.002265946002662398</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>287.1</v>
+        <v>279.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.2584440538602029</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2194689132706371</v>
+        <v>0.2544232353994982</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.352370875493646</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>157</v>
+        <v>157.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77</v>
+        <v>76.2</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1335384291468409</v>
+        <v>-0.1337954415986702</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1112337662337664</v>
+        <v>0.1236154855643044</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.073606192506492</v>
+        <v>2.073668270411603</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.393188875606706</v>
+        <v>2.393970627721901</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004822516462449603</v>
+        <v>0.004822372094267081</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.4</v>
+        <v>109.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17000</v>
+        <v>17050</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01681320155533107</v>
+        <v>-0.02053768138204374</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.196343209411765</v>
+        <v>0.2016380809384164</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.935485525307556</v>
+        <v>1.935572169051452</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.968583720173375</v>
+        <v>1.976157869740806</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005166662250502214</v>
+        <v>0.005166430970590268</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.04894186955758061</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8077325581395349</v>
+        <v>0.7666477272727272</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.186842457686018</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1093874963696352</v>
+        <v>0.1100323731467035</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.182448036951501</v>
+        <v>1.180023094688222</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.908726894297492</v>
+        <v>1.908699191097159</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.720523172059914</v>
+        <v>1.7194986716346</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005239094199319965</v>
+        <v>0.005239170240467172</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>146.4</v>
+        <v>145</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.03259823787941077</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5061475409836065</v>
+        <v>0.5206896551724138</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.368517874702478</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>293.4</v>
+        <v>294.4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23470</v>
+        <v>23530</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4721462253634601</v>
+        <v>-0.4732562862740435</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.003687772134639777</v>
+        <v>0.004540594645133789</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.610483972204213</v>
+        <v>1.61051335719733</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.051003989339911</v>
+        <v>3.057489468275297</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.597260273972603</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006209313580633371</v>
+        <v>0.006209200287169515</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>502.5</v>
+        <v>518.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03810336484814374</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3346904437810945</v>
+        <v>0.2945028913337191</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.9616438356164385</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>189.5</v>
+        <v>206</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1205083062349554</v>
+        <v>0.1062832862827208</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09963060686015823</v>
+        <v>0.03946601941747563</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.008080065765282</v>
+        <v>2.0119481252791</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.792115287848848</v>
+        <v>1.818655447683342</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004979881116537546</v>
+        <v>0.004970307074200924</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8412</v>
+        <v>8446</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03001041652294599</v>
+        <v>0.02924669262878554</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8744256734427009</v>
+        <v>0.873137732180914</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.500176441262276</v>
+        <v>4.500293843952853</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.369059156172159</v>
+        <v>4.372415161673933</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.526027397260274</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002222135094150898</v>
+        <v>0.002222077123572104</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>79.2</v>
+        <v>81</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>39.2</v>
+        <v>38.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1335567296112975</v>
+        <v>0.1256979118187518</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3061078081632653</v>
+        <v>0.370760455497382</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.112873139055122</v>
+        <v>3.117834691862563</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.746111471741288</v>
+        <v>2.769690393069294</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.438356164383562</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003212466282206216</v>
+        <v>0.003207354137825089</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1242639723976285</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5384615384615385</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.143967255146119</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1260</v>
+        <v>1270</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0580455277327699</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4561373206349206</v>
+        <v>0.4446716724409447</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.4575342465753425</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12430</v>
+        <v>12600</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-1.695616482004173</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02354541818181821</v>
+        <v>0.00973567841269829</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20710</v>
+        <v>21270</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.200920377703702</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2104674070497343</v>
+        <v>0.1785980253878703</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.869114537470215</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05497980596791393</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4534321907600596</v>
+        <v>0.4776560606060607</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.807968035221407</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69620</v>
+        <v>68950</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2499437798761603</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1154553289284688</v>
+        <v>0.1262944162436548</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.804837286394418</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>110</v>
+        <v>111.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02549753446378271</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01217272727272722</v>
+        <v>-0.002338709677419337</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.825482749453424</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.0229809783786206</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2155844155844155</v>
+        <v>0.2108667529107373</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.837258926120174</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>98.5</v>
+        <v>96.8</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917.5</v>
+        <v>912.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.04772176394871619</v>
+        <v>0.05327249279601533</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8250681198910081</v>
+        <v>0.8041881372656505</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.220068119270274</v>
+        <v>3.21733646631943</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.073400047675148</v>
+        <v>3.054609788373656</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.438356164383562</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003105524364579648</v>
+        <v>0.003108161084389102</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112.4</v>
+        <v>112.5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8912</v>
+        <v>8873</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01352985582001272</v>
+        <v>-0.01398696903957924</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2312204183123878</v>
+        <v>0.2377322776963822</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.915264694739641</v>
+        <v>1.915284034416145</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.941533361186235</v>
+        <v>1.942453065301351</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005221210429798786</v>
+        <v>0.005221157708364858</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106.6</v>
+        <v>106.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03141334543056142</v>
+        <v>0.03205084413309574</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2907243243243245</v>
+        <v>0.2940869565217392</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.553279662294862</v>
+        <v>4.552621222321237</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.414602237276759</v>
+        <v>4.411237341843712</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.934246575342466</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00219621915227583</v>
+        <v>0.002196536788734055</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5578</v>
+        <v>5595</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.029323739067205</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.934385084259591</v>
+        <v>1.925469168900804</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.463013698630137</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353.9</v>
+        <v>351.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27580</v>
+        <v>27090</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1419949107893225</v>
+        <v>-0.1412013977536799</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02654097171863667</v>
+        <v>0.03861203396087109</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.680847422271937</v>
+        <v>6.679152902116187</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.786489271780413</v>
+        <v>7.777321579990738</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.109589041095891</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001496816102499663</v>
+        <v>0.001497195849017269</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27580</v>
+        <v>27090</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1037367523153655</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1155910079767946</v>
+        <v>0.1357696566998892</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.113108071128417</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2347</v>
+        <v>2369</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03927243767381745</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.458574904985087</v>
+        <v>2.426456438159561</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>1.043990340181344</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>241.7</v>
+        <v>252.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1528956544702157</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.292325196524617</v>
+        <v>2.151504950495049</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.826358535711393</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13450</v>
+        <v>13500</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.008657029597641558</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3454275092936803</v>
+        <v>0.3404444444444445</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.28559321125808</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.01825102720097358</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2807677942264988</v>
+        <v>0.2836181676557863</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.816051931868021</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>235</v>
+        <v>236.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-3.535544158045473</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.09953191489361712</v>
+        <v>0.09163498098859346</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>235.6</v>
+        <v>235.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>235</v>
+        <v>236.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1329465156556612</v>
+        <v>-0.1331948216215309</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002553191489361728</v>
+        <v>-0.003379805661174462</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.413167828470048</v>
+        <v>4.413386458965159</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.089844984369403</v>
+        <v>5.091555252613134</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.684931506849315</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002265946002662398</v>
+        <v>0.002265833752148861</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>279.1</v>
+        <v>280</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.2584440538602029</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2544232353994982</v>
+        <v>0.2503911607142857</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.352370875493646</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>157.1</v>
+        <v>154.7</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.2</v>
+        <v>76.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1337954415986702</v>
+        <v>-0.1275594978174605</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1236154855643044</v>
+        <v>0.09923728813559318</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.073668270411603</v>
+        <v>2.072159421051172</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.393970627721901</v>
+        <v>2.375129783483639</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004822372094267081</v>
+        <v>0.00482588351958324</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.2</v>
+        <v>109.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17050</v>
+        <v>17150</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02053768138204374</v>
+        <v>-0.02007439454908469</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2016380809384164</v>
+        <v>0.1935374600583091</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.935572169051452</v>
+        <v>1.935561390627107</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.976157869740806</v>
+        <v>1.975212587425403</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005166430970590268</v>
+        <v>0.005166459740530408</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>88</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.04894186955758061</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7666477272727272</v>
+        <v>0.7747146118721462</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.186842457686018</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1100323731467035</v>
+        <v>0.1113254326985289</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.180023094688222</v>
+        <v>1.175173210161663</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.908699191097159</v>
+        <v>1.908643647542967</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.7194986716346</v>
+        <v>1.717448005224162</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.934246575342466</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005239170240467172</v>
+        <v>0.005239322705877123</v>
       </c>
     </row>
     <row r="19">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>294.4</v>
+        <v>293.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23530</v>
+        <v>23790</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4732562862740435</v>
+        <v>-0.4722575072130585</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004540594645133789</v>
+        <v>-0.009475374947456983</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.61051335719733</v>
+        <v>1.610486917924269</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.057489468275297</v>
+        <v>3.051652917731697</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.597260273972603</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006209200287169515</v>
+        <v>0.006209302223261051</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>518.1</v>
+        <v>527.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03810336484814374</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.2945028913337191</v>
+        <v>0.2707122925350511</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.9616438356164385</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>93.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1062832862827208</v>
+        <v>0.1018503917581138</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.03946601941747563</v>
+        <v>0.04839805825242727</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.0119481252791</v>
+        <v>2.013149182965884</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.818655447683342</v>
+        <v>1.827062183781321</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.2</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004970307074200924</v>
+        <v>0.004967341757190316</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8446</v>
+        <v>8636</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02924669262878554</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.873137732180914</v>
+        <v>0.831926966882816</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.500293843952853</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.1256979118187518</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.370760455497382</v>
+        <v>0.3460938149100257</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>3.117834691862563</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1242639723976285</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.6293279022403258</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.143967255146119</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0580455277327699</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4446716724409447</v>
+        <v>0.4631044848484847</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.4575342465753425</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12600</v>
+        <v>12710</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-1.695616482004173</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.00973567841269829</v>
+        <v>0.0009968173092054222</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21270</v>
+        <v>21280</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.200920377703702</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1785980253878703</v>
+        <v>0.1780441729323308</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.869114537470215</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>660</v>
+        <v>662.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05497980596791393</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4776560606060607</v>
+        <v>0.4716357326090237</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.807968035221407</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68950</v>
+        <v>69870</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2499437798761603</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1262944162436548</v>
+        <v>0.1114641477028768</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.804837286394418</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>111.6</v>
+        <v>111.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02549753446378271</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.002338709677419337</v>
+        <v>-0.004123434704830009</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.825482749453424</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.0229809783786206</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2108667529107373</v>
+        <v>0.2155844155844155</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.837258926120174</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>912.1</v>
+        <v>936.6</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05327249279601533</v>
+        <v>0.0532801392628415</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8041881372656505</v>
+        <v>0.7569933803117659</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.21733646631943</v>
+        <v>3.214592966047312</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.054609788373656</v>
+        <v>3.051982892506742</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.438356164383562</v>
+        <v>3.435616438356164</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003108161084389102</v>
+        <v>0.003110813750176302</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112.5</v>
+        <v>111.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8873</v>
+        <v>8984</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01398696903957924</v>
+        <v>-0.01085075841697745</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2377322776963822</v>
+        <v>0.2148334345503116</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.915284034416145</v>
+        <v>1.912411636418974</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.942453065301351</v>
+        <v>1.933390388449748</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.934246575342466</v>
+        <v>1.931506849315068</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005221157708364858</v>
+        <v>0.005228999766350086</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106.3</v>
+        <v>107.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03205084413309574</v>
+        <v>0.02992641667636492</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2940869565217392</v>
+        <v>0.2922150537634409</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.552621222321237</v>
+        <v>4.552073190626602</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.411237341843712</v>
+        <v>4.419804285937649</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.934246575342466</v>
+        <v>4.931506849315069</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002196536788734055</v>
+        <v>0.002196801233466873</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5595</v>
+        <v>5646</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.029323739067205</v>
+        <v>0.0294257763032114</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.925469168900804</v>
+        <v>1.8990435706695</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.463013698630137</v>
+        <v>0.4602739726027398</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4498232004730891</v>
+        <v>0.4471172018400759</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4356164383561644</v>
+        <v>0.4328767123287671</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02159763313609467</v>
+        <v>0.02172619047619048</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>351.7</v>
+        <v>362.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27090</v>
+        <v>27930</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1412013977536799</v>
+        <v>-0.1452054630411592</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03861203396087109</v>
+        <v>0.03916935195130677</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.679152902116187</v>
+        <v>6.68490892563571</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.777321579990738</v>
+        <v>7.8204862532452</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.109589041095891</v>
+        <v>7.106849315068493</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001497195849017269</v>
+        <v>0.001495906692408534</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>128.2</v>
+        <v>126.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27090</v>
+        <v>27930</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1037367523153655</v>
+        <v>-0.09787706733951661</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1357696566998892</v>
+        <v>0.08614393125671316</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.113108071128417</v>
+        <v>2.110172578239176</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.357686847683785</v>
+        <v>2.339118652062186</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.106849315068493</v>
+        <v>2.104109589041096</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004732365626079842</v>
+        <v>0.004738948891253462</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2369</v>
+        <v>2434</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03927243767381745</v>
+        <v>0.04040572971597479</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.426456438159561</v>
+        <v>2.331489789646672</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.043990340181344</v>
+        <v>1.041247802589577</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.0045396205427</v>
+        <v>1.000809369700254</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.019178082191781</v>
+        <v>1.016438356164383</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.00957863268951605</v>
+        <v>0.009603861804202665</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.5</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>252.5</v>
+        <v>239.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1528956544702157</v>
+        <v>0.156826137843082</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.151504950495049</v>
+        <v>2.308197406942702</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.826358535711393</v>
+        <v>1.823464236653996</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.584149032594498</v>
+        <v>1.576264727259595</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.854794520547945</v>
+        <v>1.852054794520548</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005475376167639974</v>
+        <v>0.005484066974820252</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.1</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13500</v>
+        <v>13480</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008657029597641558</v>
+        <v>-0.006430099954194372</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3404444444444445</v>
+        <v>0.3293768545994065</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.28559321125808</v>
+        <v>4.281729498471576</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.323017703468132</v>
+        <v>4.309439626013408</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.443835616438356</v>
+        <v>4.441095890410959</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00233339925351067</v>
+        <v>0.002335504847648513</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01825102720097358</v>
+        <v>0.01821970346946516</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2836181676557863</v>
+        <v>0.293211726457399</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.816051931868021</v>
+        <v>2.813319036230509</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.765577305243625</v>
+        <v>2.762978389285192</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.934246575342466</v>
+        <v>2.931506849315069</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003551070875801116</v>
+        <v>0.003554520433416159</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>236.7</v>
+        <v>228</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.535544158045473</v>
+        <v>-3.61103078021347</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.09163498098859346</v>
+        <v>0.1332894736842107</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1095890410958904</v>
+        <v>0.1068493150684932</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>235.9</v>
+        <v>228</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>236.7</v>
+        <v>228</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1331948216215309</v>
+        <v>-0.126606680223352</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003379805661174462</v>
+        <v>0</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.413386458965159</v>
+        <v>4.404810400751156</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.091555252613134</v>
+        <v>5.043329621387068</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.684931506849315</v>
+        <v>4.682191780821918</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002265833752148861</v>
+        <v>0.00227024527509622</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>280</v>
+        <v>287.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2584440538602029</v>
+        <v>-0.2586331588879785</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2503911607142857</v>
+        <v>0.2165028665740096</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.352370875493646</v>
+        <v>3.349688884520956</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.520725500138679</v>
+        <v>4.518260999502692</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.438356164383562</v>
+        <v>3.435616438356164</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00298296351191378</v>
+        <v>0.002985351877366997</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>154.7</v>
+        <v>159.4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.7</v>
+        <v>83.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1275594978174605</v>
+        <v>-0.1398600650615865</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.09923728813559318</v>
+        <v>0.04039520958083842</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.072159421051172</v>
+        <v>2.072390644987207</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.375129783483639</v>
+        <v>2.409364524082458</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.2</v>
+        <v>2.197260273972603</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00482588351958324</v>
+        <v>0.00482534507873236</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.1</v>
+        <v>108.7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17150</v>
+        <v>17090</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02007439454908469</v>
+        <v>-0.01827232514182536</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1935374600583091</v>
+        <v>0.1933364587478057</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.935561390627107</v>
+        <v>1.932779741498756</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.975212587425403</v>
+        <v>1.96875344456188</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.934246575342466</v>
+        <v>1.931506849315068</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005166459740530408</v>
+        <v>0.005173895289406124</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04894186955758061</v>
+        <v>0.04894117851955258</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.7747146118721462</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.186842457686018</v>
+        <v>3.18410311071414</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.038149729908441</v>
+        <v>3.035540196074767</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.438356164383562</v>
+        <v>3.435616438356164</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003137902212857127</v>
+        <v>0.003140601812281503</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.7</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1113254326985289</v>
+        <v>0.1094646543844562</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.175173210161663</v>
+        <v>1.182448036951501</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.908643647542967</v>
+        <v>1.905983853561138</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.717448005224162</v>
+        <v>1.717931117524965</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.934246575342466</v>
+        <v>1.931506849315068</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005239322705877123</v>
+        <v>0.00524663416288444</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145</v>
+        <v>143.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03259823787941077</v>
+        <v>0.03258781378435298</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5206896551724138</v>
+        <v>0.5387299371946963</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.368517874702478</v>
+        <v>3.36578356544677</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.262176663810907</v>
+        <v>3.259561579669857</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.6</v>
+        <v>3.597260273972603</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002968664668547512</v>
+        <v>0.002971076364701607</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23790</v>
+        <v>23360</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4722575072130585</v>
+        <v>-0.4728405246935358</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.009475374947456983</v>
+        <v>0.008757741010273934</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.610486917924269</v>
+        <v>1.607762625126182</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.051652917731697</v>
+        <v>3.049860052674779</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.597260273972603</v>
+        <v>1.594520547945205</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006209302223261051</v>
+        <v>0.006219823650406834</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>527.8</v>
+        <v>515.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03810336484814374</v>
+        <v>0.03810555005149456</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.2707122925350511</v>
+        <v>0.3002751996898023</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9616438356164385</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.926346901647034</v>
+        <v>0.9237057922881494</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9342465753424658</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.0103988603988604</v>
+        <v>0.01042857142857143</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>206</v>
+        <v>208.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1018503917581138</v>
+        <v>0.09696383449089482</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04839805825242727</v>
+        <v>0.04525407478427601</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.013149182965884</v>
+        <v>2.011731018633738</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.827062183781321</v>
+        <v>1.833908243262542</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.2</v>
+        <v>2.197260273972603</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004967341757190316</v>
+        <v>0.004970843471306354</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8636</v>
+        <v>8424</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02924669262878554</v>
+        <v>0.02875356341373242</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.831926966882816</v>
+        <v>0.8822122863247865</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.500293843952853</v>
+        <v>4.497629819539007</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.372415161673933</v>
+        <v>4.371921497520201</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.526027397260274</v>
+        <v>4.523287671232877</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002222077123572104</v>
+        <v>0.002223393298522947</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.9</v>
+        <v>38.4</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1256979118187518</v>
+        <v>0.1011425178305501</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3460938149100257</v>
+        <v>0.464630046875</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.117834691862563</v>
+        <v>3.130382590738099</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.769690393069294</v>
+        <v>2.842849622141118</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.438356164383562</v>
+        <v>3.435616438356164</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003207354137825089</v>
+        <v>0.003194497704397898</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.1</v>
+        <v>49.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1242639723976285</v>
+        <v>0.1243195358414259</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6293279022403258</v>
+        <v>0.606425702811245</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.143967255146119</v>
+        <v>3.141194770311314</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.796467139688938</v>
+        <v>2.793863016851775</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.438356164383562</v>
+        <v>3.435616438356164</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003180694704638468</v>
+        <v>0.003183502052949404</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>45.91975030729211</v>
+        <v>46.16389343908957</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4630136986301369</v>
+        <v>0.4602739726027397</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009868204660035816</v>
+        <v>0.009759032578537363</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4356164383561644</v>
+        <v>0.4328767123287671</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02159763313609468</v>
+        <v>0.02172619047619048</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1254</v>
+        <v>1247</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0580455277327699</v>
+        <v>0.05822530602755908</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4631044848484847</v>
+        <v>0.4713175813953487</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4575342465753425</v>
+        <v>0.4547945205479452</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4324334204746072</v>
+        <v>0.4297709740614549</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4356164383561644</v>
+        <v>0.4328767123287671</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0218562874251497</v>
+        <v>0.02198795180722891</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>485.9</v>
+        <v>490</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12710</v>
+        <v>13030</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.695616482004173</v>
+        <v>-1.70960781510035</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0009968173092054222</v>
+        <v>-0.01534744435917113</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4356164383561644</v>
+        <v>0.4328767123287671</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21280</v>
+        <v>21580</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.200920377703702</v>
+        <v>-0.2011091823242923</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1780441729323308</v>
+        <v>0.1616672845227061</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.869114537470215</v>
+        <v>2.86640809676093</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.590523969595548</v>
+        <v>3.587984782576993</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.934246575342466</v>
+        <v>2.931506849315069</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003485395884131312</v>
+        <v>0.003488686768398436</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05497980596791393</v>
+        <v>0.05497840627961202</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.4716357326090237</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.807968035221407</v>
+        <v>2.805228620078277</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.661632023036855</v>
+        <v>2.659038899166604</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.934246575342466</v>
+        <v>2.931506849315069</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00356129410113157</v>
+        <v>0.003564771843701266</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>93.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.09454495015829291</v>
+        <v>0.1049312824629598</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>2.079282229181495</v>
+        <v>2.00989926049822</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.348360888886843</v>
+        <v>2.343002878517922</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.145513428705896</v>
+        <v>2.120496464988505</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.506849315068493</v>
+        <v>2.504109589041096</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004258289280545864</v>
+        <v>0.004268027193515678</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69870</v>
+        <v>68840</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2499437798761603</v>
+        <v>-0.2502968186848208</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1114641477028768</v>
+        <v>0.1280941313190005</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.804837286394418</v>
+        <v>1.80211038816555</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.406269340845445</v>
+        <v>2.403765160772251</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.808219178082192</v>
+        <v>1.805479452054795</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005540665674066012</v>
+        <v>0.005549049639616946</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>125.1</v>
+        <v>125.3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>111.8</v>
+        <v>112</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02549753446378271</v>
+        <v>-0.0261137617498279</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.004123434704830009</v>
+        <v>-0.004312500000000052</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.825482749453424</v>
+        <v>2.822874283802332</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.899410570396771</v>
+        <v>2.898566765738804</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.934246575342466</v>
+        <v>2.931506849315069</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00353921821038704</v>
+        <v>0.00354248861076813</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0229809783786206</v>
+        <v>0.02294993301752004</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2155844155844155</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.837258926120174</v>
+        <v>1.83452042654149</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.795985423924644</v>
+        <v>1.79336286882583</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.854794520547945</v>
+        <v>1.852054794520548</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005442890959913566</v>
+        <v>0.0054510158923945</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>936.6</v>
+        <v>912.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.0532801392628415</v>
+        <v>0.05328780347174378</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7569933803117659</v>
+        <v>0.8041881372656505</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.214592966047312</v>
+        <v>3.211849456986851</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.051982892506742</v>
+        <v>3.049355975071835</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.435616438356164</v>
+        <v>3.432876712328767</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003110813750176302</v>
+        <v>0.003113470956195236</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.8</v>
+        <v>110.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8984</v>
+        <v>8851</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01085075841697745</v>
+        <v>-0.006740893008153086</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2148334345503116</v>
+        <v>0.2231617204835612</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.912411636418974</v>
+        <v>1.909498105353531</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.933390388449748</v>
+        <v>1.922457183540533</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.931506849315068</v>
+        <v>1.928767123287671</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005228999766350086</v>
+        <v>0.005236978225829957</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.3</v>
+        <v>107.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93</v>
+        <v>92.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02992641667636492</v>
+        <v>0.0286592334061812</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2922150537634409</v>
+        <v>0.3064648648648649</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.552073190626602</v>
+        <v>4.55063734375814</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.419804285937649</v>
+        <v>4.423853105065411</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.931506849315069</v>
+        <v>4.928767123287671</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002196801233466873</v>
+        <v>0.002197494382565214</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5646</v>
+        <v>5661</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0294257763032114</v>
+        <v>0.0295290403454566</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.8990435706695</v>
+        <v>1.891361950185479</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4602739726027398</v>
+        <v>0.4575342465753425</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4471172018400759</v>
+        <v>0.4444112100245542</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4328767123287671</v>
+        <v>0.4301369863013699</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02172619047619048</v>
+        <v>0.0218562874251497</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>362.8</v>
+        <v>353</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27930</v>
+        <v>27210</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1452054630411592</v>
+        <v>-0.1417865379261262</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03916935195130677</v>
+        <v>0.03785373024623295</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.68490892563571</v>
+        <v>6.6749235182443</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.8204862532452</v>
+        <v>7.777696124824633</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.106849315068493</v>
+        <v>7.104109589041096</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001495906692408534</v>
+        <v>0.001498144506475228</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>126.4</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27930</v>
+        <v>27210</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09787706733951661</v>
+        <v>-0.1098832689543343</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.08614393125671316</v>
+        <v>0.1466372657111357</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.110172578239176</v>
+        <v>2.107832944207408</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.339118652062186</v>
+        <v>2.368041034046431</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.104109589041096</v>
+        <v>2.101369863013699</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004738948891253462</v>
+        <v>0.004744208988421625</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2434</v>
+        <v>2381</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04040572971597479</v>
+        <v>0.03946948440893498</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.331489789646672</v>
+        <v>2.409187443091138</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.041247802589577</v>
+        <v>1.038510399275618</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>1.000809369700254</v>
+        <v>0.9990773320932438</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.016438356164383</v>
+        <v>1.013698630136986</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009603861804202665</v>
+        <v>0.00962917656575726</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>81.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>239.1</v>
+        <v>222.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.156826137843082</v>
+        <v>0.1669890001960051</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.308197406942702</v>
+        <v>2.502478632478632</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.823464236653996</v>
+        <v>1.820325071049502</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.576264727259595</v>
+        <v>1.559847668438832</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.852054794520548</v>
+        <v>1.849315068493151</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005484066974820252</v>
+        <v>0.005493524293567267</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>111.8</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13480</v>
+        <v>13470</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006430099954194372</v>
+        <v>-0.006034343290885128</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3293768545994065</v>
+        <v>0.3279881217520415</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.281729498471576</v>
+        <v>4.278789497880868</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.309439626013408</v>
+        <v>4.304765933309364</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.441095890410959</v>
+        <v>4.438356164383562</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002335504847648513</v>
+        <v>0.002337109597224319</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110.5</v>
+        <v>110.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1338</v>
+        <v>1312</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01821970346946516</v>
+        <v>0.01851566249580399</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.293211726457399</v>
+        <v>0.3176458780487805</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.813319036230509</v>
+        <v>2.810514769576426</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.762978389285192</v>
+        <v>2.759422238720854</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.931506849315069</v>
+        <v>2.928767123287671</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003554520433416159</v>
+        <v>0.003558067051719179</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.61103078021347</v>
+        <v>-3.689799395604212</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.1332894736842107</v>
+        <v>0.1691855203619912</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1068493150684932</v>
+        <v>0.1041095890410959</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228</v>
+        <v>225.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.126606680223352</v>
+        <v>-0.1244306552651475</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0</v>
+        <v>0.01990950226244337</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.404810400751156</v>
+        <v>4.400126722177613</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.043329621387068</v>
+        <v>5.025446298042901</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.682191780821918</v>
+        <v>4.67945205479452</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00227024527509622</v>
+        <v>0.002272661818942119</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>287.8</v>
+        <v>287.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2586331588879785</v>
+        <v>-0.2588225216280736</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2165028665740096</v>
+        <v>0.2194689132706371</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.349688884520956</v>
+        <v>3.347006953976468</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.518260999502692</v>
+        <v>4.515796892976993</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.435616438356164</v>
+        <v>3.432876712328767</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002985351877366997</v>
+        <v>0.002987744016521786</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159.4</v>
+        <v>158.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>83.5</v>
+        <v>78.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1398600650615865</v>
+        <v>-0.1370402335496236</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.04039520958083842</v>
+        <v>0.1011366538952745</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.072390644987207</v>
+        <v>2.068971746652164</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.409364524082458</v>
+        <v>2.397529788859673</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.197260273972603</v>
+        <v>2.194520547945205</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00482534507873236</v>
+        <v>0.0048333187807814</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17090</v>
+        <v>17140</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01827232514182536</v>
+        <v>-0.01833004065124536</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1933364587478057</v>
+        <v>0.1898553138856476</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.932779741498756</v>
+        <v>1.93004135810144</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.96875344456188</v>
+        <v>1.966079678532528</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.931506849315068</v>
+        <v>1.928767123287671</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005173895289406124</v>
+        <v>0.005181236121197367</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.3</v>
+        <v>100.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>87.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04894117851955258</v>
+        <v>0.04830119794834966</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7747146118721462</v>
+        <v>0.7946428571428572</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.18410311071414</v>
+        <v>3.181714319138773</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.035540196074767</v>
+        <v>3.035114645834391</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.435616438356164</v>
+        <v>3.432876712328767</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003140601812281503</v>
+        <v>0.003142959737097579</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1094646543844562</v>
+        <v>0.1108364177465873</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.182448036951501</v>
+        <v>1.177598152424943</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.905983853561138</v>
+        <v>1.903185200430082</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.717931117524965</v>
+        <v>1.713290246903169</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.931506849315068</v>
+        <v>1.928767123287671</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00524663416288444</v>
+        <v>0.005254349391609497</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>143.3</v>
+        <v>143.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03258781378435298</v>
+        <v>0.03257737738611286</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5387299371946963</v>
+        <v>0.5323141070187629</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.36578356544677</v>
+        <v>3.363049262524029</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.259561579669857</v>
+        <v>3.256946487668865</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.597260273972603</v>
+        <v>3.594520547945205</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002971076364701607</v>
+        <v>0.002973491976889693</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23360</v>
+        <v>23650</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4728405246935358</v>
+        <v>-0.4734248793423396</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.008757741010273934</v>
+        <v>-0.003611804228329851</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.607762625126182</v>
+        <v>1.605038368209563</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.049860052674779</v>
+        <v>3.048071025849015</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.594520547945205</v>
+        <v>1.591780821917808</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006219823650406834</v>
+        <v>0.006230380655108638</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>515.8</v>
+        <v>528</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03810555005149456</v>
+        <v>0.03810776889073911</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3002751996898023</v>
+        <v>0.270230962121212</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.958904109589041</v>
+        <v>0.9561643835616439</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9237057922881494</v>
+        <v>0.9210646642047047</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9315068493150684</v>
+        <v>0.9287671232876712</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01042857142857143</v>
+        <v>0.01045845272206304</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>94.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>208.6</v>
+        <v>215.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09696383449089482</v>
+        <v>0.08052687301371624</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04525407478427601</v>
+        <v>0.04632899628252796</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.011731018633738</v>
+        <v>2.013417850557607</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.833908243262542</v>
+        <v>1.863366752686075</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.197260273972603</v>
+        <v>2.194520547945205</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004970843471306354</v>
+        <v>0.004966678922226971</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8424</v>
+        <v>8522</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02875356341373242</v>
+        <v>0.02876786408886853</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8822122863247865</v>
+        <v>0.8605675076273176</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.497629819539007</v>
+        <v>4.494887899326243</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.371921497520201</v>
+        <v>4.369195477647579</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.523287671232877</v>
+        <v>4.52054794520548</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002223393298522947</v>
+        <v>0.002224749587525629</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.4</v>
+        <v>37.8</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1011425178305501</v>
+        <v>0.09883966885495762</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.464630046875</v>
+        <v>0.4981393714285713</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.130382590738099</v>
+        <v>3.129059671562308</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.842849622141118</v>
+        <v>2.847603485978018</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.435616438356164</v>
+        <v>3.432876712328767</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003194497704397898</v>
+        <v>0.003195848289785762</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1243195358414259</v>
+        <v>0.1239424306430731</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.606425702811245</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.141194770311314</v>
+        <v>3.138677343888304</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.793863016851775</v>
+        <v>2.792560595912802</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.435616438356164</v>
+        <v>3.432876712328767</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003183502052949404</v>
+        <v>0.003186055431748091</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>46.16389343908957</v>
+        <v>46.41099586111251</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4602739726027397</v>
+        <v>0.4575342465753425</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009759032578537363</v>
+        <v>0.009650382538170256</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4328767123287671</v>
+        <v>0.4301369863013699</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02172619047619048</v>
+        <v>0.0218562874251497</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1247</v>
+        <v>1262</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05822530602755908</v>
+        <v>0.05840728918125685</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4713175813953487</v>
+        <v>0.4538296545166403</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4547945205479452</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4297709740614549</v>
+        <v>0.4271085423743067</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4328767123287671</v>
+        <v>0.4301369863013699</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02198795180722891</v>
+        <v>0.02212121212121212</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>490</v>
+        <v>494.1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13030</v>
+        <v>12920</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.70960781510035</v>
+        <v>-1.723701763904011</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.01534744435917113</v>
+        <v>0.001344895665634782</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4328767123287671</v>
+        <v>0.4301369863013699</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>217.8</v>
+        <v>199.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21580</v>
+        <v>21200</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.2011091823242923</v>
+        <v>-0.1770250801935547</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1616672845227061</v>
+        <v>0.08530613207547155</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.86640809676093</v>
+        <v>2.859385497374448</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.587984782576993</v>
+        <v>3.474450349042161</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.931506849315069</v>
+        <v>2.928767123287671</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003488686768398436</v>
+        <v>0.003497254920395387</v>
       </c>
     </row>
     <row r="30">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>100.5</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>662.7</v>
+        <v>654.6</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05497840627961202</v>
+        <v>0.05310579291153353</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4716357326090237</v>
+        <v>0.49729493583868</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.805228620078277</v>
+        <v>2.802904629471614</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.659038899166604</v>
+        <v>2.661560356364949</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.931506849315069</v>
+        <v>2.928767123287671</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003564771843701266</v>
+        <v>0.003567727526243067</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1049312824629598</v>
+        <v>0.1049731669732489</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>2.00989926049822</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.343002878517922</v>
+        <v>2.340252570796617</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.120496464988505</v>
+        <v>2.117927059900518</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.504109589041096</v>
+        <v>2.501369863013699</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004268027193515678</v>
+        <v>0.004273043057312408</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68840</v>
+        <v>69260</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2502968186848208</v>
+        <v>-0.2506507615960647</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1280941313190005</v>
+        <v>0.1212532486283568</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.80211038816555</v>
+        <v>1.799383523127496</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.403765160772251</v>
+        <v>2.401261562579372</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.805479452054795</v>
+        <v>1.802739726027397</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005549049639616946</v>
+        <v>0.005557458913827924</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0261137617498279</v>
+        <v>-0.02618024662277601</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.004312500000000052</v>
+        <v>0.004657657657657577</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.822874283802332</v>
+        <v>2.820148716822312</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.898566765738804</v>
+        <v>2.89596581609891</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.931506849315069</v>
+        <v>2.928767123287671</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00354248861076813</v>
+        <v>0.003545912291911968</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02294993301752004</v>
+        <v>0.02291880352147979</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2155844155844155</v>
+        <v>0.2147955872809864</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.83452042654149</v>
+        <v>1.831781930289715</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.79336286882583</v>
+        <v>1.790740305079601</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.852054794520548</v>
+        <v>1.849315068493151</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.0054510158923945</v>
+        <v>0.005459165108380777</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05328780347174378</v>
+        <v>0.05330318529451653</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.8041881372656505</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.211849456986851</v>
+        <v>3.206362412411817</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.049355975071835</v>
+        <v>3.044102075429762</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.432876712328767</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003113470956195236</v>
+        <v>0.003118799035720366</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006740893008153086</v>
+        <v>-0.006884955204624019</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2231617204835612</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.909498105353531</v>
+        <v>1.904024744579488</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.922457183540533</v>
+        <v>1.917224751108064</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.928767123287671</v>
+        <v>1.923287671232877</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005236978225829957</v>
+        <v>0.005252032584381429</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0286592334061812</v>
+        <v>0.02864151692544225</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3064648648648649</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.55063734375814</v>
+        <v>4.545176103068998</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.423853105065411</v>
+        <v>4.418620120111719</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.928767123287671</v>
+        <v>4.923287671232877</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002197494382565214</v>
+        <v>0.002200134774370522</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0295290403454566</v>
+        <v>0.02973933806901332</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.891361950185479</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4575342465753425</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4444112100245542</v>
+        <v>0.4389992474874754</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4301369863013699</v>
+        <v>0.4246575342465753</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0218562874251497</v>
+        <v>0.02212121212121212</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1417865379261262</v>
+        <v>-0.1419022485842975</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.03785373024623295</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.6749235182443</v>
+        <v>6.669690918751789</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.777696124824633</v>
+        <v>7.772647006413934</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.104109589041096</v>
+        <v>7.098630136986301</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001498144506475228</v>
+        <v>0.00149931985182178</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1098832689543343</v>
+        <v>-0.1101665883820807</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1466372657111357</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.107832944207408</v>
+        <v>2.102362885075562</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.368041034046431</v>
+        <v>2.362647724424046</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.101369863013699</v>
+        <v>2.095890410958904</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004744208988421625</v>
+        <v>0.004756552767835123</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03946948440893498</v>
+        <v>0.03966865976718447</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.409187443091138</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.038510399275618</v>
+        <v>1.033030453089504</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9990773320932438</v>
+        <v>0.9936150747497119</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.013698630136986</v>
+        <v>1.008219178082192</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.00962917656575726</v>
+        <v>0.009680256734051557</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1669890001960051</v>
+        <v>0.1673391185457495</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.502478632478632</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.820325071049502</v>
+        <v>1.814831863968205</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.559847668438832</v>
+        <v>1.554674074684562</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.849315068493151</v>
+        <v>1.843835616438356</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005493524293567267</v>
+        <v>0.005510152316884379</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006034343290885128</v>
+        <v>-0.006064636561167299</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.3279881217520415</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.278789497880868</v>
+        <v>4.273325381499484</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.304765933309364</v>
+        <v>4.299399677977618</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.438356164383562</v>
+        <v>4.432876712328767</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002337109597224319</v>
+        <v>0.002340097958206745</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01851566249580399</v>
+        <v>0.01845327621102016</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.3176458780487805</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.810514769576426</v>
+        <v>2.805048923094165</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.759422238720854</v>
+        <v>2.754224458415869</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.928767123287671</v>
+        <v>2.923287671232877</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003558067051719179</v>
+        <v>0.003565000210038869</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.689799395604212</v>
+        <v>-3.858077695141456</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>0.1691855203619912</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.1041095890410959</v>
+        <v>0.09863013698630137</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1244306552651475</v>
+        <v>-0.124602149403414</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.01990950226244337</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.400126722177613</v>
+        <v>4.394800767536345</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.025446298042901</v>
+        <v>5.020346765235117</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.67945205479452</v>
+        <v>4.673972602739726</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002272661818942119</v>
+        <v>0.002275416003808027</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2588225216280736</v>
+        <v>-0.2592020223089249</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2194689132706371</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.347006953976468</v>
+        <v>3.341643274508094</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.515796892976993</v>
+        <v>4.510869866199356</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.432876712328767</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002987744016521786</v>
+        <v>0.002992539651459969</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1370402335496236</v>
+        <v>-0.1374758055627286</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1011366538952745</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.068971746652164</v>
+        <v>2.063597278652228</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.397529788859673</v>
+        <v>2.392509441429131</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.194520547945205</v>
+        <v>2.189041095890411</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.0048333187807814</v>
+        <v>0.004845906758769898</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01833004065124536</v>
+        <v>-0.01844594820372227</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1898553138856476</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.93004135810144</v>
+        <v>1.924564602403509</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.966079678532528</v>
+        <v>1.960732166386038</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.928767123287671</v>
+        <v>1.923287671232877</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005181236121197367</v>
+        <v>0.005195980424617294</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04830119794834966</v>
+        <v>0.04829890761931026</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.7946428571428572</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.181714319138773</v>
+        <v>3.176236122579064</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.035114645834391</v>
+        <v>3.029895480662385</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.432876712328767</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003142959737097579</v>
+        <v>0.003148380540386313</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1108364177465873</v>
+        <v>0.1109954748881098</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.177598152424943</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.903185200430082</v>
+        <v>1.89769891619999</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.713290246903169</v>
+        <v>1.708106791696077</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.928767123287671</v>
+        <v>1.923287671232877</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005254349391609497</v>
+        <v>0.005269539817214158</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03257737738611286</v>
+        <v>0.03255646755838181</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5323141070187629</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.363049262524029</v>
+        <v>3.357580675739836</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.256946487668865</v>
+        <v>3.251716280155879</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.594520547945205</v>
+        <v>3.589041095890411</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002973491976889693</v>
+        <v>0.002978334987526851</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4734248793423396</v>
+        <v>-0.474597617053232</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.003611804228329851</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.605038368209563</v>
+        <v>1.599589962481797</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.048071025849015</v>
+        <v>3.044504582393305</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.591780821917808</v>
+        <v>1.586301369863014</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006230380655108638</v>
+        <v>0.006251602119636205</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03810776889073911</v>
+        <v>0.03811230861497232</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.270230962121212</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9561643835616439</v>
+        <v>0.9506849315068492</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9210646642047047</v>
+        <v>0.9157823518875651</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9287671232876712</v>
+        <v>0.9232876712328767</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01045845272206304</v>
+        <v>0.01051873198847262</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08052687301371624</v>
+        <v>0.08055574316439855</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.04632899628252796</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.013417850557607</v>
+        <v>2.007930649274841</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.863366752686075</v>
+        <v>1.858238838650408</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.194520547945205</v>
+        <v>2.189041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004966678922226971</v>
+        <v>0.004980251685291758</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02876786408886853</v>
+        <v>0.02879651857999165</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8605675076273176</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.494887899326243</v>
+        <v>4.489404050540456</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.369195477647579</v>
+        <v>4.363743431730317</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.52054794520548</v>
+        <v>4.515068493150685</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002224749587525629</v>
+        <v>0.00222746713983032</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09883966885495762</v>
+        <v>0.0989043375258906</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4981393714285713</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.129059671562308</v>
+        <v>3.12354047255212</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.847603485978018</v>
+        <v>2.842413453007713</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.432876712328767</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003195848289785762</v>
+        <v>0.003201495254463407</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1239424306430731</v>
+        <v>0.1240534441581308</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.6181818181818182</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.138677343888304</v>
+        <v>3.133132458344135</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.792560595912802</v>
+        <v>2.78735186002719</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.432876712328767</v>
+        <v>3.427397260273973</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003186055431748091</v>
+        <v>0.003191693978136186</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>46.41099586111251</v>
+        <v>46.91429353778751</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4575342465753425</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009650382538170256</v>
+        <v>0.009434654278352991</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4301369863013699</v>
+        <v>0.4246575342465753</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0218562874251497</v>
+        <v>0.02212121212121212</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05840728918125685</v>
+        <v>0.05877803236276298</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.4538296545166403</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4271085423743067</v>
+        <v>0.4217837250260836</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4301369863013699</v>
+        <v>0.4246575342465753</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02212121212121212</v>
+        <v>0.02239263803680982</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.723701763904011</v>
+        <v>-1.744620899435026</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.001344895665634782</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4301369863013699</v>
+        <v>0.4246575342465753</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1770250801935547</v>
+        <v>-0.1773723291620662</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.08530613207547155</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.859385497374448</v>
+        <v>2.853968323023409</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.474450349042161</v>
+        <v>3.469331781796665</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.928767123287671</v>
+        <v>2.923287671232877</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003497254920395387</v>
+        <v>0.00350389312990212</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05310579291153353</v>
+        <v>0.05309992737260327</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.49729493583868</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.802904629471614</v>
+        <v>2.797426479017109</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.661560356364949</v>
+        <v>2.656373252248204</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.928767123287671</v>
+        <v>2.923287671232877</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003567727526243067</v>
+        <v>0.003574714143520066</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1049731669732489</v>
+        <v>0.1050572846599738</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>2.00989926049822</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.340252570796617</v>
+        <v>2.334751866710125</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.117927059900518</v>
+        <v>2.112788087206293</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.501369863013699</v>
+        <v>2.495890410958904</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004273043057312408</v>
+        <v>0.004283110399260928</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2506507615960647</v>
+        <v>-0.2513613734802393</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1212532486283568</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.799383523127496</v>
+        <v>1.793929893134127</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.401261562579372</v>
+        <v>2.396256123563477</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.802739726027397</v>
+        <v>1.797260273972603</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005557458913827924</v>
+        <v>0.005574353846419978</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02618024662277601</v>
+        <v>-0.02631357501724843</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.004657657657657577</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.820148716822312</v>
+        <v>2.814697657681765</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.89596581609891</v>
+        <v>2.890763992865184</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.928767123287671</v>
+        <v>2.923287671232877</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003545912291911968</v>
+        <v>0.00355277945135897</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02291880352147979</v>
+        <v>0.02285629061745103</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2147955872809864</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.831781930289715</v>
+        <v>1.826304947826534</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.790740305079601</v>
+        <v>1.785495151742263</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.849315068493151</v>
+        <v>1.843835616438356</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005459165108380777</v>
+        <v>0.005475536827461861</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>912.1</v>
+        <v>927.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05330318529451653</v>
+        <v>0.05331090299814331</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8041881372656505</v>
+        <v>0.7749973034192643</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.206362412411817</v>
+        <v>3.203618876852504</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.044102075429762</v>
+        <v>3.041475093188275</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.427397260273973</v>
+        <v>3.424657534246575</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003118799035720366</v>
+        <v>0.003121469932723338</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.9</v>
+        <v>110.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8851</v>
+        <v>8655</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006884955204624019</v>
+        <v>-0.006016298902675612</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2231617204835612</v>
+        <v>0.2486054447140382</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.904024744579488</v>
+        <v>1.901248290944222</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.917224751108064</v>
+        <v>1.912756002784863</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.923287671232877</v>
+        <v>1.920547945205479</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005252032584381429</v>
+        <v>0.005259702295397553</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.9</v>
+        <v>108.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02864151692544225</v>
+        <v>0.02738077732416245</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3064648648648649</v>
+        <v>0.291392136025505</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.545176103068998</v>
+        <v>4.543731047532381</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.418620120111719</v>
+        <v>4.422635840400514</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.923287671232877</v>
+        <v>4.920547945205479</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002200134774370522</v>
+        <v>0.002200834489407295</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5661</v>
+        <v>5633</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.02973933806901332</v>
+        <v>0.02984641772056688</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.891361950185479</v>
+        <v>1.905734067104563</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4493150684931506</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4389992474874754</v>
+        <v>0.4362932770962606</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4246575342465753</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02212121212121212</v>
+        <v>0.02225609756097561</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>353.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27210</v>
+        <v>27400</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1419022485842975</v>
+        <v>-0.1422485625889217</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03785373024623295</v>
+        <v>0.0329927007299271</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.669690918751789</v>
+        <v>6.667689321951649</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.772647006413934</v>
+        <v>7.773451644775444</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.098630136986301</v>
+        <v>7.095890410958904</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00149931985182178</v>
+        <v>0.00149976993785202</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>131.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27210</v>
+        <v>27400</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1101665883820807</v>
+        <v>-0.1138539698499813</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1466372657111357</v>
+        <v>0.1483211678832117</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.102362885075562</v>
+        <v>2.099745203805855</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.362647724424046</v>
+        <v>2.369525035789397</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.095890410958904</v>
+        <v>2.093150684931507</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004756552767835123</v>
+        <v>0.0047624826011626</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2381</v>
+        <v>2398</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03966865976718447</v>
+        <v>0.03976905648626575</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.409187443091138</v>
+        <v>2.385018891576313</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.033030453089504</v>
+        <v>1.030290477989497</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9936150747497119</v>
+        <v>0.9908839578965734</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.008219178082192</v>
+        <v>1.005479452054794</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009680256734051557</v>
+        <v>0.009706000602387344</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>222.3</v>
+        <v>223.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1673391185457495</v>
+        <v>0.1675150343687785</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.502478632478632</v>
+        <v>2.488355734767025</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.814831863968205</v>
+        <v>1.812085226922654</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.554674074684562</v>
+        <v>1.552087273893106</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.843835616438356</v>
+        <v>1.841095890410959</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005510152316884379</v>
+        <v>0.005518504235577456</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13470</v>
+        <v>13420</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006064636561167299</v>
+        <v>-0.006079811137193356</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3279881217520415</v>
+        <v>0.3329359165424739</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.273325381499484</v>
+        <v>4.270593337103426</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.299399677977618</v>
+        <v>4.296716562312335</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.432876712328767</v>
+        <v>4.43013698630137</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002340097958206745</v>
+        <v>0.002341594998783612</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1312</v>
+        <v>1286</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01845327621102016</v>
+        <v>0.01842200323823806</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3176458780487805</v>
+        <v>0.3442856858475896</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.805048923094165</v>
+        <v>2.802316017098516</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.754224458415869</v>
+        <v>2.751625562083397</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.923287671232877</v>
+        <v>2.92054794520548</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003565000210038869</v>
+        <v>0.003568476909450733</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221</v>
+        <v>233.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.858077695141456</v>
+        <v>-3.94808696389495</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.1691855203619912</v>
+        <v>0.1065952890792292</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.09863013698630137</v>
+        <v>0.0958904109589041</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225.4</v>
+        <v>233.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221</v>
+        <v>233.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.124602149403414</v>
+        <v>-0.1313888544306458</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01990950226244337</v>
+        <v>-0.001284796573875813</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.394800767536345</v>
+        <v>4.398095302635406</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.020346765235117</v>
+        <v>5.063365034019403</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.673972602739726</v>
+        <v>4.671232876712328</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002275416003808027</v>
+        <v>0.002273711530081635</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>287.1</v>
+        <v>293</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2592020223089249</v>
+        <v>-0.2593921612848881</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2194689132706371</v>
+        <v>0.1949130546075084</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.341643274508094</v>
+        <v>3.33896152575251</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.510869866199356</v>
+        <v>4.508406947927136</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.427397260273973</v>
+        <v>3.424657534246575</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002992539651459969</v>
+        <v>0.002994943165074739</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>158.2</v>
+        <v>156.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1374758055627286</v>
+        <v>-0.1335764440985509</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1011366538952745</v>
+        <v>0.09000000000000008</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.063597278652228</v>
+        <v>2.059916744961388</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.392509441429131</v>
+        <v>2.377493929996165</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.189041095890411</v>
+        <v>2.186301369863014</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004845906758769898</v>
+        <v>0.004854565129615199</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.7</v>
+        <v>108.4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17140</v>
+        <v>17060</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01844594820372227</v>
+        <v>-0.01709344386114768</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1898553138856476</v>
+        <v>0.1921356717467761</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.924564602403509</v>
+        <v>1.9217934140005</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.960732166386038</v>
+        <v>1.955214767871599</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.923287671232877</v>
+        <v>1.920547945205479</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005195980424617294</v>
+        <v>0.005203472926459618</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>86.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04829890761931026</v>
+        <v>0.04829776821552739</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7946428571428572</v>
+        <v>0.8134458672875435</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.176236122579064</v>
+        <v>3.17349702114024</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.029895480662385</v>
+        <v>3.027285869874881</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.427397260273973</v>
+        <v>3.424657534246575</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003148380540386313</v>
+        <v>0.003151097963346124</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1109954748881098</v>
+        <v>0.1110753775610274</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.177598152424943</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.89769891619999</v>
+        <v>1.89495575805277</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.708106791696077</v>
+        <v>1.705515031943625</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.923287671232877</v>
+        <v>1.920547945205479</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005269539817214158</v>
+        <v>0.005277168059203587</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105</v>
+        <v>104.7</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>143.9</v>
+        <v>142.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03255646755838181</v>
+        <v>0.03341178571165074</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5323141070187629</v>
+        <v>0.5472906403940887</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.357580675739836</v>
+        <v>3.354396307469355</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.251716280155879</v>
+        <v>3.245943537560274</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.589041095890411</v>
+        <v>3.586301369863014</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002978334987526851</v>
+        <v>0.002981162356318077</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>293.5</v>
+        <v>295.7</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23650</v>
+        <v>23580</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.474597617053232</v>
+        <v>-0.4776255371490468</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.003611804228329851</v>
+        <v>0.006836930703986388</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.599589962481797</v>
+        <v>1.596930404766039</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.044504582393305</v>
+        <v>3.057060630511113</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.586301369863014</v>
+        <v>1.583561643835616</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006251602119636205</v>
+        <v>0.006262013654543114</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>528</v>
+        <v>515.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03811230861497232</v>
+        <v>0.03811463007722156</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.270230962121212</v>
+        <v>0.3010319068865177</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9506849315068492</v>
+        <v>0.9479452054794522</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9157823518875651</v>
+        <v>0.9131411676655958</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9232876712328767</v>
+        <v>0.9205479452054794</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01051873198847262</v>
+        <v>0.01054913294797688</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>215.2</v>
+        <v>210.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08055574316439855</v>
+        <v>0.08004999601416139</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.04632899628252796</v>
+        <v>0.07231208372978104</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.007930649274841</v>
+        <v>2.005326661020378</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.858238838650408</v>
+        <v>1.856697994001089</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.189041095890411</v>
+        <v>2.186301369863014</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004980251685291758</v>
+        <v>0.004986718719887592</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8522</v>
+        <v>8661</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02879651857999165</v>
+        <v>0.02906517862899141</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8605675076273176</v>
+        <v>0.8286732239926107</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.489404050540456</v>
+        <v>4.486623088029574</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.363743431730317</v>
+        <v>4.359901764441234</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.515068493150685</v>
+        <v>4.512328767123288</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00222746713983032</v>
+        <v>0.002228847800181892</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.0989043375258906</v>
+        <v>0.09893677336949547</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.4981393714285713</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.12354047255212</v>
+        <v>3.120780809789781</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.842413453007713</v>
+        <v>2.839818345709759</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.427397260273973</v>
+        <v>3.424657534246575</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003201495254463407</v>
+        <v>0.003204326291878734</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1240534441581308</v>
+        <v>0.1241091163835318</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6181818181818182</v>
+        <v>0.6052104208416833</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.133132458344135</v>
+        <v>3.130359915583265</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.78735186002719</v>
+        <v>2.784747379021544</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.427397260273973</v>
+        <v>3.424657534246575</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003191693978136186</v>
+        <v>0.003194520844142853</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>46.91429353778751</v>
+        <v>47.17059955066739</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4493150684931507</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009434654278352991</v>
+        <v>0.009327578910877923</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4246575342465753</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02212121212121212</v>
+        <v>0.02225609756097561</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1262</v>
+        <v>1281</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05877803236276298</v>
+        <v>0.05896687604385648</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4538296545166403</v>
+        <v>0.4322662170179545</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4217837250260836</v>
+        <v>0.4191213403165738</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4246575342465753</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02239263803680982</v>
+        <v>0.02253086419753086</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>494.1</v>
+        <v>505</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12920</v>
+        <v>13000</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.744620899435026</v>
+        <v>-1.765368597610327</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.001344895665634782</v>
+        <v>0.01713681538461542</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4246575342465753</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>199.9</v>
+        <v>187.7</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21200</v>
+        <v>21120</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1773723291620662</v>
+        <v>-0.1591939989876037</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.08530613207547155</v>
+        <v>0.02292945075757569</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.853968323023409</v>
+        <v>2.847947893531116</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.469331781796665</v>
+        <v>3.387164090291891</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.923287671232877</v>
+        <v>2.92054794520548</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00350389312990212</v>
+        <v>0.00351130019713991</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>654.6</v>
+        <v>658.6</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05309992737260327</v>
+        <v>0.05309699863086673</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.49729493583868</v>
+        <v>0.4882011311873671</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.797426479017109</v>
+        <v>2.794687402894681</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.656373252248204</v>
+        <v>2.653779667521661</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.923287671232877</v>
+        <v>2.92054794520548</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003574714143520066</v>
+        <v>0.003578217724687993</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>91.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1050572846599738</v>
+        <v>0.1237474910409608</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>2.00989926049822</v>
+        <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.334751866710125</v>
+        <v>2.327271834396019</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.112788087206293</v>
+        <v>2.070991795710439</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.495890410958904</v>
+        <v>2.493150684931507</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004283110399260928</v>
+        <v>0.004296876648530931</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69260</v>
+        <v>68890</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2513613734802393</v>
+        <v>-0.2517180493738928</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1212532486283568</v>
+        <v>0.1272753665263464</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.793929893134127</v>
+        <v>1.791203128435598</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.396256123563477</v>
+        <v>2.393754288656638</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.797260273972603</v>
+        <v>1.794520547945206</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005574353846419978</v>
+        <v>0.005582839735621612</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>125.3</v>
+        <v>120</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02631357501724843</v>
+        <v>-0.01132735896672346</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.004657657657657577</v>
+        <v>-0.02018348623853217</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.814697657681765</v>
+        <v>2.8087535667162</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.890763992865184</v>
+        <v>2.840933844169825</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.923287671232877</v>
+        <v>2.92054794520548</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00355277945135897</v>
+        <v>0.003560298104646933</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>104</v>
+        <v>102.1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02285629061745103</v>
+        <v>0.03315947431356317</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2147955872809864</v>
+        <v>0.194928478543563</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.826304947826534</v>
+        <v>1.823158363188717</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.785495151742263</v>
+        <v>1.764643705561558</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.843835616438356</v>
+        <v>1.841095890410959</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005475536827461861</v>
+        <v>0.005484987043314179</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>927.1</v>
+        <v>960</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05331090299814331</v>
+        <v>0.05331863862336027</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7749973034192643</v>
+        <v>0.7141666666666666</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.203618876852504</v>
+        <v>3.200875332415373</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.041475093188275</v>
+        <v>3.038848089310156</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.424657534246575</v>
+        <v>3.421917808219178</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003121469932723338</v>
+        <v>0.003124145416951938</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.7</v>
+        <v>110.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8655</v>
+        <v>8808</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006016298902675612</v>
+        <v>-0.006559046239437926</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2486054447140382</v>
+        <v>0.2280247792915531</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.901248290944222</v>
+        <v>1.898531512455459</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.912756002784863</v>
+        <v>1.911066284582668</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.920547945205479</v>
+        <v>1.917808219178082</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005259702295397553</v>
+        <v>0.005267228873681709</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.5</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02738077732416245</v>
+        <v>0.02633427360948439</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.291392136025505</v>
+        <v>0.2959660297239917</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.543731047532381</v>
+        <v>4.542064063296587</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.422635840400514</v>
+        <v>4.42552117773748</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.920547945205479</v>
+        <v>4.917808219178082</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002200834489407295</v>
+        <v>0.002201642218305062</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5633</v>
+        <v>5665</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.02984641772056688</v>
+        <v>0.02995481615221923</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.905734067104563</v>
+        <v>1.889320388349514</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4493150684931506</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4362932770962606</v>
+        <v>0.4335873141834536</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02225609756097561</v>
+        <v>0.02239263803680982</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353.8</v>
+        <v>350.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27400</v>
+        <v>26830</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1422485625889217</v>
+        <v>-0.1412571860357881</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0329927007299271</v>
+        <v>0.04629146477823332</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.667689321951649</v>
+        <v>6.662833855944014</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.773451644775444</v>
+        <v>7.758823419070483</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.095890410958904</v>
+        <v>7.093150684931507</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00149976993785202</v>
+        <v>0.001500862878500092</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>131.1</v>
+        <v>132</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27400</v>
+        <v>26830</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1138539698499813</v>
+        <v>-0.1168718382627992</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1483211678832117</v>
+        <v>0.1807677972418935</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.099745203805855</v>
+        <v>2.097105081782557</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.369525035789397</v>
+        <v>2.374632779977646</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.093150684931507</v>
+        <v>2.09041095890411</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.0047624826011626</v>
+        <v>0.004768478264093431</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2398</v>
+        <v>2419</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03976905648626575</v>
+        <v>0.03777781544305313</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.385018891576313</v>
+        <v>2.36260174038859</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.030290477989497</v>
+        <v>1.0275556920233</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9908839578965734</v>
+        <v>0.9901499884969219</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.005479452054794</v>
+        <v>1.002739726027397</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009706000602387344</v>
+        <v>0.009731832617567993</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>223.2</v>
+        <v>230</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1675150343687785</v>
+        <v>0.1676915249270491</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.488355734767025</v>
+        <v>2.385221739130435</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.812085226922654</v>
+        <v>1.809338567398941</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.552087273893106</v>
+        <v>1.549500470607576</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.841095890410959</v>
+        <v>1.838356164383562</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005518504235577456</v>
+        <v>0.005526881579922185</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13420</v>
+        <v>13160</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006079811137193356</v>
+        <v>-0.006095004387688762</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3329359165424739</v>
+        <v>0.3592705167173251</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.270593337103426</v>
+        <v>4.267861301926546</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.296716562312335</v>
+        <v>4.294033454673664</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.43013698630137</v>
+        <v>4.427397260273972</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002341594998783612</v>
+        <v>0.002343093950941171</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110.4</v>
+        <v>111.9</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1286</v>
+        <v>1375</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01842200323823806</v>
+        <v>0.01350744272392133</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3442856858475896</v>
+        <v>0.2743562632727274</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.802316017098516</v>
+        <v>2.800646695311477</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.751625562083397</v>
+        <v>2.763321291242231</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.92054794520548</v>
+        <v>2.917808219178082</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003568476909450733</v>
+        <v>0.003570603895429173</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>191.4</v>
+        <v>185</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>233.5</v>
+        <v>232.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.94808696389495</v>
+        <v>-3.884971749306288</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.1065952890792292</v>
+        <v>0.07558139534883734</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.09315068493150686</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>233.5</v>
+        <v>232.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1313888544306458</v>
+        <v>-0.1314777930326607</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001284796573875813</v>
+        <v>0.004306632213608941</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.398095302635406</v>
+        <v>4.395434133802624</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.063365034019403</v>
+        <v>5.060819514506569</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.671232876712328</v>
+        <v>4.668493150684932</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002273711530081635</v>
+        <v>0.002275088124537245</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>293</v>
+        <v>277.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2593921612848881</v>
+        <v>-0.2595825600435939</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1949130546075084</v>
+        <v>0.2621107606344628</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.33896152575251</v>
+        <v>3.33627983776173</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.508406947927136</v>
+        <v>4.505944427724665</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.424657534246575</v>
+        <v>3.421917808219178</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002994943165074739</v>
+        <v>0.002997350488054048</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156.6</v>
+        <v>157</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1335764440985509</v>
+        <v>-0.1348279347268158</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.09000000000000008</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.059916744961388</v>
+        <v>2.057479204536937</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.377493929996165</v>
+        <v>2.378115622453984</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.186301369863014</v>
+        <v>2.183561643835616</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004854565129615199</v>
+        <v>0.00486031643865418</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.4</v>
+        <v>108.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17060</v>
+        <v>17560</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01709344386114768</v>
+        <v>-0.01903202129295755</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1921356717467761</v>
+        <v>0.1624648018223234</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.9217934140005</v>
+        <v>1.919098784392295</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.955214767871599</v>
+        <v>1.9563317315635</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.920547945205479</v>
+        <v>1.917808219178082</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005203472926459618</v>
+        <v>0.005210779185171864</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>85.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04829776821552739</v>
+        <v>0.04829663266342592</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8134458672875435</v>
+        <v>0.7522497187851518</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.17349702114024</v>
+        <v>3.170757917589314</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.027285869874881</v>
+        <v>3.024676240286409</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.424657534246575</v>
+        <v>3.421917808219178</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003151097963346124</v>
+        <v>0.003153820083370752</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1110753775610274</v>
+        <v>0.1098540824272492</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.177598152424943</v>
+        <v>1.182448036951501</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.89495575805277</v>
+        <v>1.892268493945259</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.705515031943625</v>
+        <v>1.704970521716576</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.920547945205479</v>
+        <v>1.917808219178082</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005277168059203587</v>
+        <v>0.005284662315098129</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>104.7</v>
+        <v>104.8</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>142.1</v>
+        <v>141.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03341178571165074</v>
+        <v>0.03311273285567182</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5472906403940887</v>
+        <v>0.5531404375441076</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.354396307469355</v>
+        <v>3.351812091882091</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.245943537560274</v>
+        <v>3.244381745849944</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.586301369863014</v>
+        <v>3.583561643835616</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002981162356318077</v>
+        <v>0.002983460804446485</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>295.7</v>
+        <v>301</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23580</v>
+        <v>23950</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4776255371490468</v>
+        <v>-0.4839774432219267</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006836930703986388</v>
+        <v>0.009049777870563602</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.596930404766039</v>
+        <v>1.594358896479873</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.057060630511113</v>
+        <v>3.089707757030401</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.583561643835616</v>
+        <v>1.580821917808219</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006262013654543114</v>
+        <v>0.006272113526056545</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>515.5</v>
+        <v>475</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03811463007722156</v>
+        <v>0.03811698632998083</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3010319068865177</v>
+        <v>0.4119619957894736</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9479452054794522</v>
+        <v>0.9452054794520549</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9131411676655958</v>
+        <v>0.9104999647425164</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9205479452054794</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01054913294797688</v>
+        <v>0.01057971014492753</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>210.2</v>
+        <v>206.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08004999601416139</v>
+        <v>0.08006395364186973</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07231208372978104</v>
+        <v>0.09364386220281418</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.005326661020378</v>
+        <v>2.002583189271831</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.856697994001089</v>
+        <v>1.854133898756011</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.186301369863014</v>
+        <v>2.183561643835616</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004986718719887592</v>
+        <v>0.004993550357144538</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8661</v>
+        <v>8884</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02906517862899141</v>
+        <v>0.02882524414468551</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8286732239926107</v>
+        <v>0.7847541985592077</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.486623088029574</v>
+        <v>4.48392019057232</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.359901764441234</v>
+        <v>4.358291377560462</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.512328767123288</v>
+        <v>4.50958904109589</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002228847800181892</v>
+        <v>0.002230191344847201</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09893677336949547</v>
+        <v>0.09896927712501333</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4981393714285713</v>
+        <v>0.5730463399999999</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.120780809789781</v>
+        <v>3.118021104703719</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.839818345709759</v>
+        <v>2.837223177758616</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.424657534246575</v>
+        <v>3.421917808219178</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003204326291878734</v>
+        <v>0.003207162384152695</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1241091163835318</v>
+        <v>0.1241648993195265</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6052104208416833</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.130359915583265</v>
+        <v>3.127587305915268</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.784747379021544</v>
+        <v>2.782142822470655</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.424657534246575</v>
+        <v>3.421917808219178</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003194520844142853</v>
+        <v>0.003197352790467848</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>47.17059955066739</v>
+        <v>47.43008645065078</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4493150684931507</v>
+        <v>0.4465753424657534</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009327578910877923</v>
+        <v>0.009221031288490555</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02225609756097561</v>
+        <v>0.02239263803680982</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1281</v>
+        <v>1259</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05896687604385648</v>
+        <v>0.05915809195265578</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4322662170179545</v>
+        <v>0.4572939030976966</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.441095890410959</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4191213403165738</v>
+        <v>0.4164589722368622</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02253086419753086</v>
+        <v>0.02267080745341615</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13000</v>
+        <v>12870</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.765368597610327</v>
+        <v>-1.776211572445254</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01713681538461542</v>
+        <v>0.02741092463092465</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>187.7</v>
+        <v>195</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21120</v>
+        <v>21590</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1591939989876037</v>
+        <v>-0.1705338212848573</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02292945075757569</v>
+        <v>0.03957850856878187</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.847947893531116</v>
+        <v>2.847259597825734</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.387164090291891</v>
+        <v>3.432640981499919</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.92054794520548</v>
+        <v>2.917808219178082</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00351130019713991</v>
+        <v>0.003512149017826244</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>658.6</v>
+        <v>673</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05309699863086673</v>
+        <v>0.05309407258139613</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4882011311873671</v>
+        <v>0.4563584918276375</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.794687402894681</v>
+        <v>2.791948326173895</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.653779667521661</v>
+        <v>2.651186061023146</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.92054794520548</v>
+        <v>2.917808219178082</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003578217724687993</v>
+        <v>0.003581728181088533</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1237474910409608</v>
+        <v>0.1238092628096283</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.327271834396019</v>
+        <v>2.324516381589473</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.070991795710439</v>
+        <v>2.068426074170242</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.493150684931507</v>
+        <v>2.49041095890411</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004296876648530931</v>
+        <v>0.004301970112665816</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68890</v>
+        <v>68530</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2517180493738928</v>
+        <v>-0.2520756432110951</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1272753665263464</v>
+        <v>0.1331971399387131</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.791203128435598</v>
+        <v>1.788476397441442</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.393754288656638</v>
+        <v>2.391253047460552</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.794520547945206</v>
+        <v>1.791780821917808</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005582839735621612</v>
+        <v>0.005591351395134874</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109</v>
+        <v>107.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.01132735896672346</v>
+        <v>-0.01138248981655898</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.02018348623853217</v>
+        <v>-0.01019462465245602</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.8087535667162</v>
+        <v>2.806025676588006</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.840933844169825</v>
+        <v>2.838332972746294</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.92054794520548</v>
+        <v>2.917808219178082</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003560298104646933</v>
+        <v>0.003563759264013409</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03315947431356317</v>
+        <v>0.03314207354440409</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.194928478543563</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.823158363188717</v>
+        <v>1.820419324002471</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.764643705561558</v>
+        <v>1.762022252909662</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.841095890410959</v>
+        <v>1.838356164383562</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005484987043314179</v>
+        <v>0.005493239864106402</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>960</v>
+        <v>984.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05331863862336027</v>
+        <v>0.05332639221543468</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7141666666666666</v>
+        <v>0.6708295258401868</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.200875332415373</v>
+        <v>3.198131779077859</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.038848089310156</v>
+        <v>3.036221063778065</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.421917808219178</v>
+        <v>3.419178082191781</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003124145416951938</v>
+        <v>0.003126825500256082</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8808</v>
+        <v>8769</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006559046239437926</v>
+        <v>-0.006631173199019489</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2280247792915531</v>
+        <v>0.2334864016421485</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.898531512455459</v>
+        <v>1.895794836062923</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.911066284582668</v>
+        <v>1.908450099212487</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.917808219178082</v>
+        <v>1.915068493150685</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005267228873681709</v>
+        <v>0.005274832386803745</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>108.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02633427360948439</v>
+        <v>0.02736182278460393</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2959660297239917</v>
+        <v>0.2982905982905986</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.542064063296587</v>
+        <v>4.538271040793269</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.42552117773748</v>
+        <v>4.417402846927436</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.917808219178082</v>
+        <v>4.915068493150685</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002201642218305062</v>
+        <v>0.002203482319613076</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5665</v>
+        <v>5690</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.02995481615221923</v>
+        <v>0.03006455778533456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.889320388349514</v>
+        <v>1.876625659050966</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4335873141834536</v>
+        <v>0.4308813589243516</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4191780821917808</v>
+        <v>0.4164383561643836</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02239263803680982</v>
+        <v>0.02253086419753086</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>350.9</v>
+        <v>353.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26830</v>
+        <v>27710</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1412571860357881</v>
+        <v>-0.1423286694251675</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04629146477823332</v>
+        <v>0.02114760014435224</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.662833855944014</v>
+        <v>6.66238046274109</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.758823419070483</v>
+        <v>7.767987835475155</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.093150684931507</v>
+        <v>7.090410958904109</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001500862878500092</v>
+        <v>0.001500965016321767</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26830</v>
+        <v>27710</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1168718382627992</v>
+        <v>-0.1073252551326731</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1807677972418935</v>
+        <v>0.117286178274991</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.097105081782557</v>
+        <v>2.094049406966048</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.374632779977646</v>
+        <v>2.345814552283849</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.09041095890411</v>
+        <v>2.087671232876712</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004768478264093431</v>
+        <v>0.004775436513930417</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2419</v>
+        <v>2429</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03777781544305313</v>
+        <v>0.03892143594835367</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.36260174038859</v>
+        <v>2.345287960477563</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.0275556920233</v>
+        <v>1.024813128786808</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9901499884969219</v>
+        <v>0.9864202367249578</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1.002739726027397</v>
+        <v>1</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009731832617567993</v>
+        <v>0.009757876552419052</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230</v>
+        <v>235.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1676915249270491</v>
+        <v>0.1678685929697027</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.385221739130435</v>
+        <v>2.303355960967331</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.809338567398941</v>
+        <v>1.806591885290052</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.549500470607576</v>
+        <v>1.546913664915141</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.838356164383562</v>
+        <v>1.835616438356164</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005526881579922185</v>
+        <v>0.005535284466527139</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13160</v>
+        <v>13320</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006095004387688762</v>
+        <v>-0.006110216348175175</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3592705167173251</v>
+        <v>0.3429429429429429</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.267861301926546</v>
+        <v>4.265129275985963</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.294033454673664</v>
+        <v>4.291350355081328</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.427397260273972</v>
+        <v>4.424657534246576</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002343093950941171</v>
+        <v>0.002344594818333687</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>111.9</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01350744272392133</v>
+        <v>0.01314952265898505</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2743562632727274</v>
+        <v>0.2782840816326531</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.800646695311477</v>
+        <v>2.797984818938207</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.763321291242231</v>
+        <v>2.761670174403248</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.917808219178082</v>
+        <v>2.915068493150685</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003570603895429173</v>
+        <v>0.003574000806693029</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>232.2</v>
+        <v>244</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.884971749306288</v>
+        <v>-3.980048283369922</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.07558139534883734</v>
+        <v>0.02356557377049184</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.09315068493150686</v>
+        <v>0.09041095890410959</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>233.2</v>
+        <v>242.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>232.2</v>
+        <v>244</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1314777930326607</v>
+        <v>-0.1392036528825496</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.004306632213608941</v>
+        <v>-0.006147540983606592</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.395434133802624</v>
+        <v>4.399467122055352</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.060819514506569</v>
+        <v>5.110926802591405</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.668493150684932</v>
+        <v>4.665753424657535</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002275088124537245</v>
+        <v>0.002273002552938316</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>277.4</v>
+        <v>286.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2595825600435939</v>
+        <v>-0.2597732191060214</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2621107606344628</v>
+        <v>0.2220227748691097</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.33627983776173</v>
+        <v>3.333598210620204</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.505944427724665</v>
+        <v>4.503482306590134</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.421917808219178</v>
+        <v>3.419178082191781</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002997350488054048</v>
+        <v>0.002999761629383505</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>157</v>
+        <v>155.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.5</v>
+        <v>77.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1348279347268158</v>
+        <v>-0.1300824204641511</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.09000000000000008</v>
+        <v>0.08789575289575291</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.057479204536937</v>
+        <v>2.053592448080269</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.378115622453984</v>
+        <v>2.360674731019896</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.183561643835616</v>
+        <v>2.180821917808219</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00486031643865418</v>
+        <v>0.004869515375043455</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.8</v>
+        <v>109.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17560</v>
+        <v>17730</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01903202129295755</v>
+        <v>-0.02236375776112497</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1624648018223234</v>
+        <v>0.1587261590524536</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.919098784392295</v>
+        <v>1.916436573065023</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.9563317315635</v>
+        <v>1.96027570405554</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.917808219178082</v>
+        <v>1.915068493150685</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005210779185171864</v>
+        <v>0.005218017721299617</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.5</v>
+        <v>100.8</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>88.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04829663266342592</v>
+        <v>0.04733624891159319</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7522497187851518</v>
+        <v>0.8041570438799079</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.170757917589314</v>
+        <v>3.168544387901565</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.024676240286409</v>
+        <v>3.025336315051027</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.421917808219178</v>
+        <v>3.419178082191781</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003153820083370752</v>
+        <v>0.00315602332673102</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1098540824272492</v>
+        <v>0.1112359366635334</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.182448036951501</v>
+        <v>1.177598152424943</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.892268493945259</v>
+        <v>1.889469409456652</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.704970521716576</v>
+        <v>1.700331448179899</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.917808219178082</v>
+        <v>1.915068493150685</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005284662315098129</v>
+        <v>0.005292491082391042</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>141.7</v>
+        <v>141.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03311273285567182</v>
+        <v>0.03310262956310446</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5531404375441076</v>
+        <v>0.5597448618001419</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.351812091882091</v>
+        <v>3.349077618802474</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.244381745849944</v>
+        <v>3.24176661927459</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.583561643835616</v>
+        <v>3.580821917808219</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002983460804446485</v>
+        <v>0.002985896756724226</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>301</v>
+        <v>300.9</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23950</v>
+        <v>24040</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4839774432219267</v>
+        <v>-0.4844657794994149</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.009049777870563602</v>
+        <v>0.004938159816971766</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.594358896479873</v>
+        <v>1.591632105454579</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.089707757030401</v>
+        <v>3.087345208450179</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.580821917808219</v>
+        <v>1.578082191780822</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006272113526056545</v>
+        <v>0.006282858938148866</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>475</v>
+        <v>455.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03811698632998083</v>
+        <v>0.0381193776703258</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4119619957894736</v>
+        <v>0.473378620386643</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9452054794520549</v>
+        <v>0.9424657534246577</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9104999647425164</v>
+        <v>0.9078587431241991</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9178082191780822</v>
+        <v>0.9150684931506849</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01057971014492753</v>
+        <v>0.01061046511627907</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>206.1</v>
+        <v>213</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08006395364186973</v>
+        <v>0.08007796822075873</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09364386220281418</v>
+        <v>0.05821596244131455</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>2.002583189271831</v>
+        <v>1.999839702218249</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.854133898756011</v>
+        <v>1.851569757980193</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.183561643835616</v>
+        <v>2.180821917808219</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.004993550357144538</v>
+        <v>0.005000400776576176</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8884</v>
+        <v>8819</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02882524414468551</v>
+        <v>0.02883963366209023</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7847541985592077</v>
+        <v>0.7979086404354236</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.48392019057232</v>
+        <v>4.481178256381571</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.358291377560462</v>
+        <v>4.355565347372066</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.50958904109589</v>
+        <v>4.506849315068493</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002230191344847201</v>
+        <v>0.002231555949768159</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09896927712501333</v>
+        <v>0.09900184897312733</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5730463399999999</v>
+        <v>0.5305315740540539</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.118021104703719</v>
+        <v>3.115261357179238</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.837223177758616</v>
+        <v>2.834627949070367</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.421917808219178</v>
+        <v>3.419178082191781</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003207162384152695</v>
+        <v>0.003210003544952857</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1241648993195265</v>
+        <v>0.1242207932665013</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5705882352941176</v>
+        <v>0.5767716535433072</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.127587305915268</v>
+        <v>3.12481462915331</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.782142822470655</v>
+        <v>2.77953819024637</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.421917808219178</v>
+        <v>3.419178082191781</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003197352790467848</v>
+        <v>0.003200189831007534</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>47.43008645065078</v>
+        <v>47.69281307765974</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4465753424657534</v>
+        <v>0.4438356164383562</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009221031288490555</v>
+        <v>0.009115012840405969</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4191780821917808</v>
+        <v>0.4164383561643836</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02239263803680982</v>
+        <v>0.02253086419753086</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1259</v>
+        <v>1215</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05915809195265578</v>
+        <v>0.05935172456244742</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4572939030976966</v>
+        <v>0.5100683325102879</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.441095890410959</v>
+        <v>0.4383561643835617</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4164589722368622</v>
+        <v>0.4137966212917806</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4191780821917808</v>
+        <v>0.4164383561643836</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02267080745341615</v>
+        <v>0.0228125</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12870</v>
+        <v>13050</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.776211572445254</v>
+        <v>-1.787188410488831</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02741092463092465</v>
+        <v>0.01323973946360146</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4191780821917808</v>
+        <v>0.4164383561643836</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21590</v>
+        <v>21800</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1705338212848573</v>
+        <v>-0.17070363255922</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03957850856878187</v>
+        <v>0.02956422018348626</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.847259597825734</v>
+        <v>2.844550468333388</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.432640981499919</v>
+        <v>3.430077087051171</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.917808219178082</v>
+        <v>2.915068493150685</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003512149017826244</v>
+        <v>0.003515493963395547</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05309407258139613</v>
+        <v>0.05309114922955354</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4563584918276375</v>
+        <v>0.4963805572519084</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.791948326173895</v>
+        <v>2.789209248853563</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.651186061023146</v>
+        <v>2.648592432757754</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.917808219178082</v>
+        <v>2.915068493150685</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003581728181088533</v>
+        <v>0.003585245532980453</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1238092628096283</v>
+        <v>0.1238712020045464</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.324516381589473</v>
+        <v>2.321760885763945</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.068426074170242</v>
+        <v>2.065860288637018</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.49041095890411</v>
+        <v>2.487671232876712</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004301970112665816</v>
+        <v>0.004307075746393941</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68530</v>
+        <v>67790</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2520756432110951</v>
+        <v>-0.2524341584954856</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1331971399387131</v>
+        <v>0.145567192801298</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.788476397441442</v>
+        <v>1.785749700281675</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.391253047460552</v>
+        <v>2.388752402982676</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.791780821917808</v>
+        <v>1.789041095890411</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005591351395134874</v>
+        <v>0.005599888942119185</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>120</v>
+        <v>120.3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>107.9</v>
+        <v>109</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.01138248981655898</v>
+        <v>-0.01231549360896565</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01019462465245602</v>
+        <v>-0.0177339449541285</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.806025676588006</v>
+        <v>2.803486201453092</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.838332972746294</v>
+        <v>2.838443028429124</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.917808219178082</v>
+        <v>2.915068493150685</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003563759264013409</v>
+        <v>0.003566987415460379</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1538</v>
+        <v>1520</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03314207354440409</v>
+        <v>0.0336783275943666</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.194928478543563</v>
+        <v>0.2078947368421054</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.820419324002471</v>
+        <v>1.817658431469917</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.762022252909662</v>
+        <v>1.758437207153286</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.838356164383562</v>
+        <v>1.835616438356164</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005493239864106402</v>
+        <v>0.005501583700691845</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27710</v>
+        <v>27700</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1423286694251675</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02114760014435224</v>
+        <v>0.02151624548736453</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.66238046274109</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27710</v>
+        <v>27700</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1073252551326731</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.117286178274991</v>
+        <v>0.1176895306859205</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.094049406966048</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13320</v>
+        <v>13380</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.006110216348175175</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3429429429429429</v>
+        <v>0.3369207772795217</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.265129275985963</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.01314952265898505</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2782840816326531</v>
+        <v>0.2764234061135371</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.797984818938207</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>244</v>
+        <v>244.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-3.980048283369922</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.02356557377049184</v>
+        <v>0.02147239263803691</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>242.5</v>
+        <v>241.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>244</v>
+        <v>244.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1392036528825496</v>
+        <v>-0.1387221442438581</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.006147540983606592</v>
+        <v>-0.01063394683026586</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.399467122055352</v>
+        <v>4.399047981382763</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.110926802591405</v>
+        <v>5.107582822410667</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.665753424657535</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002273002552938316</v>
+        <v>0.00227321912430168</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>286.5</v>
+        <v>286</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.2597732191060214</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2220227748691097</v>
+        <v>0.2241591783216781</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.333598210620204</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17730</v>
+        <v>17710</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02236375776112497</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1587261590524536</v>
+        <v>0.1600347148503671</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.916436573065023</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24040</v>
+        <v>24030</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4844657794994149</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004938159816971766</v>
+        <v>0.00535636129837691</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.591632105454579</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>455.2</v>
+        <v>468.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.0381193776703258</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.473378620386643</v>
+        <v>0.4324689192652711</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.9424657534246577</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>213</v>
+        <v>211.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.08007796822075873</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.05821596244131455</v>
+        <v>0.0662251655629138</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.999839702218249</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8819</v>
+        <v>8760</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02883963366209023</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7979086404354236</v>
+        <v>0.8100178424657536</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.481178256381571</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21800</v>
+        <v>21730</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.17070363255922</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02956422018348626</v>
+        <v>0.03288080994017495</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.844550468333388</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67790</v>
+        <v>67730</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2524341584954856</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.145567192801298</v>
+        <v>0.146582016831537</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.785749700281675</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5690</v>
+        <v>5735</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03006455778533456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.876625659050966</v>
+        <v>1.854054054054054</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.4438356164383562</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27700</v>
+        <v>27770</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1423286694251675</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02151624548736453</v>
+        <v>0.01894130356499812</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.66238046274109</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27700</v>
+        <v>27770</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1073252551326731</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1176895306859205</v>
+        <v>0.1148721642059776</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.094049406966048</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13380</v>
+        <v>13400</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.006110216348175175</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3369207772795217</v>
+        <v>0.3349253731343285</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.265129275985963</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.01314952265898505</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2764234061135371</v>
+        <v>0.2801501897810219</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.797984818938207</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>244.5</v>
+        <v>244.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-3.980048283369922</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.02147239263803691</v>
+        <v>0.02189034369885445</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>244.5</v>
+        <v>244.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1387221442438581</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.01063394683026586</v>
+        <v>-0.01022913256955815</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.399047981382763</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17710</v>
+        <v>17730</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02236375776112497</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1600347148503671</v>
+        <v>0.1587261590524536</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.916436573065023</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24030</v>
+        <v>24090</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4844657794994149</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.00535636129837691</v>
+        <v>0.00285236039850556</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.591632105454579</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>468.2</v>
+        <v>469</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.0381193776703258</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4324689192652711</v>
+        <v>0.4300254754797439</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.9424657534246577</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>211.4</v>
+        <v>211.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.08007796822075873</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0662251655629138</v>
+        <v>0.06572104018912528</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.999839702218249</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05935172456244742</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5100683325102879</v>
+        <v>0.4977412440816325</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.4383561643835617</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13050</v>
+        <v>13070</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-1.787188410488831</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01323973946360146</v>
+        <v>0.01168925784238706</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>984.9</v>
+        <v>979.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.05332639221543468</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6708295258401868</v>
+        <v>0.6793550362281866</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.198131779077859</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8769</v>
+        <v>8705</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.006631173199019489</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2334864016421485</v>
+        <v>0.2425551126938541</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.895794836062923</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.5</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02736182278460393</v>
+        <v>0.02840542901297618</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2982905982905986</v>
+        <v>0.299248120300752</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.538271040793269</v>
+        <v>4.53719955987455</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.417402846927436</v>
+        <v>4.411878265004084</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.915068493150685</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002203482319613076</v>
+        <v>0.002204002682279307</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5735</v>
+        <v>5715</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03006455778533456</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.854054054054054</v>
+        <v>1.864041994750656</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.4438356164383562</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353.7</v>
+        <v>359.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27770</v>
+        <v>28220</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1423286694251675</v>
+        <v>-0.1445400067311277</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01894130356499812</v>
+        <v>0.02026931254429476</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.66238046274109</v>
+        <v>6.667068066824337</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.767987835475155</v>
+        <v>7.793547470698455</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.090410958904109</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001500965016321767</v>
+        <v>0.001499909690402067</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27770</v>
+        <v>28220</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1073252551326731</v>
+        <v>-0.1170219373888278</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1148721642059776</v>
+        <v>0.1226080793763289</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.094049406966048</v>
+        <v>2.094370303129246</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.345814552283849</v>
+        <v>2.371939226820318</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.087671232876712</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004775436513930417</v>
+        <v>0.004774704828968771</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2429</v>
+        <v>2421</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03892143594835367</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.345287960477563</v>
+        <v>2.356342195786865</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>1.024813128786808</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>235.7</v>
+        <v>233.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1678685929697027</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.303355960967331</v>
+        <v>2.335908311910882</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.806591885290052</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13400</v>
+        <v>13150</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.006110216348175175</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3349253731343285</v>
+        <v>0.3603041825095057</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.265129275985963</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.01314952265898505</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2801501897810219</v>
+        <v>0.2829595903438185</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.797984818938207</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>244.4</v>
+        <v>236.1</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-3.980048283369922</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.02189034369885445</v>
+        <v>0.05781448538754774</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>241.9</v>
+        <v>237.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>244.4</v>
+        <v>236.1</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1387221442438581</v>
+        <v>-0.1348152063657307</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.01022913256955815</v>
+        <v>0.004235493434985083</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.399047981382763</v>
+        <v>4.395632531408958</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.107582822410667</v>
+        <v>5.08057072171229</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.665753424657535</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00227321912430168</v>
+        <v>0.002274985438055861</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.2597732191060214</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2241591783216781</v>
+        <v>0.2327800176056336</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.333598210620204</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1300824204641511</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.08789575289575291</v>
+        <v>0.09636186770428012</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.053592448080269</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.5</v>
+        <v>111.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17730</v>
+        <v>17860</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02236375776112497</v>
+        <v>-0.03199299306660903</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1587261590524536</v>
+        <v>0.1723523762597985</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.916436573065023</v>
+        <v>1.916660671761634</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.96027570405554</v>
+        <v>1.980007022711066</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.915068493150685</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005218017721299617</v>
+        <v>0.005217407623232984</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04733624891159319</v>
+        <v>0.04701734537525778</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8041570438799079</v>
+        <v>0.8059468822170903</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.168544387901565</v>
+        <v>3.168719001844488</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.025336315051027</v>
+        <v>3.026424553366687</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.419178082191781</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00315602332673102</v>
+        <v>0.003155849412390014</v>
       </c>
     </row>
     <row r="18">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>104.8</v>
+        <v>105</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>141.1</v>
+        <v>140.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03310262956310446</v>
+        <v>0.0325250097677606</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5597448618001419</v>
+        <v>0.5738758029978588</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.349077618802474</v>
+        <v>3.349377843458224</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.24176661927459</v>
+        <v>3.243870910411728</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.580821917808219</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002985896756724226</v>
+        <v>0.002985629113039999</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>300.9</v>
+        <v>303.4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24090</v>
+        <v>24540</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4844657794994149</v>
+        <v>-0.4871290541025583</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.00285236039850556</v>
+        <v>-0.007358035370823357</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.591632105454579</v>
+        <v>1.591702655976087</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.087345208450179</v>
+        <v>3.103514965525807</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.578082191780822</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006282858938148866</v>
+        <v>0.006282580457131711</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>469</v>
+        <v>482.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.0381193776703258</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4300254754797439</v>
+        <v>0.390590810698735</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.9424657534246577</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>96.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>211.5</v>
+        <v>209.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08007796822075873</v>
+        <v>0.08692011353628244</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06572104018912528</v>
+        <v>0.06263736263736264</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.999839702218249</v>
+        <v>1.998000954864156</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.851569757980193</v>
+        <v>1.838222450740821</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.180821917808219</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005000400776576176</v>
+        <v>0.005005002613064266</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8760</v>
+        <v>8695</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02883963366209023</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8100178424657536</v>
+        <v>0.8235487406555493</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.481178256381571</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.09900184897312733</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5305315740540539</v>
+        <v>0.5430427313351496</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>3.115261357179238</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1242207932665013</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5767716535433072</v>
+        <v>0.5798816568047336</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.12481462915331</v>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3704,7 +3704,7 @@
         <v>47.69281307765974</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.1761052631578948</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.4438356164383562</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05935172456244742</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4977412440816325</v>
+        <v>0.4916528650406504</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.4383561643835617</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13070</v>
+        <v>13220</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,10 +3940,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.787188410488831</v>
+        <v>-1.789924797541393</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01168925784238706</v>
+        <v>0.006152024205748896</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21730</v>
+        <v>21850</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.17070363255922</v>
+        <v>-0.1646469908811922</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03288080994017495</v>
+        <v>0.00613729977116706</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.844550468333388</v>
+        <v>2.843456934843436</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.430077087051171</v>
+        <v>3.403898595927636</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.915068493150685</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003515493963395547</v>
+        <v>0.003516845948134823</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05309114922955354</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4963805572519084</v>
+        <v>0.5055749078341014</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.789209248853563</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67730</v>
+        <v>68150</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2524341584954856</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.146582016831537</v>
+        <v>0.1395157740278796</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.785749700281675</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>120.3</v>
+        <v>122.1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109</v>
+        <v>109.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.01231549360896565</v>
+        <v>-0.01751943173998283</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.0177339449541285</v>
+        <v>-0.003950504124656251</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.803486201453092</v>
+        <v>2.804601275298138</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.838443028429124</v>
+        <v>2.854612463496469</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.915068493150685</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003566987415460379</v>
+        <v>0.00356556922656928</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0336783275943666</v>
+        <v>0.0309182279859741</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2078947368421054</v>
+        <v>0.2138157894736843</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.817658431469917</v>
+        <v>1.817767385461893</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.758437207153286</v>
+        <v>1.763250795374067</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.835616438356164</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005501583700691845</v>
+        <v>0.005501253944799439</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>979.9</v>
+        <v>952.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05332639221543468</v>
+        <v>0.05333416381979067</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6793550362281866</v>
+        <v>0.7276640419947507</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.198131779077859</v>
+        <v>3.195388216817318</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.036221063778065</v>
+        <v>3.033594016574592</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.419178082191781</v>
+        <v>3.416438356164384</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003126825500256082</v>
+        <v>0.003129510194526609</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.8</v>
+        <v>111.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8705</v>
+        <v>8792</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006631173199019489</v>
+        <v>-0.01139359167942828</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2425551126938541</v>
+        <v>0.241363009099181</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.895794836062923</v>
+        <v>1.893256515215862</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.908450099212487</v>
+        <v>1.915076110453395</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.915068493150685</v>
+        <v>1.912328767123288</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005274832386803745</v>
+        <v>0.00528190444328662</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>107.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02840542901297618</v>
+        <v>0.02902584701012</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.299248120300752</v>
+        <v>0.295639097744361</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.53719955987455</v>
+        <v>4.533822020742788</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.411878265004084</v>
+        <v>4.405935996569967</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.915068493150685</v>
+        <v>4.912328767123288</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002204002682279307</v>
+        <v>0.002205644587336861</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03006455778533456</v>
+        <v>0.03017566764802009</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.864041994750656</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.4410958904109589</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4308813589243516</v>
+        <v>0.4281754114985252</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4164383561643836</v>
+        <v>0.4136986301369863</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02253086419753086</v>
+        <v>0.02267080745341615</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>359.9</v>
+        <v>358.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28220</v>
+        <v>28240</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1445400067311277</v>
+        <v>-0.14417417490609</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02026931254429476</v>
+        <v>0.01614730878186976</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.667068066824337</v>
+        <v>6.663555720100004</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.793547470698455</v>
+        <v>7.78611199231901</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.090410958904109</v>
+        <v>7.087671232876712</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001499909690402067</v>
+        <v>0.001500700289762104</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>132</v>
+        <v>132.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28220</v>
+        <v>28240</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1170219373888278</v>
+        <v>-0.1174903701853691</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1226080793763289</v>
+        <v>0.1226628895184136</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.094370303129246</v>
+        <v>2.091646012951829</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.371939226820318</v>
+        <v>2.370111262571916</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.087671232876712</v>
+        <v>2.084931506849315</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004774704828968771</v>
+        <v>0.004780923702231779</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2421</v>
+        <v>2412</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03892143594835367</v>
+        <v>0.03902057231218862</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.356342195786865</v>
+        <v>2.368865860696518</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.024813128786808</v>
+        <v>1.022073156812681</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9864202367249578</v>
+        <v>0.9836890472131904</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>1</v>
+        <v>0.9972602739726028</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009757876552419052</v>
+        <v>0.009784035451224299</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>233.4</v>
+        <v>234</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1678685929697027</v>
+        <v>0.1680462412634795</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.335908311910882</v>
+        <v>2.327354700854701</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.806591885290052</v>
+        <v>1.803845180488291</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.546913664915141</v>
+        <v>1.544326856903427</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.835616438356164</v>
+        <v>1.832876712328767</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005535284466527139</v>
+        <v>0.00554371301271712</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.8</v>
+        <v>111.2</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13150</v>
+        <v>12990</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006110216348175175</v>
+        <v>-0.004882288844183284</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3603041825095057</v>
+        <v>0.3696689761354888</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.265129275985963</v>
+        <v>4.261767233811869</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.291350355081328</v>
+        <v>4.282676497498854</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.424657534246576</v>
+        <v>4.421917808219178</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002344594818333687</v>
+        <v>0.002346444432878062</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>112.8</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01314952265898505</v>
+        <v>0.01054531535054952</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2829595903438185</v>
+        <v>0.2940168087912087</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.797984818938207</v>
+        <v>2.795811087292188</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.761670174403248</v>
+        <v>2.766636037813252</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.915068493150685</v>
+        <v>2.912328767123288</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003574000806693029</v>
+        <v>0.003576779577652097</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>236.1</v>
+        <v>235.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-3.980048283369922</v>
+        <v>-4.079878601195869</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.05781448538754774</v>
+        <v>0.06050955414012749</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.09041095890410959</v>
+        <v>0.08767123287671233</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>237.1</v>
+        <v>241</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>236.1</v>
+        <v>235.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1348152063657307</v>
+        <v>-0.1380890108879931</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.004235493434985083</v>
+        <v>0.02335456475583864</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.395632531408958</v>
+        <v>4.395756530137018</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.08057072171229</v>
+        <v>5.100012165601687</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.665753424657535</v>
+        <v>4.663013698630137</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002274985438055861</v>
+        <v>0.002274921263596074</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2597732191060214</v>
+        <v>-0.2599641389945073</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2327800176056336</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.333598210620204</v>
+        <v>3.330916644412502</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.503482306590134</v>
+        <v>4.501020585525083</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.419178082191781</v>
+        <v>3.416438356164384</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.002999761629383505</v>
+        <v>0.003002176598076886</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>155.1</v>
+        <v>156</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1300824204641511</v>
+        <v>-0.1326588710238067</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.09636186770428012</v>
+        <v>0.1027237354085606</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.053592448080269</v>
+        <v>2.051475867897956</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.360674731019896</v>
+        <v>2.365246843902712</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.180821917808219</v>
+        <v>2.178082191780822</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004869515375043455</v>
+        <v>0.004874539426216355</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.6</v>
+        <v>112.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17860</v>
+        <v>17780</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03199299306660903</v>
+        <v>-0.03432396498616207</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1723523762597985</v>
+        <v>0.1829034105736782</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.916660671761634</v>
+        <v>1.913975209300045</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.980007022711066</v>
+        <v>1.982005496566577</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.915068493150685</v>
+        <v>1.912328767123288</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005217407623232984</v>
+        <v>0.005224728069313433</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>86.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04701734537525778</v>
+        <v>0.04701528298460112</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8059468822170903</v>
+        <v>0.8206635622817229</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.168719001844488</v>
+        <v>3.165980404883164</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.026424553366687</v>
+        <v>3.023814892040814</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.419178082191781</v>
+        <v>3.416438356164384</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003155849412390014</v>
+        <v>0.003158579245966318</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.8</v>
+        <v>88.7</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>173.2</v>
+        <v>164.1</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1112359366635334</v>
+        <v>0.1185749577085743</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.177598152424943</v>
+        <v>1.270201096892139</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.889469409456652</v>
+        <v>1.886414555231275</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.700331448179899</v>
+        <v>1.686444473149691</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.915068493150685</v>
+        <v>1.912328767123288</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005292491082391042</v>
+        <v>0.005301061727004115</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0325250097677606</v>
+        <v>0.03251449889886637</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5738758029978588</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.349377843458224</v>
+        <v>3.346643578867338</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.243870910411728</v>
+        <v>3.241255771649109</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.580821917808219</v>
+        <v>3.578082191780822</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002985629113039999</v>
+        <v>0.002988068422686491</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>303.4</v>
+        <v>301.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24540</v>
+        <v>24280</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4871290541025583</v>
+        <v>-0.4858123715998673</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.007358035370823357</v>
+        <v>-0.002680597693574871</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.591702655976087</v>
+        <v>1.588928049581064</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.103514965525807</v>
+        <v>3.09017168406974</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.578082191780822</v>
+        <v>1.575342465753425</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006282580457131711</v>
+        <v>0.006293551179134007</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>482.3</v>
+        <v>497.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.0381193776703258</v>
+        <v>0.03922498193336275</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.390590810698735</v>
+        <v>0.3456716649929705</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9424657534246577</v>
+        <v>0.9397260273972602</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9078587431241991</v>
+        <v>0.9042565794069001</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9150684931506849</v>
+        <v>0.9123287671232877</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01061046511627907</v>
+        <v>0.01064139941690962</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>209.3</v>
+        <v>208.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08692011353628244</v>
+        <v>0.08113712285158631</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06263736263736264</v>
+        <v>0.08040345821325645</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.998000954864156</v>
+        <v>1.996815673847468</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.838222450740821</v>
+        <v>1.846958754483156</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.180821917808219</v>
+        <v>2.178082191780822</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005005002613064266</v>
+        <v>0.005007973510510353</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8695</v>
+        <v>8708</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02883963366209023</v>
+        <v>0.02885404104701386</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8235487406555493</v>
+        <v>0.820826401010565</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.481178256381571</v>
+        <v>4.478436319379245</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.355565347372066</v>
+        <v>4.352839315110005</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.506849315068493</v>
+        <v>4.504109589041096</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002231555949768159</v>
+        <v>0.002232922227056719</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09900184897312733</v>
+        <v>0.09903448909517745</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5430427313351496</v>
+        <v>0.5346793560975609</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.115261357179238</v>
+        <v>3.112501567101213</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.834627949070367</v>
+        <v>2.832032659560757</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.419178082191781</v>
+        <v>3.416438356164384</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003210003544952857</v>
+        <v>0.00321284978799653</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50.7</v>
+        <v>49.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1242207932665013</v>
+        <v>0.1242767985259498</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.5798816568047336</v>
+        <v>0.6247464503042597</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.12481462915331</v>
+        <v>3.122041885109852</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.77953819024637</v>
+        <v>2.776933482220029</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.419178082191781</v>
+        <v>3.416438356164384</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003200189831007534</v>
+        <v>0.003203031979709696</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>47.69281307765974</v>
+        <v>47.95883973363593</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1761052631578948</v>
+        <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4438356164383562</v>
+        <v>0.441095890410959</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009115012840405969</v>
+        <v>0.009009524997135813</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4164383561643836</v>
+        <v>0.4136986301369863</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02253086419753086</v>
+        <v>0.02267080745341615</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1230</v>
+        <v>1253</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05935172456244742</v>
+        <v>0.05954781946534495</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4916528650406504</v>
+        <v>0.464272166001596</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4383561643835617</v>
+        <v>0.4356164383561644</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4137966212917806</v>
+        <v>0.4111342879984213</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4164383561643836</v>
+        <v>0.4136986301369863</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0228125</v>
+        <v>0.02295597484276729</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>508</v>
+        <v>507.3</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13220</v>
+        <v>13140</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.789924797541393</v>
+        <v>-1.800415316343941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.006152024205748896</v>
+        <v>0.01088288858447495</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4164383561643836</v>
+        <v>0.4136986301369863</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21850</v>
+        <v>21840</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1646469908811922</v>
+        <v>-0.1678648378777588</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.00613729977116706</v>
+        <v>0.01713827838827831</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.843456934843436</v>
+        <v>2.841298770790514</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.403898595927636</v>
+        <v>3.414467865465737</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.915068493150685</v>
+        <v>2.912328767123288</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003516845948134823</v>
+        <v>0.003519517237258993</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>651</v>
+        <v>654.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05309114922955354</v>
+        <v>0.05308822858072373</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5055749078341014</v>
+        <v>0.4970662364441729</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.789209248853563</v>
+        <v>2.786470170932492</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.648592432757754</v>
+        <v>2.645998782730575</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.915068493150685</v>
+        <v>2.912328767123288</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003585245532980453</v>
+        <v>0.003588769800702191</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1238712020045464</v>
+        <v>0.1239333092309622</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.321760885763945</v>
+        <v>2.319005346762171</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.065860288637018</v>
+        <v>2.063294439016958</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.487671232876712</v>
+        <v>2.484931506849315</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004307075746393941</v>
+        <v>0.004312193593672453</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68150</v>
+        <v>67880</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2524341584954856</v>
+        <v>-0.2527935987482388</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1395157740278796</v>
+        <v>0.1440483205657042</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.785749700281675</v>
+        <v>1.783023037086976</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.388752402982676</v>
+        <v>2.386252358250622</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.789041095890411</v>
+        <v>1.786301369863014</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005599888942119185</v>
+        <v>0.005608452494443123</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>122.1</v>
+        <v>121.2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.1</v>
+        <v>108.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.01751943173998283</v>
+        <v>-0.0149888872979728</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.003950504124656251</v>
+        <v>-0.009476584022038548</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.804601275298138</v>
+        <v>2.801319708985047</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.854612463496469</v>
+        <v>2.843947314767469</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.915068493150685</v>
+        <v>2.912328767123288</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00356556922656928</v>
+        <v>0.003569746062159798</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1520</v>
+        <v>1533</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0309182279859741</v>
+        <v>0.03089771475864586</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2138157894736843</v>
+        <v>0.2035225048923679</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.817767385461893</v>
+        <v>1.815028469279996</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.763250795374067</v>
+        <v>1.760629054944536</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.835616438356164</v>
+        <v>1.832876712328767</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005501253944799439</v>
+        <v>0.005509555452850226</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>952.5</v>
+        <v>964.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05333416381979067</v>
+        <v>0.05334195348201043</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7276640419947507</v>
+        <v>0.7058152793614594</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.195388216817318</v>
+        <v>3.19264464561103</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.033594016574592</v>
+        <v>3.030966947682252</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.416438356164384</v>
+        <v>3.413698630136986</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003129510194526609</v>
+        <v>0.003132199511695462</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.8</v>
+        <v>111.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8792</v>
+        <v>8799</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01139359167942828</v>
+        <v>-0.01100529499503914</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.241363009099181</v>
+        <v>0.239265989771565</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.893256515215862</v>
+        <v>1.890500364740423</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.915076110453395</v>
+        <v>1.911537397696118</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.912328767123288</v>
+        <v>1.90958904109589</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.00528190444328662</v>
+        <v>0.005289604903817652</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02902584701012</v>
+        <v>0.02901714771806255</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.295639097744361</v>
+        <v>0.3054545454545454</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.533822020742788</v>
+        <v>4.531091242161332</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.405935996569967</v>
+        <v>4.403319470632177</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.912328767123288</v>
+        <v>4.909589041095891</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002205644587336861</v>
+        <v>0.002206973875730208</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5715</v>
+        <v>6029</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03017566764802009</v>
+        <v>0.03028817139408574</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.864041994750656</v>
+        <v>1.714878089235362</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4410958904109589</v>
+        <v>0.4383561643835616</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4281754114985252</v>
+        <v>0.4254694720899501</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4136986301369863</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02267080745341615</v>
+        <v>0.0228125</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>358.7</v>
+        <v>348.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>28240</v>
+        <v>27380</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.14417417490609</v>
+        <v>-0.1405536241259569</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01614730878186976</v>
+        <v>0.01826150474799126</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.663555720100004</v>
+        <v>6.653108074193214</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.78611199231901</v>
+        <v>7.741155540305944</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.087671232876712</v>
+        <v>7.084931506849315</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001500700289762104</v>
+        <v>0.001503056900396533</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>132.1</v>
+        <v>130.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28240</v>
+        <v>27380</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1174903701853691</v>
+        <v>-0.1115317823190655</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1226628895184136</v>
+        <v>0.1412710007304601</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.091646012951829</v>
+        <v>2.088709484108523</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.370111262571916</v>
+        <v>2.350910750145277</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.084931506849315</v>
+        <v>2.082191780821918</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004780923702231779</v>
+        <v>0.004787645230743077</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2412</v>
+        <v>2382</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03902057231218862</v>
+        <v>0.03912025119749839</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.368865860696518</v>
+        <v>2.411294901763224</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.022073156812681</v>
+        <v>1.019333183492738</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9836890472131904</v>
+        <v>0.9809578653847256</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9972602739726028</v>
+        <v>0.9945205479452055</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009784035451224299</v>
+        <v>0.009810334993446471</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1680462412634795</v>
+        <v>0.1674379023130067</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.327354700854701</v>
+        <v>2.527393665158371</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.803845180488291</v>
+        <v>1.801129353005886</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.544326856903427</v>
+        <v>1.542805274214044</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.832876712328767</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.00554371301271712</v>
+        <v>0.005552072083724083</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12990</v>
+        <v>13060</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.004882288844183284</v>
+        <v>-0.00489682004912128</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3696689761354888</v>
+        <v>0.3623277182235836</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.261767233811869</v>
+        <v>4.259034881183117</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.282676497498854</v>
+        <v>4.279993237880474</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.421917808219178</v>
+        <v>4.419178082191781</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002346444432878062</v>
+        <v>0.002347949777115256</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112.8</v>
+        <v>112.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1365</v>
+        <v>1321</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01054531535054952</v>
+        <v>0.01114781810882318</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.2940168087912087</v>
+        <v>0.3347472732778198</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.795811087292188</v>
+        <v>2.792940482396483</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.766636037813252</v>
+        <v>2.762148552740977</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.912328767123288</v>
+        <v>2.90958904109589</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003576779577652097</v>
+        <v>0.003580455818170353</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>235.5</v>
+        <v>232.6</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.079878601195869</v>
+        <v>-4.184828378466772</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.06050955414012749</v>
+        <v>0.07373172828890806</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.08767123287671233</v>
+        <v>0.08493150684931507</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>241</v>
+        <v>234.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>235.5</v>
+        <v>232.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1380890108879931</v>
+        <v>-0.1326691067373467</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.02335456475583864</v>
+        <v>0.007308684436801549</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.395756530137018</v>
+        <v>4.388265914864228</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.100012165601687</v>
+        <v>5.059506065046079</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.663013698630137</v>
+        <v>4.66027397260274</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002274921263596074</v>
+        <v>0.002278804474024086</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>284</v>
+        <v>289.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2599641389945073</v>
+        <v>-0.2601553202327506</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2327800176056336</v>
+        <v>0.2085244218156712</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.330916644412502</v>
+        <v>3.328235139223314</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.501020585525083</v>
+        <v>4.498559265534431</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.416438356164384</v>
+        <v>3.413698630136986</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003002176598076886</v>
+        <v>0.00300459540317624</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1326588710238067</v>
+        <v>-0.1328741395500813</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1027237354085606</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.051475867897956</v>
+        <v>2.048788164598021</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.365246843902712</v>
+        <v>2.362734474941139</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.178082191780822</v>
+        <v>2.175342465753425</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004874539426216355</v>
+        <v>0.004880934092062188</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112.1</v>
+        <v>111.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17780</v>
+        <v>17580</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03432396498616207</v>
+        <v>-0.033501854268549</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1829034105736782</v>
+        <v>0.1942263344709898</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.913975209300045</v>
+        <v>1.911216344362144</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.982005496566577</v>
+        <v>1.977465091684915</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.912328767123288</v>
+        <v>1.90958904109589</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005224728069313433</v>
+        <v>0.005232270030286621</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>85.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04701528298460112</v>
+        <v>0.04701322280269446</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8206635622817229</v>
+        <v>0.7572471910112362</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.165980404883164</v>
+        <v>3.163241806710274</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.023814892040814</v>
+        <v>3.021205212903385</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.416438356164384</v>
+        <v>3.413698630136986</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003158579245966318</v>
+        <v>0.003161313807495436</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1185749577085743</v>
+        <v>0.1186658893817384</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.270201096892139</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.886414555231275</v>
+        <v>1.883670926025445</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.686444473149691</v>
+        <v>1.683854798742909</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.912328767123288</v>
+        <v>1.90958904109589</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005301061727004115</v>
+        <v>0.005308782899303995</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>140.1</v>
+        <v>137.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03251449889886637</v>
+        <v>0.0325039755079929</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5738758029978588</v>
+        <v>0.6036363636363635</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.346643578867338</v>
+        <v>3.343909320721597</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.241255771649109</v>
+        <v>3.238640625162136</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.578082191780822</v>
+        <v>3.575342465753425</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002988068422686491</v>
+        <v>0.002990511715742954</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24280</v>
+        <v>23970</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4858123715998673</v>
+        <v>-0.4864109860374453</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.002680597693574871</v>
+        <v>0.01021756729244894</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.588928049581064</v>
+        <v>1.586204181202618</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.09017168406974</v>
+        <v>3.088469842772506</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.575342465753425</v>
+        <v>1.572602739726027</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006293551179134007</v>
+        <v>0.006304358618206557</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>497.9</v>
+        <v>498.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03922498193336275</v>
+        <v>0.03923045173010713</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3456716649929705</v>
+        <v>0.3448613448414291</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9397260273972602</v>
+        <v>0.9369863013698631</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9042565794069001</v>
+        <v>0.9016155173378259</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9123287671232877</v>
+        <v>0.9095890410958904</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01064139941690962</v>
+        <v>0.01067251461988304</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>208.2</v>
+        <v>211.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08113712285158631</v>
+        <v>0.08115251039125407</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08040345821325645</v>
+        <v>0.06354609929077992</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.996815673847468</v>
+        <v>1.994071816535852</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.846958754483156</v>
+        <v>1.844394567251409</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.178082191780822</v>
+        <v>2.175342465753425</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005007973510510353</v>
+        <v>0.005014864518456629</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>89.2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8708</v>
+        <v>8450</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02885404104701386</v>
+        <v>0.03091769845793402</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.820826401010565</v>
+        <v>0.8597415673372784</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.478436319379245</v>
+        <v>4.475379180918715</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.352839315110005</v>
+        <v>4.341160489933455</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.504109589041096</v>
+        <v>4.501369863013698</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002232922227056719</v>
+        <v>0.002234447539693649</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09903448909517745</v>
+        <v>0.09906719767316483</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5346793560975609</v>
+        <v>0.5305315740540539</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.112501567101213</v>
+        <v>3.109741734354098</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.832032659560757</v>
+        <v>2.829437309145184</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.416438356164384</v>
+        <v>3.413698630136986</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00321284978799653</v>
+        <v>0.003215701127050999</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.3</v>
+        <v>48.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1242767985259498</v>
+        <v>0.1282754656190587</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6247464503042597</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.122041885109852</v>
+        <v>3.116940446023042</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.776933482220029</v>
+        <v>2.762570436921491</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.416438356164384</v>
+        <v>3.413698630136986</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003203031979709696</v>
+        <v>0.003208274323225897</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>47.95883973363593</v>
+        <v>48.22822822822823</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.441095890410959</v>
+        <v>0.4383561643835617</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.009009524997135813</v>
+        <v>0.008904569190491433</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4136986301369863</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02267080745341615</v>
+        <v>0.0228125</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1253</v>
+        <v>1316</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05954781946534495</v>
+        <v>0.05974642340769344</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.464272166001596</v>
+        <v>0.3941740303951367</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4356164383561644</v>
+        <v>0.4328767123287671</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4111342879984213</v>
+        <v>0.4084719728865136</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4136986301369863</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02295597484276729</v>
+        <v>0.02310126582278481</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>507.3</v>
+        <v>494.6</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13140</v>
+        <v>12950</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.800415316343941</v>
+        <v>-1.799691310849665</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01088288858447495</v>
+        <v>3.613220077225421e-05</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4136986301369863</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21840</v>
+        <v>20600</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1678648378777588</v>
+        <v>-0.1680331834137079</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.01713827838827831</v>
+        <v>0.07836407766990283</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.841298770790514</v>
+        <v>2.838589433951793</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.414467865465737</v>
+        <v>3.411902226580419</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.912328767123288</v>
+        <v>2.90958904109589</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003519517237258993</v>
+        <v>0.003522876496471108</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>654.7</v>
+        <v>651.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05308822858072373</v>
+        <v>0.05308531064031283</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.4970662364441729</v>
+        <v>0.5053436722469666</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.786470170932492</v>
+        <v>2.783731092409487</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.645998782730575</v>
+        <v>2.643405110946691</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.912328767123288</v>
+        <v>2.90958904109589</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003588769800702191</v>
+        <v>0.003592301004672258</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1239333092309622</v>
+        <v>0.12399558509709</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.319005346762171</v>
+        <v>2.31624976442611</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.063294439016958</v>
+        <v>2.060728525215723</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.484931506849315</v>
+        <v>2.482191780821918</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004312193593672453</v>
+        <v>0.004317323698671878</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67880</v>
+        <v>69000</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2527935987482388</v>
+        <v>-0.2531539675081721</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1440483205657042</v>
+        <v>0.1254782608695653</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.783023037086976</v>
+        <v>1.78029640798868</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.386252358250622</v>
+        <v>2.383752916312319</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.786301369863014</v>
+        <v>1.783561643835616</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005608452494443123</v>
+        <v>0.005617042170689807</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>121.2</v>
+        <v>124</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.9</v>
+        <v>110.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0149888872979728</v>
+        <v>-0.02302773309120533</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.009476584022038548</v>
+        <v>-0.003971119133573953</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.801319708985047</v>
+        <v>2.800298685687513</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.843947314767469</v>
+        <v>2.866303149574393</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.912328767123288</v>
+        <v>2.90958904109589</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003569746062159798</v>
+        <v>0.003571047635422098</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03089771475864586</v>
+        <v>0.03087714805629362</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2035225048923679</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.815028469279996</v>
+        <v>1.812289555210624</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.760629054944536</v>
+        <v>1.758007303418913</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.832876712328767</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005509555452850226</v>
+        <v>0.00551788204663454</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05334195348201043</v>
+        <v>0.05335758716315984</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7058152793614594</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.19264464561103</v>
+        <v>3.187157476269921</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.030966947682252</v>
+        <v>3.02571274476067</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.413698630136986</v>
+        <v>3.408219178082192</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003132199511695462</v>
+        <v>0.003137592062662516</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01100529499503914</v>
+        <v>-0.01116155173787598</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.239265989771565</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.890500364740423</v>
+        <v>1.885027522076116</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.911537397696118</v>
+        <v>1.9063048422005</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.90958904109589</v>
+        <v>1.904109589041096</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005289604903817652</v>
+        <v>0.00530496233231984</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02901714771806255</v>
+        <v>0.02899972709580366</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3054545454545454</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.531091242161332</v>
+        <v>4.525629707302213</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.403319470632177</v>
+        <v>4.398086401903254</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.909589041095891</v>
+        <v>4.904109589041096</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002206973875730208</v>
+        <v>0.002209637254206803</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03028817139408574</v>
+        <v>0.03051746639891267</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.714878089235362</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4328767123287671</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4254694720899501</v>
+        <v>0.4200576180833026</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4054794520547945</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0228125</v>
+        <v>0.02310126582278482</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1405536241259569</v>
+        <v>-0.140668964262511</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.01826150474799126</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.653108074193214</v>
+        <v>6.647875901506704</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.741155540305944</v>
+        <v>7.736105906848122</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.084931506849315</v>
+        <v>7.079452054794521</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001503056900396533</v>
+        <v>0.001504239872728905</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1115317823190655</v>
+        <v>-0.1118214812067632</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1412710007304601</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.088709484108523</v>
+        <v>2.083239623179031</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.350910750145277</v>
+        <v>2.345519035981097</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.082191780821918</v>
+        <v>2.076712328767123</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004787645230743077</v>
+        <v>0.004800215917907689</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03912025119749839</v>
+        <v>0.03932125444144435</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.411294901763224</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.019333183492738</v>
+        <v>1.013853232770984</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9809578653847256</v>
+        <v>0.9754955250249859</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9945205479452055</v>
+        <v>0.989041095890411</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009810334993446471</v>
+        <v>0.009863360570118013</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1674379023130067</v>
+        <v>0.1677937154260443</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.527393665158371</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.801129353005886</v>
+        <v>1.795635922716896</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.542805274214044</v>
+        <v>1.537631089290284</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.83013698630137</v>
+        <v>1.824657534246575</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005552072083724083</v>
+        <v>0.005569057665581478</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.00489682004912128</v>
+        <v>-0.004925936232031195</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.3623277182235836</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.259034881183117</v>
+        <v>4.25357020256541</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.279993237880474</v>
+        <v>4.274626741308833</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.419178082191781</v>
+        <v>4.413698630136986</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002347949777115256</v>
+        <v>0.002350966252765456</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01114781810882318</v>
+        <v>0.01107307904963019</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.3347472732778198</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.792940482396483</v>
+        <v>2.787477267789793</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.762148552740977</v>
+        <v>2.756949349704687</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.90958904109589</v>
+        <v>2.904109589041096</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003580455818170353</v>
+        <v>0.003587473202222401</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.184828378466772</v>
+        <v>-4.411746676605157</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>0.07373172828890806</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.08493150684931507</v>
+        <v>0.07945205479452055</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1326691067373467</v>
+        <v>-0.1328486937943935</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.007308684436801549</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.388265914864228</v>
+        <v>4.382944682364291</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.059506065046079</v>
+        <v>5.054417436724786</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.66027397260274</v>
+        <v>4.654794520547945</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002278804474024086</v>
+        <v>0.002281571118211262</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2601553202327506</v>
+        <v>-0.2605384688601428</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2085244218156712</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.328235139223314</v>
+        <v>3.32287231223984</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.498559265534431</v>
+        <v>4.493637832812932</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.413698630136986</v>
+        <v>3.408219178082192</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00300459540317624</v>
+        <v>0.003009444558903115</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1328741395500813</v>
+        <v>-0.1333062126659691</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1027237354085606</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.048788164598021</v>
+        <v>2.043413109369884</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.362734474941139</v>
+        <v>2.357710576944907</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.175342465753425</v>
+        <v>2.16986301369863</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004880934092062188</v>
+        <v>0.004893773047723885</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.033501854268549</v>
+        <v>-0.03365852535478565</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1942263344709898</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.911216344362144</v>
+        <v>1.905740539585371</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.977465091684915</v>
+        <v>1.972119162416216</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.90958904109589</v>
+        <v>1.904109589041096</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005232270030286621</v>
+        <v>0.005247304022915776</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04701322280269446</v>
+        <v>0.0470091090819088</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.7572471910112362</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.163241806710274</v>
+        <v>3.157764606720644</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.021205212903385</v>
+        <v>3.015985801202431</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.413698630136986</v>
+        <v>3.408219178082192</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003161313807495436</v>
+        <v>0.003166797163638191</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1186658893817384</v>
+        <v>0.1188486137979556</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.270201096892139</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.883670926025445</v>
+        <v>1.878183630749999</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.683854798742909</v>
+        <v>1.678675387883321</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.90958904109589</v>
+        <v>1.904109589041096</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005308782899303995</v>
+        <v>0.005324293022406327</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0325039755079929</v>
+        <v>0.03248289103326497</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.6036363636363635</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.343909320721597</v>
+        <v>3.33844082383068</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.238640625162136</v>
+        <v>3.233410309094527</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.575342465753425</v>
+        <v>3.56986301369863</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002990511715742954</v>
+        <v>0.002995410291120734</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4864109860374453</v>
+        <v>-0.4876123133206336</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01021756729244894</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.586204181202618</v>
+        <v>1.58075655455368</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.088469842772506</v>
+        <v>3.085079122018129</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.572602739726027</v>
+        <v>1.567123287671233</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006304358618206557</v>
+        <v>0.006326084792242699</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03923045173010713</v>
+        <v>0.03924155290054233</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.3448613448414291</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9369863013698631</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9016155173378259</v>
+        <v>0.8963333372450473</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9095890410958904</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01067251461988304</v>
+        <v>0.01073529411764706</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08115251039125407</v>
+        <v>0.08118346944768154</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.06354609929077992</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.994071816535852</v>
+        <v>1.988584052439777</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.844394567251409</v>
+        <v>1.8392660530184</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.175342465753425</v>
+        <v>2.16986301369863</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005014864518456629</v>
+        <v>0.005028703708918455</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03091769845793402</v>
+        <v>0.03094911447859638</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8597415673372784</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.475379180918715</v>
+        <v>4.469894885668921</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.341160489933455</v>
+        <v>4.33570854554696</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.501369863013698</v>
+        <v>4.495890410958904</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002234447539693649</v>
+        <v>0.002237189073967116</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09906719767316483</v>
+        <v>0.09913282092827408</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.5305315740540539</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.109741734354098</v>
+        <v>3.104221940388255</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.829437309145184</v>
+        <v>2.82424642525603</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.413698630136986</v>
+        <v>3.408219178082192</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003215701127050999</v>
+        <v>0.003221419148512709</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1282754656190587</v>
+        <v>0.128394156005725</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.6363636363636365</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.116940446023042</v>
+        <v>3.111390763269425</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.762570436921491</v>
+        <v>2.757361642391951</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.413698630136986</v>
+        <v>3.408219178082192</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003208274323225897</v>
+        <v>0.003213996813917413</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>48.22822822822823</v>
+        <v>48.77734579666345</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4383561643835617</v>
+        <v>0.4328767123287672</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.008904569190491433</v>
+        <v>0.008696259420842458</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4054794520547945</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0228125</v>
+        <v>0.0231012658227848</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05974642340769344</v>
+        <v>0.06015135138925808</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.3941740303951367</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4328767123287671</v>
+        <v>0.4273972602739726</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4084719728865136</v>
+        <v>0.4031473993915084</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4054794520547945</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02310126582278481</v>
+        <v>0.0233974358974359</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.799691310849665</v>
+        <v>-1.822499072057166</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>3.613220077225421e-05</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4054794520547945</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1680331834137079</v>
+        <v>-0.1683707387503126</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.07836407766990283</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.838589433951793</v>
+        <v>2.833170905516591</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.411902226580419</v>
+        <v>3.406771547767801</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.90958904109589</v>
+        <v>2.904109589041096</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003522876496471108</v>
+        <v>0.00352961410853421</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05308531064031283</v>
+        <v>0.05307948290648939</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.5053436722469666</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.783731092409487</v>
+        <v>2.778252933552855</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.643405110946691</v>
+        <v>2.638217702129096</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.90958904109589</v>
+        <v>2.904109589041096</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003592301004672258</v>
+        <v>0.003599384303434141</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.12399558509709</v>
+        <v>0.1241206451962785</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.31624976442611</v>
+        <v>2.310738469115035</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.060728525215723</v>
+        <v>2.055596504689731</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.482191780821918</v>
+        <v>2.476712328767123</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004317323698671878</v>
+        <v>0.004327620859590308</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2531539675081721</v>
+        <v>-0.2538775047942006</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1254782608695653</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.78029640798868</v>
+        <v>1.774843252610006</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.383752916312319</v>
+        <v>2.378755853112912</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.783561643835616</v>
+        <v>1.778082191780822</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005617042170689807</v>
+        <v>0.005634300372888954</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02302773309120533</v>
+        <v>-0.02315705902891907</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.003971119133573953</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.800298685687513</v>
+        <v>2.794846821933025</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.866303149574393</v>
+        <v>2.861101518689038</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.90958904109589</v>
+        <v>2.904109589041096</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003571047635422098</v>
+        <v>0.003578013621899897</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03087714805629362</v>
+        <v>0.03083585325147083</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2035225048923679</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.812289555210624</v>
+        <v>1.806811733447995</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.758007303418913</v>
+        <v>1.752763767139972</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.83013698630137</v>
+        <v>1.824657534246575</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00551788204663454</v>
+        <v>0.005534610947492957</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>964.7</v>
+        <v>982.4</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05335758716315984</v>
+        <v>0.05336543127404717</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7058152793614594</v>
+        <v>0.6750814332247557</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.187157476269921</v>
+        <v>3.18441387808926</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.02571274476067</v>
+        <v>3.023085610696096</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.408219178082192</v>
+        <v>3.405479452054795</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003137592062662516</v>
+        <v>0.003140295320531729</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.7</v>
+        <v>111.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8799</v>
+        <v>8843</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01116155173787598</v>
+        <v>-0.01170844647867609</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.239265989771565</v>
+        <v>0.2342037290512269</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.885027522076116</v>
+        <v>1.882310929471699</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.9063048422005</v>
+        <v>1.904610965018316</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.904109589041096</v>
+        <v>1.901369863013699</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.00530496233231984</v>
+        <v>0.005312618570836573</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02899972709580366</v>
+        <v>0.02899100573765359</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3054545454545454</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.525629707302213</v>
+        <v>4.522898951052682</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.398086401903254</v>
+        <v>4.395469859146483</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.904109589041096</v>
+        <v>4.901369863013699</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002209637254206803</v>
+        <v>0.002210971350061347</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6029</v>
+        <v>6505</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03051746639891267</v>
+        <v>0.03063431227466184</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.714878089235362</v>
+        <v>1.516218293620292</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4328767123287671</v>
+        <v>0.4301369863013698</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4200576180833026</v>
+        <v>0.4173517038764563</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4054794520547945</v>
+        <v>0.4027397260273973</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02310126582278482</v>
+        <v>0.0232484076433121</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>348.5</v>
+        <v>360.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27380</v>
+        <v>27800</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.140668964262511</v>
+        <v>-0.1451872705206317</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01826150474799126</v>
+        <v>0.0385611510791366</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.647875901506704</v>
+        <v>6.654733647053673</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.736105906848122</v>
+        <v>7.785019358692518</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.079452054794521</v>
+        <v>7.076712328767123</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001504239872728905</v>
+        <v>0.001502689743927981</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27380</v>
+        <v>27800</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1118214812067632</v>
+        <v>-0.1119668666184865</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1412710007304601</v>
+        <v>0.1240287769784172</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.083239623179031</v>
+        <v>2.080504709579723</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.345519035981097</v>
+        <v>2.34282329270467</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.076712328767123</v>
+        <v>2.073972602739726</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004800215917907689</v>
+        <v>0.004806526009748891</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2382</v>
+        <v>2448</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03932125444144435</v>
+        <v>0.04369486510786484</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.411294901763224</v>
+        <v>2.305550588235294</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.013853232770984</v>
+        <v>1.011102656419607</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9754955250249859</v>
+        <v>0.9687722822274407</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.989041095890411</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009863360570118013</v>
+        <v>0.009890192589752237</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1677937154260443</v>
+        <v>0.1679725016591822</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.527393665158371</v>
+        <v>2.642775700934579</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.795635922716896</v>
+        <v>1.792889173168995</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.537631089290284</v>
+        <v>1.535043993434843</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.824657534246575</v>
+        <v>1.821917808219178</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005569057665581478</v>
+        <v>0.005577589596530748</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.2</v>
+        <v>110.5</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.004925936232031195</v>
+        <v>-0.003476143523336151</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3623277182235836</v>
+        <v>0.3537519142419603</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.25357020256541</v>
+        <v>4.250093810606569</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.274626741308833</v>
+        <v>4.264919282146755</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.413698630136986</v>
+        <v>4.410958904109589</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002350966252765456</v>
+        <v>0.002352889240948969</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1321</v>
+        <v>1328</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01107307904963019</v>
+        <v>0.01103561115592495</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3347472732778198</v>
+        <v>0.3277117078313252</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.787477267789793</v>
+        <v>2.784745681618881</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.756949349704687</v>
+        <v>2.754349748803664</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.904109589041096</v>
+        <v>2.901369863013699</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003587473202222401</v>
+        <v>0.003590992192215776</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>175.8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>232.6</v>
+        <v>235</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.411746676605157</v>
+        <v>-4.24799328061067</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.07373172828890806</v>
+        <v>0.00991489361702147</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.07945205479452055</v>
+        <v>0.07671232876712329</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>232.6</v>
+        <v>235</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1328486937943935</v>
+        <v>-0.1329386381904405</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007308684436801549</v>
+        <v>-0.002978723404255312</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.382944682364291</v>
+        <v>4.3802841784088</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.054417436724786</v>
+        <v>5.051873340621631</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.654794520547945</v>
+        <v>4.652054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002281571118211262</v>
+        <v>0.002282956902497737</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>289.7</v>
+        <v>294</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2605384688601428</v>
+        <v>-0.2607304373035391</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2085244218156712</v>
+        <v>0.1908487244897958</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.32287231223984</v>
+        <v>3.320190990615535</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.493637832812932</v>
+        <v>4.491177722108901</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.408219178082192</v>
+        <v>3.405479452054795</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003009444558903115</v>
+        <v>0.003011874927757118</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1333062126659691</v>
+        <v>-0.1335230209110763</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1027237354085606</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.043413109369884</v>
+        <v>2.040725758227403</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.357710576944907</v>
+        <v>2.355199050265789</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.16986301369863</v>
+        <v>2.167123287671233</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004893773047723885</v>
+        <v>0.004900217464146732</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17580</v>
+        <v>17930</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03365852535478565</v>
+        <v>-0.03373718669756233</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1942263344709898</v>
+        <v>0.1709146101505856</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.905740539585371</v>
+        <v>1.903002644791818</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.972119162416216</v>
+        <v>1.969446219593037</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.904109589041096</v>
+        <v>1.901369863013699</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005247304022915776</v>
+        <v>0.005254853442988233</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.9</v>
+        <v>100.4</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0470091090819088</v>
+        <v>0.04861167888669925</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7572471910112362</v>
+        <v>0.7485393258426967</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.157764606720644</v>
+        <v>3.154146834673722</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.015985801202431</v>
+        <v>3.007926478582089</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.408219178082192</v>
+        <v>3.405479452054795</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003166797163638191</v>
+        <v>0.003170429445474577</v>
       </c>
     </row>
     <row r="18">
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>164.1</v>
+        <v>164</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1188486137979556</v>
+        <v>0.118940409125265</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.270201096892139</v>
+        <v>1.271585365853658</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.878183630749999</v>
+        <v>1.87543996457007</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.678675387883321</v>
+        <v>1.67608565145681</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.904109589041096</v>
+        <v>1.901369863013699</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005324293022406327</v>
+        <v>0.005332082172138431</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>137.5</v>
+        <v>140.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03248289103326497</v>
+        <v>0.03247232988563084</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.6036363636363635</v>
+        <v>0.5693950177935942</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.33844082383068</v>
+        <v>3.335706585118202</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.233410309094527</v>
+        <v>3.230795139553721</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.56986301369863</v>
+        <v>3.567123287671233</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002995410291120734</v>
+        <v>0.002997865593039157</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23970</v>
+        <v>24370</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4876123133206336</v>
+        <v>-0.4882150346560955</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01021756729244894</v>
+        <v>-0.006363763315551885</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.58075655455368</v>
+        <v>1.578032796515171</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.085079122018129</v>
+        <v>3.083390297436306</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.567123287671233</v>
+        <v>1.564383561643836</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006326084792242699</v>
+        <v>0.006337003908970316</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>498.2</v>
+        <v>501.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03924155290054233</v>
+        <v>0.03924718521461385</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3448613448414291</v>
+        <v>0.3354792146701215</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9315068493150684</v>
+        <v>0.9287671232876712</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8963333372450473</v>
+        <v>0.8936922192345148</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9041095890410958</v>
+        <v>0.9013698630136986</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01073529411764706</v>
+        <v>0.0107669616519174</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.8</v>
+        <v>96.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>211.5</v>
+        <v>209</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08118346944768154</v>
+        <v>0.08649812613200483</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06354609929077992</v>
+        <v>0.06526315789473669</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.988584052439777</v>
+        <v>1.984415875974062</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.8392660530184</v>
+        <v>1.82643285639037</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.16986301369863</v>
+        <v>2.167123287671233</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005028703708918455</v>
+        <v>0.005039266275317134</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.2</v>
+        <v>88.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8450</v>
+        <v>8664</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03094911447859638</v>
+        <v>0.03199985390815741</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8597415673372784</v>
+        <v>0.805672462603878</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.469894885668921</v>
+        <v>4.466992982621953</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.33570854554696</v>
+        <v>4.328482185056096</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.495890410958904</v>
+        <v>4.493150684931507</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002237189073967116</v>
+        <v>0.002238642424311664</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09913282092827408</v>
+        <v>0.09916573597272735</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.5305315740540539</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.104221940388255</v>
+        <v>3.101461978936281</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.82424642525603</v>
+        <v>2.821650891611522</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.408219178082192</v>
+        <v>3.405479452054795</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003221419148512709</v>
+        <v>0.003224285858706459</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.128394156005725</v>
+        <v>0.1284536789967266</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6363636363636365</v>
+        <v>0.6329896907216495</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.111390763269425</v>
+        <v>3.108615813886466</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.757361642391951</v>
+        <v>2.754757126274107</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.408219178082192</v>
+        <v>3.405479452054795</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003213996813917413</v>
+        <v>0.003216865833123895</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>48.77734579666345</v>
+        <v>49.05720646412805</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4328767123287672</v>
+        <v>0.4301369863013699</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.008696259420842458</v>
+        <v>0.008592908327986985</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4054794520547945</v>
+        <v>0.4027397260273973</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0231012658227848</v>
+        <v>0.0232484076433121</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1316</v>
+        <v>1260</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06015135138925808</v>
+        <v>0.0603577750302919</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.3941740303951367</v>
+        <v>0.4561373206349206</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4273972602739726</v>
+        <v>0.4246575342465753</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4031473993915084</v>
+        <v>0.4004851421346383</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4054794520547945</v>
+        <v>0.4027397260273973</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0233974358974359</v>
+        <v>0.0235483870967742</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12950</v>
+        <v>12810</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.822499072057166</v>
+        <v>-1.834120860090984</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>3.613220077225421e-05</v>
+        <v>0.01096548883684645</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4054794520547945</v>
+        <v>0.4027397260273973</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20600</v>
+        <v>21110</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1683707387503126</v>
+        <v>-0.1685399500238977</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.07836407766990283</v>
+        <v>0.0523117006158218</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.833170905516591</v>
+        <v>2.830461714148185</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.406771547767801</v>
+        <v>3.404206509055411</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.904109589041096</v>
+        <v>2.901369863013699</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00352961410853421</v>
+        <v>0.003532992497306912</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05307948290648939</v>
+        <v>0.0530765731240033</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.5053436722469666</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.778252933552855</v>
+        <v>2.775513853216809</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.638217702129096</v>
+        <v>2.635623965105511</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.904109589041096</v>
+        <v>2.901369863013699</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003599384303434141</v>
+        <v>0.00360293643946689</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1241206451962785</v>
+        <v>0.1241834306607652</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.89095702846975</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.310738469115035</v>
+        <v>2.307982755819999</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.055596504689731</v>
+        <v>2.053030397773633</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.476712328767123</v>
+        <v>2.473972602739726</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004327620859590308</v>
+        <v>0.004332788004929058</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69000</v>
+        <v>69470</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2538775047942006</v>
+        <v>-0.2542406804866881</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1254782608695653</v>
+        <v>0.1178638261119909</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.774843252610006</v>
+        <v>1.772116726595636</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.378755853112912</v>
+        <v>2.376258238049418</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.778082191780822</v>
+        <v>1.775342465753425</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005634300372888954</v>
+        <v>0.005642969139629263</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02315705902891907</v>
+        <v>-0.02322189771937959</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.003971119133573953</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.794846821933025</v>
+        <v>2.792120926806011</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.861101518689038</v>
+        <v>2.858500738588279</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.904109589041096</v>
+        <v>2.901369863013699</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003578013621899897</v>
+        <v>0.003581506769278541</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1533</v>
+        <v>1544</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03083585325147083</v>
+        <v>0.03359425977321756</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2035225048923679</v>
+        <v>0.189119170984456</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.806811733447995</v>
+        <v>1.803963119515418</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.752763767139972</v>
+        <v>1.745330048476883</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.824657534246575</v>
+        <v>1.821917808219178</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005534610947492957</v>
+        <v>0.005543350577303493</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96.8</v>
+        <v>95.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05336543127404717</v>
+        <v>0.05705956535127207</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6750814332247557</v>
+        <v>0.6560464169381108</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.18441387808926</v>
+        <v>3.182586704560735</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.023085610696096</v>
+        <v>3.010792209711596</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.405479452054795</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003140295320531729</v>
+        <v>0.003142098213905602</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.8</v>
+        <v>111.2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01170844647867609</v>
+        <v>-0.008888059518743809</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2342037290512269</v>
+        <v>0.227580095442723</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.882310929471699</v>
+        <v>1.882191640257558</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.904610965018316</v>
+        <v>1.89907069361269</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.901369863013699</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005312618570836573</v>
+        <v>0.005312955273051583</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.7</v>
+        <v>107.1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02899100573765359</v>
+        <v>0.03025894680138206</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3054545454545454</v>
+        <v>0.2981818181818181</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.522898951052682</v>
+        <v>4.521593620272269</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.395469859146483</v>
+        <v>4.388793355602824</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.901369863013699</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002210971350061347</v>
+        <v>0.002211609631428542</v>
       </c>
     </row>
     <row r="5">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>360.9</v>
+        <v>361.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1451872705206317</v>
+        <v>-0.1455390962906733</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0385611510791366</v>
+        <v>0.04143884892086325</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.654733647053673</v>
+        <v>6.655473685583368</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.785019358692518</v>
+        <v>7.789090942243332</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.076712328767123</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001502689743927981</v>
+        <v>0.001502522656150127</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130.2</v>
+        <v>130.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1119668666184865</v>
+        <v>-0.1132684576912811</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1240287769784172</v>
+        <v>0.1274820143884892</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.080504709579723</v>
+        <v>2.080547767602396</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.34282329270467</v>
+        <v>2.346310769757241</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.073972602739726</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004806526009748891</v>
+        <v>0.00480642653618278</v>
       </c>
     </row>
     <row r="8">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>81.8</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1679725016591822</v>
+        <v>0.1743365396427157</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.642775700934579</v>
+        <v>2.60714953271028</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.792889173168995</v>
+        <v>1.792639232873935</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.535043993434843</v>
+        <v>1.526512351748276</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.821917808219178</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005577589596530748</v>
+        <v>0.005578367256845169</v>
       </c>
     </row>
     <row r="10">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>175.8</v>
+        <v>172.5</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.24799328061067</v>
+        <v>-4.137886926775946</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.00991489361702147</v>
+        <v>-0.009042553191489278</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>234.3</v>
+        <v>233.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1329386381904405</v>
+        <v>-0.1319291439928748</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002978723404255312</v>
+        <v>-0.008085106382978768</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.3802841784088</v>
+        <v>4.37939423688694</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.051873340621631</v>
+        <v>5.044973237589022</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.652054794520548</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002282956902497737</v>
+        <v>0.002283420824682006</v>
       </c>
     </row>
     <row r="14">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>156.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1335230209110763</v>
+        <v>-0.1350936839549764</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1027237354085606</v>
+        <v>0.1069649805447472</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.040725758227403</v>
+        <v>2.04110498767555</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.355199050265789</v>
+        <v>2.3599145361881</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.167123287671233</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004900217464146732</v>
+        <v>0.004899307022608472</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.9</v>
+        <v>113</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03373718669756233</v>
+        <v>-0.03868316127201629</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1709146101505856</v>
+        <v>0.1824249414389292</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.903002644791818</v>
+        <v>1.903117800728243</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.969446219593037</v>
+        <v>1.979698809027887</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.901369863013699</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005254853442988233</v>
+        <v>0.005254535476560318</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04861167888669925</v>
+        <v>0.04796855028704187</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7485393258426967</v>
+        <v>0.7520224719101125</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.154146834673722</v>
+        <v>3.154499376424845</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.007926478582089</v>
+        <v>3.010108820117567</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.405479452054795</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003170429445474577</v>
+        <v>0.003170075123404688</v>
       </c>
     </row>
     <row r="18">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08649812613200483</v>
+        <v>0.08596455382776355</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.06526315789473669</v>
+        <v>0.0663636363636364</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.984415875974062</v>
+        <v>1.984559425654113</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.82643285639037</v>
+        <v>1.827462432967098</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.167123287671233</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005039266275317134</v>
+        <v>0.005038901768690543</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03199985390815741</v>
+        <v>0.03148163853261744</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.805672462603878</v>
+        <v>0.8097392924746076</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.466992982621953</v>
+        <v>4.467073013413984</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.328482185056096</v>
+        <v>4.330734398499645</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.493150684931507</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002238642424311664</v>
+        <v>0.002238602317439501</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>87.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.09916573597272735</v>
+        <v>0.1250346930727782</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.5305315740540539</v>
+        <v>0.4204590978378377</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.101461978936281</v>
+        <v>3.085375177611113</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.821650891611522</v>
+        <v>2.742471140320222</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.405479452054795</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003224285858706459</v>
+        <v>0.003241096924796878</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>193</v>
+        <v>189.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1685399500238977</v>
+        <v>-0.1631556194728095</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.0523117006158218</v>
+        <v>0.03322832780672669</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.830461714148185</v>
+        <v>2.82948832684348</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.404206509055411</v>
+        <v>3.381140380079956</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.901369863013699</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003532992497306912</v>
+        <v>0.003534207900817106</v>
       </c>
     </row>
     <row r="30">
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>87.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1241834306607652</v>
+        <v>0.1141338689568061</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.89095702846975</v>
+        <v>1.953732095373665</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.307982755819999</v>
+        <v>2.310536539802942</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.053030397773633</v>
+        <v>2.073841038479837</v>
       </c>
       <c r="BC31" s="8" t="n">
         <v>2.473972602739726</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004332788004929058</v>
+        <v>0.004327999071961385</v>
       </c>
     </row>
     <row r="32">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03359425977321756</v>
+        <v>0.03081512465780077</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.189119170984456</v>
+        <v>0.1949481865284974</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.803963119515418</v>
+        <v>1.804072825774152</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.745330048476883</v>
+        <v>1.750141982417118</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.821917808219178</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005543350577303493</v>
+        <v>0.005543013484341391</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>982.4</v>
+        <v>962.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05705956535127207</v>
+        <v>0.05740909429432942</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6560464169381108</v>
+        <v>0.6879933527212296</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.182586704560735</v>
+        <v>3.179673723694261</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.010792209711596</v>
+        <v>3.007042156958411</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.405479452054795</v>
+        <v>3.402739726027397</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003142098213905602</v>
+        <v>0.00314497677088127</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.2</v>
+        <v>110.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8843</v>
+        <v>8700</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.008888059518743809</v>
+        <v>-0.007542985321206714</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.227580095442723</v>
+        <v>0.2443913089655172</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.882191640257558</v>
+        <v>1.879395034345515</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.89907069361269</v>
+        <v>1.893679027452668</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.901369863013699</v>
+        <v>1.898630136986301</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005312955273051583</v>
+        <v>0.005320861137361908</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.1</v>
+        <v>107.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.03025894680138206</v>
+        <v>0.02877172409015823</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2981818181818181</v>
+        <v>0.3565842696629213</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.521593620272269</v>
+        <v>4.520384712818188</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.388793355602824</v>
+        <v>4.393962826705797</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.901369863013699</v>
+        <v>4.898630136986301</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002211609631428542</v>
+        <v>0.002212201092452063</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6505</v>
+        <v>6221</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03063431227466184</v>
+        <v>0.0307526613109903</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.516218293620292</v>
+        <v>1.631088249477576</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4301369863013698</v>
+        <v>0.4273972602739727</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4173517038764563</v>
+        <v>0.4146457984696116</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4027397260273973</v>
+        <v>0.4</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0232484076433121</v>
+        <v>0.02339743589743589</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>361.9</v>
+        <v>349.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27800</v>
+        <v>27410</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1455390962906733</v>
+        <v>-0.1410046581269376</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04143884892086325</v>
+        <v>0.01889821233126598</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.655473685583368</v>
+        <v>6.643115499615186</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.789090942243332</v>
+        <v>7.733587338354704</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.076712328767123</v>
+        <v>7.073972602739726</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001502522656150127</v>
+        <v>0.001505317798641205</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27800</v>
+        <v>27410</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1132684576912811</v>
+        <v>-0.1134156798187108</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1274820143884892</v>
+        <v>0.1435242612185335</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.080547767602396</v>
+        <v>2.077812908875913</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.346310769757241</v>
+        <v>2.343615673747807</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.073972602739726</v>
+        <v>2.071232876712329</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00480642653618278</v>
+        <v>0.004812752850500842</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2448</v>
+        <v>2358</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04369486510786484</v>
+        <v>0.04596427443869614</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.305550588235294</v>
+        <v>2.424567231552163</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.011102656419607</v>
+        <v>1.008357300394138</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9687722822274407</v>
+        <v>0.9640456419367287</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9863013698630136</v>
+        <v>0.9835616438356164</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009890192589752237</v>
+        <v>0.009917119652023436</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>80.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>214</v>
+        <v>213.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1743365396427157</v>
+        <v>0.1809984672563836</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.60714953271028</v>
+        <v>2.573193080878915</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.792639232873935</v>
+        <v>1.789638007867942</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.526512351748276</v>
+        <v>1.515360144391642</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.821917808219178</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005578367256845169</v>
+        <v>0.005587722185177185</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13060</v>
+        <v>12840</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.003476143523336151</v>
+        <v>-0.00348989712213613</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3537519142419603</v>
+        <v>0.3769470404984423</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.250093810606569</v>
+        <v>4.247361083073715</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.264919282146755</v>
+        <v>4.262235847692442</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.410958904109589</v>
+        <v>4.408219178082192</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002352889240948969</v>
+        <v>0.002354403076265707</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1328</v>
+        <v>1270</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01103561115592495</v>
+        <v>0.01099807743072789</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3277117078313252</v>
+        <v>0.3883473606299213</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.784745681618881</v>
+        <v>2.782014109590625</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.754349748803664</v>
+        <v>2.75175014838863</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.901369863013699</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003590992192215776</v>
+        <v>0.00359451807434273</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>235</v>
+        <v>227.3</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.137886926775946</v>
+        <v>-4.256543255030396</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.009042553191489278</v>
+        <v>0.02452705675318967</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.07671232876712329</v>
+        <v>0.07397260273972603</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>233.1</v>
+        <v>226</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>235</v>
+        <v>227.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1319291439928748</v>
+        <v>-0.125906265117706</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.008085106382978768</v>
+        <v>-0.005719313682358118</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.37939423688694</v>
+        <v>4.37130885340945</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.044973237589022</v>
+        <v>5.000961200114417</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.652054794520548</v>
+        <v>4.64931506849315</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002283420824682006</v>
+        <v>0.002287644349861116</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>294</v>
+        <v>278.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2607304373035391</v>
+        <v>-0.2609226692051966</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.1908487244897958</v>
+        <v>0.2584813982746226</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.320190990615535</v>
+        <v>3.317509730349703</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.491177722108901</v>
+        <v>4.488718016532932</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.405479452054795</v>
+        <v>3.402739726027397</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003011874927757118</v>
+        <v>0.003014309169470284</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156.6</v>
+        <v>156.4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1350936839549764</v>
+        <v>-0.1347894431148684</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1069649805447472</v>
+        <v>0.1142222222222224</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.04110498767555</v>
+        <v>2.038291831456891</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.3599145361881</v>
+        <v>2.355833288482981</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.167123287671233</v>
+        <v>2.164383561643836</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004899307022608472</v>
+        <v>0.004906068819817816</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17930</v>
+        <v>17490</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03868316127201629</v>
+        <v>-0.0387684437306434</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1824249414389292</v>
+        <v>0.2121714808461979</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.903117800728243</v>
+        <v>1.900380060549897</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.979698809027887</v>
+        <v>1.977026293149881</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.901369863013699</v>
+        <v>1.898630136986301</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005254535476560318</v>
+        <v>0.005262105305980942</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>89</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04796855028704187</v>
+        <v>0.04796720563643812</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.7520224719101125</v>
+        <v>0.8152502910360884</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.154499376424845</v>
+        <v>3.151760387248221</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.010108820117567</v>
+        <v>3.007499061322376</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.405479452054795</v>
+        <v>3.402739726027397</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003170075123404688</v>
+        <v>0.00317283002872275</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>88.7</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>164</v>
+        <v>163.8</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.118940409125265</v>
+        <v>0.1170253948713264</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.271585365853658</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.87543996457007</v>
+        <v>1.872782443928198</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.67608565145681</v>
+        <v>1.676580006620108</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.901369863013699</v>
+        <v>1.898630136986301</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005332082172138431</v>
+        <v>0.005339648517328476</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>140.5</v>
+        <v>136.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03247232988563084</v>
+        <v>0.03246175608845782</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5693950177935942</v>
+        <v>0.6201322556943425</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.335706585118202</v>
+        <v>3.332972352916265</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.230795139553721</v>
+        <v>3.228179962368221</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.567123287671233</v>
+        <v>3.564383561643836</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.002997865593039157</v>
+        <v>0.003000324917562024</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>301.6</v>
+        <v>290.9</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24370</v>
+        <v>23450</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4882150346560955</v>
+        <v>-0.4770074899616552</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.006363763315551885</v>
+        <v>-0.004015711641791264</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.578032796515171</v>
+        <v>1.574996231846166</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.083390297436306</v>
+        <v>3.011508198713382</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.564383561643836</v>
+        <v>1.561643835616438</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006337003908970316</v>
+        <v>0.006349221539583166</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>501.7</v>
+        <v>478.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03924718521461385</v>
+        <v>0.04037350545094512</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3354792146701215</v>
+        <v>0.3999955992470192</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9287671232876712</v>
+        <v>0.9260273972602739</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8936922192345148</v>
+        <v>0.8900912916451978</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.9013698630136986</v>
+        <v>0.8986301369863013</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.0107669616519174</v>
+        <v>0.01079881656804734</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>209</v>
+        <v>196.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08596455382776355</v>
+        <v>0.08121467546922972</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0663636363636364</v>
+        <v>0.1447328244274808</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.984559425654113</v>
+        <v>1.983096221931525</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.827462432967098</v>
+        <v>1.834137352113624</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.167123287671233</v>
+        <v>2.164383561643836</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005038901768690543</v>
+        <v>0.005042619661823598</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8664</v>
+        <v>8698</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03148163853261744</v>
+        <v>0.03123898264711993</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8097392924746076</v>
+        <v>0.8046905882961599</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.467073013413984</v>
+        <v>4.46437073091218</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.330734398499645</v>
+        <v>4.329133019634736</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.493150684931507</v>
+        <v>4.49041095890411</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002238602317439501</v>
+        <v>0.002239957342869855</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>81.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37</v>
+        <v>38.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1250346930727782</v>
+        <v>0.1325397476402468</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4204590978378377</v>
+        <v>0.3506039118110233</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.085375177611113</v>
+        <v>3.077900619105201</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.742471140320222</v>
+        <v>2.717697657427297</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.405479452054795</v>
+        <v>3.402739726027397</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003241096924796878</v>
+        <v>0.003248967799001637</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79.2</v>
+        <v>80.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>48.5</v>
+        <v>49.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1284536789967266</v>
+        <v>0.1236877525976134</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6329896907216495</v>
+        <v>0.6255060728744939</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.108615813886466</v>
+        <v>3.108690445018357</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.754757126274107</v>
+        <v>2.766507366332009</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.405479452054795</v>
+        <v>3.402739726027397</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003216865833123895</v>
+        <v>0.00321678860499761</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>49.05720646412805</v>
+        <v>49.34069226160299</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4301369863013699</v>
+        <v>0.4273972602739727</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.008592908327986985</v>
+        <v>0.008490095012061782</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4027397260273973</v>
+        <v>0.4</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0232484076433121</v>
+        <v>0.02339743589743589</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1260</v>
+        <v>1290</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0603577750302919</v>
+        <v>0.06056690699525878</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4561373206349206</v>
+        <v>0.4222736620155039</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4246575342465753</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.4004851421346383</v>
+        <v>0.3978229053125305</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4027397260273973</v>
+        <v>0.4</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0235483870967742</v>
+        <v>0.0237012987012987</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12810</v>
+        <v>12650</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.834120860090984</v>
+        <v>-1.845891644658263</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01096548883684645</v>
+        <v>0.02375240411067203</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4027397260273973</v>
+        <v>0.4</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>189.5</v>
+        <v>193.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21110</v>
+        <v>19690</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1631556194728095</v>
+        <v>-0.1700733466533129</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03322832780672669</v>
+        <v>0.1334631792788217</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.82948832684348</v>
+        <v>2.827998529139379</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.381140380079956</v>
+        <v>3.407528264980344</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.901369863013699</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003534207900817106</v>
+        <v>0.003536069731635686</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>651.1</v>
+        <v>638</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.0530765731240033</v>
+        <v>0.05307366607178936</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5053436722469666</v>
+        <v>0.5362527664576804</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.775513853216809</v>
+        <v>2.772774772273988</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.635623965105511</v>
+        <v>2.633030206345474</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.901369863013699</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00360293643946689</v>
+        <v>0.003606495594230638</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1141338689568061</v>
+        <v>0.1141862143897865</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.953732095373665</v>
+        <v>2.062725899630996</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.310536539802942</v>
+        <v>2.307783538874432</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.073841038479837</v>
+        <v>2.071272745138344</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.473972602739726</v>
+        <v>2.471232876712329</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004327999071961385</v>
+        <v>0.004333162028219192</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69470</v>
+        <v>69090</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2542406804866881</v>
+        <v>-0.2546047990204761</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1178638261119909</v>
+        <v>0.1240121580547113</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.772116726595636</v>
+        <v>1.769390235209735</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.376258238049418</v>
+        <v>2.37376123817886</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.775342465753425</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005642969139629263</v>
+        <v>0.005651664511878946</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>110.8</v>
+        <v>106</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02322189771937959</v>
+        <v>-0.02328685400205654</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.003971119133573953</v>
+        <v>0.04113207547169817</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.792120926806011</v>
+        <v>2.789395056270369</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.858500738588279</v>
+        <v>2.855899982200345</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.901369863013699</v>
+        <v>2.898630136986301</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003581506769278541</v>
+        <v>0.003585006712305123</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.5</v>
+        <v>101.9</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1544</v>
+        <v>1500</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03081512465780077</v>
+        <v>0.03413646392321452</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.1949481865284974</v>
+        <v>0.2228000000000001</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.804072825774152</v>
+        <v>1.801201992929405</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.750141982417118</v>
+        <v>1.741744978313757</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.821917808219178</v>
+        <v>1.819178082191781</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005543013484341391</v>
+        <v>0.005551848176525938</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>962.8</v>
+        <v>926.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.05740909429432942</v>
+        <v>0.0570808700745821</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6879933527212296</v>
+        <v>0.7552055237889741</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.179673723694261</v>
+        <v>3.177096694003098</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.007042156958411</v>
+        <v>3.005537971545108</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.402739726027397</v>
+        <v>3.4</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00314497677088127</v>
+        <v>0.003147527747227655</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.9</v>
+        <v>111.4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8700</v>
+        <v>8706</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007542985321206714</v>
+        <v>-0.009984776419278234</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2443913089655172</v>
+        <v>0.2491402536181946</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.879395034345515</v>
+        <v>1.876758570676123</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.893679027452668</v>
+        <v>1.895686577311606</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.898630136986301</v>
+        <v>1.895890410958904</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005320861137361908</v>
+        <v>0.005328335863891855</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.8</v>
+        <v>108.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>89</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02877172409015823</v>
+        <v>0.0277133245047094</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3565842696629213</v>
+        <v>0.2849152542372881</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.520384712818188</v>
+        <v>4.518732262415829</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.393962826705797</v>
+        <v>4.396880097466443</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.898630136986301</v>
+        <v>4.895890410958904</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002212201092452063</v>
+        <v>0.002213010069920307</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6221</v>
+        <v>5996</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0307526613109903</v>
+        <v>0.0308725426008175</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.631088249477576</v>
+        <v>1.729819879919947</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4273972602739727</v>
+        <v>0.4246575342465754</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4146457984696116</v>
+        <v>0.4119399020709145</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02339743589743589</v>
+        <v>0.02354838709677419</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>349.1</v>
+        <v>325.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27410</v>
+        <v>25230</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1410046581269376</v>
+        <v>-0.1320847387802943</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01889821233126598</v>
+        <v>0.03242172017439549</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.643115499615186</v>
+        <v>6.620939111550578</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.733587338354704</v>
+        <v>7.628554776472055</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.073972602739726</v>
+        <v>7.071232876712329</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001505317798641205</v>
+        <v>0.001510359758867813</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>130.6</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27410</v>
+        <v>25230</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1134156798187108</v>
+        <v>-0.101604254559842</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1435242612185335</v>
+        <v>0.2080856123662307</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.077812908875913</v>
+        <v>2.074680772202777</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.343615673747807</v>
+        <v>2.309317227661527</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.071232876712329</v>
+        <v>2.068493150684931</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004812752850500842</v>
+        <v>0.004820018642859727</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2358</v>
+        <v>2211</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04596427443869614</v>
+        <v>0.04716909621866602</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.424567231552163</v>
+        <v>2.648439791044776</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.008357300394138</v>
+        <v>1.00561458544553</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9640456419367287</v>
+        <v>0.9603172869375257</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9835616438356164</v>
+        <v>0.9808219178082191</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009917119652023436</v>
+        <v>0.009944167621206066</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>213.9</v>
+        <v>199.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1809984672563836</v>
+        <v>0.1771348238410152</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.573193080878915</v>
+        <v>2.858861013547416</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.789638007867942</v>
+        <v>1.787049922959967</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.515360144391642</v>
+        <v>1.518135294926359</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.819178082191781</v>
+        <v>1.816438356164384</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005587722185177185</v>
+        <v>0.005595814572117031</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>110.5</v>
+        <v>116</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12840</v>
+        <v>12600</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.00348989712213613</v>
+        <v>-0.01472146197847432</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.3769470404984423</v>
+        <v>0.4730158730158731</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.247361083073715</v>
+        <v>4.250272482732996</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.262235847692442</v>
+        <v>4.31377759559007</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.408219178082192</v>
+        <v>4.405479452054794</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002354403076265707</v>
+        <v>0.002352790330649539</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112.6</v>
+        <v>112</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1270</v>
+        <v>1225</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01099807743072789</v>
+        <v>0.01289865834921705</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.3883473606299213</v>
+        <v>0.4316781714285713</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.782014109590625</v>
+        <v>2.778861292547127</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.75175014838863</v>
+        <v>2.74347415670982</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.898630136986301</v>
+        <v>2.895890410958904</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.00359451807434273</v>
+        <v>0.003598596312388777</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>227.3</v>
+        <v>224.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.256543255030396</v>
+        <v>-4.382179305347162</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.02452705675318967</v>
+        <v>0.0373051224944323</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.07397260273972603</v>
+        <v>0.07123287671232877</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>226</v>
+        <v>222.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>227.3</v>
+        <v>224.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.125906265117706</v>
+        <v>-0.1226200393457367</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.005719313682358118</v>
+        <v>-0.0102449888641426</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.37130885340945</v>
+        <v>4.365626340620024</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.000961200114417</v>
+        <v>4.975753420860639</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.64931506849315</v>
+        <v>4.646575342465753</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002287644349861116</v>
+        <v>0.002290622059646947</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>278.2</v>
+        <v>276.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2609226692051966</v>
+        <v>-0.2611151650956904</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2584813982746226</v>
+        <v>0.2657611171366592</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.317509730349703</v>
+        <v>3.314828531527637</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.488718016532932</v>
+        <v>4.486258717107016</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.402739726027397</v>
+        <v>3.4</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003014309169470284</v>
+        <v>0.003016747293227715</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>156.4</v>
+        <v>155.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>76.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1347894431148684</v>
+        <v>-0.1315807774296746</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1142222222222224</v>
+        <v>0.08929768041237129</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.038291831456891</v>
+        <v>2.034776876105828</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.355833288482981</v>
+        <v>2.343081340465203</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.164383561643836</v>
+        <v>2.161643835616438</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004906068819817816</v>
+        <v>0.004914543760266276</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>113</v>
+        <v>110.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17490</v>
+        <v>16980</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0387684437306434</v>
+        <v>-0.02932198435667147</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2121714808461979</v>
+        <v>0.225375769140165</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.900380060549897</v>
+        <v>1.897420417571031</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.977026293149881</v>
+        <v>1.954737190904126</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.898630136986301</v>
+        <v>1.895890410958904</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005262105305980942</v>
+        <v>0.005270313267104729</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.6</v>
+        <v>101</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>85.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04796720563643812</v>
+        <v>0.04668283575655789</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8152502910360884</v>
+        <v>0.8681384248210027</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.151760387248221</v>
+        <v>3.149724017529805</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.007499061322376</v>
+        <v>3.00924397528038</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.402739726027397</v>
+        <v>3.4</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00317283002872275</v>
+        <v>0.003174881337013958</v>
       </c>
     </row>
     <row r="18">
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>163.8</v>
+        <v>156.7</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1170253948713264</v>
+        <v>0.11711497267188</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.282051282051282</v>
+        <v>1.385449904275686</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.872782443928198</v>
+        <v>1.870038872297363</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.676580006620108</v>
+        <v>1.673989623310359</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.898630136986301</v>
+        <v>1.895890410958904</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005339648517328476</v>
+        <v>0.005347482423033748</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>136.1</v>
+        <v>135.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03246175608845782</v>
+        <v>0.03536793775032152</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.6201322556943425</v>
+        <v>0.6153846153846156</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.332972352916265</v>
+        <v>3.328720334727619</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.228179962368221</v>
+        <v>3.215011990771476</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.564383561643836</v>
+        <v>3.561643835616438</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003000324917562024</v>
+        <v>0.003004157452241561</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>290.9</v>
+        <v>285</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23450</v>
+        <v>22540</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4770074899616552</v>
+        <v>-0.4707812783138428</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.004015711641791264</v>
+        <v>0.01517885093167703</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.574996231846166</v>
+        <v>1.572091678006653</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.011508198713382</v>
+        <v>2.970589689264529</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.561643835616438</v>
+        <v>1.558904109589041</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006349221539583166</v>
+        <v>0.006360952188665983</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>478.1</v>
+        <v>445.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04037350545094512</v>
+        <v>0.04038235194811704</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.3999955992470192</v>
+        <v>0.503792172545495</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9260273972602739</v>
+        <v>0.9232876712328767</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8900912916451978</v>
+        <v>0.8874503392949905</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8986301369863013</v>
+        <v>0.8958904109589041</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01079881656804734</v>
+        <v>0.01083086053412463</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.8</v>
+        <v>96.5</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>196.5</v>
+        <v>193.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08121467546922972</v>
+        <v>0.08815193720898307</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1447328244274808</v>
+        <v>0.1446621970087674</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.983096221931525</v>
+        <v>1.978491295026697</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.834137352113624</v>
+        <v>1.818212353783386</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.164383561643836</v>
+        <v>2.161643835616438</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005042619661823598</v>
+        <v>0.005054356329561241</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8698</v>
+        <v>8814</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03123898264711993</v>
+        <v>0.03073820873456143</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8046905882961599</v>
+        <v>0.7849368902881779</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.46437073091218</v>
+        <v>4.461708215119448</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.329133019634736</v>
+        <v>4.328653170427332</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.49041095890411</v>
+        <v>4.487671232876712</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002239957342869855</v>
+        <v>0.002241294033104377</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.1</v>
+        <v>36.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1325397476402468</v>
+        <v>0.132153640906258</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3506039118110233</v>
+        <v>0.396277907317073</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.077900619105201</v>
+        <v>3.075405218122369</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.717697657427297</v>
+        <v>2.716420375295169</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.402739726027397</v>
+        <v>3.4</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003248967799001637</v>
+        <v>0.003251604029632658</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.4</v>
+        <v>46.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1236877525976134</v>
+        <v>0.1250519958874132</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.6255060728744939</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.108690445018357</v>
+        <v>3.105146339078378</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.766507366332009</v>
+        <v>2.760002515820716</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.402739726027397</v>
+        <v>3.4</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00321678860499761</v>
+        <v>0.003220460135533595</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>49.34069226160299</v>
+        <v>49.6278732856867</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4273972602739727</v>
+        <v>0.4246575342465754</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.008490095012061782</v>
+        <v>0.008387820911423368</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02339743589743589</v>
+        <v>0.02354838709677419</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1290</v>
+        <v>1243</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06056690699525878</v>
+        <v>0.06077880038230611</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4222736620155039</v>
+        <v>0.4760523121480289</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3978229053125305</v>
+        <v>0.3951606895242518</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0237012987012987</v>
+        <v>0.0238562091503268</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12650</v>
+        <v>12720</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.845891644658263</v>
+        <v>-1.85781430956294</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02375240411067203</v>
+        <v>0.01811854654088063</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>193.9</v>
+        <v>165.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19690</v>
+        <v>17900</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1700733466533129</v>
+        <v>-0.1218697959812579</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1334631792788217</v>
+        <v>0.06226368715083774</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.827998529139379</v>
+        <v>2.816425135938345</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.407528264980344</v>
+        <v>3.207297873423602</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.898630136986301</v>
+        <v>2.895890410958904</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003536069731635686</v>
+        <v>0.003550600323934516</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05307366607178936</v>
+        <v>0.05307076175536867</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5362527664576804</v>
+        <v>0.568206824</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.772774772273988</v>
+        <v>2.770035690723172</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.633030206345474</v>
+        <v>2.630436425854029</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.898630136986301</v>
+        <v>2.895890410958904</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003606495594230638</v>
+        <v>0.003610061788550207</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1141862143897865</v>
+        <v>0.1142387040498001</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>2.062725899630996</v>
+        <v>1.974905802150538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.307783538874432</v>
+        <v>2.305030501083873</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.071272745138344</v>
+        <v>2.068704392250991</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.471232876712329</v>
+        <v>2.468493150684932</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004333162028219192</v>
+        <v>0.004338337386554232</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69090</v>
+        <v>69430</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2546047990204761</v>
+        <v>-0.2549698640241026</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1240121580547113</v>
+        <v>0.1185078496327236</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.769390235209735</v>
+        <v>1.766663778587009</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.37376123817886</v>
+        <v>2.371264856652943</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.772602739726027</v>
+        <v>1.76986301369863</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005651664511878946</v>
+        <v>0.005660386611875903</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>106</v>
+        <v>108.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02328685400205654</v>
+        <v>-0.02335192821188105</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.04113207547169817</v>
+        <v>0.01433823529411771</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.789395056270369</v>
+        <v>2.786669210394832</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.855899982200345</v>
+        <v>2.853299249639426</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.898630136986301</v>
+        <v>2.895890410958904</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003585006712305123</v>
+        <v>0.003588513470740627</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.9</v>
+        <v>101.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1500</v>
+        <v>1485</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03413646392321452</v>
+        <v>0.03636852569286605</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2228000000000001</v>
+        <v>0.2303030303030302</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.801201992929405</v>
+        <v>1.798374178483734</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.741744978313757</v>
+        <v>1.735265143527422</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.819178082191781</v>
+        <v>1.816438356164384</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005551848176525938</v>
+        <v>0.005560578059695739</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>926.9</v>
+        <v>930</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.0570808700745821</v>
+        <v>0.06257941794116496</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7552055237889741</v>
+        <v>0.7201075268817203</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.177096694003098</v>
+        <v>3.171623925994148</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>3.005537971545108</v>
+        <v>2.98483470735715</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.4</v>
+        <v>3.397260273972603</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003147527747227655</v>
+        <v>0.003152958936285452</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.4</v>
+        <v>111.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8706</v>
+        <v>8845</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009984776419278234</v>
+        <v>-0.01241642836743314</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2491402536181946</v>
+        <v>0.2350283446014698</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.876758570676123</v>
+        <v>1.874121700395095</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.895686577311606</v>
+        <v>1.897684159829632</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.895890410958904</v>
+        <v>1.893150684931507</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005328335863891855</v>
+        <v>0.005335832778571339</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.3</v>
+        <v>107.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0277133245047094</v>
+        <v>0.02854353552120191</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2849152542372881</v>
+        <v>0.2856170212765958</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.518732262415829</v>
+        <v>4.515139826099665</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.396880097466443</v>
+        <v>4.38983832007818</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.895890410958904</v>
+        <v>4.893150684931507</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002213010069920307</v>
+        <v>0.002214770834381523</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5996</v>
+        <v>6077</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0308725426008175</v>
+        <v>0.03099398599272422</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.729819879919947</v>
+        <v>1.693434260325819</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4246575342465754</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4119399020709145</v>
+        <v>0.4092340148938129</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02354838709677419</v>
+        <v>0.0237012987012987</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>325.6</v>
+        <v>319.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25230</v>
+        <v>25380</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1320847387802943</v>
+        <v>-0.1295609492932306</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03242172017439549</v>
+        <v>0.00614657210401881</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.620939111550578</v>
+        <v>6.612574271486798</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.628554776472055</v>
+        <v>7.596826298311862</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.071232876712329</v>
+        <v>7.068493150684931</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001510359758867813</v>
+        <v>0.001512270348798904</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>122.5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25230</v>
+        <v>25380</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.101604254559842</v>
+        <v>-0.08604587366417114</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2080856123662307</v>
+        <v>0.1583924349881796</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.074680772202777</v>
+        <v>2.071418241069972</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.309317227661527</v>
+        <v>2.266435679189479</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.068493150684931</v>
+        <v>2.065753424657534</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004820018642859727</v>
+        <v>0.004827610282525365</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95.7</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2211</v>
+        <v>2225</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04716909621866602</v>
+        <v>0.04403851940044686</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.648439791044776</v>
+        <v>2.63684846741573</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.00561458544553</v>
+        <v>1.002882625788584</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9603172869375257</v>
+        <v>0.960580100401375</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9808219178082191</v>
+        <v>0.9780821917808219</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009944167621206066</v>
+        <v>0.009971256598584331</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80.7</v>
+        <v>79.3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>199.3</v>
+        <v>188.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1771348238410152</v>
+        <v>0.1888251425394753</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.858861013547416</v>
+        <v>3.00492315845257</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.787049922959967</v>
+        <v>1.783851520844375</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.518135294926359</v>
+        <v>1.5005163139752</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.816438356164384</v>
+        <v>1.813698630136986</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005595814572117031</v>
+        <v>0.005605847730682519</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12600</v>
+        <v>12630</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01472146197847432</v>
+        <v>-0.008704051051001914</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4730158730158731</v>
+        <v>0.4315122723673792</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.250272482732996</v>
+        <v>4.244520999564621</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.31377759559007</v>
+        <v>4.281789917597051</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.405479452054794</v>
+        <v>4.402739726027397</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002352790330649539</v>
+        <v>0.002355978448693208</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>110.9</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1225</v>
+        <v>1175</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01289865834921705</v>
+        <v>0.01645640245644257</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4316781714285713</v>
+        <v>0.4779411761702128</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.778861292547127</v>
+        <v>2.775347195955868</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.74347415670982</v>
+        <v>2.73041439775357</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.895890410958904</v>
+        <v>2.893150684931507</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003598596312388777</v>
+        <v>0.003603152792764677</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>224.5</v>
+        <v>217.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.382179305347162</v>
+        <v>-4.515429597927096</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.0373051224944323</v>
+        <v>0.06970601745521376</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.07123287671232877</v>
+        <v>0.0684931506849315</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222.2</v>
+        <v>217</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>224.5</v>
+        <v>217.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1226200393457367</v>
+        <v>-0.1179678479339101</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.0102449888641426</v>
+        <v>-0.003215434083601254</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.365626340620024</v>
+        <v>4.358689107253999</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.975753420860639</v>
+        <v>4.941644243970152</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.646575342465753</v>
+        <v>4.643835616438357</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002290622059646947</v>
+        <v>0.002294267784173316</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>276.6</v>
+        <v>275</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2611151650956904</v>
+        <v>-0.2613079255069831</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2657611171366592</v>
+        <v>0.2731255454545454</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.314828531527637</v>
+        <v>3.312147394234746</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.486258717107016</v>
+        <v>4.483799824856598</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.4</v>
+        <v>3.397260273972603</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003016747293227715</v>
+        <v>0.003019189308243466</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>155.1</v>
+        <v>159</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>77.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1315807774296746</v>
+        <v>-0.1419635810098347</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.08929768041237129</v>
+        <v>0.109539052496799</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.034776876105828</v>
+        <v>2.034540384317363</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.343081340465203</v>
+        <v>2.371158542095265</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.161643835616438</v>
+        <v>2.158904109589041</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004914543760266276</v>
+        <v>0.004915115019137476</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.9</v>
+        <v>110.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16980</v>
+        <v>16930</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02932198435667147</v>
+        <v>-0.02893394502566288</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.225375769140165</v>
+        <v>0.227886516243355</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.897420417571031</v>
+        <v>1.894671659966019</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.954737190904126</v>
+        <v>1.951125415475563</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.895890410958904</v>
+        <v>1.893150684931507</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005270313267104729</v>
+        <v>0.005277959348470622</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04668283575655789</v>
+        <v>0.04668055326587719</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8681384248210027</v>
+        <v>0.8614744351961954</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.149724017529805</v>
+        <v>3.146985540636336</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.00924397528038</v>
+        <v>3.006634193037252</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.4</v>
+        <v>3.397260273972603</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003174881337013958</v>
+        <v>0.003177644088564179</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.11711497267188</v>
+        <v>0.1172048347804949</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.385449904275686</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.870038872297363</v>
+        <v>1.867295288492391</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.673989623310359</v>
+        <v>1.671399219158653</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.895890410958904</v>
+        <v>1.893150684931507</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005347482423033748</v>
+        <v>0.005355339383988783</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>104</v>
+        <v>105.5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>135.2</v>
+        <v>134</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03536793775032152</v>
+        <v>0.03099494586550001</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.6153846153846156</v>
+        <v>0.6533582089552239</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.328720334727619</v>
+        <v>3.328254411206903</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.215011990771476</v>
+        <v>3.228196631374267</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.561643835616438</v>
+        <v>3.558904109589041</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003004157452241561</v>
+        <v>0.003004578005313532</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22540</v>
+        <v>22790</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4707812783138428</v>
+        <v>-0.4713779016676019</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01517885093167703</v>
+        <v>0.004042619569986972</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.572091678006653</v>
+        <v>1.56936774412746</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.970589689264529</v>
+        <v>2.968789517271827</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.558904109589041</v>
+        <v>1.556164383561644</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006360952188665983</v>
+        <v>0.006371992821580397</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>445.1</v>
+        <v>448.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04038235194811704</v>
+        <v>0.04039127308044764</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.503792172545495</v>
+        <v>0.4910623657830251</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9232876712328767</v>
+        <v>0.9205479452054793</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8874503392949905</v>
+        <v>0.8848093683829839</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8958904109589041</v>
+        <v>0.8931506849315068</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01083086053412463</v>
+        <v>0.01086309523809524</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08815193720898307</v>
+        <v>0.08925466778113021</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1446621970087674</v>
+        <v>0.1422898401237751</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.978491295026697</v>
+        <v>1.975454601147884</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.818212353783386</v>
+        <v>1.813583783094536</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.161643835616438</v>
+        <v>2.158904109589041</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005054356329561241</v>
+        <v>0.005062125950244195</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8814</v>
+        <v>8450</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03073820873456143</v>
+        <v>0.03075384630965238</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7849368902881779</v>
+        <v>0.8618264794082842</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.461708215119448</v>
+        <v>4.458966079340172</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.328653170427332</v>
+        <v>4.325927179708664</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.487671232876712</v>
+        <v>4.484931506849315</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002241294033104377</v>
+        <v>0.002242672364414976</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>79.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.132153640906258</v>
+        <v>0.1394233389979952</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.396277907317073</v>
+        <v>0.3535743415549597</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.075405218122369</v>
+        <v>3.068051957185433</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.716420375295169</v>
+        <v>2.69263569753053</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.4</v>
+        <v>3.397260273972603</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003251604029632658</v>
+        <v>0.003259397213459772</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46.4</v>
+        <v>43.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1250519958874132</v>
+        <v>0.1295213971176787</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.7241379310344829</v>
+        <v>0.8202764976958525</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.105146339078378</v>
+        <v>3.099764484699481</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.760002515820716</v>
+        <v>2.744316745667221</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.4</v>
+        <v>3.397260273972603</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003220460135533595</v>
+        <v>0.003226051543386688</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>49.6278732856867</v>
+        <v>49.91882145383044</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4246575342465754</v>
+        <v>0.4219178082191781</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.008387820911423368</v>
+        <v>0.00828608746574669</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02354838709677419</v>
+        <v>0.0237012987012987</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1243</v>
+        <v>1263</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06077880038230611</v>
+        <v>0.06099350968690317</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4760523121480289</v>
+        <v>0.4526785621536025</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4191780821917808</v>
+        <v>0.4164383561643835</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3951606895242518</v>
+        <v>0.3924984953840797</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0238562091503268</v>
+        <v>0.02401315789473684</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12720</v>
+        <v>12890</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.85781430956294</v>
+        <v>-1.869891813512948</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01811854654088063</v>
+        <v>0.004691071528316604</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>165.2</v>
+        <v>161.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17900</v>
+        <v>17950</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1218697959812579</v>
+        <v>-0.1143416505098284</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06226368715083774</v>
+        <v>0.03365571030640657</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.816425135938345</v>
+        <v>2.812279993650822</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.207297873423602</v>
+        <v>3.175355367303553</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.895890410958904</v>
+        <v>2.893150684931507</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003550600323934516</v>
+        <v>0.003555833708797354</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05307076175536867</v>
+        <v>0.05306786018028436</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.568206824</v>
+        <v>0.5859696844660194</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.770035690723172</v>
+        <v>2.76729660856313</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.630436425854029</v>
+        <v>2.627842623636212</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.895890410958904</v>
+        <v>2.893150684931507</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003610061788550207</v>
+        <v>0.003613635043332895</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1142387040498001</v>
+        <v>0.1142913384592211</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.974905802150538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.305030501083873</v>
+        <v>2.30227742629644</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.068704392250991</v>
+        <v>2.066135979733899</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.468493150684932</v>
+        <v>2.465753424657534</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004338337386554232</v>
+        <v>0.004343525191960252</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>69430</v>
+        <v>66300</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2549698640241026</v>
+        <v>-0.2553358791445678</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1185078496327236</v>
+        <v>0.1713122171945702</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.766663778587009</v>
+        <v>1.763937356862858</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.371264856652943</v>
+        <v>2.368769096645259</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.76986301369863</v>
+        <v>1.767123287671233</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005660386611875903</v>
+        <v>0.00566913556260574</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.8</v>
+        <v>109.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02335192821188105</v>
+        <v>-0.02341712068504885</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01433823529411771</v>
+        <v>0.009698078682525146</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.786669210394832</v>
+        <v>2.783943389248384</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.853299249639426</v>
+        <v>2.850698541020146</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.895890410958904</v>
+        <v>2.893150684931507</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003588513470740627</v>
+        <v>0.003592027064422393</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03636852569286605</v>
+        <v>0.0307526111332965</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2303030303030302</v>
+        <v>0.2250996015936255</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.798374178483734</v>
+        <v>1.795856115700227</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.735265143527422</v>
+        <v>1.74227656209933</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.816438356164384</v>
+        <v>1.813698630136986</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005560578059695739</v>
+        <v>0.005568374833916399</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06257941794116496</v>
+        <v>0.06259428412277455</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7201075268817203</v>
+        <v>0.7054371002132194</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.171623925994148</v>
+        <v>3.168876789195802</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.98483470735715</v>
+        <v>2.982207637049234</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.397260273972603</v>
+        <v>3.394520547945206</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003152958936285452</v>
+        <v>0.003155692273708692</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111.9</v>
+        <v>110.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8845</v>
+        <v>8963</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.01241642836743314</v>
+        <v>-0.007765945165520989</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2350283446014698</v>
+        <v>0.2078773165234855</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.874121700395095</v>
+        <v>1.871185284219698</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.897684159829632</v>
+        <v>1.885830540790945</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.893150684931507</v>
+        <v>1.89041095890411</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005335832778571339</v>
+        <v>0.005344206201455938</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>107.9</v>
+        <v>108.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02854353552120191</v>
+        <v>0.02769462056685606</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2856170212765958</v>
+        <v>0.3184347826086957</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.515139826099665</v>
+        <v>4.513272008517847</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.38983832007818</v>
+        <v>4.391647010887744</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.893150684931507</v>
+        <v>4.890410958904109</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002214770834381523</v>
+        <v>0.002215687417272239</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6077</v>
+        <v>6084</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03099398599272422</v>
+        <v>0.03111702211564636</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.693434260325819</v>
+        <v>1.690335305719921</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4092340148938129</v>
+        <v>0.4065281371572269</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0237012987012987</v>
+        <v>0.0238562091503268</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.2</v>
+        <v>332.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25380</v>
+        <v>26000</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1295609492932306</v>
+        <v>-0.1349103730827438</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.00614657210401881</v>
+        <v>0.02307692307692299</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.612574271486798</v>
+        <v>6.62169141068892</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.596826298311862</v>
+        <v>7.654341474750187</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.068493150684931</v>
+        <v>7.065753424657534</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001512270348798904</v>
+        <v>0.001510188164893598</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>122.5</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25380</v>
+        <v>26000</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08604587366417114</v>
+        <v>-0.1052527292101359</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1583924349881796</v>
+        <v>0.1815384615384616</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.071418241069972</v>
+        <v>2.069322946925704</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.266435679189479</v>
+        <v>2.312745748974399</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.065753424657534</v>
+        <v>2.063013698630137</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004827610282525365</v>
+        <v>0.004832498482103304</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>96.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04403851940044686</v>
+        <v>0.03875897045115308</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.63684846741573</v>
+        <v>2.664024148648648</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.002882625788584</v>
+        <v>1.000155997600041</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.960580100401375</v>
+        <v>0.9628374108438781</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9780821917808219</v>
+        <v>0.9753424657534246</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009971256598584331</v>
+        <v>0.009998440267314149</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>79.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>188.7</v>
+        <v>190.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1888251425394753</v>
+        <v>0.1561753167777061</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.00492315845257</v>
+        <v>3.17438025210084</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.783851520844375</v>
+        <v>1.782393937436364</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.5005163139752</v>
+        <v>1.541629467063825</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.813698630136986</v>
+        <v>1.810958904109589</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005605847730682519</v>
+        <v>0.0056104320094261</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113</v>
+        <v>118.3</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12630</v>
+        <v>12660</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008704051051001914</v>
+        <v>-0.0192628230626048</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4315122723673792</v>
+        <v>0.4951026856240126</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.244520999564621</v>
+        <v>4.247041850731958</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.281789917597051</v>
+        <v>4.330458710655225</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.402739726027397</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002355978448693208</v>
+        <v>0.002354580046880524</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110.9</v>
+        <v>110.7</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01645640245644257</v>
+        <v>0.01708244739007624</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4779411761702128</v>
+        <v>0.4904979243336201</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.775347195955868</v>
+        <v>2.772471058952978</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.73041439775357</v>
+        <v>2.725905914576921</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.893150684931507</v>
+        <v>2.89041095890411</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003603152792764677</v>
+        <v>0.003606890671665476</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>172.5</v>
+        <v>170.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217.7</v>
+        <v>223.9</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.515429597927096</v>
+        <v>-4.564024779822285</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.06970601745521376</v>
+        <v>0.02561411344350173</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.0684931506849315</v>
+        <v>0.06575342465753424</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217</v>
+        <v>227.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.7</v>
+        <v>223.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1179678479339101</v>
+        <v>-0.1272188995430492</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003215434083601254</v>
+        <v>0.01473872264403742</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.358689107253999</v>
+        <v>4.36425998169623</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.941644243970152</v>
+        <v>5.000406149275334</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.643835616438357</v>
+        <v>4.641095890410959</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002294267784173316</v>
+        <v>0.002291339205716467</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>275</v>
+        <v>281.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2613079255069831</v>
+        <v>-0.2615009509724301</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2731255454545454</v>
+        <v>0.2419635509045761</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.312147394234746</v>
+        <v>3.30946631855656</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.483799824856598</v>
+        <v>4.481341340810596</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.397260273972603</v>
+        <v>3.394520547945206</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003019189308243466</v>
+        <v>0.003021635223760654</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1419635810098347</v>
+        <v>-0.1522484410103076</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.109539052496799</v>
+        <v>0.1316560509554141</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.034540384317363</v>
+        <v>2.034265053374194</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.371158542095265</v>
+        <v>2.399600486489849</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.158904109589041</v>
+        <v>2.156164383561644</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004915115019137476</v>
+        <v>0.004915780263448563</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.8</v>
+        <v>111.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16930</v>
+        <v>17200</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02893394502566288</v>
+        <v>-0.03085106494501117</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.227886516243355</v>
+        <v>0.2129747720930235</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.894671659966019</v>
+        <v>1.89197655634361</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.951125415475563</v>
+        <v>1.952204132831515</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.893150684931507</v>
+        <v>1.89041095890411</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005277959348470622</v>
+        <v>0.005285477754188333</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>84.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04668055326587719</v>
+        <v>0.04667827259103526</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8614744351961954</v>
+        <v>0.8816105769230771</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.146985540636336</v>
+        <v>3.144247062746205</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.006634193037252</v>
+        <v>3.004024393248053</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.397260273972603</v>
+        <v>3.394520547945206</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003177644088564179</v>
+        <v>0.003180411653550512</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>89.3</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1172048347804949</v>
+        <v>0.1152899107372636</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.385449904275686</v>
+        <v>1.393490746649649</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.867295288492391</v>
+        <v>1.864637776879777</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.671399219158653</v>
+        <v>1.671886169621275</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.893150684931507</v>
+        <v>1.89041095890411</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005355339383988783</v>
+        <v>0.00536297189941827</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>134</v>
+        <v>136.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03099494586550001</v>
+        <v>0.03098333647434325</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.6533582089552239</v>
+        <v>0.624266862170088</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.328254411206903</v>
+        <v>3.325520707567484</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.228196631374267</v>
+        <v>3.225581432712362</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.558904109589041</v>
+        <v>3.556164383561644</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003004578005313532</v>
+        <v>0.003007047881928449</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>285</v>
+        <v>286.7</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22790</v>
+        <v>23180</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4713779016676019</v>
+        <v>-0.4739683814495416</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004042619569986972</v>
+        <v>-0.006961984210526295</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.56936774412746</v>
+        <v>1.566696591918833</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.968789517271827</v>
+        <v>2.978331599602414</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.556164383561644</v>
+        <v>1.553424657534247</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006371992821580397</v>
+        <v>0.006382856803021676</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>448.9</v>
+        <v>461.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04039127308044764</v>
+        <v>0.04040026950978201</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4910623657830251</v>
+        <v>0.449724704353476</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9205479452054793</v>
+        <v>0.9178082191780821</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8848093683829839</v>
+        <v>0.8821683789168344</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8931506849315068</v>
+        <v>0.8904109589041096</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01086309523809524</v>
+        <v>0.0108955223880597</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.3</v>
+        <v>95.2</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>193.9</v>
+        <v>193.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08925466778113021</v>
+        <v>0.09527982866616168</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1422898401237751</v>
+        <v>0.1315762273901808</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.975454601147884</v>
+        <v>1.971089975769114</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.813583783094536</v>
+        <v>1.799622273852628</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.158904109589041</v>
+        <v>2.156164383561644</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005062125950244195</v>
+        <v>0.005073335120634473</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.3</v>
+        <v>89.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8450</v>
+        <v>8650</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03075384630965238</v>
+        <v>0.02973907195829788</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8618264794082842</v>
+        <v>0.8269252923699422</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.458966079340172</v>
+        <v>4.456382559463098</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.325927179708664</v>
+        <v>4.32768133289165</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.484931506849315</v>
+        <v>4.482191780821918</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002242672364414976</v>
+        <v>0.002243972519541678</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>78.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.3</v>
+        <v>37.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1394233389979952</v>
+        <v>0.1340561934802918</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3535743415549597</v>
+        <v>0.3526140321899736</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.068051957185433</v>
+        <v>3.068721077022503</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.69263569753053</v>
+        <v>2.705969152732142</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.397260273972603</v>
+        <v>3.394520547945206</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003259397213459772</v>
+        <v>0.003258686517610368</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>43.4</v>
+        <v>45.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1295213971176787</v>
+        <v>0.1256046048112506</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8202764976958525</v>
+        <v>0.771618625277162</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.099764484699481</v>
+        <v>3.099340779357087</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.744316745667221</v>
+        <v>2.75348978327679</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.397260273972603</v>
+        <v>3.394520547945206</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003226051543386688</v>
+        <v>0.003226492571131321</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>49.91882145383044</v>
+        <v>50.21361056384276</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4219178082191781</v>
+        <v>0.4191780821917809</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.00828608746574669</v>
+        <v>0.008184896116028269</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0237012987012987</v>
+        <v>0.02385620915032679</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1263</v>
+        <v>1314</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06099350968690317</v>
+        <v>0.06121109084810866</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4526785621536025</v>
+        <v>0.3962960608828006</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4164383561643835</v>
+        <v>0.4136986301369863</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3924984953840797</v>
+        <v>0.3898363235219891</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02401315789473684</v>
+        <v>0.02417218543046358</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>494.6</v>
+        <v>500</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12890</v>
+        <v>12800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.869891813512948</v>
+        <v>-1.88753352361501</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.004691071528316604</v>
+        <v>0.02280156249999998</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>161.2</v>
+        <v>162.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17950</v>
+        <v>18000</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1143416505098284</v>
+        <v>-0.1177648552426958</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.03365571030640657</v>
+        <v>0.041655</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.812279993650822</v>
+        <v>2.81018019322684</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.175355367303553</v>
+        <v>3.185296130999064</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.893150684931507</v>
+        <v>2.89041095890411</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003555833708797354</v>
+        <v>0.003558490670492315</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>618</v>
+        <v>646.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05306786018028436</v>
+        <v>0.0530649613521028</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5859696844660194</v>
+        <v>0.5169931357375019</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.76729660856313</v>
+        <v>2.764557525792632</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.627842623636212</v>
+        <v>2.625248799697053</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.893150684931507</v>
+        <v>2.89041095890411</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003613635043332895</v>
+        <v>0.003617215379568881</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1142913384592211</v>
+        <v>0.1143441181429902</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.974905802150538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.30227742629644</v>
+        <v>2.299524314376645</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.066135979733899</v>
+        <v>2.063567507502719</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.465753424657534</v>
+        <v>2.463013698630137</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004343525191960252</v>
+        <v>0.00434872548965015</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66300</v>
+        <v>67790</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2553358791445678</v>
+        <v>-0.2557028480472924</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1713122171945702</v>
+        <v>0.145567192801298</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.763937356862858</v>
+        <v>1.761210970173371</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.368769096645259</v>
+        <v>2.36627396135096</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.767123287671233</v>
+        <v>1.764383561643836</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.00566913556260574</v>
+        <v>0.005677911487807515</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>124</v>
+        <v>125.5</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.3</v>
+        <v>111.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02341712068504885</v>
+        <v>-0.02767929951321917</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.009698078682525146</v>
+        <v>0.002648114901256715</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.783943389248384</v>
+        <v>2.782111662875491</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.850698541020146</v>
+        <v>2.861310739844024</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.893150684931507</v>
+        <v>2.89041095890411</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003592027064422393</v>
+        <v>0.003594392034453556</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.5</v>
+        <v>102.7</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1506</v>
+        <v>1487</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.0307526111332965</v>
+        <v>0.02961977763326964</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2250996015936255</v>
+        <v>0.2431741761936785</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.795856115700227</v>
+        <v>1.793161115678431</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.74227656209933</v>
+        <v>1.74157602119908</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.813698630136986</v>
+        <v>1.810958904109589</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005568374833916399</v>
+        <v>0.005576743725126209</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06259428412277455</v>
+        <v>0.06262410945613817</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7054371002132194</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.168876789195802</v>
+        <v>3.163382468903182</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.982207637049234</v>
+        <v>2.976953412549836</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.394520547945206</v>
+        <v>3.389041095890411</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003155692273708692</v>
+        <v>0.003161173237287122</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007765945165520989</v>
+        <v>-0.007915609791306726</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2078773165234855</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.871185284219698</v>
+        <v>1.865712160904595</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.885830540790945</v>
+        <v>1.880598242768568</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.89041095890411</v>
+        <v>1.884931506849315</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005344206201455938</v>
+        <v>0.005359883592735697</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02769462056685606</v>
+        <v>0.02767588383945923</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3184347826086957</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.513272008517847</v>
+        <v>4.507811787715989</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.391647010887744</v>
+        <v>4.386413905982235</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.890410958904109</v>
+        <v>4.884931506849315</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002215687417272239</v>
+        <v>0.002218371234409231</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03111702211564636</v>
+        <v>0.03136799912709077</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.690335305719921</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4191780821917808</v>
+        <v>0.4136986301369864</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4065281371572269</v>
+        <v>0.4011164109097088</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3917808219178082</v>
+        <v>0.3863013698630137</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0238562091503268</v>
+        <v>0.02417218543046357</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1349103730827438</v>
+        <v>-0.1350227190391191</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02307692307692299</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.62169141068892</v>
+        <v>6.616458292601765</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.654341474750187</v>
+        <v>7.649285638175042</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.065753424657534</v>
+        <v>7.06027397260274</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001510188164893598</v>
+        <v>0.001511382609512035</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1052527292101359</v>
+        <v>-0.1055307225752294</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1815384615384616</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.069322946925704</v>
+        <v>2.063852746996878</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.312745748974399</v>
+        <v>2.307348948796577</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.063013698630137</v>
+        <v>2.057534246575342</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004832498482103304</v>
+        <v>0.004845306921509321</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03875897045115308</v>
+        <v>0.03895946839427965</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.664024148648648</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>1.000155997600041</v>
+        <v>0.9972602739726029</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9628374108438781</v>
+        <v>0.9598644646974313</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9753424657534246</v>
+        <v>0.9698630136986301</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.009998440267314149</v>
+        <v>0.01002747252747253</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1561753167777061</v>
+        <v>0.1565007675618497</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>3.17438025210084</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.782393937436364</v>
+        <v>1.776901688030224</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.541629467063825</v>
+        <v>1.53644661367265</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.810958904109589</v>
+        <v>1.805479452054795</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.0056104320094261</v>
+        <v>0.005627773369434665</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0192628230626048</v>
+        <v>-0.01930867550746229</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4951026856240126</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.247041850731958</v>
+        <v>4.241584998522083</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.330458710655225</v>
+        <v>4.325096890927333</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.4</v>
+        <v>4.394520547945206</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002354580046880524</v>
+        <v>0.002357609243592749</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01708244739007624</v>
+        <v>0.01701691648063829</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4904979243336201</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.772471058952978</v>
+        <v>2.767005887707039</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.725905914576921</v>
+        <v>2.720707829799129</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.89041095890411</v>
+        <v>2.884931506849315</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003606890671665476</v>
+        <v>0.003614014716928121</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.564024779822285</v>
+        <v>-4.869325984631674</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>0.02561411344350173</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.06575342465753424</v>
+        <v>0.06027397260273973</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1272188995430492</v>
+        <v>-0.1273945194527258</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.01473872264403742</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.36425998169623</v>
+        <v>4.358936884477026</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>5.000406149275334</v>
+        <v>4.995312293641819</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.641095890410959</v>
+        <v>4.635616438356164</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002291339205716467</v>
+        <v>0.002294137369965561</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2615009509724301</v>
+        <v>-0.2618877992066984</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2419635509045761</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.30946631855656</v>
+        <v>3.304104352387181</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.481341340810596</v>
+        <v>4.476425601468213</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.394520547945206</v>
+        <v>3.389041095890411</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003021635223760654</v>
+        <v>0.003026538793417678</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1522484410103076</v>
+        <v>-0.1527214054929026</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1316560509554141</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.034265053374194</v>
+        <v>2.028898562949334</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.399600486489849</v>
+        <v>2.394606185146978</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.156164383561644</v>
+        <v>2.150684931506849</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004915780263448563</v>
+        <v>0.00492878263241676</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03085106494501117</v>
+        <v>-0.03100242655398643</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.2129747720930235</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.89197655634361</v>
+        <v>1.886500627517504</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.952204132831515</v>
+        <v>1.946857948063384</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.89041095890411</v>
+        <v>1.884931506849315</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005285477754188333</v>
+        <v>0.005300819864109595</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04667827259103526</v>
+        <v>0.0466737167016664</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.8816105769230771</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.144247062746205</v>
+        <v>3.13877010396899</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>3.004024393248053</v>
+        <v>2.998804741041983</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.394520547945206</v>
+        <v>3.389041095890411</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003180411653550512</v>
+        <v>0.003185961274243995</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1152899107372636</v>
+        <v>0.1154654439020869</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.393490746649649</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.864637776879777</v>
+        <v>1.859150787976978</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.671886169621275</v>
+        <v>1.666704063438626</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.89041095890411</v>
+        <v>1.884931506849315</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00536297189941827</v>
+        <v>0.005378799861027641</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03098333647434325</v>
+        <v>0.03096007432106471</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.624266862170088</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.325520707567484</v>
+        <v>3.32005332256272</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.225581432712362</v>
+        <v>3.220351015774428</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.556164383561644</v>
+        <v>3.550684931506849</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003007047881928449</v>
+        <v>0.003011999817003266</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4739683814495416</v>
+        <v>-0.4751709559314573</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.006961984210526295</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.566696591918833</v>
+        <v>1.561248977025935</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.978331599602414</v>
+        <v>2.974776252706845</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.553424657534247</v>
+        <v>1.547945205479452</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006382856803021676</v>
+        <v>0.006405128296096158</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04040026950978201</v>
+        <v>0.04041849094660789</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.449724704353476</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9178082191780821</v>
+        <v>0.9123287671232877</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8821683789168344</v>
+        <v>0.8768863443528576</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8904109589041096</v>
+        <v>0.8849315068493151</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.0108955223880597</v>
+        <v>0.01096096096096096</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09527982866616168</v>
+        <v>0.09534615899750548</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1315762273901808</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.971089975769114</v>
+        <v>1.965592613718335</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.799622273852628</v>
+        <v>1.794494459648542</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.156164383561644</v>
+        <v>2.150684931506849</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005073335120634473</v>
+        <v>0.005087524205274094</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02973907195829788</v>
+        <v>0.02976917594051574</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8269252923699422</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.456382559463098</v>
+        <v>4.4508984784327</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.32768133289165</v>
+        <v>4.32222927469894</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.482191780821918</v>
+        <v>4.476712328767123</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002243972519541678</v>
+        <v>0.002246737383127488</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1340561934802918</v>
+        <v>0.1341761747987241</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3526140321899736</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.068721077022503</v>
+        <v>3.063165588522633</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.705969152732142</v>
+        <v>2.700784636977792</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.394520547945206</v>
+        <v>3.389041095890411</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003258686517610368</v>
+        <v>0.003264596611253722</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1256046048112506</v>
+        <v>0.125720130586894</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.771618625277162</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.099340779357087</v>
+        <v>3.093793132366291</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.75348978327679</v>
+        <v>2.748279122230267</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.394520547945206</v>
+        <v>3.389041095890411</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003226492571131321</v>
+        <v>0.003232278168628389</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>50.21361056384276</v>
+        <v>50.81501657607191</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4191780821917809</v>
+        <v>0.4136986301369864</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.008184896116028269</v>
+        <v>0.007984145475078971</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3917808219178082</v>
+        <v>0.3863013698630137</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02385620915032679</v>
+        <v>0.02417218543046357</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06121109084810866</v>
+        <v>0.06165510000519214</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.3962960608828006</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4136986301369863</v>
+        <v>0.4082191780821917</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3898363235219891</v>
+        <v>0.384512049233499</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3917808219178082</v>
+        <v>0.3863013698630137</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02417218543046358</v>
+        <v>0.02449664429530202</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.88753352361501</v>
+        <v>-1.912561460395316</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.02280156249999998</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3917808219178082</v>
+        <v>0.3863013698630137</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1177648552426958</v>
+        <v>-0.1180335383531307</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.041655</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.81018019322684</v>
+        <v>2.804750907950676</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.185296130999064</v>
+        <v>3.1801106163532</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.89041095890411</v>
+        <v>2.884931506849315</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003558490670492315</v>
+        <v>0.003565379004478731</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.0530649613521028</v>
+        <v>0.05305917195883096</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.5169931357375019</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.764557525792632</v>
+        <v>2.759079358415307</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.625248799697053</v>
+        <v>2.620061086674788</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.89041095890411</v>
+        <v>2.884931506849315</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003617215379568881</v>
+        <v>0.003624397380778332</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1143441181429902</v>
+        <v>0.1144501154462665</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.974905802150538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.299524314376645</v>
+        <v>2.294017978594632</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.063567507502719</v>
+        <v>2.058430383558284</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.463013698630137</v>
+        <v>2.457534246575342</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.00434872548965015</v>
+        <v>0.004359163743837016</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2557028480472924</v>
+        <v>-0.2564396619539818</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.145567192801298</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.761210970173371</v>
+        <v>1.755758302446243</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.36627396135096</v>
+        <v>2.361285577792048</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.758904109589041</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005677911487807515</v>
+        <v>0.005695544760384909</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02767929951321917</v>
+        <v>-0.0278169275341167</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.002648114901256715</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.782111662875491</v>
+        <v>2.776661495136582</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.861310739844024</v>
+        <v>2.856109691453224</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.89041095890411</v>
+        <v>2.884931506849315</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003594392034453556</v>
+        <v>0.003601447283911036</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02961977763326964</v>
+        <v>0.02957462136383464</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2431741761936785</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.793161115678431</v>
+        <v>1.787683446549072</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.74157602119908</v>
+        <v>1.736332082643026</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.810958904109589</v>
+        <v>1.805479452054795</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005576743725126209</v>
+        <v>0.005593831513797318</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06262410945613817</v>
+        <v>0.06263906876858677</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7054371002132194</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.163382468903182</v>
+        <v>3.160635285327341</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.976953412549836</v>
+        <v>2.974326258293858</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.389041095890411</v>
+        <v>3.386301369863014</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003161173237287122</v>
+        <v>0.003163920888443894</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007915609791306726</v>
+        <v>-0.007990752169903624</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2078773165234855</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.865712160904595</v>
+        <v>1.862975612390119</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.880598242768568</v>
+        <v>1.877982101946287</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.884931506849315</v>
+        <v>1.882191780821918</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005359883592735697</v>
+        <v>0.005367756793751273</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.3</v>
+        <v>108.1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02767588383945923</v>
+        <v>0.02808659612717814</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3184347826086957</v>
+        <v>0.3160000000000001</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.507811787715989</v>
+        <v>4.504650380846109</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.386413905982235</v>
+        <v>4.381586529593142</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.884931506849315</v>
+        <v>4.882191780821918</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002218371234409231</v>
+        <v>0.002219928108631973</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03136799912709077</v>
+        <v>0.03149600541143341</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.690335305719921</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4136986301369864</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.4011164109097088</v>
+        <v>0.3984105628656018</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3863013698630137</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02417218543046357</v>
+        <v>0.02433333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>332.5</v>
+        <v>318.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1350227190391191</v>
+        <v>-0.1296567780713588</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02307692307692299</v>
+        <v>-0.01876923076923076</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.616458292601765</v>
+        <v>6.601829976145505</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.649285638175042</v>
+        <v>7.585317849108021</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.06027397260274</v>
+        <v>7.057534246575343</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001511382609512035</v>
+        <v>0.00151473152688469</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1055307225752294</v>
+        <v>-0.09186236244360717</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1815384615384616</v>
+        <v>0.1446153846153846</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.063852746996878</v>
+        <v>2.06065557294869</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.307348948796577</v>
+        <v>2.269100506057077</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.057534246575342</v>
+        <v>2.054794520547945</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004845306921509321</v>
+        <v>0.004852824572565771</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03895946839427965</v>
+        <v>0.03905938073114485</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.664024148648648</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9972602739726029</v>
+        <v>0.9945205479452055</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9598644646974313</v>
+        <v>0.9571354307444883</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9698630136986301</v>
+        <v>0.9671232876712329</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01002747252747253</v>
+        <v>0.01005509641873278</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1565007675618497</v>
+        <v>0.1505165708825885</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.17438025210084</v>
+        <v>3.214422268907563</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.776901688030224</v>
+        <v>1.774397327134446</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.53644661367265</v>
+        <v>1.542261425903031</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.805479452054795</v>
+        <v>1.802739726027397</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005627773369434665</v>
+        <v>0.005635716334260629</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>118.3</v>
+        <v>116.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01930867550746229</v>
+        <v>-0.01502142841065386</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4951026856240126</v>
+        <v>0.4672985781990522</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.241584998522083</v>
+        <v>4.236723031814339</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.325096890927333</v>
+        <v>4.301335231057899</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.394520547945206</v>
+        <v>4.391780821917808</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002357609243592749</v>
+        <v>0.002360314782181451</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>110.7</v>
+        <v>109.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.01701691648063829</v>
+        <v>0.02064871805078113</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4904979243336201</v>
+        <v>0.4756871951848667</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.767005887707039</v>
+        <v>2.763473974986994</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.720707829799129</v>
+        <v>2.707566203840077</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.884931506849315</v>
+        <v>2.882191780821918</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003614014716928121</v>
+        <v>0.003618633680111666</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-4.869325984631674</v>
+        <v>-5.037767915259333</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>0.02561411344350173</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.06027397260273973</v>
+        <v>0.05753424657534247</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>227.2</v>
+        <v>225.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1273945194527258</v>
+        <v>-0.1260772511229192</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01473872264403742</v>
+        <v>0.007592675301473895</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.358936884477026</v>
+        <v>4.355023109721397</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.995312293641819</v>
+        <v>4.983304434307546</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.635616438356164</v>
+        <v>4.632876712328767</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002294137369965561</v>
+        <v>0.002296199066700183</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2618877992066984</v>
+        <v>-0.2620816230487337</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2419635509045761</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.304104352387181</v>
+        <v>3.301423462067497</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.476425601468213</v>
+        <v>4.473968348243928</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.389041095890411</v>
+        <v>3.386301369863014</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003026538793417678</v>
+        <v>0.003028996466190241</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>163</v>
+        <v>162.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1527214054929026</v>
+        <v>-0.1519666996806376</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1316560509554141</v>
+        <v>0.1288789808917199</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.028898562949334</v>
+        <v>2.025978569510898</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.394606185146978</v>
+        <v>2.38903185611689</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.150684931506849</v>
+        <v>2.147945205479452</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00492878263241676</v>
+        <v>0.004935886366465443</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.2</v>
+        <v>110.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03100242655398643</v>
+        <v>-0.02783166605229954</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2129747720930235</v>
+        <v>0.2053391395348838</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.886500627517504</v>
+        <v>1.883687101331697</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.946857948063384</v>
+        <v>1.937614130757147</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.884931506849315</v>
+        <v>1.882191780821918</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005300819864109595</v>
+        <v>0.005308737312545365</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0466737167016664</v>
+        <v>0.04828222486580824</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8816105769230771</v>
+        <v>0.8722956730769231</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.13877010396899</v>
+        <v>3.135149377104131</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.998804741041983</v>
+        <v>2.990749344724857</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.389041095890411</v>
+        <v>3.386301369863014</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003185961274243995</v>
+        <v>0.003189640682842609</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1154654439020869</v>
+        <v>0.1148847770584683</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.393490746649649</v>
+        <v>1.39617102744097</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.859150787976978</v>
+        <v>1.856435994434102</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.666704063438626</v>
+        <v>1.665137090966616</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.884931506849315</v>
+        <v>1.882191780821918</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005378799861027641</v>
+        <v>0.005386665648576968</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03096007432106471</v>
+        <v>0.03094842148609565</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.624266862170088</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.32005332256272</v>
+        <v>3.317319641234605</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.220351015774428</v>
+        <v>3.217735797541396</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.550684931506849</v>
+        <v>3.547945205479452</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003011999817003266</v>
+        <v>0.003014481895473391</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>286.7</v>
+        <v>293.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4751709559314573</v>
+        <v>-0.4832300853182542</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.006961984210526295</v>
+        <v>0.01555195754961169</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.561248977025935</v>
+        <v>1.5587226628399</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.974776252706845</v>
+        <v>3.01627981536008</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.547945205479452</v>
+        <v>1.545205479452055</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006405128296096158</v>
+        <v>0.006415509467079019</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04041849094660789</v>
+        <v>0.04042771731791284</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.449724704353476</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9123287671232877</v>
+        <v>0.9095890410958903</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8768863443528576</v>
+        <v>0.8742452992704697</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8849315068493151</v>
+        <v>0.8821917808219178</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01096096096096096</v>
+        <v>0.01099397590361446</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09534615899750548</v>
+        <v>0.09482777025004148</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1315762273901808</v>
+        <v>0.1327648578811369</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.965592613718335</v>
+        <v>1.962992846427242</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.794494459648542</v>
+        <v>1.792969542578305</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.150684931506849</v>
+        <v>2.147945205479452</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005087524205274094</v>
+        <v>0.005094262069370536</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02976917594051574</v>
+        <v>0.02978425616740303</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8269252923699422</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.4508984784327</v>
+        <v>4.44815643346119</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.32222927469894</v>
+        <v>4.319503242374384</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.476712328767123</v>
+        <v>4.473972602739726</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002246737383127488</v>
+        <v>0.002248122373749077</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>79.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1341761747987241</v>
+        <v>0.1475885039166697</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3526140321899736</v>
+        <v>0.3031489540897099</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.063165588522633</v>
+        <v>3.051877825179437</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.700784636977792</v>
+        <v>2.659383406825278</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.389041095890411</v>
+        <v>3.386301369863014</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003264596611253722</v>
+        <v>0.003276671142434099</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.125720130586894</v>
+        <v>0.125778067430715</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.771618625277162</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.093793132366291</v>
+        <v>3.091019203525222</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.748279122230267</v>
+        <v>2.745673674900809</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.389041095890411</v>
+        <v>3.386301369863014</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003232278168628389</v>
+        <v>0.003235178865467829</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>50.81501657607191</v>
+        <v>51.12179104477612</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4136986301369864</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007984145475078971</v>
+        <v>0.007884589072477338</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3863013698630137</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02417218543046357</v>
+        <v>0.02433333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06165510000519214</v>
+        <v>0.06188164753999834</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.3962960608828006</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4082191780821917</v>
+        <v>0.4054794520547945</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.384512049233499</v>
+        <v>0.3818499481501973</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3863013698630137</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02449664429530202</v>
+        <v>0.02466216216216216</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>500</v>
+        <v>498.5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.912561460395316</v>
+        <v>-1.923806076500344</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02280156249999998</v>
+        <v>0.01973315781250018</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3863013698630137</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1180335383531307</v>
+        <v>-0.1181682380404059</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.041655</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.804750907950676</v>
+        <v>2.802036328880369</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.1801106163532</v>
+        <v>3.177518036607939</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.884931506849315</v>
+        <v>2.882191780821918</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003565379004478731</v>
+        <v>0.00356883310074562</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05305917195883096</v>
+        <v>0.05305628140499086</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.5169931357375019</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.759079358415307</v>
+        <v>2.756340273805991</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.620061086674788</v>
+        <v>2.617467197601702</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.884931506849315</v>
+        <v>2.882191780821918</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003624397380778332</v>
+        <v>0.00362799908815027</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1144501154462665</v>
+        <v>0.1145033341286335</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.974905802150538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.294017978594632</v>
+        <v>2.291264754458052</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.058430383558284</v>
+        <v>2.055861731673922</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.457534246575342</v>
+        <v>2.454794520547945</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004359163743837016</v>
+        <v>0.004364401791867687</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2564396619539818</v>
+        <v>-0.2568095143819139</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.145567192801298</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.755758302446243</v>
+        <v>1.753032021684279</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.361285577792048</v>
+        <v>2.358792336027205</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.758904109589041</v>
+        <v>1.756164383561644</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005695544760384909</v>
+        <v>0.005704402359057992</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0278169275341167</v>
+        <v>-0.02788593004067704</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.002648114901256715</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.776661495136582</v>
+        <v>2.773936450538611</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.856109691453224</v>
+        <v>2.853509208702929</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.884931506849315</v>
+        <v>2.882191780821918</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003601447283911036</v>
+        <v>0.003604985254099212</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.02957462136383464</v>
+        <v>0.03010979423050729</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2431741761936785</v>
+        <v>0.2419636852723603</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.787683446549072</v>
+        <v>1.784922590475964</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.736332082643026</v>
+        <v>1.732749849067596</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.805479452054795</v>
+        <v>1.802739726027397</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005593831513797318</v>
+        <v>0.005602483857483937</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06263906876858677</v>
+        <v>0.06265405928581465</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7054371002132194</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.160635285327341</v>
+        <v>3.157888086077195</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.974326258293858</v>
+        <v>2.971699075990487</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.386301369863014</v>
+        <v>3.383561643835617</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003163920888443894</v>
+        <v>0.003166673335919969</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007990752169903624</v>
+        <v>-0.008066102447136141</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.2078773165234855</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.862975612390119</v>
+        <v>1.860239072688169</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.877982101946287</v>
+        <v>1.875365966701456</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.882191780821918</v>
+        <v>1.879452054794521</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005367756793751273</v>
+        <v>0.00537565313341652</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.1</v>
+        <v>108.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02808659612717814</v>
+        <v>0.02765711419809776</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3160000000000001</v>
+        <v>0.3184347826086957</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.504650380846109</v>
+        <v>4.502351600135006</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.381586529593142</v>
+        <v>4.381180782899834</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.882191780821918</v>
+        <v>4.879452054794521</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002219928108631973</v>
+        <v>0.002221061544749225</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03149600541143341</v>
+        <v>0.03162573527506427</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.690335305719921</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4082191780821918</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3984105628656018</v>
+        <v>0.3957047251960495</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02433333333333334</v>
+        <v>0.02449664429530201</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>318.9</v>
+        <v>348.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1296567780713588</v>
+        <v>-0.1410796154642487</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>-0.01876923076923076</v>
+        <v>0.07138461538461538</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.601829976145505</v>
+        <v>6.624097842853974</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.585317849108021</v>
+        <v>7.712120892827938</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.057534246575343</v>
+        <v>7.054794520547945</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00151473152688469</v>
+        <v>0.001509639536920174</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>124</v>
+        <v>129.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09186236244360717</v>
+        <v>-0.110497912919147</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1446153846153846</v>
+        <v>0.1944615384615385</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.06065557294869</v>
+        <v>2.05853825025001</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.269100506057077</v>
+        <v>2.314259044636616</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.054794520547945</v>
+        <v>2.052054794520548</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004852824572565771</v>
+        <v>0.00485781597635385</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03905938073114485</v>
+        <v>0.03915984517540506</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.664024148648648</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9945205479452055</v>
+        <v>0.9917808219178084</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9571354307444883</v>
+        <v>0.9544064144918923</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9671232876712329</v>
+        <v>0.9643835616438357</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01005509641873278</v>
+        <v>0.01008287292817679</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1505165708825885</v>
+        <v>0.1568283834134032</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.214422268907563</v>
+        <v>3.17438025210084</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.774397327134446</v>
+        <v>1.771409353836867</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.542261425903031</v>
+        <v>1.531263737331588</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.802739726027397</v>
+        <v>1.8</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005635716334260629</v>
+        <v>0.005645222533312263</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>116.1</v>
+        <v>115</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01502142841065386</v>
+        <v>-0.01284708203013203</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4672985781990522</v>
+        <v>0.4533965244865719</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.236723031814339</v>
+        <v>4.232899906656852</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.301335231057899</v>
+        <v>4.28798804076073</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.391780821917808</v>
+        <v>4.389041095890411</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002360314782181451</v>
+        <v>0.002362446601743061</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>109.6</v>
+        <v>106.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.02064871805078113</v>
+        <v>0.03088619975987699</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4756871951848667</v>
+        <v>0.4352942975064487</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.763473974986994</v>
+        <v>2.758493262856175</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.707566203840077</v>
+        <v>2.6758465323318</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.882191780821918</v>
+        <v>2.879452054794521</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003618633680111666</v>
+        <v>0.003625167454513153</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>170.1</v>
+        <v>168.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.037767915259333</v>
+        <v>-5.127474943820991</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.02561411344350173</v>
+        <v>0.01355515855292544</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.05753424657534247</v>
+        <v>0.0547945205479452</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225.6</v>
+        <v>223</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1260772511229192</v>
+        <v>-0.1238531594146972</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007592675301473895</v>
+        <v>-0.004019651630192023</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.355023109721397</v>
+        <v>4.350294391838442</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.983304434307546</v>
+        <v>4.965257181013474</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.632876712328767</v>
+        <v>4.63013698630137</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002296199066700183</v>
+        <v>0.002298695007574874</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2620816230487337</v>
+        <v>-0.2622757140923595</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.2419635509045761</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.301423462067497</v>
+        <v>3.298742633705844</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.473968348243928</v>
+        <v>4.471511507374762</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.386301369863014</v>
+        <v>3.383561643835617</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003028996466190241</v>
+        <v>0.003031458076729645</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>162.6</v>
+        <v>163.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1519666996806376</v>
+        <v>-0.1539389539277982</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1288789808917199</v>
+        <v>0.1337388535031847</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.025978569510898</v>
+        <v>2.0237097578689</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.38903185611689</v>
+        <v>2.391919315117836</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.147945205479452</v>
+        <v>2.145205479452055</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004935886366465443</v>
+        <v>0.004941420063384316</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.5</v>
+        <v>110.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02783166605229954</v>
+        <v>-0.02603163819118526</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2053391395348838</v>
+        <v>0.2009759209302326</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.883687101331697</v>
+        <v>1.880905484215615</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.937614130757147</v>
+        <v>1.931177190111672</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.882191780821918</v>
+        <v>1.879452054794521</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005308737312545365</v>
+        <v>0.005316588251732516</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100.5</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04828222486580824</v>
+        <v>0.04990388973951584</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8722956730769231</v>
+        <v>0.8629807692307692</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.135149377104131</v>
+        <v>3.131519981083473</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.990749344724857</v>
+        <v>2.982672996725835</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.386301369863014</v>
+        <v>3.383561643835617</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003189640682842609</v>
+        <v>0.003193337440095179</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>89.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1148847770584683</v>
+        <v>0.1398401436937778</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.39617102744097</v>
+        <v>1.299680918953414</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.856435994434102</v>
+        <v>1.852625922659771</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.665137090966616</v>
+        <v>1.625338371270319</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.882191780821918</v>
+        <v>1.879452054794521</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005386665648576968</v>
+        <v>0.005397743752631527</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03094842148609565</v>
+        <v>0.03093675409630854</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.624266862170088</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.317319641234605</v>
+        <v>3.314585967381179</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.217735797541396</v>
+        <v>3.215120572829568</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.547945205479452</v>
+        <v>3.545205479452055</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003014481895473391</v>
+        <v>0.003016968061293308</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4832300853182542</v>
+        <v>-0.4838390625561114</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01555195754961169</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.5587226628399</v>
+        <v>1.555999066744883</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.01627981536008</v>
+        <v>3.014561842766403</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.545205479452055</v>
+        <v>1.542465753424658</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006415509467079019</v>
+        <v>0.006426739073127971</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04042771731791284</v>
+        <v>0.04043702171409357</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.449724704353476</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9095890410958903</v>
+        <v>0.9068493150684932</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8742452992704697</v>
+        <v>0.871604235664819</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8821917808219178</v>
+        <v>0.8794520547945206</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01099397590361446</v>
+        <v>0.01102719033232628</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.3</v>
+        <v>95.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09482777025004148</v>
+        <v>0.09211142456074417</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1327648578811369</v>
+        <v>0.1387080103359173</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.962992846427242</v>
+        <v>1.960986030653096</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.792969542578305</v>
+        <v>1.795591536313998</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.147945205479452</v>
+        <v>2.145205479452055</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005094262069370536</v>
+        <v>0.005099475388241065</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.7</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02978425616740303</v>
+        <v>0.0290283355049697</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8269252923699422</v>
+        <v>0.8330354104046245</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.44815643346119</v>
+        <v>4.445532854084404</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.319503242374384</v>
+        <v>4.320126764928073</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.473972602739726</v>
+        <v>4.471232876712329</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002248122373749077</v>
+        <v>0.002249449127524126</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>76.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1475885039166697</v>
+        <v>0.1481322000628636</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3031489540897099</v>
+        <v>0.3014432617414247</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.051877825179437</v>
+        <v>3.048789582981977</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.659383406825278</v>
+        <v>2.655434263419358</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.386301369863014</v>
+        <v>3.383561643835617</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003276671142434099</v>
+        <v>0.003279990215073861</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.125778067430715</v>
+        <v>0.1258361206703869</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.771618625277162</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.091019203525222</v>
+        <v>3.088245204188574</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.745673674900809</v>
+        <v>2.74306814951865</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.386301369863014</v>
+        <v>3.383561643835617</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003235178865467829</v>
+        <v>0.003238084847160789</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>51.12179104477612</v>
+        <v>51.43272172478416</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.1173</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.410958904109589</v>
+        <v>0.4082191780821918</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007884589072477338</v>
+        <v>0.007785580543098771</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02433333333333334</v>
+        <v>0.02449664429530201</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06188164753999834</v>
+        <v>0.06211130611556985</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.3962960608828006</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4054794520547945</v>
+        <v>0.4027397260273973</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3818499481501973</v>
+        <v>0.3791878720322883</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02466216216216216</v>
+        <v>0.02482993197278912</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.923806076500344</v>
+        <v>-1.936731539132349</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.01973315781250018</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1181682380404059</v>
+        <v>-0.1183031773344564</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.041655</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.802036328880369</v>
+        <v>2.799321792331702</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.177518036607939</v>
+        <v>3.174925575742464</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.882191780821918</v>
+        <v>2.879452054794521</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00356883310074562</v>
+        <v>0.00357229384181319</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05305628140499086</v>
+        <v>0.05305339362055368</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.5169931357375019</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.756340273805991</v>
+        <v>2.753601188581234</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.617467197601702</v>
+        <v>2.614873286827313</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.882191780821918</v>
+        <v>2.879452054794521</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00362799908815027</v>
+        <v>0.003631607961773289</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1145033341286335</v>
+        <v>0.1145567002111004</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.974905802150538</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.291264754458052</v>
+        <v>2.288511492640376</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.055861731673922</v>
+        <v>2.053293019733249</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.454794520547945</v>
+        <v>2.452054794520548</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004364401791867687</v>
+        <v>0.004369652515252381</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2568095143819139</v>
+        <v>-0.2571803354402704</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.145567192801298</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.753032021684279</v>
+        <v>1.750305776508346</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.358792336027205</v>
+        <v>2.356299731975668</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.756164383561644</v>
+        <v>1.753424657534246</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005704402359057992</v>
+        <v>0.005713287434809717</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02788593004067704</v>
+        <v>-0.02795505868978607</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.002648114901256715</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.773936450538611</v>
+        <v>2.77121143221931</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.853509208702929</v>
+        <v>2.850908753749605</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.882191780821918</v>
+        <v>2.879452054794521</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003604985254099212</v>
+        <v>0.003608530148127872</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03010979423050729</v>
+        <v>0.03008784276788047</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2419636852723603</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.784922590475964</v>
+        <v>1.782183731132253</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.732749849067596</v>
+        <v>1.730127914473261</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.802739726027397</v>
+        <v>1.8</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005602483857483937</v>
+        <v>0.005611093752745022</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06265405928581465</v>
+        <v>0.06266908108887902</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7054371002132194</v>
+        <v>0.6928042328042325</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.157888086077195</v>
+        <v>3.155140871111595</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.971699075990487</v>
+        <v>2.969071865607151</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.383561643835617</v>
+        <v>3.380821917808219</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003166673335919969</v>
+        <v>0.003169430592326256</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8963</v>
+        <v>9019</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.008066102447136141</v>
+        <v>-0.008141661520521384</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2078773165234855</v>
+        <v>0.2003774684554829</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.860239072688169</v>
+        <v>1.857502541836875</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.875365966701456</v>
+        <v>1.872749837123345</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.879452054794521</v>
+        <v>1.876712328767123</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.00537565313341652</v>
+        <v>0.005383572713774619</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.3</v>
+        <v>108.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92</v>
+        <v>93.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02765711419809776</v>
+        <v>0.02701881480010559</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3184347826086957</v>
+        <v>0.2981003201707577</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.502351600135006</v>
+        <v>4.500266666560372</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.381180782899834</v>
+        <v>4.381873634356236</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.879452054794521</v>
+        <v>4.876712328767123</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002221061544749225</v>
+        <v>0.002222090542835135</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6084</v>
+        <v>6102</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03162573527506427</v>
+        <v>0.03175722365486652</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.690335305719921</v>
+        <v>1.682399213372665</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4082191780821918</v>
+        <v>0.4054794520547945</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3957047251960495</v>
+        <v>0.392998898150125</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3808219178082192</v>
+        <v>0.3780821917808219</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02449664429530201</v>
+        <v>0.02466216216216216</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>348.2</v>
+        <v>337.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26000</v>
+        <v>26350</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1410796154642487</v>
+        <v>-0.137197061695571</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.07138461538461538</v>
+        <v>0.02527514231499062</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.624097842853974</v>
+        <v>6.612985092402213</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.712120892827938</v>
+        <v>7.664537055701247</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.054794520547945</v>
+        <v>7.052054794520548</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001509639536920174</v>
+        <v>0.001512176401469466</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>129.4</v>
+        <v>128.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26000</v>
+        <v>26350</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.110497912919147</v>
+        <v>-0.1089760862180735</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1944615384615385</v>
+        <v>0.1740417457305503</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.05853825025001</v>
+        <v>2.055748058745095</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.314259044636616</v>
+        <v>2.307174955630011</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.052054794520548</v>
+        <v>2.049315068493151</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00485781597635385</v>
+        <v>0.004864409311958378</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2220</v>
+        <v>2025</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03915984517540506</v>
+        <v>0.04144219823102566</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.664024148648648</v>
+        <v>3.008531013333333</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9917808219178084</v>
+        <v>0.9890410958904109</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9544064144918923</v>
+        <v>0.94968409919473</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9643835616438357</v>
+        <v>0.9616438356164384</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01008287292817679</v>
+        <v>0.01011080332409972</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>190.4</v>
+        <v>225</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1568283834134032</v>
+        <v>0.1569930098246546</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>3.17438025210084</v>
+        <v>2.532453333333333</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.771409353836867</v>
+        <v>1.768663154688207</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.531263737331588</v>
+        <v>1.528672290730826</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.8</v>
+        <v>1.797260273972603</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005645222533312263</v>
+        <v>0.005653987857152411</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>115</v>
+        <v>113.6</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12660</v>
+        <v>12450</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01284708203013203</v>
+        <v>-0.01003296652549326</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4533965244865719</v>
+        <v>0.4599196787148594</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.232899906656852</v>
+        <v>4.228750923329067</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.28798804076073</v>
+        <v>4.271607821613349</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.389041095890411</v>
+        <v>4.386301369863014</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002362446601743061</v>
+        <v>0.002364764485141996</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.6</v>
+        <v>106.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1163</v>
+        <v>1100</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03088619975987699</v>
+        <v>0.03121416933838779</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4352942975064487</v>
+        <v>0.5160739727272727</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.758493262856175</v>
+        <v>2.755681551481274</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.6758465323318</v>
+        <v>2.672268897594066</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.879452054794521</v>
+        <v>2.876712328767123</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003625167454513153</v>
+        <v>0.003628866330590578</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>168.1</v>
+        <v>165.8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>223.9</v>
+        <v>221.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.127474943820991</v>
+        <v>-5.206998279429693</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01355515855292544</v>
+        <v>0.0096075778078486</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.0547945205479452</v>
+        <v>0.05205479452054795</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>223.9</v>
+        <v>221.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1238531594146972</v>
+        <v>-0.1239396604481775</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.004019651630192023</v>
+        <v>0.005863779882724351</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.350294391838442</v>
+        <v>4.347632180828653</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.965257181013474</v>
+        <v>4.962708599561564</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.63013698630137</v>
+        <v>4.627397260273972</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002298695007574874</v>
+        <v>0.002300102580916588</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>281.9</v>
+        <v>280</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2622757140923595</v>
+        <v>-0.2624700728779613</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2419635509045761</v>
+        <v>0.2503911607142857</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.298742633705844</v>
+        <v>3.296061867388353</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.471511507374762</v>
+        <v>4.469055079907225</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.383561643835617</v>
+        <v>3.380821917808219</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003031458076729645</v>
+        <v>0.003033923634426055</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>163.3</v>
+        <v>165.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.5</v>
+        <v>83</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1539389539277982</v>
+        <v>-0.1598078346037503</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1337388535031847</v>
+        <v>0.08737349397590366</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.0237097578689</v>
+        <v>2.022367998666219</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.391919315117836</v>
+        <v>2.407030298494195</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.145205479452055</v>
+        <v>2.142465753424657</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004941420063384316</v>
+        <v>0.004944698495325849</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.1</v>
+        <v>110.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02603163819118526</v>
+        <v>-0.0265708884647929</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2009759209302326</v>
+        <v>0.2090963555555556</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.880905484215615</v>
+        <v>1.87817830749536</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.931177190111672</v>
+        <v>1.929445385636004</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.879452054794521</v>
+        <v>1.876712328767123</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005316588251732516</v>
+        <v>0.00532430811286255</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83.2</v>
+        <v>82</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04990388973951584</v>
+        <v>0.04990401733752099</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8629807692307692</v>
+        <v>0.8902439024390243</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.131519981083473</v>
+        <v>3.12878018499611</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.982672996725835</v>
+        <v>2.98006306607957</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.383561643835617</v>
+        <v>3.380821917808219</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003193337440095179</v>
+        <v>0.003196133767387827</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1398401436937778</v>
+        <v>0.1385376149003813</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.299680918953414</v>
+        <v>1.305041480536056</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.852625922659771</v>
+        <v>1.849942002930741</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.625338371270319</v>
+        <v>1.624840478452357</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.879452054794521</v>
+        <v>1.876712328767123</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005397743752631527</v>
+        <v>0.00540557486891895</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105.5</v>
+        <v>105.3</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>136.4</v>
+        <v>145.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03093675409630854</v>
+        <v>0.03150462982441779</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.624266862170088</v>
+        <v>0.5177076183939602</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.314585967381179</v>
+        <v>3.311551582189655</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.215120572829568</v>
+        <v>3.21040884009735</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.545205479452055</v>
+        <v>3.542465753424658</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003016968061293308</v>
+        <v>0.00301973251867266</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23180</v>
+        <v>22980</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4838390625561114</v>
+        <v>-0.4844494600957138</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01555195754961169</v>
+        <v>0.02439052985204526</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.555999066744883</v>
+        <v>1.553275508798817</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.014561842766403</v>
+        <v>3.01284818572237</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.542465753424658</v>
+        <v>1.53972602739726</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006426739073127971</v>
+        <v>0.006438007902238301</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>461.7</v>
+        <v>461.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04043702171409357</v>
+        <v>0.04044640483785229</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.449724704353476</v>
+        <v>0.4512963920208151</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9068493150684932</v>
+        <v>0.9041095890410956</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.871604235664819</v>
+        <v>0.8689631535436907</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8794520547945206</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01102719033232628</v>
+        <v>0.01106060606060606</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>193.5</v>
+        <v>197</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09211142456074417</v>
+        <v>0.09214088550983217</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1387080103359173</v>
+        <v>0.118477157360406</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.960986030653096</v>
+        <v>1.958238359870485</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.795591536313998</v>
+        <v>1.793027242045189</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.145205479452055</v>
+        <v>2.142465753424657</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005099475388241065</v>
+        <v>0.005106630635435712</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8650</v>
+        <v>8963</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.0290283355049697</v>
+        <v>0.02929979143634024</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8330354104046245</v>
+        <v>0.7670577700546695</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.445532854084404</v>
+        <v>4.442751441160717</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.320126764928073</v>
+        <v>4.316285185447345</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.471232876712329</v>
+        <v>4.468493150684932</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002249449127524126</v>
+        <v>0.002250857409521743</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.9</v>
+        <v>38.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1481322000628636</v>
+        <v>0.1482034656401156</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3014432617414247</v>
+        <v>0.2745400418604649</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.048789582981977</v>
+        <v>3.046004163290745</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.655434263419358</v>
+        <v>2.652843554685335</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.383561643835617</v>
+        <v>3.380821917808219</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003279990215073861</v>
+        <v>0.003282989603401106</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>45.1</v>
+        <v>43.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1258361206703869</v>
+        <v>0.1294407123349204</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.771618625277162</v>
+        <v>0.8018223234624144</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.088245204188574</v>
+        <v>3.08337391962457</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.74306814951865</v>
+        <v>2.73000068613627</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.383561643835617</v>
+        <v>3.380821917808219</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003238084847160789</v>
+        <v>0.003243200552600378</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>51.43272172478416</v>
+        <v>51.74789279440442</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.1173</v>
+        <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4082191780821918</v>
+        <v>0.4054794520547946</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007785580543098771</v>
+        <v>0.007687121334594972</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3808219178082192</v>
+        <v>0.3780821917808219</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02449664429530201</v>
+        <v>0.02466216216216216</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1314</v>
+        <v>1213</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06211130611556985</v>
+        <v>0.06234413965087282</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.3962960608828006</v>
+        <v>0.5125581401483923</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4027397260273973</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3791878720322883</v>
+        <v>0.3765258215962442</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3808219178082192</v>
+        <v>0.3780821917808219</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02482993197278912</v>
+        <v>0.02499999999999999</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12800</v>
+        <v>12490</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.936731539132349</v>
+        <v>-1.949831669407576</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01973315781250018</v>
+        <v>0.04504278783026439</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3808219178082192</v>
+        <v>0.3780821917808219</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>162.9</v>
+        <v>174.3</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18000</v>
+        <v>17140</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1183031773344564</v>
+        <v>-0.1394312751344934</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.041655</v>
+        <v>0.1704743290548425</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.799321792331702</v>
+        <v>2.80049866350402</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.174925575742464</v>
+        <v>3.254241738731203</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.879452054794521</v>
+        <v>2.876712328767123</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00357229384181319</v>
+        <v>0.003570792634297447</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>646.1</v>
+        <v>621</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05305339362055368</v>
+        <v>0.05305050861120328</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5169931357375019</v>
+        <v>0.5783079951690822</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.753601188581234</v>
+        <v>2.750862102739779</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.614873286827313</v>
+        <v>2.612279354356615</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.879452054794521</v>
+        <v>2.876712328767123</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003631607961773289</v>
+        <v>0.003635224023058186</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1145567002111004</v>
+        <v>0.1146102142316823</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.974905802150538</v>
+        <v>1.985606902158273</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.288511492640376</v>
+        <v>2.285758193002705</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.053293019733249</v>
+        <v>2.050724247649492</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.452054794520548</v>
+        <v>2.449315068493151</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004369652515252381</v>
+        <v>0.004374915960320114</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67790</v>
+        <v>65540</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2571803354402704</v>
+        <v>-0.2575521288882933</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.145567192801298</v>
+        <v>0.1848947207812024</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.750305776508346</v>
+        <v>1.747579567058062</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.356299731975668</v>
+        <v>2.353807768943182</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.753424657534246</v>
+        <v>1.750684931506849</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005713287434809717</v>
+        <v>0.005722200115233872</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>111.4</v>
+        <v>108.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02795505868978607</v>
+        <v>-0.02802431384199747</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.002648114901256715</v>
+        <v>0.03230129390018499</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.77121143221931</v>
+        <v>2.768486440252279</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.850908753749605</v>
+        <v>2.848308326719028</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.879452054794521</v>
+        <v>2.876712328767123</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003608530148127872</v>
+        <v>0.003612081986245433</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.6</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1487</v>
+        <v>1430</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03008784276788047</v>
+        <v>0.03344022117075161</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2419636852723603</v>
+        <v>0.2839160839160839</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.782183731132253</v>
+        <v>1.779311665279048</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.730127914473261</v>
+        <v>1.721736418641924</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.8</v>
+        <v>1.797260273972603</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005611093752745022</v>
+        <v>0.00562015086796596</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>945</v>
+        <v>935</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06266908108887902</v>
+        <v>0.06268413425912255</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6928042328042325</v>
+        <v>0.7109090909090907</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.155140871111595</v>
+        <v>3.152393640389248</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.969071865607151</v>
+        <v>2.96644462711116</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.380821917808219</v>
+        <v>3.378082191780822</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003169430592326256</v>
+        <v>0.003172192670318047</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9019</v>
+        <v>8868</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.008141661520521384</v>
+        <v>-0.008217430292734201</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2003774684554829</v>
+        <v>0.2208169133964817</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.857502541836875</v>
+        <v>1.854766019874586</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.872749837123345</v>
+        <v>1.870133713301736</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.876712328767123</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005383572713774619</v>
+        <v>0.005391515637469016</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.6</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02701881480010559</v>
+        <v>0.02410170318619315</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2981003201707577</v>
+        <v>0.2914046121593292</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.500266666560372</v>
+        <v>4.500511147981897</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.381873634356236</v>
+        <v>4.394593948999276</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.876712328767123</v>
+        <v>4.873972602739726</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002222090542835135</v>
+        <v>0.002221969832134326</v>
       </c>
     </row>
     <row r="5">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>99.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6102</v>
+        <v>6079</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03175722365486652</v>
+        <v>0.05218886900211388</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.682399213372665</v>
+        <v>1.670834018753085</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4054794520547945</v>
+        <v>0.4027397260273972</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.392998898150125</v>
+        <v>0.3827637203664317</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3780821917808219</v>
+        <v>0.3753424657534247</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02466216216216216</v>
+        <v>0.02482993197278912</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>337.7</v>
+        <v>324</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26350</v>
+        <v>25090</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.137197061695571</v>
+        <v>-0.1318875258951935</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02527514231499062</v>
+        <v>0.03308090872857705</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.612985092402213</v>
+        <v>6.598583760122161</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.664537055701247</v>
+        <v>7.601070088212463</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.052054794520548</v>
+        <v>7.049315068493151</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001512176401469466</v>
+        <v>0.001515476708871067</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>128.9</v>
+        <v>122.4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26350</v>
+        <v>25090</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1089760862180735</v>
+        <v>-0.08650457987978862</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1740417457305503</v>
+        <v>0.1708250298923875</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.055748058745095</v>
+        <v>2.052255668710518</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.307174955630011</v>
+        <v>2.246596560320413</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.049315068493151</v>
+        <v>2.046575342465753</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004864409311958378</v>
+        <v>0.004872687235057435</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2025</v>
+        <v>2114</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04144219823102566</v>
+        <v>0.04154980887874207</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>3.008531013333333</v>
+        <v>2.839770719962157</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9890410958904109</v>
+        <v>0.9863013698630138</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.94968409919473</v>
+        <v>0.9469555478338527</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9616438356164384</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01011080332409972</v>
+        <v>0.01013888888888889</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>225</v>
+        <v>217.6</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1569930098246546</v>
+        <v>0.157158185439306</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.532453333333333</v>
+        <v>2.652582720588236</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.768663154688207</v>
+        <v>1.76591693403328</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.528672290730826</v>
+        <v>1.526080838604502</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.797260273972603</v>
+        <v>1.794520547945206</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005653987857152411</v>
+        <v>0.005662780512082423</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.6</v>
+        <v>114.5</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12450</v>
+        <v>12350</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01003296652549326</v>
+        <v>-0.0118781207265979</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4599196787148594</v>
+        <v>0.4834008097165992</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.228750923329067</v>
+        <v>4.226936119649737</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.271607821613349</v>
+        <v>4.27774772354797</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.386301369863014</v>
+        <v>4.383561643835616</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002364764485141996</v>
+        <v>0.002365779779238453</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.5</v>
+        <v>106.3</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03121416933838779</v>
+        <v>0.03189375920977589</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5160739727272727</v>
+        <v>0.5201365972602738</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.755681551481274</v>
+        <v>2.752792625763767</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.672268897594066</v>
+        <v>2.667709346233333</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.876712328767123</v>
+        <v>2.873972602739726</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003628866330590578</v>
+        <v>0.003632674654243336</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>165.8</v>
+        <v>162.7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221.7</v>
+        <v>221.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.206998279429693</v>
+        <v>-5.247569593972543</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.0096075778078486</v>
+        <v>-0.009715960324616746</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.05205479452054795</v>
+        <v>0.04931506849315068</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223</v>
+        <v>222.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.7</v>
+        <v>221.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1239396604481775</v>
+        <v>-0.1239365969909986</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.005863779882724351</v>
+        <v>0.004959422903516586</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.347632180828653</v>
+        <v>4.344889709804218</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.962708599561564</v>
+        <v>4.959560797632789</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.627397260273972</v>
+        <v>4.624657534246575</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002300102580916588</v>
+        <v>0.002301554393299112</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>309.9</v>
+        <v>239</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>280</v>
+        <v>270.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2624700728779613</v>
+        <v>-0.2025196665840748</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.2503911607142857</v>
+        <v>-0.003284422296050193</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.296061867388353</v>
+        <v>3.274218567519429</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.469055079907225</v>
+        <v>4.105704467337332</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.380821917808219</v>
+        <v>3.378082191780822</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003033923634426055</v>
+        <v>0.003054163854301294</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>165.6</v>
+        <v>162.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>83</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1598078346037503</v>
+        <v>-0.1531771443234592</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.08737349397590366</v>
+        <v>0.08334554334554345</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.022367998666219</v>
+        <v>2.018048475669881</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.407030298494195</v>
+        <v>2.38308220207121</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.142465753424657</v>
+        <v>2.13972602739726</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004944698495325849</v>
+        <v>0.004955282353502708</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.2</v>
+        <v>109.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17100</v>
+        <v>16900</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0265708884647929</v>
+        <v>-0.02381022156188133</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2090963555555556</v>
+        <v>0.216744179881657</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.87817830749536</v>
+        <v>1.875374339268816</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.929445385636004</v>
+        <v>1.921116549969794</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.876712328767123</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00532430811286255</v>
+        <v>0.005332268758619609</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.04990401733752099</v>
+        <v>0.05384931200704636</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8902439024390243</v>
+        <v>0.8450602409638552</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.12878018499611</v>
+        <v>3.123869884387786</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.98006306607957</v>
+        <v>2.964247211433297</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.380821917808219</v>
+        <v>3.378082191780822</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003196133767387827</v>
+        <v>0.003201157657038521</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1385376149003813</v>
+        <v>0.1329991968605202</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.305041480536056</v>
+        <v>1.326483726866624</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.849942002930741</v>
+        <v>1.847439641437861</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.624840478452357</v>
+        <v>1.630574537525725</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.876712328767123</v>
+        <v>1.873972602739726</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.00540557486891895</v>
+        <v>0.005412896733241583</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105.3</v>
+        <v>106.8</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145.7</v>
+        <v>153.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.03150462982441779</v>
+        <v>0.02717881627608077</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5177076183939602</v>
+        <v>0.4649248856956238</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.311551582189655</v>
+        <v>3.311051928013379</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.21040884009735</v>
+        <v>3.223442574504426</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.542465753424658</v>
+        <v>3.53972602739726</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.00301973251867266</v>
+        <v>0.003020188211303581</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22980</v>
+        <v>22660</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4844494600957138</v>
+        <v>-0.485061282457799</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02439052985204526</v>
+        <v>0.03885676857899378</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.553275508798817</v>
+        <v>1.550551989125178</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.01284818572237</v>
+        <v>3.011138872069967</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.53972602739726</v>
+        <v>1.536986301369863</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006438007902238301</v>
+        <v>0.0064493161597516</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>461.2</v>
+        <v>465.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04044640483785229</v>
+        <v>0.04045586740043687</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4512963920208151</v>
+        <v>0.439126845839604</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9041095890410956</v>
+        <v>0.9013698630136987</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8689631535436907</v>
+        <v>0.8663220529148993</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.873972602739726</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01106060606060606</v>
+        <v>0.01109422492401216</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.8</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>197</v>
+        <v>207.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09214088550983217</v>
+        <v>0.08564307863184731</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.118477157360406</v>
+        <v>0.07311207311207313</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.958238359870485</v>
+        <v>1.957248638608328</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.793027242045189</v>
+        <v>1.802847249829933</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.142465753424657</v>
+        <v>2.13972602739726</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005106630635435712</v>
+        <v>0.00510921290363515</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8963</v>
+        <v>8900</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02929979143634024</v>
+        <v>0.02905763927560578</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7670577700546695</v>
+        <v>0.7815456516853934</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.442751441160717</v>
+        <v>4.440048903105786</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.316285185447345</v>
+        <v>4.314674643717053</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.468493150684932</v>
+        <v>4.465753424657534</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002250857409521743</v>
+        <v>0.002252227445739407</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.7</v>
+        <v>34.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1482034656401156</v>
+        <v>0.1482748785717118</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2745400418604649</v>
+        <v>0.4422426789473681</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.046004163290745</v>
+        <v>3.043218646442223</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.652843554685335</v>
+        <v>2.650252742816726</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.380821917808219</v>
+        <v>3.378082191780822</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003282989603401106</v>
+        <v>0.003285994587240991</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>43.9</v>
+        <v>39.9</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1294407123349204</v>
+        <v>0.147522409070545</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8018223234624144</v>
+        <v>0.8847117794486217</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.08337391962457</v>
+        <v>3.069838634370297</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.73000068613627</v>
+        <v>2.675188397285213</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.380821917808219</v>
+        <v>3.378082191780822</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003243200552600378</v>
+        <v>0.003257500211261513</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>51.74789279440442</v>
+        <v>52.06739072267762</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4054794520547946</v>
+        <v>0.4027397260273972</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007687121334594972</v>
+        <v>0.007589212895958194</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3780821917808219</v>
+        <v>0.3753424657534247</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02466216216216216</v>
+        <v>0.02482993197278912</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1213</v>
+        <v>1243</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06234413965087282</v>
+        <v>0.06258021382815751</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5125581401483923</v>
+        <v>0.4760523121480289</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.3972602739726028</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3765258215962442</v>
+        <v>0.3738637975775902</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3780821917808219</v>
+        <v>0.3753424657534247</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02499999999999999</v>
+        <v>0.02517241379310345</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12490</v>
+        <v>12400</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.949831669407576</v>
+        <v>-1.963110031971869</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04504278783026439</v>
+        <v>0.05262777580645173</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3780821917808219</v>
+        <v>0.3753424657534247</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>174.3</v>
+        <v>153</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17140</v>
+        <v>17230</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1394312751344934</v>
+        <v>-0.09861935286738067</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1704743290548425</v>
+        <v>0.02207196749854901</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.80049866350402</v>
+        <v>2.790144649389537</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.254241738731203</v>
+        <v>3.095412197128108</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.876712328767123</v>
+        <v>2.873972602739726</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003570792634297447</v>
+        <v>0.003584043573578856</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>621</v>
+        <v>642.9</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05305050861120328</v>
+        <v>0.05304762638264824</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5783079951690822</v>
+        <v>0.5245438870741952</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.750862102739779</v>
+        <v>2.748123016280362</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.612279354356615</v>
+        <v>2.609685400194588</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.876712328767123</v>
+        <v>2.873972602739726</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003635224023058186</v>
+        <v>0.003638847293501145</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1146102142316823</v>
+        <v>0.1146638767310588</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.985606902158273</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.285758193002705</v>
+        <v>2.283004855405451</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.050724247649492</v>
+        <v>2.048155415335384</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.449315068493151</v>
+        <v>2.446575342465753</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004374915960320114</v>
+        <v>0.004380192173627264</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65540</v>
+        <v>66120</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2575521288882933</v>
+        <v>-0.2579248985043388</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1848947207812024</v>
+        <v>0.1745009074410164</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.747579567058062</v>
+        <v>1.744853393473756</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.353807768943182</v>
+        <v>2.351316450258179</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.750684931506849</v>
+        <v>1.747945205479452</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005722200115233872</v>
+        <v>0.005731140528713084</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.2</v>
+        <v>107.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02802431384199747</v>
+        <v>-0.02809369585923055</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03230129390018499</v>
+        <v>0.03999068901303549</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.768486440252279</v>
+        <v>2.765761474711391</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.848308326719028</v>
+        <v>2.845707927737448</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.876712328767123</v>
+        <v>2.873972602739726</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003612081986245433</v>
+        <v>0.003615640788778977</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1430</v>
+        <v>1477</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03344022117075161</v>
+        <v>0.03060480191860513</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2839160839160839</v>
+        <v>0.2491536899119837</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.779311665279048</v>
+        <v>1.776683869006128</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.721736418641924</v>
+        <v>1.723923530822483</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.797260273972603</v>
+        <v>1.794520547945206</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00562015086796596</v>
+        <v>0.005628463326789798</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>935</v>
+        <v>931.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06268413425912255</v>
+        <v>0.0626992188781762</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7109090909090907</v>
+        <v>0.7166004936151946</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.152393640389248</v>
+        <v>3.149646393868711</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.96644462711116</v>
+        <v>2.963817360469684</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.378082191780822</v>
+        <v>3.375342465753425</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003172192670318047</v>
+        <v>0.003174959582595238</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8868</v>
+        <v>9176</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.008217430292734201</v>
+        <v>-0.008293409671644479</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2208169133964817</v>
+        <v>0.1798391878814298</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.854766019874586</v>
+        <v>1.852029506839873</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.870133713301736</v>
+        <v>1.867517595326924</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.873972602739726</v>
+        <v>1.871232876712329</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005391515637469016</v>
+        <v>0.005399482007747839</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>109.4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02410170318619315</v>
+        <v>0.02533143091360552</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2914046121593292</v>
+        <v>0.2697202072538862</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.500511147981897</v>
+        <v>4.496515066320406</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.394593948999276</v>
+        <v>4.385425951795759</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.873972602739726</v>
+        <v>4.871232876712329</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002221969832134326</v>
+        <v>0.002223944510917255</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6079</v>
+        <v>6112</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05218886900211388</v>
+        <v>0.05246166263115411</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.670834018753085</v>
+        <v>1.656413612565445</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4027397260273972</v>
+        <v>0.4</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3827637203664317</v>
+        <v>0.3800613496932516</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3753424657534247</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02482993197278912</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>324</v>
+        <v>326.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25090</v>
+        <v>25490</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1318875258951935</v>
+        <v>-0.1331013494773597</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03308090872857705</v>
+        <v>0.02597096900745388</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.598583760122161</v>
+        <v>6.598531668251848</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.601070088212463</v>
+        <v>7.611652947289387</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.049315068493151</v>
+        <v>7.046575342465753</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001515476708871067</v>
+        <v>0.001515488672747297</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>122.4</v>
+        <v>124.5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25090</v>
+        <v>25490</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08650457987978862</v>
+        <v>-0.09412952623930322</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1708250298923875</v>
+        <v>0.1722244017261672</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.052255668710518</v>
+        <v>2.049772904085037</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.246596560320413</v>
+        <v>2.262765995203994</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.046575342465753</v>
+        <v>2.043835616438356</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004872687235057435</v>
+        <v>0.004878589223260189</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2114</v>
+        <v>2135</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04154980887874207</v>
+        <v>0.04165801913574779</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.839770719962157</v>
+        <v>2.802002483372365</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9863013698630138</v>
+        <v>0.9835616438356163</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9469555478338527</v>
+        <v>0.9442270167052201</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.958904109589041</v>
+        <v>0.9561643835616438</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01013888888888889</v>
+        <v>0.01016713091922006</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>217.6</v>
+        <v>224.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.157158185439306</v>
+        <v>0.1573239129388589</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.652582720588236</v>
+        <v>2.540320712694878</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.76591693403328</v>
+        <v>1.763170691767535</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.526080838604502</v>
+        <v>1.523489381024034</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.794520547945206</v>
+        <v>1.791780821917808</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005662780512082423</v>
+        <v>0.005671600626468697</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12350</v>
+        <v>12180</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0118781207265979</v>
+        <v>-0.01390761516789867</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4834008097165992</v>
+        <v>0.5172413793103448</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.226936119649737</v>
+        <v>4.225209749765038</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.27774772354797</v>
+        <v>4.284801114739823</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.383561643835616</v>
+        <v>4.380821917808219</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002365779779238453</v>
+        <v>0.002366746408401641</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.3</v>
+        <v>106.8</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1095</v>
+        <v>1078</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03189375920977589</v>
+        <v>0.0301231250407712</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5201365972602738</v>
+        <v>0.5513720445269017</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.752792625763767</v>
+        <v>2.750441524256714</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.667709346233333</v>
+        <v>2.670012406670178</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.873972602739726</v>
+        <v>2.871232876712329</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003632674654243336</v>
+        <v>0.003635779896357703</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>162.7</v>
+        <v>162</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221.8</v>
+        <v>220.3</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.247569593972543</v>
+        <v>-5.41964226838114</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.009715960324616746</v>
+        <v>-0.007262823422605535</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.04931506849315068</v>
+        <v>0.04657534246575343</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222.9</v>
+        <v>219.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.8</v>
+        <v>220.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1239365969909986</v>
+        <v>-0.1213083342226818</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.004959422903516586</v>
+        <v>-0.001815705855651384</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.344889709804218</v>
+        <v>4.339789041370107</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.959560797632789</v>
+        <v>4.938921365017151</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.624657534246575</v>
+        <v>4.621917808219179</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002301554393299112</v>
+        <v>0.002304259470834305</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>239</v>
+        <v>236.2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>270.9</v>
+        <v>254</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2025196665840748</v>
+        <v>-0.1998329972404735</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.003284422296050193</v>
+        <v>0.05057854330708667</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.274218567519429</v>
+        <v>3.270579353952547</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.105704467337332</v>
+        <v>4.087370939658021</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.378082191780822</v>
+        <v>3.375342465753425</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003054163854301294</v>
+        <v>0.003057562259700209</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>162.8</v>
+        <v>168.5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1531771443234592</v>
+        <v>-0.167245520878991</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.08334554334554345</v>
+        <v>0.1624367088607597</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.018048475669881</v>
+        <v>2.018652973035392</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.38308220207121</v>
+        <v>2.424067385582994</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.13972602739726</v>
+        <v>2.136986301369863</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004955282353502708</v>
+        <v>0.004953798465401055</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.6</v>
+        <v>109.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16900</v>
+        <v>17220</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02381022156188133</v>
+        <v>-0.02529756605123249</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.216744179881657</v>
+        <v>0.1974019837398375</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.875374339268816</v>
+        <v>1.872669223495276</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.921116549969794</v>
+        <v>1.921272747733497</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.873972602739726</v>
+        <v>1.871232876712329</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005332268758619609</v>
+        <v>0.005339971349203534</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83</v>
+        <v>79.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05384931200704636</v>
+        <v>0.05385239272431451</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8450602409638552</v>
+        <v>0.9311475409836065</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.123869884387786</v>
+        <v>3.121128460059767</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.964247211433297</v>
+        <v>2.961637209923997</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.378082191780822</v>
+        <v>3.375342465753425</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003201157657038521</v>
+        <v>0.003203969374528246</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>86.8</v>
+        <v>86.3</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1329991968605202</v>
+        <v>0.136645951328989</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.326483726866624</v>
+        <v>1.313082322910019</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.847439641437861</v>
+        <v>1.844543610100812</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.630574537525725</v>
+        <v>1.622795214238994</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.873972602739726</v>
+        <v>1.871232876712329</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005412896733241583</v>
+        <v>0.005421395268314345</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106.8</v>
+        <v>107.5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.1</v>
+        <v>160.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02717881627608077</v>
+        <v>0.02517707771774106</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4649248856956238</v>
+        <v>0.4082969432314409</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.311051928013379</v>
+        <v>3.309345265710671</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.223442574504426</v>
+        <v>3.22807184986809</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.53972602739726</v>
+        <v>3.536986301369863</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003020188211303581</v>
+        <v>0.003021745752434367</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>293.2</v>
+        <v>285.1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22660</v>
+        <v>22900</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.485061282457799</v>
+        <v>-0.4763200454450691</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.03885676857899378</v>
+        <v>-0.0004296891703057248</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.550551989125178</v>
+        <v>1.547580770001844</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.011138872069967</v>
+        <v>2.955203376682832</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.536986301369863</v>
+        <v>1.534246575342466</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.0064493161597516</v>
+        <v>0.00646169828020549</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>465.1</v>
+        <v>455.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04045586740043687</v>
+        <v>0.04046541012177205</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.439126845839604</v>
+        <v>0.4684903378674854</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.9013698630136987</v>
+        <v>0.8986301369863013</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8663220529148993</v>
+        <v>0.8636809337862843</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.873972602739726</v>
+        <v>0.8712328767123287</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01109422492401216</v>
+        <v>0.01112804878048781</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>207.9</v>
+        <v>200.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08564307863184731</v>
+        <v>0.08566464096354019</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.07311207311207313</v>
+        <v>0.112718204488778</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.957248638608328</v>
+        <v>1.954503112905446</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.802847249829933</v>
+        <v>1.800282554261693</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.13972602739726</v>
+        <v>2.136986301369863</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.00510921290363515</v>
+        <v>0.005116389906964437</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8900</v>
+        <v>8768</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02905763927560578</v>
+        <v>0.02753688138694008</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7815456516853934</v>
+        <v>0.8204221421076641</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.440048903105786</v>
+        <v>4.437542273837401</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.314674643717053</v>
+        <v>4.318620921759745</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.465753424657534</v>
+        <v>4.463013698630137</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002252227445739407</v>
+        <v>0.002253499658799288</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34.2</v>
+        <v>38.5</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1482748785717118</v>
+        <v>0.1483464392724631</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.4422426789473681</v>
+        <v>0.281161029090909</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.043218646442223</v>
+        <v>3.040433032154014</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.650252742816726</v>
+        <v>2.647661827627807</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.378082191780822</v>
+        <v>3.375342465753425</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003285994587240991</v>
+        <v>0.003289005182566194</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>39.9</v>
+        <v>40.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.147522409070545</v>
+        <v>0.1428555114798401</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8847117794486217</v>
+        <v>0.8722358722358721</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.069838634370297</v>
+        <v>3.069901620642297</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.675188397285213</v>
+        <v>2.686167752445975</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.378082191780822</v>
+        <v>3.375342465753425</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003257500211261513</v>
+        <v>0.003257433375961983</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>52.06739072267762</v>
+        <v>52.39130434782609</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4027397260273972</v>
+        <v>0.4</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007589212895958194</v>
+        <v>0.00749185667752443</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3753424657534247</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02482993197278912</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1243</v>
+        <v>1185</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06258021382815751</v>
+        <v>0.06281959615418203</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4760523121480289</v>
+        <v>0.5482979105485231</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3972602739726028</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3738637975775902</v>
+        <v>0.3712018007315447</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3753424657534247</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02517241379310345</v>
+        <v>0.02534722222222222</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>498.5</v>
+        <v>511.5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12400</v>
+        <v>12580</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.963110031971869</v>
+        <v>-1.989795918367347</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.05262777580645173</v>
+        <v>0.06462422734499196</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3753424657534247</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17230</v>
+        <v>17710</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.09861935286738067</v>
+        <v>-0.1070168886869794</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02207196749854901</v>
+        <v>0.02036702428006776</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.790144649389537</v>
+        <v>2.788988148662307</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.095412197128108</v>
+        <v>3.123226087178117</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.873972602739726</v>
+        <v>2.871232876712329</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003584043573578856</v>
+        <v>0.003585529757376825</v>
       </c>
     </row>
     <row r="30">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100.5</v>
+        <v>100.1</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>642.9</v>
+        <v>599.6</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05304762638264824</v>
+        <v>0.05456717375217992</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.5245438870741952</v>
+        <v>0.628132510006671</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.748123016280362</v>
+        <v>2.745045976999173</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.609685400194588</v>
+        <v>2.603007229242895</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.873972602739726</v>
+        <v>2.871232876712329</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003638847293501145</v>
+        <v>0.003642926232853773</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1146638767310588</v>
+        <v>0.1147176882525884</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.985606902158273</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.283004855405451</v>
+        <v>2.280251479708322</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.048155415335384</v>
+        <v>2.045586522703164</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.446575342465753</v>
+        <v>2.443835616438356</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004380192173627264</v>
+        <v>0.004385481201958982</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66120</v>
+        <v>66850</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2579248985043388</v>
+        <v>-0.2582986480859968</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1745009074410164</v>
+        <v>0.1616753926701571</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.744853393473756</v>
+        <v>1.742127255896484</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.351316450258179</v>
+        <v>2.348825779271972</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.747945205479452</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005731140528713084</v>
+        <v>0.005740108804424901</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>107.4</v>
+        <v>107.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02809369585923055</v>
+        <v>-0.02816320510477703</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03999068901303549</v>
+        <v>0.04290382819794591</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.765761474711391</v>
+        <v>2.763036535670795</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.845707927737448</v>
+        <v>2.843107556931601</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.873972602739726</v>
+        <v>2.871232876712329</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003615640788778977</v>
+        <v>0.003619206576134635</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1477</v>
+        <v>1388</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03060480191860513</v>
+        <v>0.03340550427181321</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2491536899119837</v>
+        <v>0.3227665706051874</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.776683869006128</v>
+        <v>1.773833583534935</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.723923530822483</v>
+        <v>1.716493260585895</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.794520547945206</v>
+        <v>1.791780821917808</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005628463326789798</v>
+        <v>0.005637507426188073</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>931.9</v>
+        <v>915.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0626992188781762</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7166004936151946</v>
+        <v>0.7465880554645703</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.149646393868711</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.9</v>
+        <v>110.6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9176</v>
+        <v>9294</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.008293409671644479</v>
+        <v>-0.006848432745651026</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1798391878814298</v>
+        <v>0.1617084131697868</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.852029506839873</v>
+        <v>1.851968405798095</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.867517595326924</v>
+        <v>1.864738945051476</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.871232876712329</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005399482007747839</v>
+        <v>0.005399660150082615</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.4</v>
+        <v>108.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02533143091360552</v>
+        <v>0.02637208313622604</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2697202072538862</v>
+        <v>0.2626086956521743</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.496515066320406</v>
+        <v>4.495449993781361</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.385425951795759</v>
+        <v>4.379941804384306</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.871232876712329</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002223944510917255</v>
+        <v>0.002224471413058356</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6112</v>
+        <v>6121</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05246166263115411</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.656413612565445</v>
+        <v>1.652507760169907</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.4</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>326.9</v>
+        <v>330.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25490</v>
+        <v>25670</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1331013494773597</v>
+        <v>-0.134679396519448</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02597096900745388</v>
+        <v>0.03124269575379812</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.598531668251848</v>
+        <v>6.602006535918385</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.611652947289387</v>
+        <v>7.629549682930628</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.046575342465753</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001515488672747297</v>
+        <v>0.001514691017888992</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25490</v>
+        <v>25670</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09412952623930322</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1722244017261672</v>
+        <v>0.1640046747175692</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.049772904085037</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2135</v>
+        <v>2124</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04165801913574779</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.802002483372365</v>
+        <v>2.82169270338983</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9835616438356163</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>224.5</v>
+        <v>222</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1573239129388589</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.540320712694878</v>
+        <v>2.580189189189189</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.763170691767535</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12180</v>
+        <v>12240</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01390761516789867</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5172413793103448</v>
+        <v>0.5098039215686274</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.225209749765038</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.0301231250407712</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5513720445269017</v>
+        <v>0.5586011780055917</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.750441524256714</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>162</v>
+        <v>162.7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.3</v>
+        <v>220.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.41964226838114</v>
+        <v>-5.458147762063842</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.007262823422605535</v>
+        <v>-0.002520435967302337</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219.9</v>
+        <v>220.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.3</v>
+        <v>220.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1213083342226818</v>
+        <v>-0.1220368603853333</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001815705855651384</v>
+        <v>0.002270663033605791</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.339789041370107</v>
+        <v>4.340444649990495</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.938921365017151</v>
+        <v>4.943766377134572</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.621917808219179</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002304259470834305</v>
+        <v>0.002303911420693246</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>254</v>
+        <v>256.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1998329972404735</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.05057854330708667</v>
+        <v>0.04033898635477584</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.270579353952547</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>168.5</v>
+        <v>164.5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.167245520878991</v>
+        <v>-0.1576154826628032</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1624367088607597</v>
+        <v>0.1220588235294118</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.018652973035392</v>
+        <v>2.016366915385983</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.424067385582994</v>
+        <v>2.393641946031701</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.136986301369863</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004953798465401055</v>
+        <v>0.004959414838487246</v>
       </c>
     </row>
     <row r="16">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>107.5</v>
+        <v>109.2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.3</v>
+        <v>159.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02517707771774106</v>
+        <v>0.02042100427229302</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4082969432314409</v>
+        <v>0.4341463414634148</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.309345265710671</v>
+        <v>3.31179086555617</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.22807184986809</v>
+        <v>3.245514206087862</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.536986301369863</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003021745752434367</v>
+        <v>0.003019514337092852</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>285.1</v>
+        <v>285.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22900</v>
+        <v>22670</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4763200454450691</v>
+        <v>-0.4764381929238076</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.0004296891703057248</v>
+        <v>0.01006567869430963</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.547580770001844</v>
+        <v>1.547583898162324</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.955203376682832</v>
+        <v>2.955876225587838</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.534246575342466</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00646169828020549</v>
+        <v>0.006461685219053058</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>455.8</v>
+        <v>456.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04046541012177205</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4684903378674854</v>
+        <v>0.4665598071866781</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8986301369863013</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>200.5</v>
+        <v>197.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.08566464096354019</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.112718204488778</v>
+        <v>0.130192502532928</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.954503112905446</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8768</v>
+        <v>8800</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02753688138694008</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8204221421076641</v>
+        <v>0.8138024252272726</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.437542273837401</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.1483464392724631</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.281161029090909</v>
+        <v>0.3153253232</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>3.040433032154014</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1428555114798401</v>
+        <v>0.1437972697023842</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8722358722358721</v>
+        <v>0.8811881188118813</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.069901620642297</v>
+        <v>3.0693369599936</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.686167752445975</v>
+        <v>2.683462394338676</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.375342465753425</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003257433375961983</v>
+        <v>0.003258032640385255</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.06281959615418203</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5482979105485231</v>
+        <v>0.5443880673400672</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3945205479452055</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12580</v>
+        <v>12550</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-1.989795918367347</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06462422734499196</v>
+        <v>0.06716914581673317</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>157</v>
+        <v>156.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17710</v>
+        <v>17750</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1070168886869794</v>
+        <v>-0.1053849162406542</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.02036702428006776</v>
+        <v>0.01288</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.788988148662307</v>
+        <v>2.788681128748863</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.123226087178117</v>
+        <v>3.117185457046269</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.871232876712329</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003585529757376825</v>
+        <v>0.003585924506358489</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>599.6</v>
+        <v>607.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05456717375217992</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.628132510006671</v>
+        <v>0.6080188650963596</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.745045976999173</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>27.8</v>
+        <v>28</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1147176882525884</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.985606902158273</v>
+        <v>1.964281138571429</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.280251479708322</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66850</v>
+        <v>66730</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2582986480859968</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1616753926701571</v>
+        <v>0.1637644237973925</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.742127255896484</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>107.1</v>
+        <v>108.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02816320510477703</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.04290382819794591</v>
+        <v>0.03134810710988001</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.763036535670795</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1388</v>
+        <v>1409</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03340550427181321</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3227665706051874</v>
+        <v>0.3030518097941803</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.773833583534935</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.0626992188781762</v>
+        <v>0.06272948279068044</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7465880554645703</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.149646393868711</v>
+        <v>3.144151853266563</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.963817360469684</v>
+        <v>2.958562742618338</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.375342465753425</v>
+        <v>3.36986301369863</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003174959582595238</v>
+        <v>0.003180507961029513</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006848432745651026</v>
+        <v>-0.006997310260553203</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1617084131697868</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.851968405798095</v>
+        <v>1.846495248687999</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.864738945051476</v>
+        <v>1.859506794661855</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.871232876712329</v>
+        <v>1.865753424657534</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005399660150082615</v>
+        <v>0.005415665167351694</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02637208313622604</v>
+        <v>0.02635201679206315</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.2626086956521743</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.495449993781361</v>
+        <v>4.489991095304364</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.379941804384306</v>
+        <v>4.374708698228268</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.871232876712329</v>
+        <v>4.865753424657535</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002224471413058356</v>
+        <v>0.002227175909203474</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05246166263115411</v>
+        <v>0.05301863337251882</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.652507760169907</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3800613496932516</v>
+        <v>0.3746567586194259</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3726027397260274</v>
+        <v>0.3671232876712329</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.025</v>
+        <v>0.02534722222222222</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.134679396519448</v>
+        <v>-0.1347919548500608</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.03124269575379812</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.602006535918385</v>
+        <v>6.596774109406176</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.629549682930628</v>
+        <v>7.624494647715585</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.046575342465753</v>
+        <v>7.041095890410959</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001514691017888992</v>
+        <v>0.001515892439873187</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09412952623930322</v>
+        <v>-0.09438407074527616</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1640046747175692</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.049772904085037</v>
+        <v>2.044302002397724</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.262765995203994</v>
+        <v>2.257360914665095</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.043835616438356</v>
+        <v>2.038356164383562</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004878589223260189</v>
+        <v>0.004891645162148834</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04165801913574779</v>
+        <v>0.04187625863255132</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.82169270338983</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9835616438356163</v>
+        <v>0.9780821917808219</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9442270167052201</v>
+        <v>0.9387700158025883</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9561643835616438</v>
+        <v>0.9506849315068493</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01016713091922006</v>
+        <v>0.01022408963585434</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1573239129388589</v>
+        <v>0.1576570344064356</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.580189189189189</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.763170691767535</v>
+        <v>1.757678141981979</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.523489381024034</v>
+        <v>1.518306449788206</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.791780821917808</v>
+        <v>1.786301369863014</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005671600626468697</v>
+        <v>0.005689323751118552</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01390761516789867</v>
+        <v>-0.01394749121969255</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.5098039215686274</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.225209749765038</v>
+        <v>4.219750166784847</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.284801114739823</v>
+        <v>4.279437584925822</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.380821917808219</v>
+        <v>4.375342465753425</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002366746408401641</v>
+        <v>0.002369808544286236</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0301231250407712</v>
+        <v>0.0300788224048309</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.5586011780055917</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.750441524256714</v>
+        <v>2.7449717914287</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.670012406670178</v>
+        <v>2.664817227307193</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.871232876712329</v>
+        <v>2.865753424657534</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003635779896357703</v>
+        <v>0.003643024686528822</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.458147762063842</v>
+        <v>-5.934237208062581</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>-0.002520435967302337</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.04657534246575343</v>
+        <v>0.0410958904109589</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1220368603853333</v>
+        <v>-0.1222086905571683</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>0.002270663033605791</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.340444649990495</v>
+        <v>4.33511969776586</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.943766377134572</v>
+        <v>4.938667825861171</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.621917808219179</v>
+        <v>4.616438356164384</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002303911420693246</v>
+        <v>0.002306741381363376</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1998329972404735</v>
+        <v>-0.2001548017335972</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>0.04033898635477584</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.270579353952547</v>
+        <v>3.265207838112248</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.087370939658021</v>
+        <v>4.082299731484682</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.375342465753425</v>
+        <v>3.36986301369863</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003057562259700209</v>
+        <v>0.003062592182732666</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1576154826628032</v>
+        <v>-0.1581032918134026</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1220588235294118</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.016366915385983</v>
+        <v>2.011003589482212</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.393641946031701</v>
+        <v>2.388658335312667</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.136986301369863</v>
+        <v>2.131506849315068</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004959414838487246</v>
+        <v>0.004972641546887928</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02529756605123249</v>
+        <v>-0.02543575685680888</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1974019837398375</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.872669223495276</v>
+        <v>1.867192987241607</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.921272747733497</v>
+        <v>1.915926015528217</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.871232876712329</v>
+        <v>1.865753424657534</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005339971349203534</v>
+        <v>0.005355632796571789</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05385239272431451</v>
+        <v>0.05385858881789529</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9311475409836065</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.121128460059767</v>
+        <v>3.115645592281309</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.961637209923997</v>
+        <v>2.956417137308814</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.375342465753425</v>
+        <v>3.36986301369863</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003203969374528246</v>
+        <v>0.003209607673213529</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.136645951328989</v>
+        <v>0.1368847359668179</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.313082322910019</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.844543610100812</v>
+        <v>1.839053925178417</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.622795214238994</v>
+        <v>1.617625663356688</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.871232876712329</v>
+        <v>1.865753424657534</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005421395268314345</v>
+        <v>0.005437578454383737</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02042100427229302</v>
+        <v>0.02038301592442061</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4341463414634148</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.31179086555617</v>
+        <v>3.306330896672431</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.245514206087862</v>
+        <v>3.240284133578061</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.536986301369863</v>
+        <v>3.531506849315068</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003019514337092852</v>
+        <v>0.003024500666301802</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4764381929238076</v>
+        <v>-0.4776587640916766</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>0.01006567869430963</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.547583898162324</v>
+        <v>1.54213676401901</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.955876225587838</v>
+        <v>2.952355008574647</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.534246575342466</v>
+        <v>1.528767123287671</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006461685219053058</v>
+        <v>0.006484509177991902</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04046541012177205</v>
+        <v>0.04048473896457302</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.4665598071866781</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8986301369863013</v>
+        <v>0.8931506849315068</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8636809337862843</v>
+        <v>0.8583986400610891</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8712328767123287</v>
+        <v>0.8657534246575342</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01112804878048781</v>
+        <v>0.01119631901840491</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08566464096354019</v>
+        <v>0.08570800696570717</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.130192502532928</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.954503112905446</v>
+        <v>1.949011996433627</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.800282554261693</v>
+        <v>1.795153009767927</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.136986301369863</v>
+        <v>2.131506849315068</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005116389906964437</v>
+        <v>0.005130804745326537</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02753688138694008</v>
+        <v>0.02756439960617934</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8138024252272726</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.437542273837401</v>
+        <v>4.432058610775495</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.318620921759745</v>
+        <v>4.313168705021417</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.463013698630137</v>
+        <v>4.457534246575342</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002253499658799288</v>
+        <v>0.002256287851358144</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1483464392724631</v>
+        <v>0.1484900056486501</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3153253232</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.040433032154014</v>
+        <v>3.034861510123362</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.647661827627807</v>
+        <v>2.642479686542258</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.375342465753425</v>
+        <v>3.36986301369863</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003289005182566194</v>
+        <v>0.003295043271873555</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1437972697023842</v>
+        <v>0.1439426679256112</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.8811881188118813</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.0693369599936</v>
+        <v>3.063770288668921</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.683462394338676</v>
+        <v>2.678255103662374</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.375342465753425</v>
+        <v>3.36986301369863</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003258032640385255</v>
+        <v>0.003263952273766771</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>52.39130434782609</v>
+        <v>53.05274638112235</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.4</v>
+        <v>0.3945205479452055</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.00749185667752443</v>
+        <v>0.0072988067093477</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3726027397260274</v>
+        <v>0.3671232876712329</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.025</v>
+        <v>0.02534722222222222</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06281959615418203</v>
+        <v>0.06330856478749174</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5443880673400672</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.389041095890411</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3712018007315447</v>
+        <v>0.3658778916806365</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3726027397260274</v>
+        <v>0.3671232876712329</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02534722222222222</v>
+        <v>0.02570422535211268</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-1.989795918367347</v>
+        <v>-2.01745951716416</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.06716914581673317</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3726027397260274</v>
+        <v>0.3671232876712329</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1053849162406542</v>
+        <v>-0.1056372095824775</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.01288</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.788681128748863</v>
+        <v>2.783249161113621</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.117185457046269</v>
+        <v>3.111991231001789</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.871232876712329</v>
+        <v>2.865753424657534</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003585924506358489</v>
+        <v>0.003592923026696915</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05456717375217992</v>
+        <v>0.05456400540096172</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6080188650963596</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.745045976999173</v>
+        <v>2.739567228523875</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.603007229242895</v>
+        <v>2.597819776223302</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.871232876712329</v>
+        <v>2.865753424657534</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003642926232853773</v>
+        <v>0.00365021157206212</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1147176882525884</v>
+        <v>0.1148257605490448</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.964281138571429</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.280251479708322</v>
+        <v>2.274744613449765</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.045586522703164</v>
+        <v>2.040448556130841</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.443835616438356</v>
+        <v>2.438356164383562</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004385481201958982</v>
+        <v>0.004396097891989068</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2582986480859968</v>
+        <v>-0.2590491024333958</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1637644237973925</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.742127255896484</v>
+        <v>1.736675089330907</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.348825779271972</v>
+        <v>2.343846393916808</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.745205479452055</v>
+        <v>1.73972602739726</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005740108804424901</v>
+        <v>0.005758129463268068</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02816320510477703</v>
+        <v>-0.02830260674087709</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>0.03134810710988001</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.763036535670795</v>
+        <v>2.757586737388442</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.843107556931601</v>
+        <v>2.837906900356452</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.871232876712329</v>
+        <v>2.865753424657534</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003619206576134635</v>
+        <v>0.003626359187334375</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03340550427181321</v>
+        <v>0.03337060703145556</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.3030518097941803</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.773833583534935</v>
+        <v>1.768355508913033</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.716493260585895</v>
+        <v>1.711250055769396</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.791780821917808</v>
+        <v>1.786301369863014</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005637507426188073</v>
+        <v>0.005654971497301903</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>915.9</v>
+        <v>934</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06272948279068044</v>
+        <v>0.06274466224884075</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7465880554645703</v>
+        <v>0.7127408993576014</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.144151853266563</v>
+        <v>3.141404559101325</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.958562742618338</v>
+        <v>2.955935391342166</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.36986301369863</v>
+        <v>3.367123287671233</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003180507961029513</v>
+        <v>0.003183289452811115</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9294</v>
+        <v>9007</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.006997310260553203</v>
+        <v>-0.007072060694868053</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1617084131697868</v>
+        <v>0.1987252128344619</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.846495248687999</v>
+        <v>1.843758683342752</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.859506794661855</v>
+        <v>1.856890727269741</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.865753424657534</v>
+        <v>1.863013698630137</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005415665167351694</v>
+        <v>0.005423703270034181</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02635201679206315</v>
+        <v>0.02634196997747748</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2626086956521743</v>
+        <v>0.2600000000000002</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.489991095304364</v>
+        <v>4.487261659798113</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.374708698228268</v>
+        <v>4.372092139909843</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.865753424657535</v>
+        <v>4.863013698630137</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002227175909203474</v>
+        <v>0.002228530618036192</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6121</v>
+        <v>6077</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05301863337251882</v>
+        <v>0.05330296969325873</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.652507760169907</v>
+        <v>1.671713016290933</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3746567586194259</v>
+        <v>0.3719545403274634</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3671232876712329</v>
+        <v>0.3643835616438356</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02534722222222222</v>
+        <v>0.02552447552447553</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>330.9</v>
+        <v>320.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25670</v>
+        <v>24830</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1347919548500608</v>
+        <v>-0.130856290446623</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03124269575379812</v>
+        <v>0.03391059202577518</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.596774109406176</v>
+        <v>6.585331372445058</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.624494647715585</v>
+        <v>7.576803812834396</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.041095890410959</v>
+        <v>7.038356164383561</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001515892439873187</v>
+        <v>0.001518526469577964</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>124.5</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25670</v>
+        <v>24830</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09438407074527616</v>
+        <v>-0.09977825517929413</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1640046747175692</v>
+        <v>0.2178815948449457</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.044302002397724</v>
+        <v>2.04174304898999</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.257360914665095</v>
+        <v>2.268044579834757</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.038356164383562</v>
+        <v>2.035616438356164</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004891645162148834</v>
+        <v>0.004897775949303123</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2124</v>
+        <v>2116</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04187625863255132</v>
+        <v>0.03977448664119997</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.82169270338983</v>
+        <v>2.844108511342155</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9780821917808219</v>
+        <v>0.9753424657534248</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9387700158025883</v>
+        <v>0.9380326967860974</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9506849315068493</v>
+        <v>0.947945205479452</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01022408963585434</v>
+        <v>0.01025280898876404</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>222</v>
+        <v>220.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1576570344064356</v>
+        <v>0.1578244338256496</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.580189189189189</v>
+        <v>2.609455040871935</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.757678141981979</v>
+        <v>1.754931834249641</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.518306449788206</v>
+        <v>1.515714976277575</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.786301369863014</v>
+        <v>1.783561643835616</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005689323751118552</v>
+        <v>0.005698227022177027</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>115.5</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12240</v>
+        <v>12400</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01394749121969255</v>
+        <v>-0.01093780073454823</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5098039215686274</v>
+        <v>0.4709677419354839</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.219750166784847</v>
+        <v>4.215506290360236</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.279437584925822</v>
+        <v>4.262124559497847</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.375342465753425</v>
+        <v>4.372602739726028</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002369808544286236</v>
+        <v>0.002372194301516616</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0300788224048309</v>
+        <v>0.03005661656477794</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5586011780055917</v>
+        <v>0.5732634656632172</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.7449717914287</v>
+        <v>2.742236936893935</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.664817227307193</v>
+        <v>2.662219622489539</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.865753424657534</v>
+        <v>2.863013698630137</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003643024686528822</v>
+        <v>0.003646657903793957</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>162.7</v>
+        <v>164.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.2</v>
+        <v>222.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-5.934237208062581</v>
+        <v>-6.309448640377404</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.002520435967302337</v>
+        <v>-0.002516853932584162</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.0410958904109589</v>
+        <v>0.03835616438356165</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220.7</v>
+        <v>221</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.2</v>
+        <v>222.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1222086905571683</v>
+        <v>-0.1225674578958862</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002270663033605791</v>
+        <v>-0.006741573033707815</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.33511969776586</v>
+        <v>4.332702392325989</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.938667825861171</v>
+        <v>4.937932187853459</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.616438356164384</v>
+        <v>4.613698630136986</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002306741381363376</v>
+        <v>0.002308028360708974</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>256.5</v>
+        <v>252.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2001548017335972</v>
+        <v>-0.2003160558723085</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04033898635477584</v>
+        <v>0.05681960396039609</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.265207838112248</v>
+        <v>3.26252217803291</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.082299731484682</v>
+        <v>4.079764514456675</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.36986301369863</v>
+        <v>3.367123287671233</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003062592182732666</v>
+        <v>0.003065113263392236</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.5</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1581032918134026</v>
+        <v>-0.1546358985918589</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1220588235294118</v>
+        <v>0.1174213836477989</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.011003589482212</v>
+        <v>2.007437675999361</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.388658335312667</v>
+        <v>2.374642680775691</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.131506849315068</v>
+        <v>2.128767123287671</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004972641546887928</v>
+        <v>0.004981474702581593</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.9</v>
+        <v>109.5</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17220</v>
+        <v>17130</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02543575685680888</v>
+        <v>-0.0236023162949325</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1974019837398375</v>
+        <v>0.199312014010508</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.867192987241607</v>
+        <v>1.864410597434331</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.915926015528217</v>
+        <v>1.909478718097306</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.865753424657534</v>
+        <v>1.863013698630137</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005355632796571789</v>
+        <v>0.00536362538046141</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05385858881789529</v>
+        <v>0.05386170425211224</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9311475409836065</v>
+        <v>0.9238693467336683</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.115645592281309</v>
+        <v>3.112904148798828</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.956417137308814</v>
+        <v>2.953807066182317</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.36986301369863</v>
+        <v>3.367123287671233</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003209607673213529</v>
+        <v>0.003212434280656758</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>86.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1368847359668179</v>
+        <v>0.1507838989002862</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.313082322910019</v>
+        <v>1.262156987874921</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.839053925178417</v>
+        <v>1.835718945131382</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.617625663356688</v>
+        <v>1.595189980399999</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.865753424657534</v>
+        <v>1.863013698630137</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005437578454383737</v>
+        <v>0.005447456990364231</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>109.2</v>
+        <v>110.6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>159.9</v>
+        <v>165.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02038301592442061</v>
+        <v>0.01651230163192359</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4341463414634148</v>
+        <v>0.4033836858006041</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.306330896672431</v>
+        <v>3.305572139372638</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.240284133578061</v>
+        <v>3.251876179034749</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.531506849315068</v>
+        <v>3.528767123287671</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003024500666301802</v>
+        <v>0.003025194906772748</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>285.2</v>
+        <v>283.8</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22670</v>
+        <v>22530</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4776587640916766</v>
+        <v>-0.4766080818976832</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01006567869430963</v>
+        <v>0.01135310625832231</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.54213676401901</v>
+        <v>1.539369218221697</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.952355008574647</v>
+        <v>2.941140596520959</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.528767123287671</v>
+        <v>1.526027397260274</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006484509177991902</v>
+        <v>0.006496167314266655</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>456.4</v>
+        <v>454.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04048473896457302</v>
+        <v>0.04049452657047594</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4665598071866781</v>
+        <v>0.4713956825675971</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8931506849315068</v>
+        <v>0.8904109589041096</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8583986400610891</v>
+        <v>0.8557574654803332</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8657534246575342</v>
+        <v>0.863013698630137</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01119631901840491</v>
+        <v>0.01123076923076923</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>197.4</v>
+        <v>194.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08570800696570717</v>
+        <v>0.0961735225592229</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.130192502532928</v>
+        <v>0.1268933539412673</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.949011996433627</v>
+        <v>1.943451367771093</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.795153009767927</v>
+        <v>1.772941352600581</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.131506849315068</v>
+        <v>2.128767123287671</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005130804745326537</v>
+        <v>0.005145485071473031</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8800</v>
+        <v>9008</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02756439960617934</v>
+        <v>0.02911646758703873</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8138024252272726</v>
+        <v>0.760186090142096</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.432058610775495</v>
+        <v>4.429080966383171</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.313168705021417</v>
+        <v>4.303770375735996</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.457534246575342</v>
+        <v>4.454794520547945</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002256287851358144</v>
+        <v>0.002257804740057867</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1484900056486501</v>
+        <v>0.1485620121617083</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.3153253232</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.034861510123362</v>
+        <v>3.032075601810523</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.642479686542258</v>
+        <v>2.639888460270294</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.36986301369863</v>
+        <v>3.367123287671233</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003295043271873555</v>
+        <v>0.003298070798112279</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>40.4</v>
+        <v>37.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1439426679256112</v>
+        <v>0.1440155876007502</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.8811881188118813</v>
+        <v>1.026666666666667</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.063770288668921</v>
+        <v>3.060986816549356</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.678255103662374</v>
+        <v>2.675651319549685</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.36986301369863</v>
+        <v>3.367123287671233</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003263952273766771</v>
+        <v>0.003266920310121747</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>53.05274638112235</v>
+        <v>53.39046506406792</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3945205479452055</v>
+        <v>0.3917808219178082</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.0072988067093477</v>
+        <v>0.007203115867024112</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3671232876712329</v>
+        <v>0.3643835616438356</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02534722222222222</v>
+        <v>0.02552447552447552</v>
       </c>
     </row>
     <row r="27">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1188</v>
+        <v>1199</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.06330856478749174</v>
+        <v>0.05302190841142748</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5443880673400672</v>
+        <v>0.5364271559633027</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.389041095890411</v>
+        <v>0.3863013698630138</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3658778916806365</v>
+        <v>0.3668502685245951</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3671232876712329</v>
+        <v>0.3643835616438356</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02570422535211268</v>
+        <v>0.02588652482269503</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12550</v>
+        <v>12480</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.01745951716416</v>
+        <v>-2.031581493064661</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06716914581673317</v>
+        <v>0.07315487019230771</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3671232876712329</v>
+        <v>0.3643835616438356</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>156.2</v>
+        <v>161</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17750</v>
+        <v>17680</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1056372095824775</v>
+        <v>-0.1154087131423084</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.01288</v>
+        <v>0.04813914027149302</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.783249161113621</v>
+        <v>2.782342633909491</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.111991231001789</v>
+        <v>3.145342572605623</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.865753424657534</v>
+        <v>2.863013698630137</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003592923026696915</v>
+        <v>0.003594093652638649</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05456400540096172</v>
+        <v>0.05456242941800649</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6080188650963596</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.739567228523875</v>
+        <v>2.736827852466523</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.597819776223302</v>
+        <v>2.595226016137259</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.865753424657534</v>
+        <v>2.863013698630137</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00365021157206212</v>
+        <v>0.003653865182272118</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1148257605490448</v>
+        <v>0.1148800224242407</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.964281138571429</v>
+        <v>1.371424910857143</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.274744613449765</v>
+        <v>2.271991122604226</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.040448556130841</v>
+        <v>2.037879482012707</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.438356164383562</v>
+        <v>2.435616438356164</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004396097891989068</v>
+        <v>0.00440142564841437</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66730</v>
+        <v>66150</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2590491024333958</v>
+        <v>-0.2594258148915651</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1637644237973925</v>
+        <v>0.1739682539682539</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.736675089330907</v>
+        <v>1.733949060628366</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.343846393916808</v>
+        <v>2.341357686366668</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.73972602739726</v>
+        <v>1.736986301369863</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005758129463268068</v>
+        <v>0.00576718210878473</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.3</v>
+        <v>108.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02830260674087709</v>
+        <v>-0.02837249986493383</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03134810710988001</v>
+        <v>0.02849907918968708</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.757586737388442</v>
+        <v>2.754861878296361</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.837906900356452</v>
+        <v>2.835306614843041</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.865753424657534</v>
+        <v>2.863013698630137</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003626359187334375</v>
+        <v>0.003629946052389428</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03337060703145556</v>
+        <v>0.03335309025598467</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3030518097941803</v>
+        <v>0.3021276595744682</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.768355508913033</v>
+        <v>1.76561647429374</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.711250055769396</v>
+        <v>1.708628435858606</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.786301369863014</v>
+        <v>1.783561643835616</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005654971497301903</v>
+        <v>0.005663744162786017</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>934</v>
+        <v>900</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06274466224884075</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7127408993576014</v>
+        <v>0.7774444444444442</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.141404559101325</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9007</v>
+        <v>8969</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.007072060694868053</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1987252128344619</v>
+        <v>0.2038039906344074</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.843758683342752</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.9</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.8</v>
+        <v>95.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02634196997747748</v>
+        <v>0.02823324844607059</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2600000000000002</v>
+        <v>0.2705882352941178</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.487261659798113</v>
+        <v>4.485321664587754</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.372092139909843</v>
+        <v>4.362163615469787</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.863013698630137</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002228530618036192</v>
+        <v>0.002229494504028865</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6077</v>
+        <v>6010</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05330296969325873</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.671713016290933</v>
+        <v>1.701497504159734</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3917808219178082</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>320.9</v>
+        <v>317</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24830</v>
+        <v>24790</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.130856290446623</v>
+        <v>-0.1292593484040188</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03391059202577518</v>
+        <v>0.02299314239612738</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.585331372445058</v>
+        <v>6.581761321574076</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.576803812834396</v>
+        <v>7.558807906246665</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.038356164383561</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001518526469577964</v>
+        <v>0.001519350142221266</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24830</v>
+        <v>24790</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09977825517929413</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2178815948449457</v>
+        <v>0.2198467123840258</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.04174304898999</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1578244338256496</v>
+        <v>0.1641333550466761</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.609455040871935</v>
+        <v>2.574831970935513</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.754931834249641</v>
+        <v>1.754683850373265</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.515714976277575</v>
+        <v>1.507287668346992</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.783561643835616</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005698227022177027</v>
+        <v>0.005699032334441756</v>
       </c>
     </row>
     <row r="10">
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03005661656477794</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5732634656632172</v>
+        <v>0.5673655707591378</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.742236936893935</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>222.5</v>
+        <v>221.6</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.309448640377404</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.002516853932584162</v>
+        <v>0.00153429602888111</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>222.5</v>
+        <v>221.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1225674578958862</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.006741573033707815</v>
+        <v>-0.002707581227436751</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.332702392325989</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>236.2</v>
+        <v>215</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.5</v>
+        <v>254</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.2003160558723085</v>
+        <v>-0.1771553570807602</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.05681960396039609</v>
+        <v>-0.04371555118110237</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.26252217803291</v>
+        <v>3.254618486781017</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.079764514456675</v>
+        <v>3.955325607072646</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.367123287671233</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003065113263392236</v>
+        <v>0.003072556749928164</v>
       </c>
     </row>
     <row r="15">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.5</v>
+        <v>109.4</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17130</v>
+        <v>17180</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0236023162949325</v>
+        <v>-0.02312493652040827</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.199312014010508</v>
+        <v>0.1947295087310827</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.864410597434331</v>
+        <v>1.864399489517963</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.909478718097306</v>
+        <v>1.908534222254628</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.863013698630137</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00536362538046141</v>
+        <v>0.005363657336435704</v>
       </c>
     </row>
     <row r="17">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>84.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1507838989002862</v>
+        <v>0.1377181796059199</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.262156987874921</v>
+        <v>1.310402042118699</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.835718945131382</v>
+        <v>1.836278484519565</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.595189980399999</v>
+        <v>1.614001180112645</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.863013698630137</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005447456990364231</v>
+        <v>0.005445797075064216</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>165.5</v>
+        <v>164</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01651230163192359</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4033836858006041</v>
+        <v>0.416219512195122</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.305572139372638</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22530</v>
+        <v>22490</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4766080818976832</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01135310625832231</v>
+        <v>0.01315186678523794</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.539369218221697</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>454.9</v>
+        <v>454.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04049452657047594</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4713956825675971</v>
+        <v>0.4733389742460925</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8904109589041096</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>194.1</v>
+        <v>197</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.0961735225592229</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1268933539412673</v>
+        <v>0.1103045685279185</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.943451367771093</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9008</v>
+        <v>9014</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02911646758703873</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.760186090142096</v>
+        <v>0.7590144552917684</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.429080966383171</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>76.3</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1485620121617083</v>
+        <v>0.1647319920153992</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3153253232</v>
+        <v>0.2584370719999998</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.032075601810523</v>
+        <v>3.02163618297718</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.639888460270294</v>
+        <v>2.594275939607942</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.367123287671233</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003298070798112279</v>
+        <v>0.003309465267968537</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1440155876007502</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.026666666666667</v>
+        <v>1.054054054054054</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.060986816549356</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1199</v>
+        <v>1209</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05302190841142748</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5364271559633027</v>
+        <v>0.5237189081885856</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3863013698630138</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12480</v>
+        <v>12530</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.031581493064661</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07315487019230771</v>
+        <v>0.0688725283320033</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17680</v>
+        <v>17560</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1154087131423084</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.04813914027149302</v>
+        <v>0.05530182232346226</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.782342633909491</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66150</v>
+        <v>66360</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2594258148915651</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1739682539682539</v>
+        <v>0.170253164556962</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.733949060628366</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>125.5</v>
+        <v>123</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.6</v>
+        <v>108.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02837249986493383</v>
+        <v>-0.021282355475427</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02849907918968708</v>
+        <v>0.007083716651334004</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.754861878296361</v>
+        <v>2.753350821626612</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.835306614843041</v>
+        <v>2.813222829924655</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.863013698630137</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003629946052389428</v>
+        <v>0.003631938190169405</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>922.6</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06274466224884075</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7774444444444442</v>
+        <v>0.7339041838283111</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.141404559101325</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>110.6</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8969</v>
+        <v>8902</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.007072060694868053</v>
+        <v>0.03183177269717103</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2038039906344074</v>
+        <v>0.1295210020220174</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.843758683342752</v>
+        <v>1.842116527539363</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.856890727269741</v>
+        <v>1.785287656653697</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.863013698630137</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005423703270034181</v>
+        <v>0.005428538233331885</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02823324844607059</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2705882352941178</v>
+        <v>0.2679245283018867</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.485321664587754</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6010</v>
+        <v>6004</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05330296969325873</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.701497504159734</v>
+        <v>1.704197201865423</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3917808219178082</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>317</v>
+        <v>318.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24790</v>
+        <v>24660</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1292593484040188</v>
+        <v>-0.1297121110858376</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02299314239612738</v>
+        <v>0.03195458231954573</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.581761321574076</v>
+        <v>6.582775775554456</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.558807906246665</v>
+        <v>7.563905989508403</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.038356164383561</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001519350142221266</v>
+        <v>0.001519115999231755</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24790</v>
+        <v>24660</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09977825517929413</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2198467123840258</v>
+        <v>0.2262773722627738</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.04174304898999</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2116</v>
+        <v>2110</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03977448664119997</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.844108511342155</v>
+        <v>2.855039625592417</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9753424657534248</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220.2</v>
+        <v>219</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1641333550466761</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.574831970935513</v>
+        <v>2.594420091324201</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.754683850373265</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>114.7</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01093780073454823</v>
+        <v>-0.01235781566952633</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4709677419354839</v>
+        <v>0.48</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.215506290360236</v>
+        <v>4.216217109346274</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.262124559497847</v>
+        <v>4.268972281904365</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.372602739726028</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002372194301516616</v>
+        <v>0.002371794369372621</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03005661656477794</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5673655707591378</v>
+        <v>0.5762290895381714</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.742236936893935</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221.6</v>
+        <v>220.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.309448640377404</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.00153429602888111</v>
+        <v>0.007901907356948401</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.6</v>
+        <v>220.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1225674578958862</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002707581227436751</v>
+        <v>0.003633060853769354</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.332702392325989</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>254</v>
+        <v>252.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1771553570807602</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.04371555118110237</v>
+        <v>-0.03879600316580922</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.254618486781017</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>163</v>
+        <v>164.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1546358985918589</v>
+        <v>-0.1576096879998791</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1174213836477989</v>
+        <v>0.117215980024969</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.007437675999361</v>
+        <v>2.008146357638096</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.374642680775691</v>
+        <v>2.3838668714863</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.128767123287671</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004981474702581593</v>
+        <v>0.004979716723317722</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17180</v>
+        <v>17040</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02312493652040827</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1947295087310827</v>
+        <v>0.2045453615023476</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.864399489517963</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>86.2</v>
+        <v>84.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1377181796059199</v>
+        <v>0.150046731106056</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.310402042118699</v>
+        <v>1.264837268666242</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.836278484519565</v>
+        <v>1.835750496768693</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.614001180112645</v>
+        <v>1.596239915401665</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.863013698630137</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005445797075064216</v>
+        <v>0.005447363363159703</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>164</v>
+        <v>162.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01651230163192359</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.416219512195122</v>
+        <v>0.4301724137931033</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.305572139372638</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22490</v>
+        <v>22280</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4766080818976832</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01315186678523794</v>
+        <v>0.02270132333931785</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.539369218221697</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>197</v>
+        <v>197.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.0961735225592229</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1103045685279185</v>
+        <v>0.1091784989858011</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.943451367771093</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9014</v>
+        <v>8865</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02911646758703873</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7590144552917684</v>
+        <v>0.7885793908629444</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.429080966383171</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37</v>
+        <v>36.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1440155876007502</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.054054054054054</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.060986816549356</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12530</v>
+        <v>12470</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.031581493064661</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0688725283320033</v>
+        <v>0.07401545950280664</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17560</v>
+        <v>17480</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1154087131423084</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.05530182232346226</v>
+        <v>0.06013157894736842</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.782342633909491</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66360</v>
+        <v>65820</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2594258148915651</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.170253164556962</v>
+        <v>0.1798541476754785</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.733949060628366</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>123</v>
+        <v>124.7</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.021282355475427</v>
+        <v>-0.02612506997572669</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.007083716651334004</v>
+        <v>0.02100275988960432</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.753350821626612</v>
+        <v>2.754383541426676</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.813222829924655</v>
+        <v>2.828272354601042</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.863013698630137</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003631938190169405</v>
+        <v>0.003630576442821882</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03335309025598467</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3021276595744682</v>
+        <v>0.3030518097941803</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.76561647429374</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>922.6</v>
+        <v>960</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06274466224884075</v>
+        <v>0.0627598734852331</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7339041838283111</v>
+        <v>0.6663541666666666</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.141404559101325</v>
+        <v>3.138657248970643</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.955935391342166</v>
+        <v>2.953308011787909</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.367123287671233</v>
+        <v>3.364383561643836</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003183289452811115</v>
+        <v>0.003186075830127552</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8902</v>
+        <v>8862</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.03183177269717103</v>
+        <v>-0.009082244817938782</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1295210020220174</v>
+        <v>0.2227450372376438</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.842116527539363</v>
+        <v>1.841103962025081</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.785287656653697</v>
+        <v>1.857978578340051</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.863013698630137</v>
+        <v>1.86027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005428538233331885</v>
+        <v>0.005431523806510484</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>108.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02823324844607059</v>
+        <v>0.0271704291679412</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2679245283018867</v>
+        <v>0.2791578947368423</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.485321664587754</v>
+        <v>4.483672837346839</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.362163615469787</v>
+        <v>4.365071958875253</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.863013698630137</v>
+        <v>4.86027397260274</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002229494504028865</v>
+        <v>0.002230314379029801</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6004</v>
+        <v>5894</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05330296969325873</v>
+        <v>0.05359131652360136</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.704197201865423</v>
+        <v>1.754665761791653</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3917808219178082</v>
+        <v>0.389041095890411</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3719545403274634</v>
+        <v>0.369252374985473</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3643835616438356</v>
+        <v>0.3616438356164384</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02552447552447553</v>
+        <v>0.02570422535211267</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>318.1</v>
+        <v>329.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24660</v>
+        <v>24420</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1297121110858376</v>
+        <v>-0.1345118216160013</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03195458231954573</v>
+        <v>0.08075348075348066</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.582775775554456</v>
+        <v>6.590679660290006</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.563905989508403</v>
+        <v>7.61498518974093</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.038356164383561</v>
+        <v>7.035616438356165</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001519115999231755</v>
+        <v>0.001517294196568488</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>124.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24660</v>
+        <v>24420</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09977825517929413</v>
+        <v>-0.09534838206485317</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2262773722627738</v>
+        <v>0.2255528255528256</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.04174304898999</v>
+        <v>2.038854926083943</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.268044579834757</v>
+        <v>2.253745956634221</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.035616438356164</v>
+        <v>2.032876712328767</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004897775949303123</v>
+        <v>0.004904713852891505</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2110</v>
+        <v>2141</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03977448664119997</v>
+        <v>0.03987894721058787</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.855039625592417</v>
+        <v>2.799221676786548</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9753424657534248</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9380326967860974</v>
+        <v>0.935303808520189</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.947945205479452</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01025280898876404</v>
+        <v>0.01028169014084507</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>219</v>
+        <v>220.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1641333550466761</v>
+        <v>0.1587770400416522</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.594420091324201</v>
+        <v>2.595330615942029</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.754683850373265</v>
+        <v>1.752154655983011</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.507287668346992</v>
+        <v>1.512072292975386</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.783561643835616</v>
+        <v>1.780821917808219</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005699032334441756</v>
+        <v>0.005707258754730015</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12400</v>
+        <v>12390</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01235781566952633</v>
+        <v>-0.01237688104725336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.48</v>
+        <v>0.4811945117029863</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.216217109346274</v>
+        <v>4.21348691304892</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.268972281904365</v>
+        <v>4.266290280362013</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.372602739726028</v>
+        <v>4.36986301369863</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002371794369372621</v>
+        <v>0.002373331211503373</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.8</v>
+        <v>106.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03005661656477794</v>
+        <v>0.03108651105522765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5762290895381714</v>
+        <v>0.5703214406779662</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.742236936893935</v>
+        <v>2.739271216180463</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.662219622489539</v>
+        <v>2.656684174228074</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.863013698630137</v>
+        <v>2.86027397260274</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003646657903793957</v>
+        <v>0.003650606022847064</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>164.4</v>
+        <v>163.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.2</v>
+        <v>217.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-6.309448640377404</v>
+        <v>-6.52701650736998</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.007901907356948401</v>
+        <v>0.01234482758620681</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.03835616438356165</v>
+        <v>0.03561643835616438</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221</v>
+        <v>218.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.2</v>
+        <v>217.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1225674578958862</v>
+        <v>-0.1207340585197642</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.003633060853769354</v>
+        <v>0.006436781609195474</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.332702392325989</v>
+        <v>4.328312701824918</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.937932187853459</v>
+        <v>4.922643420645004</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.613698630136986</v>
+        <v>4.610958904109589</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002308028360708974</v>
+        <v>0.002310369118151692</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.7</v>
+        <v>249.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1771553570807602</v>
+        <v>-0.1773032712519349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03879600316580922</v>
+        <v>-0.02802621048419363</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.254618486781017</v>
+        <v>3.251930122122199</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.955325607072646</v>
+        <v>3.952768995533517</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.367123287671233</v>
+        <v>3.364383561643836</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003072556749928164</v>
+        <v>0.003075096826949661</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.2</v>
+        <v>164.6</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1576096879998791</v>
+        <v>-0.1588393416947684</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.117215980024969</v>
+        <v>0.1213375000000001</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.008146357638096</v>
+        <v>2.005699293248466</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.3838668714863</v>
+        <v>2.384442583524465</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.128767123287671</v>
+        <v>2.126027397260274</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004979716723317722</v>
+        <v>0.004985792253934448</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.4</v>
+        <v>108.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17040</v>
+        <v>16870</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02312493652040827</v>
+        <v>-0.02079111018683608</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2045453615023476</v>
+        <v>0.2111229259039717</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.864399489517963</v>
+        <v>1.861605462464263</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.908534222254628</v>
+        <v>1.901132109635425</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.863013698630137</v>
+        <v>1.86027397260274</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005363657336435704</v>
+        <v>0.005371707486699518</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>79.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05386170425211224</v>
+        <v>0.05386483131672164</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9238693467336683</v>
+        <v>0.8952970297029701</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.112904148798828</v>
+        <v>3.110162698899392</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.953807066182317</v>
+        <v>2.951196971829383</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.367123287671233</v>
+        <v>3.364383561643836</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003212434280656758</v>
+        <v>0.003215265877742906</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.150046731106056</v>
+        <v>0.1494491281348289</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.264837268666242</v>
+        <v>1.267517549457562</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.835750496768693</v>
+        <v>1.83303635038356</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.596239915401665</v>
+        <v>1.594708548222543</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.863013698630137</v>
+        <v>1.86027397260274</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005447363363159703</v>
+        <v>0.005455429183336988</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110.6</v>
+        <v>110.5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>162.4</v>
+        <v>160.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01651230163192359</v>
+        <v>0.0167637430225932</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4301724137931033</v>
+        <v>0.4466957605985038</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.305572139372638</v>
+        <v>3.302703983295598</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.251876179034749</v>
+        <v>3.248251135979197</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.528767123287671</v>
+        <v>3.526027397260274</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003025194906772748</v>
+        <v>0.003027822066578766</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>283.8</v>
+        <v>281.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22280</v>
+        <v>22440</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4766080818976832</v>
+        <v>-0.4744575935276181</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02270132333931785</v>
+        <v>0.007180154634581104</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.539369218221697</v>
+        <v>1.536572556853341</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.941140596520959</v>
+        <v>2.923784147443658</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.526027397260274</v>
+        <v>1.523287671232877</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006496167314266655</v>
+        <v>0.006507990758652117</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>454.3</v>
+        <v>450.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04049452657047594</v>
+        <v>0.04050439730428182</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4733389742460925</v>
+        <v>0.4844486493679305</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8904109589041096</v>
+        <v>0.8876712328767125</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8557574654803332</v>
+        <v>0.853116272431403</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.863013698630137</v>
+        <v>0.8602739726027397</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01123076923076923</v>
+        <v>0.01126543209876543</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>197.2</v>
+        <v>201</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.0961735225592229</v>
+        <v>0.09620848941622284</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1091784989858011</v>
+        <v>0.0882089552238805</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.943451367771093</v>
+        <v>1.940702196987122</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.772941352600581</v>
+        <v>1.770376908885852</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.128767123287671</v>
+        <v>2.126027397260274</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005145485071473031</v>
+        <v>0.005152774091524542</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8865</v>
+        <v>8866</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02911646758703873</v>
+        <v>0.02836003089041632</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7885793908629444</v>
+        <v>0.7943389150688021</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.429080966383171</v>
+        <v>4.426457296472332</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.303770375735996</v>
+        <v>4.304384810288316</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.454794520547945</v>
+        <v>4.452054794520548</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002257804740057867</v>
+        <v>0.002259142996357269</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1647319920153992</v>
+        <v>0.1648170408110691</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2584370719999998</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.02163618297718</v>
+        <v>3.01884119003143</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.594275939607942</v>
+        <v>2.591687006853362</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.367123287671233</v>
+        <v>3.364383561643836</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003309465267968537</v>
+        <v>0.003312529335104205</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>76</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36.1</v>
+        <v>35.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1440155876007502</v>
+        <v>0.1459882778081318</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.105263157894737</v>
+        <v>1.135593220338983</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.060986816549356</v>
+        <v>3.057062579929016</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.675651319549685</v>
+        <v>2.667621160816836</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.367123287671233</v>
+        <v>3.364383561643836</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003266920310121747</v>
+        <v>0.003271113933242478</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>53.39046506406792</v>
+        <v>53.73298017457089</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3917808219178082</v>
+        <v>0.389041095890411</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007203115867024112</v>
+        <v>0.007107983059748693</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3643835616438356</v>
+        <v>0.3616438356164384</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02552447552447552</v>
+        <v>0.02570422535211268</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1209</v>
+        <v>1198</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05302190841142748</v>
+        <v>0.05320156835308347</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5237189081885856</v>
+        <v>0.5377096494156928</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3863013698630138</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3668502685245951</v>
+        <v>0.3641863583961434</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3643835616438356</v>
+        <v>0.3616438356164384</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02588652482269503</v>
+        <v>0.02607142857142857</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12470</v>
+        <v>12580</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.031581493064661</v>
+        <v>-2.045902369290619</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.07401545950280664</v>
+        <v>0.06462422734499196</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3643835616438356</v>
+        <v>0.3616438356164384</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>161</v>
+        <v>175.5</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17480</v>
+        <v>17440</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1154087131423084</v>
+        <v>-0.1424480130791624</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06013157894736842</v>
+        <v>0.158259747706422</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.782342633909491</v>
+        <v>2.784615054922972</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.145342572605623</v>
+        <v>3.247167632275599</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.863013698630137</v>
+        <v>2.86027397260274</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003594093652638649</v>
+        <v>0.003591160646180095</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>607.1</v>
+        <v>606.6</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05456242941800649</v>
+        <v>0.05456085891522029</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6080188650963596</v>
+        <v>0.6093443010220903</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.736827852466523</v>
+        <v>2.734088475191948</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.595226016137259</v>
+        <v>2.592632233671543</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.863013698630137</v>
+        <v>2.86027397260274</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003653865182272118</v>
+        <v>0.003657526115462648</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>35</v>
+        <v>30.7</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1148800224242407</v>
+        <v>0.1149344355221624</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.371424910857143</v>
+        <v>1.703578888599349</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.271991122604226</v>
+        <v>2.269237593090583</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.037879482012707</v>
+        <v>2.035310347220391</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.435616438356164</v>
+        <v>2.432876712328767</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.00440142564841437</v>
+        <v>0.004406766409320992</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65820</v>
+        <v>65860</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2594258148915651</v>
+        <v>-0.2598035227004473</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1798541476754785</v>
+        <v>0.1791375645308229</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.733949060628366</v>
+        <v>1.731223068504398</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.341357686366668</v>
+        <v>2.338869640153372</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.736986301369863</v>
+        <v>1.734246575342466</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.00576718210878473</v>
+        <v>0.005776263141317191</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.7</v>
+        <v>109.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02612506997572669</v>
+        <v>-0.02619329580887693</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.02100275988960432</v>
+        <v>0.01354337899543379</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.754383541426676</v>
+        <v>2.751658345115426</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.828272354601042</v>
+        <v>2.825672007876601</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.863013698630137</v>
+        <v>2.86027397260274</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003630576442821882</v>
+        <v>0.003634172104887725</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1409</v>
+        <v>1399</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03335309025598467</v>
+        <v>0.03333552775983969</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3030518097941803</v>
+        <v>0.3123659756969264</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.76561647429374</v>
+        <v>1.7628774414801</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.708628435858606</v>
+        <v>1.706006804296983</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.783561643835616</v>
+        <v>1.780821917808219</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005663744162786017</v>
+        <v>0.005672544083157628</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>960</v>
+        <v>948.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627598734852331</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6663541666666666</v>
+        <v>0.6872692753928908</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.138657248970643</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>111</v>
+        <v>108.6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8862</v>
+        <v>8870</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.009082244817938782</v>
+        <v>0.002694087903768772</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2227450372376438</v>
+        <v>0.195228337316798</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.841103962025081</v>
+        <v>1.840606190921416</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.857978578340051</v>
+        <v>1.835660759473895</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.86027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005431523806510484</v>
+        <v>0.005432992700624327</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.5</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0271704291679412</v>
+        <v>0.02612289587069846</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2791578947368423</v>
+        <v>0.2864067439409905</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.483672837346839</v>
+        <v>4.484746281909323</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.365071958875253</v>
+        <v>4.370574226495425</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.86027397260274</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002230314379029801</v>
+        <v>0.002229780543068454</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5894</v>
+        <v>5964</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05359131652360136</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.754665761791653</v>
+        <v>1.722334004024145</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.389041095890411</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24420</v>
+        <v>24290</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1345118216160013</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.08075348075348066</v>
+        <v>0.08653766982297251</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.590679660290006</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24420</v>
+        <v>24290</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09534838206485317</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2255528255528256</v>
+        <v>0.2321119802387814</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.038854926083943</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2141</v>
+        <v>2132</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03987894721058787</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.799221676786548</v>
+        <v>2.815259666979362</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9726027397260274</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12390</v>
+        <v>12340</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01237688104725336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4811945117029863</v>
+        <v>0.487196110210697</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.21348691304892</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03108651105522765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5703214406779662</v>
+        <v>0.5732843113207546</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.739271216180463</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217.5</v>
+        <v>216.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.52701650736998</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01234482758620681</v>
+        <v>0.01561346863468627</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.5</v>
+        <v>216.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1207340585197642</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.006436781609195474</v>
+        <v>0.009686346863468698</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.328312701824918</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.9</v>
+        <v>247.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1773032712519349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02802621048419363</v>
+        <v>-0.01740999190938508</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.251930122122199</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>79.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1588393416947684</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1213375000000001</v>
+        <v>0.1312358133669611</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.005699293248466</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16870</v>
+        <v>16810</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02079111018683608</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2111229259039717</v>
+        <v>0.215445791790601</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.861605462464263</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05386483131672164</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8952970297029701</v>
+        <v>0.9023602484472049</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.110162698899392</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.4</v>
+        <v>163</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0167637430225932</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4466957605985038</v>
+        <v>0.4236196319018406</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.302703983295598</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22440</v>
+        <v>22300</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4744575935276181</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007180154634581104</v>
+        <v>0.01350325874439462</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.536572556853341</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>450.9</v>
+        <v>443.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04050439730428182</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.4844486493679305</v>
+        <v>0.5085370655848545</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8876712328767125</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>201</v>
+        <v>195.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09620848941622284</v>
+        <v>0.09676751463649036</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.0882089552238805</v>
+        <v>0.1153649821337415</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.940702196987122</v>
+        <v>1.940551183219732</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.770376908885852</v>
+        <v>1.769336853364865</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.126027397260274</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005152774091524542</v>
+        <v>0.005153175080601667</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8866</v>
+        <v>8805</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02836003089041632</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7943389150688021</v>
+        <v>0.8067698831345826</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.426457296472332</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1459882778081318</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.135593220338983</v>
+        <v>1.129577464788732</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.057062579929016</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1198</v>
+        <v>1181</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05320156835308347</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5377096494156928</v>
+        <v>0.5598443353090601</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3835616438356164</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12580</v>
+        <v>12700</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.045902369290619</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.06462422734499196</v>
+        <v>0.05456478582677171</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65860</v>
+        <v>65510</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2598035227004473</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1791375645308229</v>
+        <v>0.1854373378110212</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.731223068504398</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1399</v>
+        <v>1414</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03333552775983969</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3123659756969264</v>
+        <v>0.2984441301272984</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.7628774414801</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>948.1</v>
+        <v>932.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627598734852331</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.6872692753928908</v>
+        <v>0.714944253859348</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.138657248970643</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108.6</v>
+        <v>108.3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8870</v>
+        <v>8800</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.002694087903768772</v>
+        <v>0.004194472539103104</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.195228337316798</v>
+        <v>0.2014078359090907</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.840606190921416</v>
+        <v>1.840542808727033</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.835660759473895</v>
+        <v>1.832854948975396</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.86027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005432992700624327</v>
+        <v>0.005433179794886845</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>109.3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02612289587069846</v>
+        <v>0.02549729856923299</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2864067439409905</v>
+        <v>0.2858823529411765</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.484746281909323</v>
+        <v>4.485386518091842</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.370574226495425</v>
+        <v>4.373864781847621</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.86027397260274</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002229780543068454</v>
+        <v>0.002229462268115562</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5964</v>
+        <v>5961</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05359131652360136</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.722334004024145</v>
+        <v>1.723704076497232</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.389041095890411</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>329.9</v>
+        <v>315.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24290</v>
+        <v>24510</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1345118216160013</v>
+        <v>-0.1286934620915947</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.08653766982297251</v>
+        <v>0.02978376172990616</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.590679660290006</v>
+        <v>6.577751138782523</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.61498518974093</v>
+        <v>7.5492962035756</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.035616438356165</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001517294196568488</v>
+        <v>0.00152027642715758</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24290</v>
+        <v>24510</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09534838206485317</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2321119802387814</v>
+        <v>0.2210526315789474</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.038854926083943</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2132</v>
+        <v>2162</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03987894721058787</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.815259666979362</v>
+        <v>2.762318968547641</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9726027397260274</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.3</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1587770400416522</v>
+        <v>0.1533153340947997</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.595330615942029</v>
+        <v>2.625543478260869</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.752154655983011</v>
+        <v>1.752369425954374</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.512072292975386</v>
+        <v>1.519419168504989</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.780821917808219</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005707258754730015</v>
+        <v>0.005706559274482782</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12340</v>
+        <v>12270</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01237688104725336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.487196110210697</v>
+        <v>0.4956805215973921</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.21348691304892</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03108651105522765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5732843113207546</v>
+        <v>0.5837429914529915</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.739271216180463</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>163.1</v>
+        <v>161.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>216.8</v>
+        <v>215.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-6.52701650736998</v>
+        <v>-6.415620896963624</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01561346863468627</v>
+        <v>0.01155988857938728</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218.9</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.8</v>
+        <v>215.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1207340585197642</v>
+        <v>-0.1180445233870089</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.009686346863468698</v>
+        <v>0.00278551532033422</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.328312701824918</v>
+        <v>4.325881875996314</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.922643420645004</v>
+        <v>4.904875575589338</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.610958904109589</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002310369118151692</v>
+        <v>0.002311667374804786</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.2</v>
+        <v>247.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1773032712519349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01740999190938508</v>
+        <v>-0.01978914447134783</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.251930122122199</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.6</v>
+        <v>164.5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.3</v>
+        <v>78.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1588393416947684</v>
+        <v>-0.1585934321311151</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1312358133669611</v>
+        <v>0.1420700636942676</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.005699293248466</v>
+        <v>2.005640783595283</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.384442583524465</v>
+        <v>2.383676168199127</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.126027397260274</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004985792253934448</v>
+        <v>0.004985937702201162</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16810</v>
+        <v>16800</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02079111018683608</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.215445791790601</v>
+        <v>0.2161692714285717</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.861605462464263</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>84.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1494491281348289</v>
+        <v>0.1576299960982047</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.267517549457562</v>
+        <v>1.238034460753031</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.83303635038356</v>
+        <v>1.832686298480819</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.594708548222543</v>
+        <v>1.583136498413045</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.86027397260274</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005455429183336988</v>
+        <v>0.005456471196565048</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>163</v>
+        <v>161.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0167637430225932</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4236196319018406</v>
+        <v>0.4341779975278122</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.302703983295598</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>281.5</v>
+        <v>277.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22300</v>
+        <v>22240</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4744575935276181</v>
+        <v>-0.4695617997043006</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01350325874439462</v>
+        <v>0.00179720998201427</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.536572556853341</v>
+        <v>1.536442962590333</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.923784147443658</v>
+        <v>2.896554135305157</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.523287671232877</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006507990758652117</v>
+        <v>0.006508539687760822</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>443.7</v>
+        <v>440.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04050439730428182</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5085370655848545</v>
+        <v>0.5191509214707215</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8876712328767125</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>195.9</v>
+        <v>198.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09676751463649036</v>
+        <v>0.09453668718870832</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1153649821337415</v>
+        <v>0.1076224129227663</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.940551183219732</v>
+        <v>1.94115361453731</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.769336853364865</v>
+        <v>1.773493421698927</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.126027397260274</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005153175080601667</v>
+        <v>0.005151575807864944</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8805</v>
+        <v>8786</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02836003089041632</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8067698831345826</v>
+        <v>0.8106770795583884</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.426457296472332</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1181</v>
+        <v>1150</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05320156835308347</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5598443353090601</v>
+        <v>0.6018923130434783</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3835616438356164</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.045902369290619</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.05456478582677171</v>
+        <v>0.04632599843749996</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17440</v>
+        <v>17680</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1424480130791624</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.158259747706422</v>
+        <v>0.1425367647058824</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.784615054922972</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65510</v>
+        <v>65860</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2598035227004473</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1854373378110212</v>
+        <v>0.1791375645308229</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.731223068504398</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.5</v>
+        <v>109.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02619329580887693</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01354337899543379</v>
+        <v>0.01632783882783895</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.751658345115426</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>932.8</v>
+        <v>930</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627598734852331</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.714944253859348</v>
+        <v>0.7201075268817203</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.138657248970643</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8800</v>
+        <v>8769</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.004194472539103104</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2014078359090907</v>
+        <v>0.205655029763941</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.840542808727033</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5961</v>
+        <v>5953</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05359131652360136</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.723704076497232</v>
+        <v>1.727364354107173</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.389041095890411</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24510</v>
+        <v>24350</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1286934620915947</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02978376172990616</v>
+        <v>0.03655030800821346</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.577751138782523</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24510</v>
+        <v>24350</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09534838206485317</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2210526315789474</v>
+        <v>0.229075975359343</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.038854926083943</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2162</v>
+        <v>2138</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03987894721058787</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.762318968547641</v>
+        <v>2.804552670720299</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9726027397260274</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12270</v>
+        <v>12260</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01237688104725336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4956805215973921</v>
+        <v>0.4969004893964111</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.21348691304892</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03108651105522765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5837429914529915</v>
+        <v>0.5882679714285715</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.739271216180463</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>215.4</v>
+        <v>215.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.415620896963624</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01155988857938728</v>
+        <v>0.009684893419833251</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>215.4</v>
+        <v>215.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1180445233870089</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.00278551532033422</v>
+        <v>0.000926784059314123</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.325881875996314</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.8</v>
+        <v>246.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1773032712519349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01978914447134783</v>
+        <v>-0.01301808208045507</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.251930122122199</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1585934321311151</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1420700636942676</v>
+        <v>0.1377220812182742</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.005640783595283</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16800</v>
+        <v>16760</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02079111018683608</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2161692714285717</v>
+        <v>0.2190718233890216</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.861605462464263</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161.8</v>
+        <v>161.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0167637430225932</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4341779975278122</v>
+        <v>0.4350649350649352</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.302703983295598</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22240</v>
+        <v>22090</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4695617997043006</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.00179720998201427</v>
+        <v>0.008599816659121684</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.536442962590333</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>440.6</v>
+        <v>437.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04050439730428182</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5191509214707215</v>
+        <v>0.531315250514756</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8876712328767125</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>198.1</v>
+        <v>197.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09453668718870832</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1076224129227663</v>
+        <v>0.1093023255813952</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.94115361453731</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8786</v>
+        <v>8802</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02836003089041632</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8106770795583884</v>
+        <v>0.8073856874573959</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.426457296472332</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1459882778081318</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.129577464788732</v>
+        <v>1.123595505617977</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.057062579929016</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12800</v>
+        <v>12950</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.045902369290619</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04632599843749996</v>
+        <v>0.03420639227799227</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17680</v>
+        <v>17980</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1424480130791624</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1425367647058824</v>
+        <v>0.1234733036707452</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.784615054922972</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65860</v>
+        <v>65740</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2598035227004473</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1791375645308229</v>
+        <v>0.1812899300273807</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.731223068504398</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8769</v>
+        <v>8839</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.004194472539103104</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.205655029763941</v>
+        <v>0.1961069075687294</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.840542808727033</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>315.5</v>
+        <v>319.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24350</v>
+        <v>24910</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1286934620915947</v>
+        <v>-0.130177076862389</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03655030800821346</v>
+        <v>0.0248093135287033</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.577751138782523</v>
+        <v>6.581075967906584</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.5492962035756</v>
+        <v>7.565995092618891</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.035616438356165</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152027642715758</v>
+        <v>0.001519508367441162</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24350</v>
+        <v>24910</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09534838206485317</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.229075975359343</v>
+        <v>0.2014452027298275</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.038854926083943</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2138</v>
+        <v>2128</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03987894721058787</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.804552670720299</v>
+        <v>2.822431207706767</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9726027397260274</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220.8</v>
+        <v>215.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1533153340947997</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.625543478260869</v>
+        <v>2.714709976798144</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.752369425954374</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12260</v>
+        <v>12220</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01237688104725336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4969004893964111</v>
+        <v>0.5018003273322422</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.21348691304892</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03108651105522765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5882679714285715</v>
+        <v>0.5943416539196942</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.739271216180463</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>215.8</v>
+        <v>216.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.415620896963624</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.009684893419833251</v>
+        <v>0.005491462851868967</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>215.8</v>
+        <v>216.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1180445233870089</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.000926784059314123</v>
+        <v>-0.00323027226580519</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.325881875996314</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>246.1</v>
+        <v>242.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1773032712519349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01301808208045507</v>
+        <v>0.0008086114544705314</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.251930122122199</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.5</v>
+        <v>161.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>78.8</v>
+        <v>80.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1585934321311151</v>
+        <v>-0.1518683034576522</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1377220812182742</v>
+        <v>0.0981444582814448</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.005640783595283</v>
+        <v>2.004037252501893</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.383676168199127</v>
+        <v>2.362884515072277</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.126027397260274</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004985937702201162</v>
+        <v>0.004989927201959811</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16760</v>
+        <v>16800</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02079111018683608</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2190718233890216</v>
+        <v>0.2161692714285717</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.861605462464263</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161.7</v>
+        <v>161</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0167637430225932</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4350649350649352</v>
+        <v>0.441304347826087</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.302703983295598</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22090</v>
+        <v>22140</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4695617997043006</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.008599816659121684</v>
+        <v>0.006322039295392878</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.536442962590333</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437.1</v>
+        <v>437.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04050439730428182</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.531315250514756</v>
+        <v>0.5299151908571427</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8876712328767125</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>197.8</v>
+        <v>195.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09453668718870832</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1093023255813952</v>
+        <v>0.1223529411764706</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.94115361453731</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8802</v>
+        <v>8738</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02836003089041632</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8073856874573959</v>
+        <v>0.8206235775921262</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.426457296472332</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.5</v>
+        <v>35.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.1648170408110691</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2584370719999998</v>
+        <v>0.3145234038997213</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>3.01884119003143</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.6</v>
+        <v>34.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1459882778081318</v>
+        <v>0.1464652989254285</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.123595505617977</v>
+        <v>1.194767441860465</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.057062579929016</v>
+        <v>3.056775846347075</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.667621160816836</v>
+        <v>2.666261115109339</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.364383561643836</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003271113933242478</v>
+        <v>0.003271420772298451</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05320156835308347</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6018923130434783</v>
+        <v>0.5839863800515908</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3835616438356164</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12950</v>
+        <v>12870</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.045902369290619</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03420639227799227</v>
+        <v>0.04063502564102572</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65740</v>
+        <v>65430</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2598035227004473</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1812899300273807</v>
+        <v>0.1868867491976158</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.731223068504398</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>930</v>
+        <v>928.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627598734852331</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7201075268817203</v>
+        <v>0.722144471956077</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.138657248970643</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108.3</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8839</v>
+        <v>8883</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.004194472539103104</v>
+        <v>0.0007035254860898776</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1961069075687294</v>
+        <v>0.1978750287065181</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.840542808727033</v>
+        <v>1.840690293146272</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.832854948975396</v>
+        <v>1.839396231018733</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.86027397260274</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005433179794886845</v>
+        <v>0.005432744463984274</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.2</v>
+        <v>94.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02549729856923299</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2858823529411765</v>
+        <v>0.2926715945089757</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.485386518091842</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5953</v>
+        <v>6008</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05359131652360136</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.727364354107173</v>
+        <v>1.702396804260986</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.389041095890411</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.1</v>
+        <v>321.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24910</v>
+        <v>24860</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.130177076862389</v>
+        <v>-0.1311957644403934</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0248093135287033</v>
+        <v>0.03491552695092515</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.581075967906584</v>
+        <v>6.583347671289775</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.565995092618891</v>
+        <v>7.577481096244157</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.035616438356165</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001519508367441162</v>
+        <v>0.001518984033550343</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>124.7</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24910</v>
+        <v>24860</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09534838206485317</v>
+        <v>-0.09640792327904545</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2014452027298275</v>
+        <v>0.2067578439259856</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.038854926083943</v>
+        <v>2.038890469327455</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.253745956634221</v>
+        <v>2.256428007565521</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.032876712328767</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004904713852891505</v>
+        <v>0.004904628350780699</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2128</v>
+        <v>2142</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03987894721058787</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.822431207706767</v>
+        <v>2.797447997198879</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9726027397260274</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215.5</v>
+        <v>220.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1533153340947997</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.714709976798144</v>
+        <v>2.625543478260869</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.752369425954374</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12220</v>
+        <v>12040</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01237688104725336</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5018003273322422</v>
+        <v>0.5242524916943521</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.21348691304892</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03108651105522765</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5943416539196942</v>
+        <v>0.6035397788461538</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.739271216180463</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>216.7</v>
+        <v>217.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.415620896963624</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.005491462851868967</v>
+        <v>0.0004132231404958553</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>216</v>
+        <v>217.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.7</v>
+        <v>217.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1180445233870089</v>
+        <v>-0.1191629296893166</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.00323027226580519</v>
+        <v>-0.002754820936639257</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.325881875996314</v>
+        <v>4.326894201883505</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.904875575589338</v>
+        <v>4.912252614842095</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.610958904109589</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002311667374804786</v>
+        <v>0.002311126534049985</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>242.7</v>
+        <v>243.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1773032712519349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.0008086114544705314</v>
+        <v>-0.002069638455217682</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.251930122122199</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161.8</v>
+        <v>164.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.3</v>
+        <v>79.2</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1518683034576522</v>
+        <v>-0.1576075565621539</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.0981444582814448</v>
+        <v>0.1292234848484848</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.004037252501893</v>
+        <v>2.005406124130165</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.362884515072277</v>
+        <v>2.380607921820857</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.126027397260274</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004989927201959811</v>
+        <v>0.004986521123913217</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16800</v>
+        <v>16780</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02079111018683608</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2161692714285717</v>
+        <v>0.2176188176400478</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.861605462464263</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>80.5</v>
+        <v>77.3</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05386483131672164</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9023602484472049</v>
+        <v>0.9811125485122896</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.110162698899392</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>83.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1576299960982047</v>
+        <v>0.1494491281348289</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.238034460753031</v>
+        <v>1.267517549457562</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.832686298480819</v>
+        <v>1.83303635038356</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.583136498413045</v>
+        <v>1.594708548222543</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.86027397260274</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005456471196565048</v>
+        <v>0.005455429183336988</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110.5</v>
+        <v>110.4</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0167637430225932</v>
+        <v>0.01703723235545353</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.441304347826087</v>
+        <v>0.4400000000000002</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.302703983295598</v>
+        <v>3.302564251679856</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.248251135979197</v>
+        <v>3.247240264774902</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.526027397260274</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003027822066578766</v>
+        <v>0.003027950173842486</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>277.5</v>
+        <v>276.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22140</v>
+        <v>22080</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4695617997043006</v>
+        <v>-0.4679455228714516</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006322039295392878</v>
+        <v>0.004329498007246357</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.536442962590333</v>
+        <v>1.536400186364259</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.896554135305157</v>
+        <v>2.887674575460913</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.523287671232877</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006508539687760822</v>
+        <v>0.00650872089755731</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437.5</v>
+        <v>441.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,16 +3126,16 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04050439730428182</v>
+        <v>0.04754863961251216</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5299151908571427</v>
+        <v>0.5082877805486283</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8876712328767125</v>
+        <v>0.8876712328767123</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.853116272431403</v>
+        <v>0.8473794908511948</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.8602739726027397</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>195.5</v>
+        <v>197.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09453668718870832</v>
+        <v>0.0928727467680432</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1223529411764706</v>
+        <v>0.115045592705167</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.94115361453731</v>
+        <v>1.941602612251988</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.773493421698927</v>
+        <v>1.776604474760576</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.126027397260274</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005151575807864944</v>
+        <v>0.005150384500359421</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8738</v>
+        <v>8708</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02836003089041632</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8206235775921262</v>
+        <v>0.8268958223472669</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.426457296472332</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1163</v>
+        <v>1204</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05320156835308347</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5839863800515908</v>
+        <v>0.5300466445182723</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3835616438356164</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12870</v>
+        <v>12890</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.045902369290619</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04063502564102572</v>
+        <v>0.03902038634600458</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17980</v>
+        <v>18160</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1424480130791624</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1234733036707452</v>
+        <v>0.1123375550660792</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.784615054922972</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100.1</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05456085891522029</v>
+        <v>0.05648232312802692</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6093443010220903</v>
+        <v>0.6013056181998022</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.734088475191948</v>
+        <v>2.733661586689639</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.592632233671543</v>
+        <v>2.587512849808816</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.86027397260274</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003657526115462648</v>
+        <v>0.003658097274618993</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65430</v>
+        <v>65420</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2598035227004473</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1868867491976158</v>
+        <v>0.1870681748700702</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.731223068504398</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.2</v>
+        <v>109.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02619329580887693</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01632783882783895</v>
+        <v>0.01725939505041252</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.751658345115426</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1414</v>
+        <v>1398</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03333552775983969</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.2984441301272984</v>
+        <v>0.3133047210300428</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.7628774414801</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>928.9</v>
+        <v>917.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.0627598734852331</v>
+        <v>0.06277511658294421</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.722144471956077</v>
+        <v>0.7429723251252995</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.138657248970643</v>
+        <v>3.135909922832332</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.953308011787909</v>
+        <v>2.95068060392209</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.364383561643836</v>
+        <v>3.361643835616438</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003186075830127552</v>
+        <v>0.003188867105904646</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>109.7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8883</v>
+        <v>8860</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.0007035254860898776</v>
+        <v>-0.002822367759337993</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1978750287065181</v>
+        <v>0.2086973819413094</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.840690293146272</v>
+        <v>1.838099574150847</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.839396231018733</v>
+        <v>1.843302050428698</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.86027397260274</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005432744463984274</v>
+        <v>0.005440401673897202</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.3</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02549729856923299</v>
+        <v>0.02403483591872434</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2926715945089757</v>
+        <v>0.2954784437434281</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.485386518091842</v>
+        <v>4.48414103775469</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.373864781847621</v>
+        <v>4.378895014574082</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.86027397260274</v>
+        <v>4.857534246575343</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002229462268115562</v>
+        <v>0.00223008150631391</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05359131652360136</v>
+        <v>0.05388375919295909</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.702396804260986</v>
+        <v>1.701048078522708</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.389041095890411</v>
+        <v>0.3863013698630138</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.369252374985473</v>
+        <v>0.3665502637205785</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3616438356164384</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02570422535211267</v>
+        <v>0.02588652482269503</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>321.6</v>
+        <v>325.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24860</v>
+        <v>25040</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1311957644403934</v>
+        <v>-0.1326620385692406</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03491552695092515</v>
+        <v>0.03865814696485614</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.583347671289775</v>
+        <v>6.583861808178956</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.577481096244157</v>
+        <v>7.590883947150459</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.035616438356165</v>
+        <v>7.032876712328767</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001518984033550343</v>
+        <v>0.001518865415367204</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24860</v>
+        <v>25040</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09640792327904545</v>
+        <v>-0.09653842416138732</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2067578439259856</v>
+        <v>0.1980830670926517</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.038890469327455</v>
+        <v>2.036155118912985</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.256428007565521</v>
+        <v>2.253726304876864</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.032876712328767</v>
+        <v>2.03013698630137</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004904628350780699</v>
+        <v>0.004911217179435017</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2142</v>
+        <v>2160</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03987894721058787</v>
+        <v>0.04220824241024504</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.797447997198879</v>
+        <v>2.757997824999999</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9726027397260274</v>
+        <v>0.9698630136986301</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.935303808520189</v>
+        <v>0.9305846703492702</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9452054794520548</v>
+        <v>0.9424657534246575</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01028169014084507</v>
+        <v>0.01031073446327684</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220.8</v>
+        <v>222.1</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1533153340947997</v>
+        <v>0.1534765397073027</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.625543478260869</v>
+        <v>2.604322377307519</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.752369425954374</v>
+        <v>1.749623359471448</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.519419168504989</v>
+        <v>1.516826133208933</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.780821917808219</v>
+        <v>1.778082191780822</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005706559274482782</v>
+        <v>0.005715515825658014</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12040</v>
+        <v>12120</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01237688104725336</v>
+        <v>-0.0123959702987876</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5242524916943521</v>
+        <v>0.5141914191419141</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.21348691304892</v>
+        <v>4.210756728317136</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.266290280362013</v>
+        <v>4.263608290046213</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.36986301369863</v>
+        <v>4.367123287671233</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002373331211503373</v>
+        <v>0.002374870040045411</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.5</v>
+        <v>105.9</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03108651105522765</v>
+        <v>0.03318354782504609</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6035397788461538</v>
+        <v>0.6099863902912623</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.739271216180463</v>
+        <v>2.736070963932248</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.656684174228074</v>
+        <v>2.64819447589148</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.86027397260274</v>
+        <v>2.857534246575343</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003650606022847064</v>
+        <v>0.003654875963314973</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>161.4</v>
+        <v>163.9</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217.8</v>
+        <v>220.3</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-6.415620896963624</v>
+        <v>-6.908423080683004</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.0004132231404958553</v>
+        <v>0.004380390376758969</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.03561643835616438</v>
+        <v>0.03287671232876712</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217.2</v>
+        <v>220</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.8</v>
+        <v>220.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1191629296893166</v>
+        <v>-0.1218284607036763</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002754820936639257</v>
+        <v>-0.001361779391738538</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.326894201883505</v>
+        <v>4.326558571207115</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.912252614842095</v>
+        <v>4.926780677353736</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.610958904109589</v>
+        <v>4.608219178082192</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002311126534049985</v>
+        <v>0.002311305818566554</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.4</v>
+        <v>252.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1773032712519349</v>
+        <v>-0.1774514052261183</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.002069638455217682</v>
+        <v>-0.03879600316580922</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.251930122122199</v>
+        <v>3.24924182236838</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.952768995533517</v>
+        <v>3.95021259900346</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.364383561643836</v>
+        <v>3.361643835616438</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003075096826949661</v>
+        <v>0.003077641045722777</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>164.1</v>
+        <v>179</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>79.2</v>
+        <v>80</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1576075565621539</v>
+        <v>-0.1923546737049981</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1292234848484848</v>
+        <v>0.2194375000000002</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.005406124130165</v>
+        <v>2.010850427356863</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.380607921820857</v>
+        <v>2.489769162141323</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.126027397260274</v>
+        <v>2.123287671232877</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004986521123913217</v>
+        <v>0.004973020302233207</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16780</v>
+        <v>16870</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02079111018683608</v>
+        <v>-0.02085447430594875</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2176188176400478</v>
+        <v>0.2111229259039717</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.861605462464263</v>
+        <v>1.858867210647074</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.901132109635425</v>
+        <v>1.898458566033324</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.86027397260274</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005371707486699518</v>
+        <v>0.005379620417597763</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>77.3</v>
+        <v>83.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05386483131672164</v>
+        <v>0.05386797004093438</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9811125485122896</v>
+        <v>0.8340119760479041</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.110162698899392</v>
+        <v>3.107421242566834</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.951196971829383</v>
+        <v>2.948586854239565</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.364383561643836</v>
+        <v>3.361643835616438</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003215265877742906</v>
+        <v>0.003218102477712247</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>84.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1494491281348289</v>
+        <v>0.1459181436284167</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.267517549457562</v>
+        <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.83303635038356</v>
+        <v>1.83044779187567</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.594708548222543</v>
+        <v>1.59736347840673</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.86027397260274</v>
+        <v>1.857534246575342</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005455429183336988</v>
+        <v>0.005463144070202049</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>161</v>
+        <v>162.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01703723235545353</v>
+        <v>0.01701585790202862</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4400000000000002</v>
+        <v>0.4302282541640965</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.302564251679856</v>
+        <v>3.29983544782521</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.247240264774902</v>
+        <v>3.244625363691321</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.526027397260274</v>
+        <v>3.523287671232877</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003027950173842486</v>
+        <v>0.003030454141763524</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>276.2</v>
+        <v>276.8</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22080</v>
+        <v>22050</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4679455228714516</v>
+        <v>-0.469302490249079</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004329498007246357</v>
+        <v>0.007880645079365145</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.536400186364259</v>
+        <v>1.533696373453977</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.887674575460913</v>
+        <v>2.889963388322298</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.523287671232877</v>
+        <v>1.52054794520548</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00650872089755731</v>
+        <v>0.006520195374446503</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>441.1</v>
+        <v>438.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04754863961251216</v>
+        <v>0.04757900525019422</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5082877805486283</v>
+        <v>0.5186161606939055</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8876712328767123</v>
+        <v>0.8849315068493151</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8473794908511948</v>
+        <v>0.8447396353060417</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8602739726027397</v>
+        <v>0.8575342465753425</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01126543209876543</v>
+        <v>0.01130030959752322</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.7</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>197.4</v>
+        <v>199.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.0928727467680432</v>
+        <v>0.09124541478576922</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.115045592705167</v>
+        <v>0.1073219658976929</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.941602612251988</v>
+        <v>1.93930171825577</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.776604474760576</v>
+        <v>1.77714535335435</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.126027397260274</v>
+        <v>2.123287671232877</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005150384500359421</v>
+        <v>0.005156495199207121</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8708</v>
+        <v>8598</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02836003089041632</v>
+        <v>0.02837432548832911</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8268958223472669</v>
+        <v>0.8502685300069783</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.426457296472332</v>
+        <v>4.423715379081166</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.304384810288316</v>
+        <v>4.301658714574132</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.452054794520548</v>
+        <v>4.449315068493151</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002259142996357269</v>
+        <v>0.002260543263539949</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35.9</v>
+        <v>37.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1648170408110691</v>
+        <v>0.1649022669467873</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3145234038997213</v>
+        <v>0.2720051266846359</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.01884119003143</v>
+        <v>3.016046078099338</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.591687006853362</v>
+        <v>2.589097955834874</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.364383561643836</v>
+        <v>3.361643835616438</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003312529335104205</v>
+        <v>0.003315599212032541</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34.4</v>
+        <v>37.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1464652989254285</v>
+        <v>0.1465404210257525</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.194767441860465</v>
+        <v>1.013333333333333</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.056775846347075</v>
+        <v>3.053990954238083</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.666261115109339</v>
+        <v>2.663657467484513</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.364383561643836</v>
+        <v>3.361643835616438</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003271420772298451</v>
+        <v>0.003274403935651088</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>53.73298017457089</v>
+        <v>54.08039369282863</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.389041095890411</v>
+        <v>0.3863013698630137</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007107983059748693</v>
+        <v>0.007013409744624057</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3616438356164384</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02570422535211268</v>
+        <v>0.02588652482269503</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1204</v>
+        <v>1184</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05320156835308347</v>
+        <v>0.05338384333138538</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5300466445182723</v>
+        <v>0.5558920270270271</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3641863583961434</v>
+        <v>0.3615224594710401</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3616438356164384</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02607142857142857</v>
+        <v>0.0262589928057554</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12890</v>
+        <v>12790</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.045902369290619</v>
+        <v>-2.060426377763913</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03902038634600458</v>
+        <v>0.04714407974980461</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3616438356164384</v>
+        <v>0.3589041095890411</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18160</v>
+        <v>18250</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1424480130791624</v>
+        <v>-0.1452120691617787</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1123375550660792</v>
+        <v>0.1163123287671233</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.784615054922972</v>
+        <v>2.782382622074527</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.247167632275599</v>
+        <v>3.255056045709571</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.86027397260274</v>
+        <v>2.857534246575343</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003591160646180095</v>
+        <v>0.003594041998632116</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>606.6</v>
+        <v>600.5</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648232312802692</v>
+        <v>0.05648239571552759</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6013056181998022</v>
+        <v>0.6175720033305578</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.733661586689639</v>
+        <v>2.730921844528055</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.587512849808816</v>
+        <v>2.584919403866142</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.86027397260274</v>
+        <v>2.857534246575343</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003658097274618993</v>
+        <v>0.00366176718679701</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1149344355221624</v>
+        <v>0.1149890003998215</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.703578888599349</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.269237593090583</v>
+        <v>2.266484024764988</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.035310347220391</v>
+        <v>2.032741151663608</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.432876712328767</v>
+        <v>2.43013698630137</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004406766409320992</v>
+        <v>0.004412120222659368</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65420</v>
+        <v>65370</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2598035227004473</v>
+        <v>-0.2601822297556118</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1870681748700702</v>
+        <v>0.1879761358421295</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.731223068504398</v>
+        <v>1.728497113103741</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.338869640153372</v>
+        <v>2.336382258745632</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.734246575342466</v>
+        <v>1.731506849315068</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005776263141317191</v>
+        <v>0.005785372694110956</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>124.7</v>
+        <v>121</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.1</v>
+        <v>108.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02619329580887693</v>
+        <v>-0.01558449395414333</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01725939505041252</v>
+        <v>-0.00563250230840262</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.751658345115426</v>
+        <v>2.746652786628786</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.825672007876601</v>
+        <v>2.790135638620101</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.86027397260274</v>
+        <v>2.857534246575343</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003634172104887725</v>
+        <v>0.003640795097466214</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03333552775983969</v>
+        <v>0.03331791932851421</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3133047210300428</v>
+        <v>0.310492505353319</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.7628774414801</v>
+        <v>1.760138410480588</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.706006804296983</v>
+        <v>1.703385161097745</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.780821917808219</v>
+        <v>1.778082191780822</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005672544083157628</v>
+        <v>0.005681371385600069</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8860</v>
+        <v>8767</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002822367759337993</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2086973819413094</v>
+        <v>0.2215191974449642</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.838099574150847</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>109.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02403483591872434</v>
+        <v>0.02507077287097663</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2954784437434281</v>
+        <v>0.2909473684210528</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.48414103775469</v>
+        <v>4.483082940097794</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.378895014574082</v>
+        <v>4.373437482313301</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.857534246575343</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00223008150631391</v>
+        <v>0.002230607850360641</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6011</v>
+        <v>5877</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05388375919295909</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.701048078522708</v>
+        <v>1.762633996937213</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3863013698630138</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>325.1</v>
+        <v>318.4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25040</v>
+        <v>24790</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1326620385692406</v>
+        <v>-0.129945074237845</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03865814696485614</v>
+        <v>0.02751109318273492</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.583861808178956</v>
+        <v>6.577817594525714</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.590883947150459</v>
+        <v>7.560232578148608</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.032876712328767</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001518865415367204</v>
+        <v>0.001520261067792811</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25040</v>
+        <v>24790</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09653842416138732</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1980830670926517</v>
+        <v>0.2101653892698669</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.036155118912985</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2160</v>
+        <v>2155</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04220824241024504</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.757997824999999</v>
+        <v>2.766717077494199</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9698630136986301</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12120</v>
+        <v>11960</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.0123959702987876</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5141914191419141</v>
+        <v>0.534448160535117</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.210756728317136</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.9</v>
+        <v>106.3</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03318354782504609</v>
+        <v>0.03176941446355087</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6099863902912623</v>
+        <v>0.622368005847953</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.736070963932248</v>
+        <v>2.736381572533258</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.64819447589148</v>
+        <v>2.652125110682786</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.857534246575343</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003654875963314973</v>
+        <v>0.003654461095768273</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.3</v>
+        <v>219</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.908423080683004</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.004380390376758969</v>
+        <v>0.01034246575342479</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220</v>
+        <v>219.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.3</v>
+        <v>219</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1218284607036763</v>
+        <v>-0.1214623315231932</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001361779391738538</v>
+        <v>0.002739726027397138</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.326558571207115</v>
+        <v>4.326229070579682</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.926780677353736</v>
+        <v>4.924352393540988</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.608219178082192</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002311305818566554</v>
+        <v>0.00231148185564295</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.7</v>
+        <v>249</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1774514052261183</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03879600316580922</v>
+        <v>-0.02451305220883526</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.24924182236838</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16870</v>
+        <v>16790</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02085447430594875</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2111229259039717</v>
+        <v>0.2168936128648007</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.858867210647074</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>162.1</v>
+        <v>160.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01701585790202862</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4302282541640965</v>
+        <v>0.4480949406620864</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.29983544782521</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22050</v>
+        <v>22040</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.469302490249079</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007880645079365145</v>
+        <v>0.008337941197822163</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.533696373453977</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>438.1</v>
+        <v>426</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04757900525019422</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5186161606939055</v>
+        <v>0.5617505633802817</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8849315068493151</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>199.4</v>
+        <v>188</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09124541478576922</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1073219658976929</v>
+        <v>0.1744680851063829</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.93930171825577</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8598</v>
+        <v>8538</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02837432548832911</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8502685300069783</v>
+        <v>0.8632711198172873</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.423715379081166</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.5</v>
+        <v>35.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1465404210257525</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.013333333333333</v>
+        <v>1.120786516853932</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.053990954238083</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1184</v>
+        <v>1166</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05338384333138538</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5558920270270271</v>
+        <v>0.5799109433962264</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3808219178082192</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12790</v>
+        <v>12740</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.060426377763913</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04714407974980461</v>
+        <v>0.0512537503924646</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18250</v>
+        <v>18350</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1452120691617787</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1163123287671233</v>
+        <v>0.1102288828337874</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.782382622074527</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1149890003998215</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.703578888599349</v>
+        <v>1.677415221935484</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.266484024764988</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65370</v>
+        <v>65070</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2601822297556118</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1879761358421295</v>
+        <v>0.193453204241586</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.728497113103741</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917.8</v>
+        <v>900.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06277511658294421</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7429723251252995</v>
+        <v>0.7764575235980009</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.135909922832332</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8767</v>
+        <v>8770</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002822367759337993</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2215191974449642</v>
+        <v>0.2211013459521094</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.838099574150847</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.5</v>
+        <v>109.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02507077287097663</v>
+        <v>0.02569522050242756</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2909473684210528</v>
+        <v>0.2942222222222224</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.483082940097794</v>
+        <v>4.482444306369152</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.373437482313301</v>
+        <v>4.370152279907737</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.857534246575343</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002230607850360641</v>
+        <v>0.002230925654958143</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5877</v>
+        <v>5904</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05388375919295909</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.762633996937213</v>
+        <v>1.75</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3863013698630138</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>318.4</v>
+        <v>322</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24790</v>
+        <v>25150</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.129945074237845</v>
+        <v>-0.1314132485439638</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02751109318273492</v>
+        <v>0.02425447316103391</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.577817594525714</v>
+        <v>6.581091761590961</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.560232578148608</v>
+        <v>7.576781191468663</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.032876712328767</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001520261067792811</v>
+        <v>0.001519504720837159</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24790</v>
+        <v>25150</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09653842416138732</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2101653892698669</v>
+        <v>0.1928429423459244</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.036155118912985</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2155</v>
+        <v>2194</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04220824241024504</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.766717077494199</v>
+        <v>2.699760848678213</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9698630136986301</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>222.1</v>
+        <v>221.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1534765397073027</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.604322377307519</v>
+        <v>2.615718157181572</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.749623359471448</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11960</v>
+        <v>11890</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.0123959702987876</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.534448160535117</v>
+        <v>0.5434819175777965</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.210756728317136</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>219</v>
+        <v>218.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-6.908423080683004</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01034246575342479</v>
+        <v>0.01265446224256306</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>219</v>
+        <v>218.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1214623315231932</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002739726027397138</v>
+        <v>0.005034324942791768</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.326229070579682</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249</v>
+        <v>252.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1774514052261183</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02451305220883526</v>
+        <v>-0.03650833002776666</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.24924182236838</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.9</v>
+        <v>108.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02085447430594875</v>
+        <v>-0.01794779633629569</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2168936128648007</v>
+        <v>0.2101889648600357</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.858867210647074</v>
+        <v>1.858799589346867</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.898458566033324</v>
+        <v>1.892770651511513</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.857534246575342</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005379620417597763</v>
+        <v>0.005379816122895603</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>83.5</v>
+        <v>79.8</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05386797004093438</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.8340119760479041</v>
+        <v>0.9190476190476189</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.107421242566834</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.1</v>
+        <v>160.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01701585790202862</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4480949406620864</v>
+        <v>0.4444859813084114</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.29983544782521</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22040</v>
+        <v>22070</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.469302490249079</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.008337941197822163</v>
+        <v>0.006967296057997174</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.533696373453977</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>426</v>
+        <v>420.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04757900525019422</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5617505633802817</v>
+        <v>0.5814255764202521</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8849315068493151</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>188</v>
+        <v>189.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09124541478576922</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1744680851063829</v>
+        <v>0.1645569620253164</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.93930171825577</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8538</v>
+        <v>8559</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02837432548832911</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8632711198172873</v>
+        <v>0.8586994766912022</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.423715379081166</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.1</v>
+        <v>35.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.1649022669467873</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2720051266846359</v>
+        <v>0.3444840512820511</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>3.016046078099338</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>35.6</v>
+        <v>36.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1465404210257525</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.120786516853932</v>
+        <v>1.079889807162535</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.053990954238083</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12740</v>
+        <v>12800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.060426377763913</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.0512537503924646</v>
+        <v>0.04632599843749996</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18350</v>
+        <v>18460</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1452120691617787</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1102288828337874</v>
+        <v>0.1036132177681475</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.782382622074527</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>31</v>
+        <v>32.6</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1149890003998215</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.677415221935484</v>
+        <v>1.546008339877301</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.266484024764988</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65070</v>
+        <v>64910</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2601822297556118</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.193453204241586</v>
+        <v>0.1963950084732706</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.728497113103741</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>121</v>
+        <v>124.9</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>108.3</v>
+        <v>109.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.01558449395414333</v>
+        <v>-0.02682627398939896</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.00563250230840262</v>
+        <v>0.01889092575618712</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.746652786628786</v>
+        <v>2.749053395296029</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.790135638620101</v>
+        <v>2.824833143169016</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.857534246575343</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003640795097466214</v>
+        <v>0.003637615776074499</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900.5</v>
+        <v>890</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06277511658294421</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7764575235980009</v>
+        <v>0.7974157303370784</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.135909922832332</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8770</v>
+        <v>8775</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002822367759337993</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2211013459521094</v>
+        <v>0.2204055617094018</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.838099574150847</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.2</v>
+        <v>109.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02569522050242756</v>
+        <v>0.02507077287097663</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2942222222222224</v>
+        <v>0.2977777777777779</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.482444306369152</v>
+        <v>4.483082940097794</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.370152279907737</v>
+        <v>4.373437482313301</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.857534246575343</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002230925654958143</v>
+        <v>0.002230607850360641</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5904</v>
+        <v>5870</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05388375919295909</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.75</v>
+        <v>1.765928449744464</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3863013698630138</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>322</v>
+        <v>327.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25150</v>
+        <v>25480</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1314132485439638</v>
+        <v>-0.1335397654696555</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02425447316103391</v>
+        <v>0.02762951334379915</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.581091761590961</v>
+        <v>6.585800609822259</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.576781191468663</v>
+        <v>7.60081114789073</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.032876712328767</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001519504720837159</v>
+        <v>0.001518418274778271</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25150</v>
+        <v>25480</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09653842416138732</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1928429423459244</v>
+        <v>0.1773940345368916</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.036155118912985</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2194</v>
+        <v>2177</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04220824241024504</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.699760848678213</v>
+        <v>2.728651953146532</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9698630136986301</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>221.4</v>
+        <v>228</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1534765397073027</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.615718157181572</v>
+        <v>2.511052631578947</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.749623359471448</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11890</v>
+        <v>11860</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.0123959702987876</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5434819175777965</v>
+        <v>0.5473861720067454</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.210756728317136</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1026</v>
+        <v>1012</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03176941446355087</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.622368005847953</v>
+        <v>0.6448118320158103</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.736381572533258</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>163.9</v>
+        <v>161.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218.5</v>
+        <v>218</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-6.908423080683004</v>
+        <v>-6.751141873084833</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01265446224256306</v>
+        <v>0.0007339449541283738</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.5</v>
+        <v>218</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1214623315231932</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.005034324942791768</v>
+        <v>0.007339449541284404</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.326229070579682</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.1</v>
+        <v>253.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1774514052261183</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03650833002776666</v>
+        <v>-0.042207216088328</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.24924182236838</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.3</v>
+        <v>109</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16790</v>
+        <v>16830</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01794779633629569</v>
+        <v>-0.02133652310705087</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2101889648600357</v>
+        <v>0.2151161972667857</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.858799589346867</v>
+        <v>1.858878425992704</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.892770651511513</v>
+        <v>1.899405127382758</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.857534246575342</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005379816122895603</v>
+        <v>0.005379587960229115</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>79.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05386797004093438</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9190476190476189</v>
+        <v>0.9409378960709756</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.107421242566834</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160.5</v>
+        <v>157.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01701585790202862</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4444859813084114</v>
+        <v>0.4710659898477161</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.29983544782521</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22070</v>
+        <v>22110</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.469302490249079</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006967296057997174</v>
+        <v>0.005145555133423851</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.533696373453977</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>420.7</v>
+        <v>425.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04757900525019422</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5814255764202521</v>
+        <v>0.5635857579318448</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8849315068493151</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8559</v>
+        <v>8523</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02837432548832911</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8586994766912022</v>
+        <v>0.8665503720520944</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.423715379081166</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.5</v>
+        <v>76.2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1465404210257525</v>
+        <v>0.1432163416198715</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.079889807162535</v>
+        <v>1.110803324099723</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.053990954238083</v>
+        <v>3.055986698148863</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.663657467484513</v>
+        <v>2.673148193297085</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.361643835616438</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003274403935651088</v>
+        <v>0.003272265552090725</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1166</v>
+        <v>1196</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05338384333138538</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5799109433962264</v>
+        <v>0.5402810702341136</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3808219178082192</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12800</v>
+        <v>12680</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.060426377763913</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04632599843749996</v>
+        <v>0.05622813722397479</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18460</v>
+        <v>18730</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1452120691617787</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1036132177681475</v>
+        <v>0.0877042178323546</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.782382622074527</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32.6</v>
+        <v>37</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1149890003998215</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.546008339877301</v>
+        <v>1.243239780540541</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.266484024764988</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64910</v>
+        <v>65480</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2601822297556118</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1963950084732706</v>
+        <v>0.1859804520464263</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.728497113103741</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.1</v>
+        <v>109.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.02682627398939896</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01889092575618712</v>
+        <v>0.01795787545787553</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.749053395296029</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>890</v>
+        <v>906.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06277511658294421</v>
+        <v>0.0627903916253561</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7974157303370784</v>
+        <v>0.7639210497298488</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.135909922832332</v>
+        <v>3.133162580644048</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.95068060392209</v>
+        <v>2.948053167711096</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.361643835616438</v>
+        <v>3.358904109589041</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003188867105904646</v>
+        <v>0.00319166329311402</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8775</v>
+        <v>8715</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.002822367759337993</v>
+        <v>-0.002892037708495751</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2204055617094018</v>
+        <v>0.2288076654044751</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.838099574150847</v>
+        <v>1.835362792898602</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.843302050428698</v>
+        <v>1.840686126586194</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.857534246575342</v>
+        <v>1.854794520547945</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005440401673897202</v>
+        <v>0.005448514069639022</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.5</v>
+        <v>109.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.5</v>
+        <v>95.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02507077287097663</v>
+        <v>0.02423046345139016</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2977777777777779</v>
+        <v>0.291584470094439</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.483082940097794</v>
+        <v>4.481201630626782</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.373437482313301</v>
+        <v>4.375188778828448</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.857534246575343</v>
+        <v>4.854794520547945</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002230607850360641</v>
+        <v>0.002231544309824173</v>
       </c>
     </row>
     <row r="5">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>98.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5870</v>
+        <v>5887</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05388375919295909</v>
+        <v>0.03817077716954133</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.765928449744464</v>
+        <v>1.774757941226431</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3863013698630138</v>
+        <v>0.3835616438356165</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3665502637205785</v>
+        <v>0.3694591027512402</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3589041095890411</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02588652482269503</v>
+        <v>0.02607142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>327.3</v>
+        <v>330.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25480</v>
+        <v>25350</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1335397654696555</v>
+        <v>-0.1347032120466064</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02762951334379915</v>
+        <v>0.04173570019723871</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.585800609822259</v>
+        <v>6.585620455563791</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.60081114789073</v>
+        <v>7.610822722617692</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.032876712328767</v>
+        <v>7.03013698630137</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001518418274778271</v>
+        <v>0.001518459812173295</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>126.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25480</v>
+        <v>25350</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09653842416138732</v>
+        <v>-0.1033084321245896</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1773940345368916</v>
+        <v>0.2014201183431952</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.036155118912985</v>
+        <v>2.033641738826322</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.253726304876864</v>
+        <v>2.267938956585442</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.03013698630137</v>
+        <v>2.027397260273973</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004911217179435017</v>
+        <v>0.004917286958208928</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2177</v>
+        <v>2163</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04220824241024504</v>
+        <v>0.04232015783918441</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.728651953146532</v>
+        <v>2.752785622746186</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9698630136986301</v>
+        <v>0.967123287671233</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9305846703492702</v>
+        <v>0.9278562641215338</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9424657534246575</v>
+        <v>0.9397260273972603</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01031073446327684</v>
+        <v>0.0103399433427762</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>228</v>
+        <v>225.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1534765397073027</v>
+        <v>0.1536382883243639</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.511052631578947</v>
+        <v>2.553129161118509</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.749623359471448</v>
+        <v>1.746877271716199</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.516826133208933</v>
+        <v>1.514233091425478</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.778082191780822</v>
+        <v>1.775342465753425</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005715515825658014</v>
+        <v>0.005724500605686867</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11860</v>
+        <v>11700</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0123959702987876</v>
+        <v>-0.01241508346996629</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5473861720067454</v>
+        <v>0.5685470085470086</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.210756728317136</v>
+        <v>4.208026555172458</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.263608290046213</v>
+        <v>4.260926310982684</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.367123287671233</v>
+        <v>4.364383561643836</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002374870040045411</v>
+        <v>0.00237641085884026</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03176941446355087</v>
+        <v>0.03139589691370251</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6448118320158103</v>
+        <v>0.6382649675516223</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.736381572533258</v>
+        <v>2.733723851127348</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.652125110682786</v>
+        <v>2.650508751593454</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.857534246575343</v>
+        <v>2.854794520547945</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003654461095768273</v>
+        <v>0.003658013956265607</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218</v>
+        <v>218.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-6.751141873084833</v>
+        <v>-7.107364821925811</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.0007339449541283738</v>
+        <v>-0.0001833180568285853</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.03287671232876712</v>
+        <v>0.03013698630136986</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219.6</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218</v>
+        <v>218.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1214623315231932</v>
+        <v>-0.1200745954236147</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.007339449541284404</v>
+        <v>-0.0009165902841429263</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.326229070579682</v>
+        <v>4.322238364121582</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.924352393540988</v>
+        <v>4.912050887089002</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.608219178082192</v>
+        <v>4.605479452054794</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00231148185564295</v>
+        <v>0.002313616038164133</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>215</v>
+        <v>204.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>253.6</v>
+        <v>260.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1774514052261183</v>
+        <v>-0.1647099800856918</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.042207216088328</v>
+        <v>-0.1133003265462927</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.24924182236838</v>
+        <v>3.242036966269263</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.95021259900346</v>
+        <v>3.881330901812835</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.361643835616438</v>
+        <v>3.358904109589041</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003077641045722777</v>
+        <v>0.003084480560845482</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>179</v>
+        <v>175.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1923546737049981</v>
+        <v>-0.1855855066042497</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2194375000000002</v>
+        <v>0.1684268292682927</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.010850427356863</v>
+        <v>2.006530452126356</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.489769162141323</v>
+        <v>2.463770559583249</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.123287671232877</v>
+        <v>2.120547945205479</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004973020302233207</v>
+        <v>0.004983727004692514</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16830</v>
+        <v>16720</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02133652310705087</v>
+        <v>-0.02140071741299814</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2151161972667857</v>
+        <v>0.2231103827751197</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.858878425992704</v>
+        <v>1.856140193529227</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.899405127382758</v>
+        <v>1.896731610738952</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.857534246575342</v>
+        <v>1.854794520547945</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005379587960229115</v>
+        <v>0.005387524086198577</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05386797004093438</v>
+        <v>0.05320567313479053</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9409378960709756</v>
+        <v>0.9622762148337598</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.107421242566834</v>
+        <v>3.105046503772815</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.948586854239565</v>
+        <v>2.948186268813829</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.361643835616438</v>
+        <v>3.358904109589041</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003218102477712247</v>
+        <v>0.003220563681687025</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1459181436284167</v>
+        <v>0.1460518943649718</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.83044779187567</v>
+        <v>1.827702338870817</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.59736347840673</v>
+        <v>1.594781482284926</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.857534246575342</v>
+        <v>1.854794520547945</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005463144070202049</v>
+        <v>0.005471350442205023</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.6</v>
+        <v>158.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01701585790202862</v>
+        <v>0.01699445257158434</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4710659898477161</v>
+        <v>0.4664136622390895</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.29983544782521</v>
+        <v>3.297106659493218</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.244625363691321</v>
+        <v>3.242010466385647</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.523287671232877</v>
+        <v>3.520547945205479</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003030454141763524</v>
+        <v>0.003032962240153023</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22110</v>
+        <v>22180</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.469302490249079</v>
+        <v>-0.4699133997490303</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.005145555133423851</v>
+        <v>0.001973319386834982</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.533696373453977</v>
+        <v>1.530972816439928</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.889963388322298</v>
+        <v>2.888156040381116</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.52054794520548</v>
+        <v>1.517808219178082</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006520195374446503</v>
+        <v>0.006531794616219025</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>425.5</v>
+        <v>423.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04757900525019422</v>
+        <v>0.04760958274845391</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5635857579318448</v>
+        <v>0.5713409069437885</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8849315068493151</v>
+        <v>0.8821917808219178</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8447396353060417</v>
+        <v>0.8420997624968697</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8575342465753425</v>
+        <v>0.8547945205479452</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01130030959752322</v>
+        <v>0.01133540372670807</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>189.6</v>
+        <v>187</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09124541478576922</v>
+        <v>0.09127432530148286</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1645569620253164</v>
+        <v>0.1807486631016042</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.93930171825577</v>
+        <v>1.936554198599898</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.77714535335435</v>
+        <v>1.774580555686484</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.123287671232877</v>
+        <v>2.120547945205479</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005156495199207121</v>
+        <v>0.005163811065670076</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8523</v>
+        <v>8640</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02837432548832911</v>
+        <v>0.02838863806266149</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8665503720520944</v>
+        <v>0.8412741690972223</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.423715379081166</v>
+        <v>4.42097345886548</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.301658714574132</v>
+        <v>4.298932616752717</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.449315068493151</v>
+        <v>4.446575342465754</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002260543263539949</v>
+        <v>0.00226194526907796</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35.1</v>
+        <v>39</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1649022669467873</v>
+        <v>0.1649876709311094</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.3444840512820511</v>
+        <v>0.210035646153846</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.016046078099338</v>
+        <v>3.013250846827317</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.589097955834874</v>
+        <v>2.586508786328181</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.361643835616438</v>
+        <v>3.358904109589041</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003315599212032541</v>
+        <v>0.003318674915674247</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>76.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1432163416198715</v>
+        <v>0.1461379076659537</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.110803324099723</v>
+        <v>1.016</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.055986698148863</v>
+        <v>3.051493199304135</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.673148193297085</v>
+        <v>2.662413640535048</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.361643835616438</v>
+        <v>3.358904109589041</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003272265552090725</v>
+        <v>0.003277084150893867</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>54.08039369282863</v>
+        <v>54.43281051292921</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3863013698630137</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.007013409744624057</v>
+        <v>0.006919397380115773</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3589041095890411</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02588652482269503</v>
+        <v>0.02607142857142857</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1196</v>
+        <v>1100</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05338384333138538</v>
+        <v>0.0535687901881742</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5402810702341136</v>
+        <v>0.6747056</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3808219178082192</v>
+        <v>0.3780821917808219</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3615224594710401</v>
+        <v>0.3588585722184253</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3589041095890411</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.0262589928057554</v>
+        <v>0.02644927536231885</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12680</v>
+        <v>12870</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.060426377763913</v>
+        <v>-2.075157871318475</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.05622813722397479</v>
+        <v>0.04063502564102572</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3589041095890411</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>177</v>
+        <v>176.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18730</v>
+        <v>19070</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1452120691617787</v>
+        <v>-0.1451947715673795</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.0877042178323546</v>
+        <v>0.06770791819611954</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.782382622074527</v>
+        <v>2.77963972432668</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.255056045709571</v>
+        <v>3.251781378810066</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.857534246575343</v>
+        <v>2.854794520547945</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003594041998632116</v>
+        <v>0.003597588533680323</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>600.5</v>
+        <v>594</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648239571552759</v>
+        <v>0.05648247720084134</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6175720033305578</v>
+        <v>0.6352727070707072</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.730921844528055</v>
+        <v>2.728182100388734</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.584919403866142</v>
+        <v>2.582325934659204</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.857534246575343</v>
+        <v>2.854794520547945</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.00366176718679701</v>
+        <v>0.003665444472557429</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>37</v>
+        <v>33.7</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1149890003998215</v>
+        <v>0.1150437176170122</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.243239780540541</v>
+        <v>1.46290421008902</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.266484024764988</v>
+        <v>2.263730417482869</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.032741151663608</v>
+        <v>2.030171895251554</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.43013698630137</v>
+        <v>2.427397260273973</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004412120222659368</v>
+        <v>0.004417487136617352</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65480</v>
+        <v>65290</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2601822297556118</v>
+        <v>-0.2605619399725927</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1859804520464263</v>
+        <v>0.1894317659672231</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.728497113103741</v>
+        <v>1.725771194571882</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.336382258745632</v>
+        <v>2.333895545636258</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.731506849315068</v>
+        <v>1.728767123287671</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005785372694110956</v>
+        <v>0.005794510901244203</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>124.9</v>
+        <v>128.9</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>109.2</v>
+        <v>114.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.02682627398939896</v>
+        <v>-0.03794023690747838</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01795787545787553</v>
+        <v>0.001930131004366897</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.749053395296029</v>
+        <v>2.748672420641323</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.824833143169016</v>
+        <v>2.857070346446848</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.857534246575343</v>
+        <v>2.854794520547945</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003637615776074499</v>
+        <v>0.003638119961078079</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1401</v>
+        <v>1351</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03331791932851421</v>
+        <v>0.03330026474617065</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.310492505353319</v>
+        <v>0.3589933382679498</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.760138410480588</v>
+        <v>1.757399381303729</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.703385161097745</v>
+        <v>1.700763506274173</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.778082191780822</v>
+        <v>1.775342465753425</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005681371385600069</v>
+        <v>0.00569022619808907</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>906.9</v>
+        <v>873</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627903916253561</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7639210497298488</v>
+        <v>0.8324169530355094</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.133162580644048</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8715</v>
+        <v>8759</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002892037708495751</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2288076654044751</v>
+        <v>0.2226348674506222</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.835362792898602</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.3</v>
+        <v>94.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02423046345139016</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.291584470094439</v>
+        <v>0.3025185185185189</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.481201630626782</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5887</v>
+        <v>5960</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03817077716954133</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.774757941226431</v>
+        <v>1.740771812080537</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3835616438356165</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25350</v>
+        <v>25730</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1347032120466064</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04173570019723871</v>
+        <v>0.02635056354450049</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.585620455563791</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25350</v>
+        <v>25730</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1033084321245896</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2014201183431952</v>
+        <v>0.1836766420520792</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.033641738826322</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2163</v>
+        <v>2183</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04232015783918441</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.752785622746186</v>
+        <v>2.718403711406321</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.967123287671233</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11700</v>
+        <v>11720</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01241508346996629</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5685470085470086</v>
+        <v>0.5658703071672355</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.208026555172458</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1017</v>
+        <v>1032</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03139589691370251</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6382649675516223</v>
+        <v>0.614452976744186</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.733723851127348</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218.2</v>
+        <v>216</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-7.107364821925811</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.0001833180568285853</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.2</v>
+        <v>216</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1200745954236147</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.0009165902841429263</v>
+        <v>0.0092592592592593</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.322238364121582</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>260.3</v>
+        <v>258.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1647099800856918</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.1133003265462927</v>
+        <v>-0.1081610316846986</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.242036966269263</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>175.8</v>
+        <v>173.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>82</v>
+        <v>80.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1855855066042497</v>
+        <v>-0.1810835367337496</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1684268292682927</v>
+        <v>0.176658385093168</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.006530452126356</v>
+        <v>2.005475667190799</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.463770559583249</v>
+        <v>2.448938026220592</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.120547945205479</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004983727004692514</v>
+        <v>0.0049863482083568</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16720</v>
+        <v>16780</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02140071741299814</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2231103827751197</v>
+        <v>0.2187369249106079</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.856140193529227</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05320567313479053</v>
+        <v>0.05254202546853467</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9622762148337598</v>
+        <v>0.9662404092071613</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.105046503772815</v>
+        <v>3.105411990345909</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.948186268813829</v>
+        <v>2.950392397836606</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.358904109589041</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003220563681687025</v>
+        <v>0.003220184642516985</v>
       </c>
     </row>
     <row r="18">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158.1</v>
+        <v>158.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01699445257158434</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4664136622390895</v>
+        <v>0.4654867256637172</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.297106659493218</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22180</v>
+        <v>22130</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4699133997490303</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.001973319386834982</v>
+        <v>0.004237154270221311</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.530972816439928</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>423.4</v>
+        <v>421.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04760958274845391</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5713409069437885</v>
+        <v>0.5787986236355009</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8821917808219178</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09127432530148286</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1807486631016042</v>
+        <v>0.1682539682539681</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.936554198599898</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8640</v>
+        <v>8740</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02838863806266149</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8412741690972223</v>
+        <v>0.8202069589244851</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.42097345886548</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1461379076659537</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.016</v>
+        <v>1.071232876712329</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.051493199304135</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1100</v>
+        <v>1166</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0535687901881742</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.6747056</v>
+        <v>0.5799109433962264</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3780821917808219</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12870</v>
+        <v>12860</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.075157871318475</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04063502564102572</v>
+        <v>0.04144422861586317</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19070</v>
+        <v>19480</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1451947715673795</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06770791819611954</v>
+        <v>0.04523562628336752</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.77963972432668</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1150437176170122</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.46290421008902</v>
+        <v>1.371424910857143</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.263730417482869</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65290</v>
+        <v>65730</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2605619399725927</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1894317659672231</v>
+        <v>0.1814696485623004</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.725771194571882</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>128.9</v>
+        <v>129</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>114.5</v>
+        <v>115</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.03794023690747838</v>
+        <v>-0.03821026907490702</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.001930131004366897</v>
+        <v>-0.001652173913043509</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.748672420641323</v>
+        <v>2.748729548972602</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.857070346446848</v>
+        <v>2.857931895705259</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.854794520547945</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003638119961078079</v>
+        <v>0.003638044348065353</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>873</v>
+        <v>903.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627903916253561</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8324169530355094</v>
+        <v>0.769775417634694</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.133162580644048</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8759</v>
+        <v>8699</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002892037708495751</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2226348674506222</v>
+        <v>0.2310678013564778</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.835362792898602</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.9</v>
+        <v>109.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.5</v>
+        <v>93.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02423046345139016</v>
+        <v>0.02485232541406409</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3025185185185189</v>
+        <v>0.3100533617929564</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.481201630626782</v>
+        <v>4.480566477154809</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.375188778828448</v>
+        <v>4.371914241736785</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.854794520547945</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002231544309824173</v>
+        <v>0.002231860647752306</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5960</v>
+        <v>6028</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03817077716954133</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.740771812080537</v>
+        <v>1.70985401459854</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3835616438356165</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>330.1</v>
+        <v>332.6</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25730</v>
+        <v>25740</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1347032120466064</v>
+        <v>-0.1356826234221555</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02635056354450049</v>
+        <v>0.03372183372183368</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.585620455563791</v>
+        <v>6.587766024177511</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.610822722617692</v>
+        <v>7.621929400819104</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.03013698630137</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001518459812173295</v>
+        <v>0.001517965265205136</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25730</v>
+        <v>25740</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1033084321245896</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1836766420520792</v>
+        <v>0.1832167832167833</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.033641738826322</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2183</v>
+        <v>2215</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04232015783918441</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.718403711406321</v>
+        <v>2.664684109255079</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.967123287671233</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114.7</v>
+        <v>114.8</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11720</v>
+        <v>11730</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01241508346996629</v>
+        <v>-0.01261740980685598</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5658703071672355</v>
+        <v>0.5658994032395568</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.208026555172458</v>
+        <v>4.208127656531247</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.260926310982684</v>
+        <v>4.261901818329698</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.364383561643836</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.00237641085884026</v>
+        <v>0.002376353764952792</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1032</v>
+        <v>1010</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03139589691370251</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.614452976744186</v>
+        <v>0.6496192792079207</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.733723851127348</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218</v>
+        <v>215.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1200745954236147</v>
+        <v>-0.1176505748124478</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0092592592592593</v>
+        <v>-0.002777777777777768</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.322238364121582</v>
+        <v>4.320045332418032</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.912050887089002</v>
+        <v>4.896070886542215</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.605479452054794</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002313616038164133</v>
+        <v>0.002314790524293587</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>204.3</v>
+        <v>225</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>258.8</v>
+        <v>257.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1647099800856918</v>
+        <v>-0.1889031162154035</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.1081610316846986</v>
+        <v>-0.01398855702094659</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.242036966269263</v>
+        <v>3.250443115859715</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.881330901812835</v>
+        <v>4.007465915407138</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.358904109589041</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003084480560845482</v>
+        <v>0.003076503616140067</v>
       </c>
     </row>
     <row r="15">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16780</v>
+        <v>16820</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02140071741299814</v>
+        <v>-0.01654278178020404</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2187369249106079</v>
+        <v>0.2046841379310347</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.856140193529227</v>
+        <v>1.856027180251483</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.896731610738952</v>
+        <v>1.887247503873293</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.854794520547945</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005387524086198577</v>
+        <v>0.005387852131909539</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158.2</v>
+        <v>157.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01699445257158434</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4654867256637172</v>
+        <v>0.4738715829624922</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.297106659493218</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22130</v>
+        <v>22110</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4699133997490303</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004237154270221311</v>
+        <v>0.005145555133423851</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.530972816439928</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>189</v>
+        <v>184.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09127432530148286</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1682539682539681</v>
+        <v>0.1973969631236441</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.936554198599898</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8740</v>
+        <v>8792</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02838863806266149</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8202069589244851</v>
+        <v>0.8094414036624205</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.42097345886548</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36.5</v>
+        <v>37.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1461379076659537</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.071232876712329</v>
+        <v>1.032258064516129</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.051493199304135</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1166</v>
+        <v>1192</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0535687901881742</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5799109433962264</v>
+        <v>0.545449798657718</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3780821917808219</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12860</v>
+        <v>12900</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.075157871318475</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04144422861586317</v>
+        <v>0.03821494418604643</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>176.9</v>
+        <v>177</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19480</v>
+        <v>20160</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1451947715673795</v>
+        <v>-0.1453679677517393</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.04523562628336752</v>
+        <v>0.01055059523809532</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.77963972432668</v>
+        <v>2.779671480240368</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.251781378810066</v>
+        <v>3.252477528753458</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.854794520547945</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003597588533680323</v>
+        <v>0.003597547433603652</v>
       </c>
     </row>
     <row r="30">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65730</v>
+        <v>65840</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2605619399725927</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1814696485623004</v>
+        <v>0.1794957472660996</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.725771194571882</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>115</v>
+        <v>116.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.03821026907490702</v>
+        <v>-0.04355082202319691</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.001652173913043509</v>
+        <v>0.001632302405498276</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.748729548972602</v>
+        <v>2.749857625035379</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.857931895705259</v>
+        <v>2.875069254439854</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.854794520547945</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003638044348065353</v>
+        <v>0.003636551910527129</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>903.9</v>
+        <v>902</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0627903916253561</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.769775417634694</v>
+        <v>0.7735033259423501</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.133162580644048</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8699</v>
+        <v>8742</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.002892037708495751</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2310678013564778</v>
+        <v>0.225012446122169</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.835362792898602</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.6</v>
+        <v>109.5</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.7</v>
+        <v>95.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02485232541406409</v>
+        <v>0.02506009288538742</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3100533617929564</v>
+        <v>0.2868835257082898</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.480566477154809</v>
+        <v>4.480354131265893</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.371914241736785</v>
+        <v>4.370820952217914</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.854794520547945</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002231860647752306</v>
+        <v>0.002231966426541057</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6028</v>
+        <v>5992</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03817077716954133</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.70985401459854</v>
+        <v>1.726134846461949</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3835616438356165</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25740</v>
+        <v>25610</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1356826234221555</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03372183372183368</v>
+        <v>0.03896915267473644</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.587766024177511</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25740</v>
+        <v>25610</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1033084321245896</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1832167832167833</v>
+        <v>0.1892229597813355</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.033641738826322</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2215</v>
+        <v>2255</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04232015783918441</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.664684109255079</v>
+        <v>2.59967862616408</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.967123287671233</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114.8</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11730</v>
+        <v>11670</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01261740980685598</v>
+        <v>-0.01099258716516677</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5658994032395568</v>
+        <v>0.5629820051413881</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.208127656531247</v>
+        <v>4.207314574587342</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.261901818329698</v>
+        <v>4.25407789667394</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.364383561643836</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002376353764952792</v>
+        <v>0.002376813005711799</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1010</v>
+        <v>1028</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03139589691370251</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6496192792079207</v>
+        <v>0.6207348949416343</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.733723851127348</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>216</v>
+        <v>215.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-7.107364821925811</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.01375464684014882</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216</v>
+        <v>215.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1176505748124478</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002777777777777768</v>
+        <v>0.0009293680297397522</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.320045332418032</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>257.8</v>
+        <v>258.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1889031162154035</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01398855702094659</v>
+        <v>-0.01703886310904879</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.250443115859715</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1810835367337496</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.176658385093168</v>
+        <v>0.1751985111662535</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.005475667190799</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16820</v>
+        <v>16950</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01654278178020404</v>
+        <v>-0.02140071741299814</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2046841379310347</v>
+        <v>0.2065136047197642</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.856027180251483</v>
+        <v>1.856140193529227</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.887247503873293</v>
+        <v>1.896731610738952</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.854794520547945</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005387852131909539</v>
+        <v>0.005387524086198577</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05254202546853467</v>
+        <v>0.05320567313479053</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9662404092071613</v>
+        <v>0.9622762148337598</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.105411990345909</v>
+        <v>3.105046503772815</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.950392397836606</v>
+        <v>2.948186268813829</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.358904109589041</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003220184642516985</v>
+        <v>0.003220563681687025</v>
       </c>
     </row>
     <row r="18">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.3</v>
+        <v>157.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01699445257158434</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4738715829624922</v>
+        <v>0.4720000000000002</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.297106659493218</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22110</v>
+        <v>22170</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4699133997490303</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.005145555133423851</v>
+        <v>0.002425269463238511</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.530972816439928</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>421.4</v>
+        <v>418.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04760958274845391</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5787986236355009</v>
+        <v>0.5904990198422184</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8821917808219178</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>184.4</v>
+        <v>188.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09127432530148286</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1973969631236441</v>
+        <v>0.1694915254237286</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.936554198599898</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8792</v>
+        <v>8860</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02838863806266149</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8094414036624205</v>
+        <v>0.7955540430022574</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.42097345886548</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.2</v>
+        <v>36.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1461379076659537</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.032258064516129</v>
+        <v>1.071232876712329</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.051493199304135</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12900</v>
+        <v>12770</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.075157871318475</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03821494418604643</v>
+        <v>0.04878408613938912</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20160</v>
+        <v>20200</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1453679677517393</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.01055059523809532</v>
+        <v>0.008549504950495113</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.779671480240368</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65840</v>
+        <v>66370</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2605619399725927</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1794957472660996</v>
+        <v>0.1700768419466627</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.725771194571882</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>116.4</v>
+        <v>124.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.04355082202319691</v>
+        <v>-0.0461789845020259</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.001632302405498276</v>
+        <v>-0.05940752602081667</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.749857625035379</v>
+        <v>2.750411521678739</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.875069254439854</v>
+        <v>2.883571945877912</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.854794520547945</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003636551910527129</v>
+        <v>0.003635819556884494</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>902</v>
+        <v>899.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.0627903916253561</v>
+        <v>0.06280569869614726</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7735033259423501</v>
+        <v>0.7776419602178017</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.133162580644048</v>
+        <v>3.1304152223633</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.948053167711096</v>
+        <v>2.945425703121184</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.358904109589041</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.00319166329311402</v>
+        <v>0.003194464404773282</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109.7</v>
+        <v>104.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8742</v>
+        <v>8840</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.002892037708495751</v>
+        <v>0.02154813621564855</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.225012446122169</v>
+        <v>0.1584249398190045</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.835362792898602</v>
+        <v>1.831591153597694</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.840686126586194</v>
+        <v>1.792956287290456</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.854794520547945</v>
+        <v>1.852054794520548</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005448514069639022</v>
+        <v>0.005459733729526673</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.3</v>
+        <v>94.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02506009288538742</v>
+        <v>0.02504940296978497</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2868835257082898</v>
+        <v>0.2950369588173181</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.480354131265893</v>
+        <v>4.477625332402143</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.370820952217914</v>
+        <v>4.36820441964018</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.854794520547945</v>
+        <v>4.852054794520548</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002231966426541057</v>
+        <v>0.00223332665366962</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5992</v>
+        <v>6011</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03817077716954133</v>
+        <v>0.03835756649719211</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.726134846461949</v>
+        <v>1.717517883879554</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3835616438356165</v>
+        <v>0.3808219178082191</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3694591027512402</v>
+        <v>0.3667541221786329</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342466</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02607142857142857</v>
+        <v>0.0262589928057554</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>332.6</v>
+        <v>332.7</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25610</v>
+        <v>25050</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1356826234221555</v>
+        <v>-0.1357783394867167</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03896915267473644</v>
+        <v>0.06251497005988016</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.587766024177511</v>
+        <v>6.585235533872154</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.621929400819104</v>
+        <v>7.619845503479993</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.03013698630137</v>
+        <v>7.027397260273973</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001517965265205136</v>
+        <v>0.001518548569533085</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>126.9</v>
+        <v>133.6</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25610</v>
+        <v>25050</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1033084321245896</v>
+        <v>-0.1257507088306198</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1892229597813355</v>
+        <v>0.28</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.033641738826322</v>
+        <v>2.031643233095465</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.267938956585442</v>
+        <v>2.323871753305027</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.027397260273973</v>
+        <v>2.024657534246575</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004917286958208928</v>
+        <v>0.00492212404082568</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.3</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2255</v>
+        <v>2203</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04232015783918441</v>
+        <v>0.0458054105867879</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.59967862616408</v>
+        <v>2.67316742623695</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.967123287671233</v>
+        <v>0.9643835616438358</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9278562641215338</v>
+        <v>0.9221443605868634</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9397260273972603</v>
+        <v>0.9369863013698631</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.0103399433427762</v>
+        <v>0.01036931818181818</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>225.3</v>
+        <v>221.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1536382883243639</v>
+        <v>0.153800582622776</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.553129161118509</v>
+        <v>2.617352010845007</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.746877271716199</v>
+        <v>1.744131162584202</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.514233091425478</v>
+        <v>1.511640043220908</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.775342465753425</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005724500605686867</v>
+        <v>0.005733513748578086</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>114.7</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11670</v>
+        <v>11750</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01099258716516677</v>
+        <v>-0.01243422060674362</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5629820051413881</v>
+        <v>0.5618723404255319</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.207314574587342</v>
+        <v>4.205296393636474</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.25407789667394</v>
+        <v>4.258244343197206</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.364383561643836</v>
+        <v>4.361643835616438</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002376813005711799</v>
+        <v>0.002377953671739326</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03139589691370251</v>
+        <v>0.03137472506029296</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6207348949416343</v>
+        <v>0.6128900987415296</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.733723851127348</v>
+        <v>2.730988772851757</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.650508751593454</v>
+        <v>2.647911284322104</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.854794520547945</v>
+        <v>2.852054794520548</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003658013956265607</v>
+        <v>0.003661677447892905</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>161.6</v>
+        <v>161.5</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>215.2</v>
+        <v>217.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-7.107364821925811</v>
+        <v>-7.495462107565265</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01375464684014882</v>
+        <v>0.001492880110243622</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.03013698630136986</v>
+        <v>0.0273972602739726</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215.4</v>
+        <v>217.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>215.2</v>
+        <v>217.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1176505748124478</v>
+        <v>-0.1198819811414429</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0009293680297397522</v>
+        <v>0</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.320045332418032</v>
+        <v>4.319324745326358</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.896070886542215</v>
+        <v>4.907665395747922</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.605479452054794</v>
+        <v>4.602739726027397</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002314790524293587</v>
+        <v>0.002315176697658658</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225</v>
+        <v>217.4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>258.6</v>
+        <v>252.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1889031162154035</v>
+        <v>-0.180525208599639</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01703886310904879</v>
+        <v>-0.02768151227236737</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.250443115859715</v>
+        <v>3.244826895453685</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>4.007465915407138</v>
+        <v>3.959642114077429</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.358904109589041</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003076503616140067</v>
+        <v>0.003081828498774762</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>173.8</v>
+        <v>179.9</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1810835367337496</v>
+        <v>-0.1948590288858243</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1751985111662535</v>
+        <v>0.1971367521367522</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.005475667190799</v>
+        <v>2.005953860873671</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.448938026220592</v>
+        <v>2.491431852111287</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.120547945205479</v>
+        <v>2.117808219178082</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.0049863482083568</v>
+        <v>0.004985159526871975</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109</v>
+        <v>108.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16950</v>
+        <v>17130</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02140071741299814</v>
+        <v>-0.01757903511653431</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2065136047197642</v>
+        <v>0.185073606538237</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.856140193529227</v>
+        <v>1.853311559056743</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.896731610738952</v>
+        <v>1.886473950885792</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.854794520547945</v>
+        <v>1.852054794520548</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005387524086198577</v>
+        <v>0.005395746846304447</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.2</v>
+        <v>77</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05320567313479053</v>
+        <v>0.05122126505252669</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9622762148337598</v>
+        <v>1.004935064935065</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.105046503772815</v>
+        <v>3.103398908256542</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.948186268813829</v>
+        <v>2.952184294047242</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.358904109589041</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003220563681687025</v>
+        <v>0.003222273480020619</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1460518943649718</v>
+        <v>0.1461860788370266</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.827702338870817</v>
+        <v>1.824956867363666</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.594781482284926</v>
+        <v>1.592199470102928</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.854794520547945</v>
+        <v>1.852054794520548</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005471350442205023</v>
+        <v>0.005479581560985606</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.5</v>
+        <v>157.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01699445257158434</v>
+        <v>0.01697301628728914</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4720000000000002</v>
+        <v>0.4701331642358912</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.297106659493218</v>
+        <v>3.29437788672203</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.242010466385647</v>
+        <v>3.239395572902189</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.520547945205479</v>
+        <v>3.517808219178082</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003032962240153023</v>
+        <v>0.003035474479204386</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22170</v>
+        <v>22620</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4699133997490303</v>
+        <v>-0.4705257858875754</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.002425269463238511</v>
+        <v>-0.0175168778072502</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.530972816439928</v>
+        <v>1.528249299040612</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.888156040381116</v>
+        <v>2.886352646280362</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.517808219178082</v>
+        <v>1.515068493150685</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006531794616219025</v>
+        <v>0.00654343503136412</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>418.3</v>
+        <v>427.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04760958274845391</v>
+        <v>0.04764037408035542</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5904990198422184</v>
+        <v>0.5566348619560133</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8821917808219178</v>
+        <v>0.8794520547945207</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8420997624968697</v>
+        <v>0.8394598724457574</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8547945205479452</v>
+        <v>0.852054794520548</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01133540372670807</v>
+        <v>0.01137071651090342</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>188.8</v>
+        <v>189.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09127432530148286</v>
+        <v>0.09130333854743847</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1694915254237286</v>
+        <v>0.1670190274841437</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.936554198599898</v>
+        <v>1.933806651159913</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.774580555686484</v>
+        <v>1.772015701641557</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.120547945205479</v>
+        <v>2.117808219178082</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005163811065670076</v>
+        <v>0.005171147794947298</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8860</v>
+        <v>8729</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02838863806266149</v>
+        <v>0.02840296864725578</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7955540430022574</v>
+        <v>0.822500724137931</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.42097345886548</v>
+        <v>4.418231535819824</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.298932616752717</v>
+        <v>4.296206516820437</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.446575342465754</v>
+        <v>4.443835616438356</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00226194526907796</v>
+        <v>0.002263349016213215</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>39</v>
+        <v>37.1</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1649876709311094</v>
+        <v>0.1650732532745829</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.210035646153846</v>
+        <v>0.2720051266846359</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.013250846827317</v>
+        <v>3.010455495860354</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.586508786328181</v>
+        <v>2.583919498108033</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.358904109589041</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003318674915674247</v>
+        <v>0.003321756463017273</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36.5</v>
+        <v>38.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1461379076659537</v>
+        <v>0.146212950396431</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.071232876712329</v>
+        <v>0.9790575916230364</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.051493199304135</v>
+        <v>3.048708367695715</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.662413640535048</v>
+        <v>2.65980973835733</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.358904109589041</v>
+        <v>3.356164383561644</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003277084150893867</v>
+        <v>0.003280077591533701</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>54.43281051292921</v>
+        <v>54.7903385476672</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.01572727272727259</v>
+        <v>0.4897333333333334</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3835616438356164</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006919397380115773</v>
+        <v>0.006825947426055594</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342466</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02607142857142857</v>
+        <v>0.0262589928057554</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0535687901881742</v>
+        <v>0.0537564674249076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.545449798657718</v>
+        <v>0.5585246700507613</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3780821917808219</v>
+        <v>0.3753424657534247</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3588585722184253</v>
+        <v>0.3561946971207294</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342466</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02644927536231885</v>
+        <v>0.02664233576642336</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12770</v>
+        <v>13090</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.075157871318475</v>
+        <v>-2.090101328049645</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04878408613938912</v>
+        <v>0.02314536134453782</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342466</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>177</v>
+        <v>177.2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20200</v>
+        <v>19320</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1453679677517393</v>
+        <v>-0.1458703786768288</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.008549504950495113</v>
+        <v>0.05567908902691499</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.779671480240368</v>
+        <v>2.777023851343066</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.252477528753458</v>
+        <v>3.251290883743209</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.854794520547945</v>
+        <v>2.852054794520548</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003597547433603652</v>
+        <v>0.003600977353926452</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>594</v>
+        <v>591.3</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648247720084134</v>
+        <v>0.05648256760816966</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6352727070707072</v>
+        <v>0.6427397057331306</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.728182100388734</v>
+        <v>2.725442354266294</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.582325934659204</v>
+        <v>2.579732442189345</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.854794520547945</v>
+        <v>2.852054794520548</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003665444472557429</v>
+        <v>0.003669129154152322</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1150437176170122</v>
+        <v>0.1150985877363275</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.371424910857143</v>
+        <v>1.357950905681818</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.263730417482869</v>
+        <v>2.260976771098921</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.030171895251554</v>
+        <v>2.02760257789291</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.427397260273973</v>
+        <v>2.424657534246575</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004417487136617352</v>
+        <v>0.004422867199621702</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66370</v>
+        <v>67610</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2605619399725927</v>
+        <v>-0.2609426572870134</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1700768419466627</v>
+        <v>0.148617068480994</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.725771194571882</v>
+        <v>1.723045313055064</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.333895545636258</v>
+        <v>2.331409504342358</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.728767123287671</v>
+        <v>1.726027397260274</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005794510901244203</v>
+        <v>0.005803677897634271</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>132</v>
+        <v>142.8</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>124.9</v>
+        <v>126.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0461789845020259</v>
+        <v>-0.07301928559879893</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.05940752602081667</v>
+        <v>0.007068145800317005</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.750411521678739</v>
+        <v>2.753280956997778</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.883571945877912</v>
+        <v>2.970159911877245</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.854794520547945</v>
+        <v>2.852054794520548</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003635819556884494</v>
+        <v>0.003632030350765278</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1351</v>
+        <v>1316</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03330026474617065</v>
+        <v>0.03328256379563222</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3589933382679498</v>
+        <v>0.3951367781155015</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.757399381303729</v>
+        <v>1.754660353958105</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.700763506274173</v>
+        <v>1.698141839839611</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.775342465753425</v>
+        <v>1.772602739726027</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.00569022619808907</v>
+        <v>0.005699108649398916</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>899.9</v>
+        <v>902</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06280569869614726</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7776419602178017</v>
+        <v>0.7735033259423501</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.1304152223633</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8840</v>
+        <v>8880</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.02154813621564855</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1584249398190045</v>
+        <v>0.1532068094594596</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.831591153597694</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.5</v>
+        <v>109.1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02504940296978497</v>
+        <v>0.02588329093717196</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2950369588173181</v>
+        <v>0.2848790746582546</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.477625332402143</v>
+        <v>4.476772389318022</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.36820441964018</v>
+        <v>4.363822306949136</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.852054794520548</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00223332665366962</v>
+        <v>0.002233752161235825</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6011</v>
+        <v>6043</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03835756649719211</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.717517883879554</v>
+        <v>1.703127585636274</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3808219178082191</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>332.7</v>
+        <v>330.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25050</v>
+        <v>25300</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1357783394867167</v>
+        <v>-0.1347596281296408</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06251497005988016</v>
+        <v>0.04379446640316198</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.585235533872154</v>
+        <v>6.58300454488077</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.619845503479993</v>
+        <v>7.608295635408833</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.027397260273973</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001518548569533085</v>
+        <v>0.001519063207661984</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>133.6</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25050</v>
+        <v>25300</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1257507088306198</v>
+        <v>-0.100317484936954</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.28</v>
+        <v>0.1952569169960474</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.031643233095465</v>
+        <v>2.030802171429455</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.323871753305027</v>
+        <v>2.257243124578391</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.024657534246575</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00492212404082568</v>
+        <v>0.004924162550486703</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2203</v>
+        <v>2176</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.0458054105867879</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.67316742623695</v>
+        <v>2.718744411764706</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9643835616438358</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03137472506029296</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6128900987415296</v>
+        <v>0.6366556699410608</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.730988772851757</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>161.5</v>
+        <v>160.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217.7</v>
+        <v>218.1</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-7.495462107565265</v>
+        <v>-7.386595756895599</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.001492880110243622</v>
+        <v>-0.009009628610728959</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.7</v>
+        <v>218.1</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1198819811414429</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0</v>
+        <v>-0.001834021091242533</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.319324745326358</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.6</v>
+        <v>250.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.180525208599639</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02768151227236737</v>
+        <v>-0.01796221511395435</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.244826895453685</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1948590288858243</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1971367521367522</v>
+        <v>0.2015379901960785</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.005953860873671</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17130</v>
+        <v>16980</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.01757903511653431</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.185073606538237</v>
+        <v>0.1955424546525324</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.853311559056743</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>157.7</v>
+        <v>158.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01697301628728914</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4701331642358912</v>
+        <v>0.4664136622390895</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.29437788672203</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22620</v>
+        <v>22420</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4705257858875754</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.0175168778072502</v>
+        <v>-0.008752532381801958</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.528249299040612</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>427.4</v>
+        <v>433.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04764037408035542</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5566348619560133</v>
+        <v>0.5354390491576275</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8794520547945207</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>189.2</v>
+        <v>188.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09130333854743847</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1670190274841437</v>
+        <v>0.1701112877583466</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.933806651159913</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8729</v>
+        <v>8633</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02840296864725578</v>
+        <v>0.02917559210665068</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.822500724137931</v>
+        <v>0.8366450017375189</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.418231535819824</v>
+        <v>4.418112983008284</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.296206516820437</v>
+        <v>4.292866073479954</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.443835616438356</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002263349016213215</v>
+        <v>0.002263409749469788</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1650732532745829</v>
+        <v>0.1812420486865467</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2720051266846359</v>
+        <v>0.2179884706199462</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.010455495860354</v>
+        <v>2.999879033966138</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.583919498108033</v>
+        <v>2.539597229290797</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.356164383561644</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003321756463017273</v>
+        <v>0.003333467745457391</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.146212950396431</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9790575916230364</v>
+        <v>1.043243243243243</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.048708367695715</v>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3704,7 +3704,7 @@
         <v>54.7903385476672</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.4897333333333334</v>
+        <v>0.2414444444444444</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.3808219178082192</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1182</v>
+        <v>1227</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0537564674249076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5585246700507613</v>
+        <v>0.5013660635696822</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3753424657534247</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13090</v>
+        <v>12890</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.090101328049645</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02314536134453782</v>
+        <v>0.03902038634600458</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19320</v>
+        <v>19050</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1458703786768288</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.05567908902691499</v>
+        <v>0.07064146981627273</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.777023851343066</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1150985877363275</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.357950905681818</v>
+        <v>1.344629149152543</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.260976771098921</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67610</v>
+        <v>67130</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2609426572870134</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.148617068480994</v>
+        <v>0.1568300312825861</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.723045313055064</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142.8</v>
+        <v>142</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>126.2</v>
+        <v>127.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07301928559879893</v>
+        <v>-0.0711345263747029</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.007068145800317005</v>
+        <v>-0.01033672670321073</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.753280956997778</v>
+        <v>2.752889925972216</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.970159911877245</v>
+        <v>2.963712188835999</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.852054794520548</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003632030350765278</v>
+        <v>0.003632546258262898</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1316</v>
+        <v>1345</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03328256379563222</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3951367781155015</v>
+        <v>0.3650557620817845</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.754660353958105</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>902</v>
+        <v>900.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06280569869614726</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7735033259423501</v>
+        <v>0.7770495445456562</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.1304152223633</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>104.9</v>
+        <v>109.4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8880</v>
+        <v>8921</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.02154813621564855</v>
+        <v>-0.001478998448737052</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1532068094594596</v>
+        <v>0.1971496926353549</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.831591153597694</v>
+        <v>1.832563344770077</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.792956287290456</v>
+        <v>1.835277717667509</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.852054794520548</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005459733729526673</v>
+        <v>0.005456837292167193</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02588329093717196</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2848790746582546</v>
+        <v>0.288945147679325</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.476772389318022</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6043</v>
+        <v>6036</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03835756649719211</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.703127585636274</v>
+        <v>1.706262425447316</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3808219178082191</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25300</v>
+        <v>25320</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1347596281296408</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04379446640316198</v>
+        <v>0.04296998420221176</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.58300454488077</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25300</v>
+        <v>25320</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.100317484936954</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1952569169960474</v>
+        <v>0.1943127962085307</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.030802171429455</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2176</v>
+        <v>2192</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0458054105867879</v>
+        <v>0.0446788373116063</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.718744411764706</v>
+        <v>2.695445708941605</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9643835616438358</v>
+        <v>0.9643835616438355</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9221443605868634</v>
+        <v>0.923138793665617</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.9369863013698631</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>221.3</v>
+        <v>221.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.153800582622776</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.617352010845007</v>
+        <v>2.614085778781038</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.744131162584202</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114.7</v>
+        <v>113.6</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11750</v>
+        <v>11930</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01243422060674362</v>
+        <v>-0.01019264319123639</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5618723404255319</v>
+        <v>0.5235540653813915</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.205296393636474</v>
+        <v>4.204173566411577</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.258244343197206</v>
+        <v>4.247466476675064</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.361643835616438</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002377953671739326</v>
+        <v>0.002378588762341556</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218.1</v>
+        <v>218.3</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-7.386595756895599</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.009009628610728959</v>
+        <v>-0.009917544663307298</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217.7</v>
+        <v>217.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.1</v>
+        <v>218.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1198819811414429</v>
+        <v>-0.1196964105175506</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001834021091242533</v>
+        <v>-0.003664681630783373</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.319324745326358</v>
+        <v>4.319157151681933</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.907665395747922</v>
+        <v>4.906440463591958</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.602739726027397</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002315176697658658</v>
+        <v>0.002315266532060746</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250.1</v>
+        <v>250</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.180525208599639</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01796221511395435</v>
+        <v>-0.01756939999999996</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.244826895453685</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1948590288858243</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2015379901960785</v>
+        <v>0.2000673194614444</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>2.005953860873671</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.2</v>
+        <v>108</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16980</v>
+        <v>17060</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01757903511653431</v>
+        <v>-0.01660059119259039</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1955424546525324</v>
+        <v>0.1877366471277844</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.853311559056743</v>
+        <v>1.853288798927825</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.886473950885792</v>
+        <v>1.88457383879796</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.852054794520548</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005395746846304447</v>
+        <v>0.005395813111148817</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05122126505252669</v>
+        <v>0.05287603695872988</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>1.004935064935065</v>
+        <v>0.9948701298701297</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.103398908256542</v>
+        <v>3.102488346904959</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.952184294047242</v>
+        <v>2.946679607094685</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.356164383561644</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003222273480020619</v>
+        <v>0.003223219197576034</v>
       </c>
     </row>
     <row r="18">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110.4</v>
+        <v>110</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01697301628728914</v>
+        <v>0.01807254123633946</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4664136622390895</v>
+        <v>0.4611005692599621</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.29437788672203</v>
+        <v>3.293815734237887</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.239395572902189</v>
+        <v>3.235344831359367</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.517808219178082</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003035474479204386</v>
+        <v>0.003035992540825533</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22420</v>
+        <v>22440</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4705257858875754</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.008752532381801958</v>
+        <v>-0.009635997147950159</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.528249299040612</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>433.3</v>
+        <v>432.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04764037408035542</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5354390491576275</v>
+        <v>0.5372128927911275</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8794520547945207</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>188.7</v>
+        <v>188.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09130333854743847</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1701112877583466</v>
+        <v>0.1725969198088155</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.933806651159913</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8633</v>
+        <v>8617</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02917559210665068</v>
+        <v>0.02866015832525704</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8366450017375189</v>
+        <v>0.8441442861784845</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.418112983008284</v>
+        <v>4.418192094411705</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.292866073479954</v>
+        <v>4.295094019782863</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.443835616438356</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002263409749469788</v>
+        <v>0.002263369221236074</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.1</v>
+        <v>37.6</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1812420486865467</v>
+        <v>0.1801698169006841</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2179884706199462</v>
+        <v>0.2052304186170211</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.999879033966138</v>
+        <v>3.000584539798203</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.539597229290797</v>
+        <v>2.542502355871311</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.356164383561644</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003333467745457391</v>
+        <v>0.003332683971194668</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.146212950396431</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.043243243243243</v>
+        <v>1.032258064516129</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.048708367695715</v>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3704,7 +3704,7 @@
         <v>54.7903385476672</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.2414444444444444</v>
+        <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.3808219178082192</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1227</v>
+        <v>1212</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0537564674249076</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5013660635696822</v>
+        <v>0.5199473267326733</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3753424657534247</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>511.5</v>
+        <v>512</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12890</v>
+        <v>12960</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,10 +3940,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.090101328049645</v>
+        <v>-2.090621423397424</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03902038634600458</v>
+        <v>0.03441856790123454</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>177.2</v>
+        <v>177</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19050</v>
+        <v>19010</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1458703786768288</v>
+        <v>-0.1455241420058902</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.07064146981627273</v>
+        <v>0.071683324566018</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.777023851343066</v>
+        <v>2.776960385926777</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.251290883743209</v>
+        <v>3.249899174969926</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.852054794520548</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003600977353926452</v>
+        <v>0.003601059651653123</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>591.3</v>
+        <v>595.1</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05648256760816966</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6427397057331306</v>
+        <v>0.632250021845068</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.725442354266294</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67130</v>
+        <v>67430</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2609426572870134</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1568300312825861</v>
+        <v>0.1516832270502744</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.723045313055064</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142</v>
+        <v>142.5</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.7</v>
+        <v>126.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0711345263747029</v>
+        <v>-0.07231421501605924</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01033672670321073</v>
+        <v>-0.0005910165484633856</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.752889925972216</v>
+        <v>2.753134726810069</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.963712188835999</v>
+        <v>2.967744867253441</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.852054794520548</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003632546258262898</v>
+        <v>0.003632223262675757</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03328256379563222</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3650557620817845</v>
+        <v>0.3701492537313433</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.754660353958105</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06280569869614726</v>
+        <v>0.06283640925907183</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.7770495445456562</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.1304152223633</v>
+        <v>3.124920457353682</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.945425703121184</v>
+        <v>2.940170688668953</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.356164383561644</v>
+        <v>3.350684931506849</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003194464404773282</v>
+        <v>0.003200081453743124</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001478998448737052</v>
+        <v>-0.001615441418538931</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1971496926353549</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.832563344770077</v>
+        <v>1.827089659151592</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.835277717667509</v>
+        <v>1.830045991243679</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.852054794520548</v>
+        <v>1.846575342465753</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005456837292167193</v>
+        <v>0.005473185155370806</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02588329093717196</v>
+        <v>0.02586269044313367</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.288945147679325</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.476772389318022</v>
+        <v>4.471314021874609</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.363822306949136</v>
+        <v>4.358589179165071</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.852054794520548</v>
+        <v>4.846575342465753</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002233752161235825</v>
+        <v>0.002236479019607636</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03835756649719211</v>
+        <v>0.03873934332752311</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.706262425447316</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3808219178082191</v>
+        <v>0.3753424657534246</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3667541221786329</v>
+        <v>0.3613442276587342</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3534246575342466</v>
+        <v>0.3479452054794521</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.0262589928057554</v>
+        <v>0.02664233576642336</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1347596281296408</v>
+        <v>-0.1348725866167765</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.04296998420221176</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.58300454488077</v>
+        <v>6.577772917570417</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.608295635408833</v>
+        <v>7.603241806714864</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.027397260273973</v>
+        <v>7.021917808219178</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001519063207661984</v>
+        <v>0.00152027139357277</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.100317484936954</v>
+        <v>-0.1005891631636719</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.1943127962085307</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.030802171429455</v>
+        <v>2.025331798570025</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.257243124578391</v>
+        <v>2.251842779317755</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.024657534246575</v>
+        <v>2.019178082191781</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004924162550486703</v>
+        <v>0.004937462596035103</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0446788373116063</v>
+        <v>0.04491864062705204</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.695445708941605</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9643835616438355</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.923138793665617</v>
+        <v>0.9176830351247308</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9369863013698631</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01036931818181818</v>
+        <v>0.01042857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.153800582622776</v>
+        <v>0.1541268190592726</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.614085778781038</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.744131162584202</v>
+        <v>1.738638879768831</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.511640043220908</v>
+        <v>1.50645392781531</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.772602739726027</v>
+        <v>1.767123287671233</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005733513748578086</v>
+        <v>0.005751625663248482</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01019264319123639</v>
+        <v>-0.0102283717389169</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.5235540653813915</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.204173566411577</v>
+        <v>4.198712050952155</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.247466476675064</v>
+        <v>4.242101845583124</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.361643835616438</v>
+        <v>4.356164383561643</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002378588762341556</v>
+        <v>0.002381682734764407</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03137472506029296</v>
+        <v>0.03133227756372305</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.6366556699410608</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.730988772851757</v>
+        <v>2.725518638935359</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.647911284322104</v>
+        <v>2.642716317745575</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.852054794520548</v>
+        <v>2.846575342465754</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003661677447892905</v>
+        <v>0.003669026458724272</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-7.386595756895599</v>
+        <v>-8.312095359708033</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>-0.009917544663307298</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.0273972602739726</v>
+        <v>0.02191780821917808</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1196964105175506</v>
+        <v>-0.1198669618621897</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.003664681630783373</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.319157151681933</v>
+        <v>4.313831731157698</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.906440463591958</v>
+        <v>4.901340529478276</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.602739726027397</v>
+        <v>4.597260273972603</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002315266532060746</v>
+        <v>0.002318124726046352</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.180525208599639</v>
+        <v>-0.1808263383495776</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.01756939999999996</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.244826895453685</v>
+        <v>3.239451466688388</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.959642114077429</v>
+        <v>3.954535672157396</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.356164383561644</v>
+        <v>3.350684931506849</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003081828498774762</v>
+        <v>0.003086942373679935</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1948590288858243</v>
+        <v>-0.1954197939133104</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.2000673194614444</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.005953860873671</v>
+        <v>2.000604796131594</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.491431852111287</v>
+        <v>2.486520027458939</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.117808219178082</v>
+        <v>2.112328767123288</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004985159526871975</v>
+        <v>0.004998488466755745</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01660059119259039</v>
+        <v>-0.01671670751663067</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1877366471277844</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.853288798927825</v>
+        <v>1.847812047864019</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.88457383879796</v>
+        <v>1.879226528091619</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.852054794520548</v>
+        <v>1.846575342465753</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005395813111148817</v>
+        <v>0.005411805822761854</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05287603695872988</v>
+        <v>0.05288089226191906</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9948701298701297</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.102488346904959</v>
+        <v>3.097006220906566</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.946679607094685</v>
+        <v>2.941459232157992</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.356164383561644</v>
+        <v>3.350684931506849</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003223219197576034</v>
+        <v>0.003228924737862737</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1461860788370266</v>
+        <v>0.1464557571353908</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.824956867363666</v>
+        <v>1.819465868496307</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.592199470102928</v>
+        <v>1.587035397722232</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.852054794520548</v>
+        <v>1.846575342465753</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005479581560985606</v>
+        <v>0.005496118489029132</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01807254123633946</v>
+        <v>0.01803109958437523</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.4611005692599621</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.293815734237887</v>
+        <v>3.288357482213846</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.235344831359367</v>
+        <v>3.230114957741823</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.517808219178082</v>
+        <v>3.512328767123288</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003035992540825533</v>
+        <v>0.003041031899386931</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4705257858875754</v>
+        <v>-0.4717550077932099</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.009635997147950159</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.528249299040612</v>
+        <v>1.522802383623514</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.886352646280362</v>
+        <v>2.88275782277059</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.515068493150685</v>
+        <v>1.50958904109589</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.00654343503136412</v>
+        <v>0.006566840259472779</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04764037408035542</v>
+        <v>0.04770260626105696</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5372128927911275</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8794520547945207</v>
+        <v>0.8739726027397261</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8394598724457574</v>
+        <v>0.8341800407070453</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.852054794520548</v>
+        <v>0.8465753424657534</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01137071651090342</v>
+        <v>0.01144200626959248</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09130333854743847</v>
+        <v>0.09136167497620339</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1725969198088155</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.933806651159913</v>
+        <v>1.928311472453029</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.772015701641557</v>
+        <v>1.766885824073926</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.117808219178082</v>
+        <v>2.112328767123288</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005171147794947298</v>
+        <v>0.005185884201206809</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02866015832525704</v>
+        <v>0.02868919271622247</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.8441442861784845</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.418192094411705</v>
+        <v>4.412708188382837</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.295094019782863</v>
+        <v>4.289641827315416</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.443835616438356</v>
+        <v>4.438356164383562</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002263369221236074</v>
+        <v>0.002266182029966678</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1801698169006841</v>
+        <v>0.1803659887587031</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2052304186170211</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>3.000584539798203</v>
+        <v>2.994976054394214</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.542502355871311</v>
+        <v>2.53732832267032</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.356164383561644</v>
+        <v>3.350684931506849</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003332683971194668</v>
+        <v>0.003338924858957737</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.146212950396431</v>
+        <v>0.1463634936051985</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>1.032258064516129</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.048708367695715</v>
+        <v>3.043138420509634</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.65980973835733</v>
+        <v>2.654601649027803</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.356164383561644</v>
+        <v>3.350684931506849</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003280077591533701</v>
+        <v>0.00328608121556472</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>54.7903385476672</v>
+        <v>55.52117566679352</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3808219178082192</v>
+        <v>0.3753424657534247</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006825947426055594</v>
+        <v>0.006640740595456869</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3534246575342466</v>
+        <v>0.3479452054794521</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.0262589928057554</v>
+        <v>0.02664233576642336</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0537564674249076</v>
+        <v>0.05414025571093652</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5199473267326733</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3753424657534247</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3561946971207294</v>
+        <v>0.3508669853891369</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3534246575342466</v>
+        <v>0.3479452054794521</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02664233576642336</v>
+        <v>0.02703703703703704</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.090621423397424</v>
+        <v>-2.121170328983483</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.03441856790123454</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3534246575342466</v>
+        <v>0.3479452054794521</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1455241420058902</v>
+        <v>-0.1458373204316521</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.071683324566018</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.776960385926777</v>
+        <v>2.771538340331838</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.249899174969926</v>
+        <v>3.244742958955358</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.852054794520548</v>
+        <v>2.846575342465754</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003601059651653123</v>
+        <v>0.003608104515271722</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648256760816966</v>
+        <v>0.05648277528617419</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.632250021845068</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.725442354266294</v>
+        <v>2.719962856050436</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.579732442189345</v>
+        <v>2.57454538746613</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.852054794520548</v>
+        <v>2.846575342465754</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003669129154152322</v>
+        <v>0.003676520794302557</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1150985877363275</v>
+        <v>0.1152087889458046</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.344629149152543</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.260976771098921</v>
+        <v>2.255469360440656</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.02760257789291</v>
+        <v>2.022463759967968</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.424657534246575</v>
+        <v>2.419178082191781</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004422867199621702</v>
+        <v>0.004433666967679968</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2609426572870134</v>
+        <v>-0.2617071290518718</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1516832270502744</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.723045313055064</v>
+        <v>1.717593661655329</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.331409504342358</v>
+        <v>2.32643945139219</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.726027397260274</v>
+        <v>1.720547945205479</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005803677897634271</v>
+        <v>0.005822098802089496</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07231421501605924</v>
+        <v>-0.07252412197553083</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.0005910165484633856</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.753134726810069</v>
+        <v>2.747698815379443</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.967744867253441</v>
+        <v>2.962555555872853</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.852054794520548</v>
+        <v>2.846575342465754</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003632223262675757</v>
+        <v>0.003639409073522875</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03328256379563222</v>
+        <v>0.03324702191449617</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.3701492537313433</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.754660353958105</v>
+        <v>1.749182304795149</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.698141839839611</v>
+        <v>1.692898472191191</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.772602739726027</v>
+        <v>1.767123287671233</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005699108649398916</v>
+        <v>0.005716956987608632</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900.2</v>
+        <v>879.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06283640925907183</v>
+        <v>0.0628518129200564</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.7770495445456562</v>
+        <v>0.8180475053983405</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.124920457353682</v>
+        <v>3.12217305053906</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.940170688668953</v>
+        <v>2.937543138738474</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.350684931506849</v>
+        <v>3.347945205479452</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003200081453743124</v>
+        <v>0.003202897417320749</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8921</v>
+        <v>8846</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001615441418538931</v>
+        <v>-0.001683951090218829</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1971496926353549</v>
+        <v>0.2072996165498531</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.827089659151592</v>
+        <v>1.824352828548115</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.830045991243679</v>
+        <v>1.82743013151037</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.846575342465753</v>
+        <v>1.843835616438356</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005473185155370806</v>
+        <v>0.005481395837206753</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.8</v>
+        <v>94</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02586269044313367</v>
+        <v>0.02585237598844218</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.288945147679325</v>
+        <v>0.2999148936170213</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.471314021874609</v>
+        <v>4.468584852439883</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.358589179165071</v>
+        <v>4.35597261071239</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.846575342465753</v>
+        <v>4.843835616438356</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002236479019607636</v>
+        <v>0.002237844939777728</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03873934332752311</v>
+        <v>0.03893445139043041</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.706262425447316</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3753424657534246</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3613442276587342</v>
+        <v>0.3586393147588516</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3479452054794521</v>
+        <v>0.3452054794520548</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02664233576642336</v>
+        <v>0.02683823529411765</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25320</v>
+        <v>26020</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1348725866167765</v>
+        <v>-0.1349291291133407</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04296998420221176</v>
+        <v>0.01491160645657197</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.577772917570417</v>
+        <v>6.575157201029361</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.603241806714864</v>
+        <v>7.60071506544905</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.021917808219178</v>
+        <v>7.019178082191781</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152027139357277</v>
+        <v>0.001520876185049153</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25320</v>
+        <v>26020</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1005891631636719</v>
+        <v>-0.1007255227177172</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1943127962085307</v>
+        <v>0.1621829362029208</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.025331798570025</v>
+        <v>2.02259662876072</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.251842779317755</v>
+        <v>2.249142703208095</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.019178082191781</v>
+        <v>2.016438356164384</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004937462596035103</v>
+        <v>0.004944139556945259</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04491864062705204</v>
+        <v>0.04503957312426211</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.695445708941605</v>
+        <v>2.688714478142076</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.958904109589041</v>
+        <v>0.9561643835616439</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9176830351247308</v>
+        <v>0.9149551922738046</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9315068493150684</v>
+        <v>0.9287671232876712</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01042857142857143</v>
+        <v>0.01045845272206304</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1541268190592726</v>
+        <v>0.1542907666398288</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.614085778781038</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.738638879768831</v>
+        <v>1.735892705873155</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.50645392781531</v>
+        <v>1.503860860748618</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.767123287671233</v>
+        <v>1.764383561643836</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005751625663248482</v>
+        <v>0.00576072470733149</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11930</v>
+        <v>11880</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.0102283717389169</v>
+        <v>-0.01024626965810743</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5235540653813915</v>
+        <v>0.52996632996633</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.198712050952155</v>
+        <v>4.195981309627854</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.242101845583124</v>
+        <v>4.239419545484742</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.356164383561643</v>
+        <v>4.353424657534247</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002381682734764407</v>
+        <v>0.002383232732008263</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03133227756372305</v>
+        <v>0.03131100170951452</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6366556699410608</v>
+        <v>0.6334465411764705</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.725518638935359</v>
+        <v>2.72278358334039</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.642716317745575</v>
+        <v>2.640118818500984</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.846575342465754</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003669026458724272</v>
+        <v>0.003672712022059318</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218.3</v>
+        <v>216.3</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-8.312095359708033</v>
+        <v>-8.867394860429528</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.009917544663307298</v>
+        <v>-0.0007628294036060579</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.02191780821917808</v>
+        <v>0.01917808219178082</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>218.3</v>
+        <v>216.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1198669618621897</v>
+        <v>-0.1199523839618034</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003664681630783373</v>
+        <v>0.00554785020804438</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.313831731157698</v>
+        <v>4.311169134472611</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.901340529478276</v>
+        <v>4.89879076530047</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.597260273972603</v>
+        <v>4.594520547945206</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002318124726046352</v>
+        <v>0.002319556409893278</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250</v>
+        <v>248.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1808263383495776</v>
+        <v>-0.1809772393485517</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01756939999999996</v>
+        <v>-0.01124134460547499</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.239451466688388</v>
+        <v>3.236763850668007</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.954535672157396</v>
+        <v>3.951982785061425</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.350684931506849</v>
+        <v>3.347945205479452</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003086942373679935</v>
+        <v>0.003089505586864543</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1954197939133104</v>
+        <v>-0.1957011624676217</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.2000673194614444</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>2.000604796131594</v>
+        <v>1.997930475082386</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.486520027458939</v>
+        <v>2.484064854814559</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.112328767123288</v>
+        <v>2.10958904109589</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.004998488466755745</v>
+        <v>0.005005179171506278</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108</v>
+        <v>109.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17060</v>
+        <v>17440</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01671670751663067</v>
+        <v>-0.02262790587631654</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1877366471277844</v>
+        <v>0.1747665871559634</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.847812047864019</v>
+        <v>1.845209842431805</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.879226528091619</v>
+        <v>1.887929738863916</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.846575342465753</v>
+        <v>1.843835616438356</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005411805822761854</v>
+        <v>0.005419437816796481</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05288089226191906</v>
+        <v>0.05288333553857251</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9948701298701297</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.097006220906566</v>
+        <v>3.094265149297271</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.941459232157992</v>
+        <v>2.9388490109538</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.350684931506849</v>
+        <v>3.347945205479452</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003228924737862737</v>
+        <v>0.003231785098400849</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1464557571353908</v>
+        <v>0.1465912550676179</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.819465868496307</v>
+        <v>1.816720340961663</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.587035397722232</v>
+        <v>1.584453337605933</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.846575342465753</v>
+        <v>1.843835616438356</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005496118489029132</v>
+        <v>0.005504424525079407</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158.1</v>
+        <v>160</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01803109958437523</v>
+        <v>0.01801033391197211</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4611005692599621</v>
+        <v>0.4437500000000001</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.288357482213846</v>
+        <v>3.285628378783696</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.230114957741823</v>
+        <v>3.227500025621357</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.512328767123288</v>
+        <v>3.50958904109589</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003041031899386931</v>
+        <v>0.003043557836477506</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>276.8</v>
+        <v>293.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22440</v>
+        <v>23110</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4717550077932099</v>
+        <v>-0.4922267773572519</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.009635997147950159</v>
+        <v>0.01967030852444829</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.522802383623514</v>
+        <v>1.520604846831339</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.88275782277059</v>
+        <v>2.994653477229903</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.50958904109589</v>
+        <v>1.506849315068493</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006566840259472779</v>
+        <v>0.006576330478518573</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>432.8</v>
+        <v>435.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04770260626105696</v>
+        <v>0.04773405118086889</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5372128927911275</v>
+        <v>0.5280333945796969</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8739726027397261</v>
+        <v>0.8712328767123287</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8341800407070453</v>
+        <v>0.8315400990646328</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8465753424657534</v>
+        <v>0.8438356164383561</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01144200626959248</v>
+        <v>0.01147798742138365</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09136167497620339</v>
+        <v>0.09139099903839987</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.1725969198088155</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.928311472453029</v>
+        <v>1.92556384094712</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.766885824073926</v>
+        <v>1.764320800376484</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.112328767123288</v>
+        <v>2.10958904109589</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005185884201206809</v>
+        <v>0.005193284059115556</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8617</v>
+        <v>8679</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02868919271622247</v>
+        <v>0.02870373736777239</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8441442861784845</v>
+        <v>0.830970309252218</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.412708188382837</v>
+        <v>4.409966231050102</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.289641827315416</v>
+        <v>4.286915727879282</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.438356164383562</v>
+        <v>4.435616438356164</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002266182029966678</v>
+        <v>0.002267591059902243</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1803659887587031</v>
+        <v>0.1804643844171809</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.2052304186170211</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.994976054394214</v>
+        <v>2.992171600612994</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.53732832267032</v>
+        <v>2.534741107068884</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.350684931506849</v>
+        <v>3.347945205479452</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003338924858957737</v>
+        <v>0.003342054311975737</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.2</v>
+        <v>38.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1463634936051985</v>
+        <v>0.1478795591928168</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.032258064516129</v>
+        <v>0.9712041884816751</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.043138420509634</v>
+        <v>3.039486694272557</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.654601649027803</v>
+        <v>2.647914295477053</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.350684931506849</v>
+        <v>3.347945205479452</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00328608121556472</v>
+        <v>0.003290029207511733</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>55.52117566679352</v>
+        <v>55.89471667885628</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3753424657534247</v>
+        <v>0.3726027397260274</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006640740595456869</v>
+        <v>0.006548986645441849</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3479452054794521</v>
+        <v>0.3452054794520548</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02664233576642336</v>
+        <v>0.02683823529411765</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05414025571093652</v>
+        <v>0.05433649262407654</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5199473267326733</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3671232876712328</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3508669853891369</v>
+        <v>0.3482031497909373</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3479452054794521</v>
+        <v>0.3452054794520548</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02703703703703704</v>
+        <v>0.02723880597014926</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12960</v>
+        <v>12950</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.121170328983483</v>
+        <v>-2.129245771474061</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03441856790123454</v>
+        <v>0.02106398455598457</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3479452054794521</v>
+        <v>0.3452054794520548</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>177</v>
+        <v>180.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19010</v>
+        <v>19540</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1458373204316521</v>
+        <v>-0.15266481450489</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.071683324566018</v>
+        <v>0.06558802456499491</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.771538340331838</v>
+        <v>2.770047082856572</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.244742958955358</v>
+        <v>3.269127885015177</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.846575342465754</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003608104515271722</v>
+        <v>0.003610046941760875</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648277528617419</v>
+        <v>0.05648289260575051</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.632250021845068</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.719962856050436</v>
+        <v>2.717223103946147</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.57454538746613</v>
+        <v>2.571951825215344</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.846575342465754</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003676520794302557</v>
+        <v>0.003680227797812142</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>35.4</v>
+        <v>38</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1152087889458046</v>
+        <v>0.1152641211753079</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.344629149152543</v>
+        <v>1.184207154736842</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.255469360440656</v>
+        <v>2.252715595872043</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.022463759967968</v>
+        <v>2.019894259216414</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.419178082191781</v>
+        <v>2.416438356164384</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004433666967679968</v>
+        <v>0.004439086770795373</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67430</v>
+        <v>67090</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2617071290518718</v>
+        <v>-0.2620908914751411</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1516832270502744</v>
+        <v>0.1575197495901028</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.717593661655329</v>
+        <v>1.714867892068715</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.32643945139219</v>
+        <v>2.323955446893557</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.720547945205479</v>
+        <v>1.717808219178082</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005822098802089496</v>
+        <v>0.005831352984244515</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142.5</v>
+        <v>139.5</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>126.9</v>
+        <v>124.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07252412197553083</v>
+        <v>-0.0654472786184884</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.0005910165484633856</v>
+        <v>-0.003571428571428559</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.747698815379443</v>
+        <v>2.743488188884586</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.962555555872853</v>
+        <v>2.935616285862394</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.846575342465754</v>
+        <v>2.843835616438356</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003639409073522875</v>
+        <v>0.003644994733535076</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03324702191449617</v>
+        <v>0.03322918054274702</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.3701492537313433</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.749182304795149</v>
+        <v>1.746443282995246</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.692898472191191</v>
+        <v>1.690276771004332</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.767123287671233</v>
+        <v>1.764383561643836</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005716956987608632</v>
+        <v>0.005725923136106345</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8846</v>
+        <v>8826</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001683951090218829</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2072996165498531</v>
+        <v>0.210035396329028</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.824352828548115</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6036</v>
+        <v>6022</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.03893445139043041</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.706262425447316</v>
+        <v>1.712553968781136</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3726027397260274</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>330.1</v>
+        <v>331.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26020</v>
+        <v>25490</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1349291291133407</v>
+        <v>-0.1354009012640104</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01491160645657197</v>
+        <v>0.03978030600235383</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.575157201029361</v>
+        <v>6.576190812891491</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.60071506544905</v>
+        <v>7.606057908810717</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.019178082191781</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001520876185049153</v>
+        <v>0.001520637141549591</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26020</v>
+        <v>25490</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1007255227177172</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1621829362029208</v>
+        <v>0.1863475872891329</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.02259662876072</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2196</v>
+        <v>2151</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04503957312426211</v>
+        <v>0.04390572635903247</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.688714478142076</v>
+        <v>2.769802951185495</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9561643835616439</v>
+        <v>0.9561643835616437</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9149551922738046</v>
+        <v>0.9159489783589789</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.9287671232876712</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>221.5</v>
+        <v>230</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1542907666398288</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.614085778781038</v>
+        <v>2.480521739130435</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.735892705873155</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11880</v>
+        <v>12070</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01024626965810743</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.52996632996633</v>
+        <v>0.5058823529411764</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.195981309627854</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03131100170951452</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6334465411764705</v>
+        <v>0.6431119053254437</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.72278358334039</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>216.3</v>
+        <v>214.6</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-8.867394860429528</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.0007628294036060579</v>
+        <v>0.00715284249767012</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217.5</v>
+        <v>214</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.3</v>
+        <v>214.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1199523839618034</v>
+        <v>-0.1166651434635235</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.00554785020804438</v>
+        <v>-0.002795899347623476</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.311169134472611</v>
+        <v>4.308192030878334</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.89879076530047</v>
+        <v>4.877190115389079</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.594520547945206</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002319556409893278</v>
+        <v>0.002321159300311237</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.4</v>
+        <v>249.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1809772393485517</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01124134460547499</v>
+        <v>-0.01560060120240481</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.236763850668007</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.2</v>
+        <v>109.1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17440</v>
+        <v>17480</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02262790587631654</v>
+        <v>-0.02214396408579385</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1747665871559634</v>
+        <v>0.1710050022883296</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.845209842431805</v>
+        <v>1.845198582351628</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.887929738863916</v>
+        <v>1.886983885748106</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.843835616438356</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005419437816796481</v>
+        <v>0.005419470888198614</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01801033391197211</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4437500000000001</v>
+        <v>0.4620253164556962</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.285628378783696</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23110</v>
+        <v>23200</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4922267773572519</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01967030852444829</v>
+        <v>0.01571469094827571</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.520604846831339</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>435.4</v>
+        <v>440.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04773405118086889</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5280333945796969</v>
+        <v>0.5106851498637603</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>188.3</v>
+        <v>185</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09139099903839987</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1725969198088155</v>
+        <v>0.1935135135135133</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.92556384094712</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8679</v>
+        <v>8759</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02870373736777239</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.830970309252218</v>
+        <v>0.814247210183811</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.409966231050102</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05433649262407654</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5199473267326733</v>
+        <v>0.5224596363636365</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3671232876712328</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12950</v>
+        <v>12970</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.129245771474061</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02106398455598457</v>
+        <v>0.01948948342328438</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19540</v>
+        <v>18740</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.15266481450489</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.06558802456499491</v>
+        <v>0.1110773745997866</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770047082856572</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>595.1</v>
+        <v>595</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05648289260575051</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.632250021845068</v>
+        <v>0.6325243495798318</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.717223103946147</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67090</v>
+        <v>67560</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2620908914751411</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1575197495901028</v>
+        <v>0.1494671403197159</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.714867892068715</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>879.9</v>
+        <v>869.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0628518129200564</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8180475053983405</v>
+        <v>0.8389470054029198</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.12217305053906</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8826</v>
+        <v>8777</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001683951090218829</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.210035396329028</v>
+        <v>0.2167907494588128</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.824352828548115</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1272,16 +1272,16 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.03893445139043041</v>
+        <v>0.05541057233264984</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.712553968781136</v>
+        <v>1.69611424775822</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3726027397260274</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3586393147588516</v>
+        <v>0.353040560227199</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.3452054794520548</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25490</v>
+        <v>25450</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1354009012640104</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03978030600235383</v>
+        <v>0.04141453831041253</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.576190812891491</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25490</v>
+        <v>25450</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1007255227177172</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1863475872891329</v>
+        <v>0.188212180746562</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.02259662876072</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2151</v>
+        <v>2124</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04390572635903247</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.769802951185495</v>
+        <v>2.817724175141243</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9561643835616437</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.6</v>
+        <v>112.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12070</v>
+        <v>12140</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01024626965810743</v>
+        <v>-0.007139931866633545</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5058823529411764</v>
+        <v>0.4774299835255353</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.195981309627854</v>
+        <v>4.194417081317418</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.239419545484742</v>
+        <v>4.224580296801705</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.353424657534247</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002383232732008263</v>
+        <v>0.002384121513461679</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03131100170951452</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6431119053254437</v>
+        <v>0.6528923333333332</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.72278358334039</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>214.6</v>
+        <v>215.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-8.867394860429528</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.00715284249767012</v>
+        <v>0.002946635730858516</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>214.6</v>
+        <v>215.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1166651434635235</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002795899347623476</v>
+        <v>-0.00696055684454755</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.308192030878334</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249.5</v>
+        <v>247.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1809772393485517</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01560060120240481</v>
+        <v>-0.00924707543364256</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.236763850668007</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1957011624676217</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2000673194614444</v>
+        <v>0.2119344870210136</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.997930475082386</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05288333553857251</v>
+        <v>0.05455310897542036</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9948701298701297</v>
+        <v>0.9848051948051946</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.094265149297271</v>
+        <v>3.093344780125969</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.9388490109538</v>
+        <v>2.933322896493466</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.347945205479452</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003231785098400849</v>
+        <v>0.003232746658001949</v>
       </c>
     </row>
     <row r="18">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>158</v>
+        <v>155.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01801033391197211</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4620253164556962</v>
+        <v>0.4884020618556701</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.285628378783696</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23200</v>
+        <v>23100</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4922267773572519</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01571469094827571</v>
+        <v>0.02011172424242424</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.520604846831339</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>440.4</v>
+        <v>435.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04773405118086889</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5106851498637603</v>
+        <v>0.5290869685129855</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>185</v>
+        <v>183.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09139099903839987</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1935135135135133</v>
+        <v>0.203925845147219</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.92556384094712</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8759</v>
+        <v>8682</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02870373736777239</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.814247210183811</v>
+        <v>0.8303376311909698</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.409966231050102</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1478795591928168</v>
+        <v>0.1464389949463028</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9712041884816751</v>
+        <v>0.9790575916230364</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.039486694272557</v>
+        <v>3.040353304377789</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.647914295477053</v>
+        <v>2.651997461513592</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.347945205479452</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003290029207511733</v>
+        <v>0.003289091430788998</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18740</v>
+        <v>18620</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.15266481450489</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1110773745997866</v>
+        <v>0.1182379162191192</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770047082856572</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67560</v>
+        <v>67470</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2620908914751411</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1494671403197159</v>
+        <v>0.1510004446420632</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.714867892068715</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>869.9</v>
+        <v>862.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0628518129200564</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8389470054029198</v>
+        <v>0.8555851989328382</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.12217305053906</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8777</v>
+        <v>8727</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001683951090218829</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2167907494588128</v>
+        <v>0.2237621643176351</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.824352828548115</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02585237598844218</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2999148936170213</v>
+        <v>0.312481203007519</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.468584852439883</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6022</v>
+        <v>5906</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05541057233264984</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.69611424775822</v>
+        <v>1.749068743650525</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3726027397260274</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25450</v>
+        <v>25480</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1354009012640104</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04141453831041253</v>
+        <v>0.04018838304552586</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.576190812891491</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25450</v>
+        <v>25480</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1007255227177172</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.188212180746562</v>
+        <v>0.1868131868131868</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.02259662876072</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2124</v>
+        <v>2165</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04390572635903247</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.817724175141243</v>
+        <v>2.745425472517321</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9561643835616437</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12140</v>
+        <v>12160</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007139931866633545</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4774299835255353</v>
+        <v>0.4750000000000001</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.194417081317418</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03131100170951452</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6528923333333332</v>
+        <v>0.6414930758620689</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.72278358334039</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>215.5</v>
+        <v>214.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-8.867394860429528</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.002946635730858516</v>
+        <v>0.006215083798882803</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>215.5</v>
+        <v>214.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1166651434635235</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.00696055684454755</v>
+        <v>-0.003724394785847407</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.308192030878334</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>247.9</v>
+        <v>248.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1809772393485517</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.00924707543364256</v>
+        <v>-0.01283098874598076</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.236763850668007</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17480</v>
+        <v>17420</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.02214396408579385</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1710050022883296</v>
+        <v>0.1750383145809415</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.845198582351628</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155.2</v>
+        <v>154.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01801033391197211</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4884020618556701</v>
+        <v>0.4922480620155039</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.285628378783696</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23100</v>
+        <v>22970</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4922267773572519</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02011172424242424</v>
+        <v>0.02588510361340868</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.520604846831339</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>435.1</v>
+        <v>432</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04773405118086889</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5290869685129855</v>
+        <v>0.5400595833333333</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>183.4</v>
+        <v>186.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09139099903839987</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.203925845147219</v>
+        <v>0.1864588930682429</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.92556384094712</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8682</v>
+        <v>8641</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02870373736777239</v>
+        <v>0.02844606880231099</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8303376311909698</v>
+        <v>0.8410610833236893</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.409966231050102</v>
+        <v>4.410005749648344</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.286915727879282</v>
+        <v>4.288028204321952</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.435616438356164</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002267591059902243</v>
+        <v>0.002267570739742778</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1464389949463028</v>
+        <v>0.1469183258173419</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9790575916230364</v>
+        <v>0.9764397905759161</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.040353304377789</v>
+        <v>3.040065069771512</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.651997461513592</v>
+        <v>2.650637801610708</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.347945205479452</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003289091430788998</v>
+        <v>0.003289403276079083</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12970</v>
+        <v>12980</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.129245771474061</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01948948342328438</v>
+        <v>0.01870405238828954</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18620</v>
+        <v>18670</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.15266481450489</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1182379162191192</v>
+        <v>0.115243170862346</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770047082856572</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67470</v>
+        <v>67280</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2620908914751411</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1510004446420632</v>
+        <v>0.1542508917954815</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.714867892068715</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03322918054274702</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3701492537313433</v>
+        <v>0.3711725168035849</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.746443282995246</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>862.1</v>
+        <v>846.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0628518129200564</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8555851989328382</v>
+        <v>0.8904514299220039</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.12217305053906</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8727</v>
+        <v>8740</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>-0.001683951090218829</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2237621643176351</v>
+        <v>0.2219419231121282</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.824352828548115</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.1</v>
+        <v>108.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02585237598844218</v>
+        <v>0.02669137400103486</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.312481203007519</v>
+        <v>0.2992956243329776</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.468584852439883</v>
+        <v>4.46772560340322</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.35597261071239</v>
+        <v>4.351576059310221</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.843835616438356</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002237844939777728</v>
+        <v>0.002238275330155159</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5906</v>
+        <v>5946</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05541057233264984</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.749068743650525</v>
+        <v>1.730575176589304</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3726027397260274</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>331.3</v>
+        <v>320.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25480</v>
+        <v>25410</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1354009012640104</v>
+        <v>-0.1309170893374</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04018838304552586</v>
+        <v>0.007792207792207684</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.576190812891491</v>
+        <v>6.566288766632241</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.606057908810717</v>
+        <v>7.555422717524176</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.019178082191781</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001520637141549591</v>
+        <v>0.001522930281533881</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25480</v>
+        <v>25410</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1007255227177172</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1868131868131868</v>
+        <v>0.1900826446280992</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.02259662876072</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2165</v>
+        <v>2144</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04390572635903247</v>
+        <v>0.04503957312426211</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.745425472517321</v>
+        <v>2.778179568097014</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9561643835616437</v>
+        <v>0.9561643835616439</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9159489783589789</v>
+        <v>0.9149551922738046</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.9287671232876712</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230</v>
+        <v>220.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1542907666398288</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.480521739130435</v>
+        <v>2.632123411978221</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.735892705873155</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12160</v>
+        <v>12190</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.007139931866633545</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4750000000000001</v>
+        <v>0.4713699753896636</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.194417081317418</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03131100170951452</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6414930758620689</v>
+        <v>0.6366556699410608</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.72278358334039</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>214.8</v>
+        <v>216.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-8.867394860429528</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.006215083798882803</v>
+        <v>-0.001224584103512005</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>214.8</v>
+        <v>216.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1166651434635235</v>
+        <v>-0.1176112452307452</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003724394785847407</v>
+        <v>-0.006469500924214389</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.308192030878334</v>
+        <v>4.309050763769803</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.877190115389079</v>
+        <v>4.883392654858371</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.594520547945206</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002321159300311237</v>
+        <v>0.0023206967260816</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.8</v>
+        <v>248.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1809772393485517</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01283098874598076</v>
+        <v>-0.0116392354124748</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.236763850668007</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.1</v>
+        <v>108.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17420</v>
+        <v>17450</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02214396408579385</v>
+        <v>-0.01775745361681125</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1750383145809415</v>
+        <v>0.1633415977077364</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.845198582351628</v>
+        <v>1.845096531380997</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.886983885748106</v>
+        <v>1.878453074726815</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.843835616438356</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005419470888198614</v>
+        <v>0.005419770635260646</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>77</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05455310897542036</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9848051948051946</v>
+        <v>1.000392670157068</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.093344780125969</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>154.8</v>
+        <v>155</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01801033391197211</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4922480620155039</v>
+        <v>0.4903225806451612</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.285628378783696</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22970</v>
+        <v>22950</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4922267773572519</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.02588510361340868</v>
+        <v>0.0267791211328976</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.520604846831339</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>432</v>
+        <v>430.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04773405118086889</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5400595833333333</v>
+        <v>0.5461439460841273</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8641</v>
+        <v>8742</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02844606880231099</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.8410610833236893</v>
+        <v>0.819790530885381</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.410005749648344</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.2</v>
+        <v>36.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1469183258173419</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9764397905759161</v>
+        <v>1.057220708446866</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.040065069771512</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12980</v>
+        <v>13070</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.129245771474061</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01870405238828954</v>
+        <v>0.01168925784238706</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18670</v>
+        <v>18620</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.15266481450489</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.115243170862346</v>
+        <v>0.1182379162191192</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770047082856572</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>39.1</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1152641211753079</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.184207154736842</v>
+        <v>1.122758871611253</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.252715595872043</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67280</v>
+        <v>66910</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2620908914751411</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1542508917954815</v>
+        <v>0.1606336870422955</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.714867892068715</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>124.6</v>
+        <v>126.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.0654472786184884</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.003571428571428559</v>
+        <v>-0.0162044374009509</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.743488188884586</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1339</v>
+        <v>1390</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03322918054274702</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3711725168035849</v>
+        <v>0.3208633093525179</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.746443282995246</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>846.2</v>
+        <v>864.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.0628518129200564</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8904514299220039</v>
+        <v>0.850433776749566</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.12217305053906</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>109.4</v>
+        <v>107.1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8740</v>
+        <v>8621</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>-0.001683951090218829</v>
+        <v>0.009943896631189176</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2219419231121282</v>
+        <v>0.2127645716274214</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.824352828548115</v>
+        <v>1.823861651913177</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.82743013151037</v>
+        <v>1.805903929908311</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.843835616438356</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005481395837206753</v>
+        <v>0.005482872009239458</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.7</v>
+        <v>93.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02669137400103486</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2992956243329776</v>
+        <v>0.3020748663101607</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.46772560340322</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5946</v>
+        <v>5921</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,16 +1272,16 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05541057233264984</v>
+        <v>0.05265071872187384</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.730575176589304</v>
+        <v>1.744891065698362</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3726027397260274</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.353040560227199</v>
+        <v>0.3539661666487444</v>
       </c>
       <c r="BC5" s="8" t="n">
         <v>0.3452054794520548</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>320.1</v>
+        <v>320</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25410</v>
+        <v>25060</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1309170893374</v>
+        <v>-0.1308762232748138</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.007792207792207684</v>
+        <v>0.02154828411811649</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.566288766632241</v>
+        <v>6.566197709562267</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.555422717524176</v>
+        <v>7.554962693925326</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.019178082191781</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001522930281533881</v>
+        <v>0.00152295140084453</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25410</v>
+        <v>25060</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.1007255227177172</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1900826446280992</v>
+        <v>0.2067039106145252</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.02259662876072</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2144</v>
+        <v>2075</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04503957312426211</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.778179568097014</v>
+        <v>2.903815418795181</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9561643835616439</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>220.4</v>
+        <v>230.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1542907666398288</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.632123411978221</v>
+        <v>2.475987841945289</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.735892705873155</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.1</v>
+        <v>113.5</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12190</v>
+        <v>11930</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.007139931866633545</v>
+        <v>-0.01004078281418942</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4713699753896636</v>
+        <v>0.5222129086336966</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.194417081317418</v>
+        <v>4.195878136339084</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.224580296801705</v>
+        <v>4.238435345111331</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.353424657534247</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002384121513461679</v>
+        <v>0.002383291333795749</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03131100170951452</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6366556699410608</v>
+        <v>0.6561784015904573</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.72278358334039</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>248.5</v>
+        <v>246</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1809772393485517</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.0116392354124748</v>
+        <v>-0.001594918699186931</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.236763850668007</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>179.9</v>
+        <v>180</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1957011624676217</v>
+        <v>-0.1959174628112661</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2119344870210136</v>
+        <v>0.208128078817734</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.997930475082386</v>
+        <v>1.997980746599425</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.484064854814559</v>
+        <v>2.484795595219424</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.10958904109589</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005005179171506278</v>
+        <v>0.005005053235382804</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.2</v>
+        <v>108.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17450</v>
+        <v>17100</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01775745361681125</v>
+        <v>-0.01971394267155476</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1633415977077364</v>
+        <v>0.1915414175438597</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.845096531380997</v>
+        <v>1.845142045930911</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.878453074726815</v>
+        <v>1.88224858666198</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.843835616438356</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005419770635260646</v>
+        <v>0.005419636944512206</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05455310897542036</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>1.000392670157068</v>
+        <v>1.005643044619422</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.093344780125969</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155</v>
+        <v>155.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01801033391197211</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4903225806451612</v>
+        <v>0.4893617021276597</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.285628378783696</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22950</v>
+        <v>22630</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.4922267773572519</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0267791211328976</v>
+        <v>0.04129831330092792</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.520604846831339</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>430.3</v>
+        <v>423.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04773405118086889</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5461439460841273</v>
+        <v>0.5698578102878715</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8712328767123287</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>186.1</v>
+        <v>187.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09139099903839987</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1864588930682429</v>
+        <v>0.180117584179583</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.92556384094712</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8742</v>
+        <v>8670</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02844606880231099</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.819790530885381</v>
+        <v>0.834902978200692</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.410005749648344</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>70.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1804643844171809</v>
+        <v>0.2086569766737161</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2052304186170211</v>
+        <v>0.1192653388297871</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.992171600612994</v>
+        <v>2.973425539965594</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.534741107068884</v>
+        <v>2.460107042238409</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.347945205479452</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003342054311975737</v>
+        <v>0.003363124405030742</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1469183258173419</v>
+        <v>0.1464389949463028</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.057220708446866</v>
+        <v>1.026809651474531</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.040065069771512</v>
+        <v>3.040353304377789</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.650637801610708</v>
+        <v>2.651997461513592</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.347945205479452</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003289403276079083</v>
+        <v>0.003289091430788998</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05433649262407654</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5224596363636365</v>
+        <v>0.4620445714285715</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3671232876712328</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13070</v>
+        <v>12980</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.129245771474061</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01168925784238706</v>
+        <v>0.01870405238828954</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18620</v>
+        <v>18400</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.15266481450489</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1182379162191192</v>
+        <v>0.131608152173913</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770047082856572</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66910</v>
+        <v>66180</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2620908914751411</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1606336870422955</v>
+        <v>0.1734360834088848</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.714867892068715</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>126.2</v>
+        <v>123.3</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.0654472786184884</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.0162044374009509</v>
+        <v>0.006934306569343018</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.743488188884586</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1390</v>
+        <v>1349</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03322918054274702</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3208633093525179</v>
+        <v>0.3610081541882877</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.746443282995246</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>864.5</v>
+        <v>855.2</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.0628518129200564</v>
+        <v>0.06286724894712532</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.850433776749566</v>
+        <v>0.8705565949485496</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.12217305053906</v>
+        <v>3.119425627460473</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.937543138738474</v>
+        <v>2.934915560292756</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.347945205479452</v>
+        <v>3.345205479452055</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003202897417320749</v>
+        <v>0.003205718357882765</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8621</v>
+        <v>8617</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.009943896631189176</v>
+        <v>0.009890538887215162</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2127645716274214</v>
+        <v>0.2133275353371242</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.823861651913177</v>
+        <v>1.821124178639023</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.805903929908311</v>
+        <v>1.803288681806738</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.843835616438356</v>
+        <v>1.841095890410959</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005482872009239458</v>
+        <v>0.005491113740235594</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.7</v>
+        <v>108.4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93.5</v>
+        <v>92.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02669137400103486</v>
+        <v>0.02731359007972506</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3020748663101607</v>
+        <v>0.315362946912243</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.46772560340322</v>
+        <v>4.464347917026495</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.351576059310221</v>
+        <v>4.345652544789209</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.843835616438356</v>
+        <v>4.841095890410959</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002238275330155159</v>
+        <v>0.002239968789587654</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5921</v>
+        <v>5791</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05265071872187384</v>
+        <v>0.05294941214176091</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.744891065698362</v>
+        <v>1.806510101882231</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3726027397260274</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3539661666487444</v>
+        <v>0.3512638018822833</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3452054794520548</v>
+        <v>0.3424657534246575</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02683823529411765</v>
+        <v>0.02703703703703704</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25060</v>
+        <v>24500</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1308762232748138</v>
+        <v>-0.1288681797960156</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02154828411811649</v>
+        <v>0.02857142857142847</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.566197709562267</v>
+        <v>6.558965612090361</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.554962693925326</v>
+        <v>7.529245815581059</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.019178082191781</v>
+        <v>7.016438356164383</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.00152295140084453</v>
+        <v>0.001524630649315597</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>123.9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25060</v>
+        <v>24500</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.1007255227177172</v>
+        <v>-0.09339219190500352</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2067039106145252</v>
+        <v>0.2137142857142857</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.02259662876072</v>
+        <v>2.019611139951455</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.249142703208095</v>
+        <v>2.227656900722209</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.016438356164384</v>
+        <v>2.013698630136986</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004944139556945259</v>
+        <v>0.004951448227919939</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2075</v>
+        <v>2081</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04503957312426211</v>
+        <v>0.0451612007469467</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.903815418795181</v>
+        <v>2.892559824123017</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9561643835616439</v>
+        <v>0.9534246575342467</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9149551922738046</v>
+        <v>0.9122273739714615</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9287671232876712</v>
+        <v>0.9260273972602739</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01045845272206304</v>
+        <v>0.01048850574712644</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230.3</v>
+        <v>235</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1542907666398288</v>
+        <v>0.1544552707869758</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.475987841945289</v>
+        <v>2.406468085106383</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.735892705873155</v>
+        <v>1.733146510176117</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.503860860748618</v>
+        <v>1.501267787529486</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.00576072470733149</v>
+        <v>0.005769852658898313</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>113.5</v>
+        <v>112.6</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11930</v>
+        <v>11720</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01004078281418942</v>
+        <v>-0.008197845312697238</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5222129086336966</v>
+        <v>0.5372013651877132</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.195878136339084</v>
+        <v>4.192211175963799</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.238435345111331</v>
+        <v>4.226862339581756</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.353424657534247</v>
+        <v>4.35068493150685</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002383291333795749</v>
+        <v>0.002385376017633696</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03131100170951452</v>
+        <v>0.03128969097662571</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6561784015904573</v>
+        <v>0.6463591620553359</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.72278358334039</v>
+        <v>2.720048535351619</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.640118818500984</v>
+        <v>2.6375213086594</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.843835616438356</v>
+        <v>2.841095890410959</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003672712022059318</v>
+        <v>0.003676404986908554</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>216.4</v>
+        <v>212</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-8.867394860429528</v>
+        <v>-9.50202267490574</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.001224584103512005</v>
+        <v>0.01950471698113221</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.01917808219178082</v>
+        <v>0.01643835616438356</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>215</v>
+        <v>214.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>216.4</v>
+        <v>212</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1176112452307452</v>
+        <v>-0.1170337196278046</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.006469500924214389</v>
+        <v>0.01084905660377355</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.309050763769803</v>
+        <v>4.305787026257953</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.883392654858371</v>
+        <v>4.876502219816301</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.594520547945206</v>
+        <v>4.591780821917808</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.0023206967260816</v>
+        <v>0.002322455787761231</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>246</v>
+        <v>235.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1809772393485517</v>
+        <v>-0.1811283650896597</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.001594918699186931</v>
+        <v>0.04159308736217127</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.236763850668007</v>
+        <v>3.23407630038021</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.951982785061425</v>
+        <v>3.949430121284289</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.347945205479452</v>
+        <v>3.345205479452055</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003089505586864543</v>
+        <v>0.003092072997419499</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1959174628112661</v>
+        <v>-0.1896255000058667</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.208128078817734</v>
+        <v>0.1879926108374383</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.997980746599425</v>
+        <v>1.993775780776176</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.484795595219424</v>
+        <v>2.460314065645711</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.10958904109589</v>
+        <v>2.106849315068493</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005005053235382804</v>
+        <v>0.005015609125368654</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.6</v>
+        <v>108.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17100</v>
+        <v>16740</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01971394267155476</v>
+        <v>-0.01830810423634138</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1915414175438597</v>
+        <v>0.2138036272401433</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.845142045930911</v>
+        <v>1.842369614919682</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.88224858666198</v>
+        <v>1.876728964423713</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.843835616438356</v>
+        <v>1.841095890410959</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005419636944512206</v>
+        <v>0.005427792511892868</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05455310897542036</v>
+        <v>0.05321909016563546</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>1.005643044619422</v>
+        <v>1.013779527559055</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.093344780125969</v>
+        <v>3.091340482027312</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.933322896493466</v>
+        <v>2.935135254281376</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.347945205479452</v>
+        <v>3.345205479452055</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003232746658001949</v>
+        <v>0.003234842638052592</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1465912550676179</v>
+        <v>0.1467271949473812</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.816720340961663</v>
+        <v>1.81397479457584</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.584453337605933</v>
+        <v>1.581871261594242</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.843835616438356</v>
+        <v>1.841095890410959</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005504424525079407</v>
+        <v>0.005512755761492424</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155.1</v>
+        <v>159.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01801033391197211</v>
+        <v>0.01798953824230569</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4893617021276597</v>
+        <v>0.4519170333123823</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.285628378783696</v>
+        <v>3.282899290457713</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.227500025621357</v>
+        <v>3.224885096683876</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.50958904109589</v>
+        <v>3.506849315068493</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003043557836477506</v>
+        <v>0.003046087959221487</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>293.5</v>
+        <v>280.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22630</v>
+        <v>22240</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4922267773572519</v>
+        <v>-0.477193549081915</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.04129831330092792</v>
+        <v>0.01154442607913664</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.520604846831339</v>
+        <v>1.517466911701287</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.994653477229903</v>
+        <v>2.902540527257282</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.506849315068493</v>
+        <v>1.504109589041096</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006576330478518573</v>
+        <v>0.006589929521948284</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>423.8</v>
+        <v>433</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04773405118086889</v>
+        <v>0.04776571807714202</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5698578102878715</v>
+        <v>0.5365028637413396</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8712328767123287</v>
+        <v>0.8684931506849316</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8315400990646328</v>
+        <v>0.8289001402706598</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8438356164383561</v>
+        <v>0.8410958904109589</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01147798742138365</v>
+        <v>0.01151419558359621</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>95.2</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>187.1</v>
+        <v>187.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09139099903839987</v>
+        <v>0.09589354658136284</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.180117584179583</v>
+        <v>0.1659211927582533</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.92556384094712</v>
+        <v>1.921609178024986</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.764320800376484</v>
+        <v>1.753463357841134</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.10958904109589</v>
+        <v>2.106849315068493</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005193284059115556</v>
+        <v>0.005203971814017831</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.3</v>
+        <v>90.5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8670</v>
+        <v>9086</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02844606880231099</v>
+        <v>0.02794586770942603</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.834902978200692</v>
+        <v>0.754770397864847</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.410005749648344</v>
+        <v>4.407342675769114</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.288028204321952</v>
+        <v>4.28752409461989</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.435616438356164</v>
+        <v>4.432876712328767</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002267570739742778</v>
+        <v>0.002268940886983544</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>37.6</v>
+        <v>38.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2086569766737161</v>
+        <v>0.2070039548826594</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1192653388297871</v>
+        <v>0.09246289302325561</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.973425539965594</v>
+        <v>2.971795844141209</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.460107042238409</v>
+        <v>2.462126020481943</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.347945205479452</v>
+        <v>3.345205479452055</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003363124405030742</v>
+        <v>0.003364968700563549</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1464389949463028</v>
+        <v>0.1469943686646569</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.026809651474531</v>
+        <v>1.013333333333333</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.040353304377789</v>
+        <v>3.037279606145893</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.651997461513592</v>
+        <v>2.648033581613767</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.347945205479452</v>
+        <v>3.345205479452055</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003289091430788998</v>
+        <v>0.003292419960205554</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>55.89471667885628</v>
+        <v>56.27383300460225</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>0.01572727272727259</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3726027397260274</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006548986645441849</v>
+        <v>0.006457800958928484</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3452054794520548</v>
+        <v>0.3424657534246575</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02683823529411765</v>
+        <v>0.02703703703703703</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1260</v>
+        <v>1203</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05433649262407654</v>
+        <v>0.05453571178101615</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.4620445714285715</v>
+        <v>0.5313185037406483</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3671232876712328</v>
+        <v>0.3643835616438357</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3482031497909373</v>
+        <v>0.3455393284201106</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3452054794520548</v>
+        <v>0.3424657534246575</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02723880597014926</v>
+        <v>0.02744360902255639</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12980</v>
+        <v>13050</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.129245771474061</v>
+        <v>-2.145033023318506</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01870405238828954</v>
+        <v>0.01323973946360146</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3452054794520548</v>
+        <v>0.3424657534246575</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>180.9</v>
+        <v>190</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18400</v>
+        <v>17790</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.15266481450489</v>
+        <v>-0.1676599706402295</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.131608152173913</v>
+        <v>0.2292861157953907</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.770047082856572</v>
+        <v>2.770028907288571</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.269127885015177</v>
+        <v>3.328001549341867</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.843835616438356</v>
+        <v>2.841095890410959</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003610046941760875</v>
+        <v>0.003610070629114283</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>595</v>
+        <v>594.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648289260575051</v>
+        <v>0.05648301894514204</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6325243495798318</v>
+        <v>0.6333478863292414</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.717223103946147</v>
+        <v>2.714483349837002</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.571951825215344</v>
+        <v>2.569358239706787</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.843835616438356</v>
+        <v>2.841095890410959</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003680227797812142</v>
+        <v>0.003683942287065595</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1152641211753079</v>
+        <v>0.1153196085856532</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.122758871611253</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.252715595872043</v>
+        <v>2.249961791613001</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.019894259216414</v>
+        <v>2.017324697147751</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.416438356164384</v>
+        <v>2.413698630136986</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004439086770795373</v>
+        <v>0.004444519919083152</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66180</v>
+        <v>64520</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2620908914751411</v>
+        <v>-0.2624756769417703</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1734360834088848</v>
+        <v>0.2036267823930564</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.714867892068715</v>
+        <v>1.712142160089762</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.323955446893557</v>
+        <v>2.321472128526104</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.717808219178082</v>
+        <v>1.715068493150685</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005831352984244515</v>
+        <v>0.0058406365038495</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>139.5</v>
+        <v>139.8</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>123.3</v>
+        <v>119.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0654472786184884</v>
+        <v>-0.06627550169396419</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.006934306569343018</v>
+        <v>0.03771476230191828</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.743488188884586</v>
+        <v>2.740920921548781</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.935616285862394</v>
+        <v>2.935470715956755</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.843835616438356</v>
+        <v>2.841095890410959</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003644994733535076</v>
+        <v>0.003648408796248457</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03322918054274702</v>
+        <v>0.03321129192047901</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3610081541882877</v>
+        <v>0.3660714285714286</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.746443282995246</v>
+        <v>1.743704263061437</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.690276771004332</v>
+        <v>1.687655058260476</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.764383561643836</v>
+        <v>1.761643835616438</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005725923136106345</v>
+        <v>0.005734917446633358</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>855.2</v>
+        <v>841.1</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06286724894712532</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8705565949485496</v>
+        <v>0.9019141600285339</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.119425627460473</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>107.1</v>
+        <v>104.8</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8617</v>
+        <v>8641</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.009890538887215162</v>
+        <v>0.02192852597626129</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.2133275353371242</v>
+        <v>0.1839734215947226</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.821124178639023</v>
+        <v>1.820616206275075</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.803288681806738</v>
+        <v>1.781549452820898</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.841095890410959</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005491113740235594</v>
+        <v>0.005492645822624908</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.4</v>
+        <v>108.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02731359007972506</v>
+        <v>0.02773624675533625</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.315362946912243</v>
+        <v>0.3044564047362757</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.464347917026495</v>
+        <v>4.463914213175286</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.345652544789209</v>
+        <v>4.343443395392836</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.841095890410959</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002239968789587654</v>
+        <v>0.002240186419910334</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5791</v>
+        <v>5838</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05294941214176091</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.806510101882231</v>
+        <v>1.783915724563207</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3698630136986302</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24500</v>
+        <v>24350</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1288681797960156</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02857142857142847</v>
+        <v>0.03490759753593431</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.558965612090361</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24500</v>
+        <v>24350</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09339219190500352</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2137142857142857</v>
+        <v>0.2211909650924024</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.019611139951455</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2081</v>
+        <v>2092</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.0451612007469467</v>
+        <v>0.03949929638415043</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.892559824123017</v>
+        <v>2.892238414913958</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9534246575342467</v>
+        <v>0.9534246575342465</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9122273739714615</v>
+        <v>0.9171960585742477</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.9260273972602739</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1544552707869758</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.406468085106383</v>
+        <v>2.480521739130435</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.733146510176117</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106.4</v>
+        <v>105.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1012</v>
+        <v>990</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03128969097662571</v>
+        <v>0.03449391883538724</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6463591620553359</v>
+        <v>0.6687094848484847</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.720048535351619</v>
+        <v>2.719344592630544</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.6375213086594</v>
+        <v>2.628671414223418</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.841095890410959</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003676404986908554</v>
+        <v>0.003677356678921869</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>160.1</v>
+        <v>157.7</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>212</v>
+        <v>213.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-9.50202267490574</v>
+        <v>-9.256591502004929</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.01950471698113221</v>
+        <v>-0.002366447985004627</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>214.3</v>
+        <v>211</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212</v>
+        <v>213.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1170337196278046</v>
+        <v>-0.1138757185980412</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01084905660377355</v>
+        <v>-0.01124648547328966</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.305787026257953</v>
+        <v>4.302911569198072</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.876502219816301</v>
+        <v>4.855878187188743</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.591780821917808</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002322455787761231</v>
+        <v>0.002324007788489989</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>235.8</v>
+        <v>240.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1811283650896597</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.04159308736217127</v>
+        <v>0.01996532392026573</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.23407630038021</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16740</v>
+        <v>17080</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.01830810423634138</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.2138036272401433</v>
+        <v>0.1896412599531616</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.842369614919682</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>159.1</v>
+        <v>156.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01798953824230569</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4519170333123823</v>
+        <v>0.475095785440613</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.282899290457713</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22240</v>
+        <v>22680</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.477193549081915</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.01154442607913664</v>
+        <v>-0.008079892592592675</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.517466911701287</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>433</v>
+        <v>430.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04776571807714202</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5365028637413396</v>
+        <v>0.544349442896936</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8684931506849316</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>187.8</v>
+        <v>183.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09589354658136284</v>
+        <v>0.1004235344755982</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1659211927582533</v>
+        <v>0.1806416530723218</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.921609178024986</v>
+        <v>1.9203846515501</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.753463357841134</v>
+        <v>1.745132298052177</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.106849315068493</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005203971814017831</v>
+        <v>0.005207290108222945</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9086</v>
+        <v>9227</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02794586770942603</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.754770397864847</v>
+        <v>0.727955330551642</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.407342675769114</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.40000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2070039548826594</v>
+        <v>0.2322667080796917</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.09246289302325561</v>
+        <v>0.02397515813953488</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.971795844141209</v>
+        <v>2.954686624595078</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.462126020481943</v>
+        <v>2.39776552042011</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.345205479452055</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003364968700563549</v>
+        <v>0.003384453673279291</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1203</v>
+        <v>1184</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05453571178101615</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5313185037406483</v>
+        <v>0.5558920270270271</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3643835616438357</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13050</v>
+        <v>13000</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.145033023318506</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01323973946360146</v>
+        <v>0.01713681538461542</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17790</v>
+        <v>17660</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1676599706402295</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2292861157953907</v>
+        <v>0.238335220838052</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770028907288571</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64520</v>
+        <v>64360</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2624756769417703</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2036267823930564</v>
+        <v>0.2066190180236172</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.712142160089762</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>119.9</v>
+        <v>120</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.06627550169396419</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03771476230191828</v>
+        <v>0.03685000000000005</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.740920921548781</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1344</v>
+        <v>1335</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03321129192047901</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3660714285714286</v>
+        <v>0.3752808988764045</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.743704263061437</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>841.1</v>
+        <v>829.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06286724894712532</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9019141600285339</v>
+        <v>0.9275816363417277</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.119425627460473</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8641</v>
+        <v>8719</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.02192852597626129</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1839734215947226</v>
+        <v>0.1733816189930037</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.820616206275075</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02773624675533625</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3044564047362757</v>
+        <v>0.3172173913043479</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.463914213175286</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5838</v>
+        <v>5857</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05294941214176091</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.783915724563207</v>
+        <v>1.774884753286666</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3698630136986302</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24350</v>
+        <v>24600</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1288681797960156</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03490759753593431</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.558965612090361</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>123.9</v>
+        <v>117.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24350</v>
+        <v>24600</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09339219190500352</v>
+        <v>-0.0682370428479248</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2211909650924024</v>
+        <v>0.1434146341463414</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.019611139951455</v>
+        <v>2.018756787925314</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.227656900722209</v>
+        <v>2.166599103805999</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.013698630136986</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004951448227919939</v>
+        <v>0.004953543715524568</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2092</v>
+        <v>2086</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03949929638415043</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.892238414913958</v>
+        <v>2.903433731543624</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9534246575342465</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230</v>
+        <v>234.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1544552707869758</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.480521739130435</v>
+        <v>2.407918263090677</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.733146510176117</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112.6</v>
+        <v>111.9</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11720</v>
+        <v>11620</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.008197845312697238</v>
+        <v>-0.006737674069455539</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5372013651877132</v>
+        <v>0.5407917383820999</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.192211175963799</v>
+        <v>4.191474079169926</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.226862339581756</v>
+        <v>4.219906433321244</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.35068493150685</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002385376017633696</v>
+        <v>0.002385795500846897</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>990</v>
+        <v>991.3</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03449391883538724</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6687094848484847</v>
+        <v>0.6665211237768587</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.719344592630544</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157.7</v>
+        <v>157.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>213.4</v>
+        <v>212.6</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-9.256591502004929</v>
+        <v>-9.204542012708913</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.002366447985004627</v>
+        <v>-0.001787394167450551</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>211</v>
+        <v>213.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>213.4</v>
+        <v>212.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1138757185980412</v>
+        <v>-0.1162738117548097</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.01124648547328966</v>
+        <v>0.004233301975540948</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.302911569198072</v>
+        <v>4.305096663997173</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.855878187188743</v>
+        <v>4.871527766474564</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.591780821917808</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002324007788489989</v>
+        <v>0.002322828215131238</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>240.8</v>
+        <v>242</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1811283650896597</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01996532392026573</v>
+        <v>0.01490764462809913</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.23407630038021</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.3</v>
+        <v>107.8</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17080</v>
+        <v>17140</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01830810423634138</v>
+        <v>-0.0158468971624525</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1896412599531616</v>
+        <v>0.1800037059509918</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.842369614919682</v>
+        <v>1.842312363445059</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.876728964423713</v>
+        <v>1.87197739674166</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.841095890410959</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005427792511892868</v>
+        <v>0.005427961185311894</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>156.6</v>
+        <v>153</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01798953824230569</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.475095785440613</v>
+        <v>0.5098039215686274</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.282899290457713</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>280.2</v>
+        <v>280</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22680</v>
+        <v>22810</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.477193549081915</v>
+        <v>-0.4769486359457286</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.008079892592592675</v>
+        <v>-0.01443707145988604</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.517466911701287</v>
+        <v>1.517460426958017</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.902540527257282</v>
+        <v>2.901169046182941</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.504109589041096</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006589929521948284</v>
+        <v>0.006589957683474186</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>430.8</v>
+        <v>430.3</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04776571807714202</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.544349442896936</v>
+        <v>0.5461439460841273</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8684931506849316</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>183.9</v>
+        <v>182.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.1004235344755982</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1806416530723218</v>
+        <v>0.1883962780514505</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.9203846515501</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9227</v>
+        <v>9328</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02794586770942603</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.727955330551642</v>
+        <v>0.7092456941466552</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.407342675769114</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>61.3</v>
+        <v>62.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2322667080796917</v>
+        <v>0.2258976949993705</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.02397515813953488</v>
+        <v>0.04067948372093011</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.954686624595078</v>
+        <v>2.959029058088172</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.39776552042011</v>
+        <v>2.413765088358121</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.345205479452055</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003384453673279291</v>
+        <v>0.003379486920774276</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1469943686646569</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.013333333333333</v>
+        <v>0.9816272965879265</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.037279606145893</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05453571178101615</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5558920270270271</v>
+        <v>0.5638167741935485</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3643835616438357</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13000</v>
+        <v>12900</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.145033023318506</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01713681538461542</v>
+        <v>0.02502159689922467</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17660</v>
+        <v>17870</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1676599706402295</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.238335220838052</v>
+        <v>0.223782876329043</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770028907288571</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64360</v>
+        <v>64850</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2624756769417703</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.2066190180236172</v>
+        <v>0.1975019275250578</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.712142160089762</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>120</v>
+        <v>122.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.06627550169396419</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.03685000000000005</v>
+        <v>0.01818330605564644</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.740920921548781</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>829.9</v>
+        <v>822</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06286724894712532</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9275816363417277</v>
+        <v>0.9461070559610703</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.119425627460473</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8719</v>
+        <v>8641</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.02192852597626129</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1733816189930037</v>
+        <v>0.1839734215947226</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.820616206275075</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02773624675533625</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3172173913043479</v>
+        <v>0.3186507072905331</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.463914213175286</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5857</v>
+        <v>5812</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05294941214176091</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.774884753286666</v>
+        <v>1.79636958017894</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3698630136986302</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>315</v>
+        <v>313.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24600</v>
+        <v>24590</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1288681797960156</v>
+        <v>-0.128409025909568</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.02122814152094343</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.558965612090361</v>
+        <v>6.557933409646254</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.529245815581059</v>
+        <v>7.524095137045138</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.016438356164383</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524630649315597</v>
+        <v>0.001524870622396182</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>117.2</v>
+        <v>121.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24600</v>
+        <v>24590</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.0682370428479248</v>
+        <v>-0.08313270150148448</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1434146341463414</v>
+        <v>0.1819438796258641</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.018756787925314</v>
+        <v>2.019264809926389</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.166599103805999</v>
+        <v>2.202352306853115</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.013698630136986</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004953543715524568</v>
+        <v>0.004952297465315876</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2086</v>
+        <v>2101</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03949929638415043</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.903433731543624</v>
+        <v>2.875565332698715</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9534246575342465</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>234.9</v>
+        <v>229.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1544552707869758</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.407918263090677</v>
+        <v>2.48355091383812</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.733146510176117</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11620</v>
+        <v>11700</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.006737674069455539</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5407917383820999</v>
+        <v>0.5302564102564102</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.191474079169926</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.5</v>
+        <v>105.7</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>991.3</v>
+        <v>996.1</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03449391883538724</v>
+        <v>0.03377859504226127</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6665211237768587</v>
+        <v>0.6616345607870695</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.719344592630544</v>
+        <v>2.719501841925433</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.628671414223418</v>
+        <v>2.630642436366424</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.841095890410959</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003677356678921869</v>
+        <v>0.003677144043748801</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>212.6</v>
+        <v>211.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-9.204542012708913</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.001787394167450551</v>
+        <v>0.004829545454545503</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.6</v>
+        <v>211.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1162738117548097</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.004233301975540948</v>
+        <v>0.0108901515151516</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.305096663997173</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>242</v>
+        <v>242.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1811283650896597</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01490764462809913</v>
+        <v>0.01114717990942782</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.23407630038021</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17140</v>
+        <v>17120</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.0158468971624525</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1800037059509918</v>
+        <v>0.1813822149532711</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.842312363445059</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01798953824230569</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5098039215686274</v>
+        <v>0.4903225806451612</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.282899290457713</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22810</v>
+        <v>22790</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4769486359457286</v>
+        <v>-0.481792505018929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01443707145988604</v>
+        <v>0.0005196630100920974</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.517460426958017</v>
+        <v>1.517588697445183</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.901169046182941</v>
+        <v>2.928534828506517</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.504109589041096</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006589957683474186</v>
+        <v>0.006589400683356904</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>430.3</v>
+        <v>427</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04776571807714202</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5461439460841273</v>
+        <v>0.5580930679156908</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8684931506849316</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>182.7</v>
+        <v>180.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1004235344755982</v>
+        <v>0.100993841791344</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1883962780514505</v>
+        <v>0.2042754025541365</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.9203846515501</v>
+        <v>1.920230333929174</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.745132298052177</v>
+        <v>1.744088169289769</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.106849315068493</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005207290108222945</v>
+        <v>0.005207708587509919</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.5</v>
+        <v>90.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9328</v>
+        <v>9610</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02794586770942603</v>
+        <v>0.02743266207200229</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7092456941466552</v>
+        <v>0.6627553432882416</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.407342675769114</v>
+        <v>4.407421233514404</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.28752409461989</v>
+        <v>4.289742185756532</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.432876712328767</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002268940886983544</v>
+        <v>0.002268900445448498</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>62.3</v>
+        <v>63.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2258976949993705</v>
+        <v>0.2196659867156249</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.04067948372093011</v>
+        <v>0.05738380930232534</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.959029058088172</v>
+        <v>2.963259047002978</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.413765088358121</v>
+        <v>2.429566028140691</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.345205479452055</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003379486920774276</v>
+        <v>0.003374662775471465</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12900</v>
+        <v>12910</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,10 +3940,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.145033023318506</v>
+        <v>-2.150476557710941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02502159689922467</v>
+        <v>0.03436848954298988</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17870</v>
+        <v>18000</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1676599706402295</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.223782876329043</v>
+        <v>0.2149444444444444</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770028907288571</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64850</v>
+        <v>64900</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2624756769417703</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1975019275250578</v>
+        <v>0.1965793528505393</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.712142160089762</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>122.2</v>
+        <v>125.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.06627550169396419</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>0.01818330605564644</v>
+        <v>-0.009378980891719624</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.740920921548781</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8641</v>
+        <v>8640</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.02192852597626129</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1839734215947226</v>
+        <v>0.1841104555555555</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.820616206275075</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02773624675533625</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3186507072905331</v>
+        <v>0.3172173913043479</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.463914213175286</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5812</v>
+        <v>5933</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05294941214176091</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.79636958017894</v>
+        <v>1.739339288724086</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3698630136986302</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>313.9</v>
+        <v>313.8</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24590</v>
+        <v>24580</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.128409025909568</v>
+        <v>-0.1283671902392606</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02122814152094343</v>
+        <v>0.02131814483319783</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.557933409646254</v>
+        <v>6.557839268344832</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.524095137045138</v>
+        <v>7.523625998136692</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.016438356164383</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524870622396182</v>
+        <v>0.001524892512732163</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24590</v>
+        <v>24580</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08313270150148448</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1819438796258641</v>
+        <v>0.1824247355573636</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.019264809926389</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2101</v>
+        <v>2110</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03949929638415043</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.875565332698715</v>
+        <v>2.859034485308057</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9534246575342465</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>229.8</v>
+        <v>235</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1544552707869758</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.48355091383812</v>
+        <v>2.406468085106383</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.733146510176117</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11700</v>
+        <v>11730</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.006737674069455539</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5302564102564102</v>
+        <v>0.5263427109974426</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.191474079169926</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>996.1</v>
+        <v>996.6</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03377859504226127</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.6616345607870695</v>
+        <v>0.660800909090909</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.719501841925433</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>211.2</v>
+        <v>212.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-9.204542012708913</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>0.004829545454545503</v>
+        <v>-0.0008474576271186862</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>211.2</v>
+        <v>212.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1162738117548097</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.0108901515151516</v>
+        <v>0.00517890772128049</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.305096663997173</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>242.9</v>
+        <v>241.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1811283650896597</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.01114717990942782</v>
+        <v>0.0153272013228607</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.23407630038021</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>107.8</v>
+        <v>108.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.0158468971624525</v>
+        <v>-0.01781726862176821</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1813822149532711</v>
+        <v>0.1857658224299066</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.842312363445059</v>
+        <v>1.842358196789972</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.87197739674166</v>
+        <v>1.875779463363923</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.841095890410959</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005427961185311894</v>
+        <v>0.005427826150975133</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>155</v>
+        <v>153.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01798953824230569</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4903225806451612</v>
+        <v>0.5078328981723239</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.282899290457713</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22790</v>
+        <v>22750</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.481792505018929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0005196630100920974</v>
+        <v>0.002278818461538323</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.517588697445183</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>427</v>
+        <v>423.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04776571807714202</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5580930679156908</v>
+        <v>0.570228321925891</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8684931506849316</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>180.1</v>
+        <v>180.2</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.100993841791344</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2042754025541365</v>
+        <v>0.2036071032186459</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.920230333929174</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>90.7</v>
+        <v>91</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9610</v>
+        <v>9661</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02743266207200229</v>
+        <v>0.02666546061512362</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6627553432882416</v>
+        <v>0.6594484390849809</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.407421233514404</v>
+        <v>4.407538506402915</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.289742185756532</v>
+        <v>4.29306202992565</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.432876712328767</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002268900445448498</v>
+        <v>0.002268840076036275</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2196659867156249</v>
+        <v>0.2184356678474524</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.05738380930232534</v>
+        <v>0.06072467441860452</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.963259047002978</v>
+        <v>2.964091953987516</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.429566028140691</v>
+        <v>2.432702876487542</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.345205479452055</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003374662775471465</v>
+        <v>0.003373714498481486</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1469943686646569</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9816272965879265</v>
+        <v>0.986842105263158</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.037279606145893</v>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3704,7 +3704,7 @@
         <v>56.27383300460225</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>0.01572727272727259</v>
+        <v>-0.02843478260869559</v>
       </c>
       <c r="BA26" s="8" t="n">
         <v>0.3698630136986302</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12910</v>
+        <v>12940</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.150476557710941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03436848954298988</v>
+        <v>0.03197041731066474</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18000</v>
+        <v>18010</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1676599706402295</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2149444444444444</v>
+        <v>0.2142698500832871</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770028907288571</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>64900</v>
+        <v>65580</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2624756769417703</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1965793528505393</v>
+        <v>0.1841720036596524</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.712142160089762</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06286724894712532</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9461070559610703</v>
+        <v>0.953235653235653</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.119425627460473</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8640</v>
+        <v>8780</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.02192852597626129</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1841104555555555</v>
+        <v>0.1652294232346241</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.820616206275075</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5933</v>
+        <v>5921</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05294941214176091</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.739339288724086</v>
+        <v>1.744891065698362</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3698630136986302</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>313.8</v>
+        <v>316.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24580</v>
+        <v>24860</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1283671902392606</v>
+        <v>-0.1294912497481557</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02131814483319783</v>
+        <v>0.01850362027353181</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.557839268344832</v>
+        <v>6.560363333889629</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.523625998136692</v>
+        <v>7.536240539789715</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.016438356164383</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524892512732163</v>
+        <v>0.001524305818298484</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>121.1</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24580</v>
+        <v>24860</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08313270150148448</v>
+        <v>-0.09013257573521996</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1824247355573636</v>
+        <v>0.1874497184231698</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.019264809926389</v>
+        <v>2.019501421182418</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.202352306853115</v>
+        <v>2.219555692758513</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.013698630136986</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004952297465315876</v>
+        <v>0.00495171723828003</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2110</v>
+        <v>2098</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03949929638415043</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.859034485308057</v>
+        <v>2.881107132507149</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9534246575342465</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>235</v>
+        <v>238.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1544552707869758</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.406468085106383</v>
+        <v>2.360705289672544</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.733146510176117</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.9</v>
+        <v>110.8</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11730</v>
+        <v>11920</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.006737674069455539</v>
+        <v>-0.004419840143397853</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5263427109974426</v>
+        <v>0.4872483221476509</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.191474079169926</v>
+        <v>4.190299590111092</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.219906433321244</v>
+        <v>4.208902265302916</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.35068493150685</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002385795500846897</v>
+        <v>0.002386464209766654</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>996.6</v>
+        <v>1006</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03377859504226127</v>
+        <v>0.03485228745123355</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.660800909090909</v>
+        <v>0.640612815109344</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.719501841925433</v>
+        <v>2.719265791363898</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.630642436366424</v>
+        <v>2.627684959813205</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.841095890410959</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003677144043748801</v>
+        <v>0.003677463244585706</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157.2</v>
+        <v>157.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>212.4</v>
+        <v>213</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-9.204542012708913</v>
+        <v>-9.246207319121783</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.0008474576271186862</v>
+        <v>-0.001126760563380236</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>213.5</v>
+        <v>212.8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>212.4</v>
+        <v>213</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1162738117548097</v>
+        <v>-0.1156059357667944</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.00517890772128049</v>
+        <v>-0.0009389671361501595</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.305096663997173</v>
+        <v>4.304489096246022</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.871527766474564</v>
+        <v>4.867161902514729</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.591780821917808</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002322828215131238</v>
+        <v>0.002323156076460056</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>241.9</v>
+        <v>245</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1811283650896597</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.0153272013228607</v>
+        <v>0.002480204081632742</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.23407630038021</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>177</v>
+        <v>173.4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1896255000058667</v>
+        <v>-0.1815128079075159</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1879926108374383</v>
+        <v>0.1638300492610838</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.993775780776176</v>
+        <v>1.991877743488901</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.460314065645711</v>
+        <v>2.433608934547422</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.106849315068493</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005015609125368654</v>
+        <v>0.005020388441353013</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>108.2</v>
+        <v>106.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.01781726862176821</v>
+        <v>-0.007851063584615622</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1857658224299066</v>
+        <v>0.163847785046729</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.842358196789972</v>
+        <v>1.842126414334303</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.875779463363923</v>
+        <v>1.856703511662141</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.841095890410959</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005427826150975133</v>
+        <v>0.005428509098065208</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.2</v>
+        <v>153.4</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01798953824230569</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5078328981723239</v>
+        <v>0.5058670143415906</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.282899290457713</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22750</v>
+        <v>23070</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.481792505018929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.002278818461538323</v>
+        <v>-0.01162361855223248</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.517588697445183</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>423.7</v>
+        <v>426.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04776571807714202</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.570228321925891</v>
+        <v>0.5610176912247771</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8684931506849316</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>180.2</v>
+        <v>180</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.100993841791344</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2036071032186459</v>
+        <v>0.2049444444444444</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.920230333929174</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9661</v>
+        <v>9657</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02666546061512362</v>
+        <v>0.02438241311370935</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6594484390849809</v>
+        <v>0.6765547202029618</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.407538506402915</v>
+        <v>4.407886323052187</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.29306202992565</v>
+        <v>4.302969542061924</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.432876712328767</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002268840076036275</v>
+        <v>0.002268661046838345</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1178</v>
+        <v>1194</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05453571178101615</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5638167741935485</v>
+        <v>0.5428611055276382</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3643835616438357</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12940</v>
+        <v>13000</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.150476557710941</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.03197041731066474</v>
+        <v>0.02720747692307701</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18010</v>
+        <v>18180</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1676599706402295</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2142698500832871</v>
+        <v>0.202915291529153</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.770028907288571</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>65580</v>
+        <v>66280</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2624756769417703</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1841720036596524</v>
+        <v>0.1716656608328304</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.712142160089762</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>125.6</v>
+        <v>125</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.06627550169396419</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.009378980891719624</v>
+        <v>-0.004623999999999961</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.740920921548781</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>819</v>
+        <v>856</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06286724894712532</v>
+        <v>0.07039177318668359</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.953235653235653</v>
+        <v>0.8271028037383177</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.119425627460473</v>
+        <v>3.112918959982039</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.934915560292756</v>
+        <v>2.908205236587824</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.345205479452055</v>
+        <v>3.342465753424658</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003205718357882765</v>
+        <v>0.003212418995982375</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>104.8</v>
+        <v>107.2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8780</v>
+        <v>8824</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.02192852597626129</v>
+        <v>0.009322069896764811</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1652294232346241</v>
+        <v>0.185970705349048</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.820616206275075</v>
+        <v>1.818408453917869</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.781549452820898</v>
+        <v>1.801613685217305</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.841095890410959</v>
+        <v>1.838356164383562</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005492645822624908</v>
+        <v>0.005499314512344246</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.2</v>
+        <v>109.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92</v>
+        <v>94.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02773624675533625</v>
+        <v>0.02416375588731291</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3172173913043479</v>
+        <v>0.2997676874340023</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.463914213175286</v>
+        <v>4.464831371132245</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.343443395392836</v>
+        <v>4.359489725609372</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.841095890410959</v>
+        <v>4.838356164383562</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002240186419910334</v>
+        <v>0.002239726244681012</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5921</v>
+        <v>5903</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05294941214176091</v>
+        <v>0.05325256976639808</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.744891065698362</v>
+        <v>1.753261053701508</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3698630136986302</v>
+        <v>0.3671232876712329</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3512638018822833</v>
+        <v>0.3485614924753115</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3424657534246575</v>
+        <v>0.3397260273972603</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02703703703703704</v>
+        <v>0.02723880597014925</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>316.5</v>
+        <v>319.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24860</v>
+        <v>24820</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1294912497481557</v>
+        <v>-0.1307823191010174</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01850362027353181</v>
+        <v>0.0298146655922642</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.560363333889629</v>
+        <v>6.56050896627573</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.536240539789715</v>
+        <v>7.54760183834568</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.016438356164383</v>
+        <v>7.013698630136986</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524305818298484</v>
+        <v>0.001524271981244894</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24860</v>
+        <v>24820</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09013257573521996</v>
+        <v>-0.09025681128454807</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1874497184231698</v>
+        <v>0.1893634165995166</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.019501421182418</v>
+        <v>2.016765882326986</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.219555692758513</v>
+        <v>2.216851862529071</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.013698630136986</v>
+        <v>2.010958904109589</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.00495171723828003</v>
+        <v>0.004958433741680416</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03949929638415043</v>
+        <v>0.03960538913520929</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.881107132507149</v>
+        <v>2.873721581351094</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9534246575342465</v>
+        <v>0.9506849315068491</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9171960585742477</v>
+        <v>0.9144671059253279</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9260273972602739</v>
+        <v>0.9232876712328767</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01048850574712644</v>
+        <v>0.01051873198847262</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>83.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>238.2</v>
+        <v>231.3</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1544552707869758</v>
+        <v>0.160947414288893</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.360705289672544</v>
+        <v>2.427998270644184</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.733146510176117</v>
+        <v>1.730151529304168</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.501267787529486</v>
+        <v>1.490292762626053</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.761643835616438</v>
+        <v>1.758904109589041</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005769852658898313</v>
+        <v>0.005779840569237193</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>110.8</v>
+        <v>111.3</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11920</v>
+        <v>12120</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.004419840143397853</v>
+        <v>-0.005492091648701787</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4872483221476509</v>
+        <v>0.4693069306930693</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.190299590111092</v>
+        <v>4.18810387176399</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.208902265302916</v>
+        <v>4.211232345760886</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.35068493150685</v>
+        <v>4.347945205479452</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002386464209766654</v>
+        <v>0.002387715373398343</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105.4</v>
+        <v>104.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1006</v>
+        <v>1037</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03485228745123355</v>
+        <v>0.03772045497864172</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.640612815109344</v>
+        <v>0.5794882430086787</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.719265791363898</v>
+        <v>2.715894876557588</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.627684959813205</v>
+        <v>2.617173886789662</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.841095890410959</v>
+        <v>2.838356164383562</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003677463244585706</v>
+        <v>0.003682027638961879</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>157.6</v>
+        <v>159.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-9.246207319121783</v>
+        <v>-10.15800668000952</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.001126760563380236</v>
+        <v>-0.008341013824884724</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.01643835616438356</v>
+        <v>0.0136986301369863</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>212.8</v>
+        <v>213</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1156059357667944</v>
+        <v>-0.1158807357736761</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.0009389671361501595</v>
+        <v>-0.01843317972350234</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.304489096246022</v>
+        <v>4.301999448481613</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.867161902514729</v>
+        <v>4.865858739370657</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.591780821917808</v>
+        <v>4.589041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002323156076460056</v>
+        <v>0.002324500530452065</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>245</v>
+        <v>245.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1811283650896597</v>
+        <v>-0.1812797160692919</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.002480204081632742</v>
+        <v>3.114820846916722e-05</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.23407630038021</v>
+        <v>3.231388815943629</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.949430121284289</v>
+        <v>3.946877681385399</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.345205479452055</v>
+        <v>3.342465753424658</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003092072997419499</v>
+        <v>0.003094644615547387</v>
       </c>
     </row>
     <row r="15">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>173.4</v>
+        <v>176.2</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.2</v>
+        <v>82</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1815128079075159</v>
+        <v>-0.1881195698381118</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1638300492610838</v>
+        <v>0.1710853658536584</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.991877743488901</v>
+        <v>1.990684475677455</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.433608934547422</v>
+        <v>2.451942923763434</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.106849315068493</v>
+        <v>2.104109589041096</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005020388441353013</v>
+        <v>0.00502339779215733</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106.2</v>
+        <v>109.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17120</v>
+        <v>17680</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.007851063584615622</v>
+        <v>-0.02324553264777342</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.163847785046729</v>
+        <v>0.1598807194570135</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.842126414334303</v>
+        <v>1.839744761339811</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.856703511662141</v>
+        <v>1.883528381832711</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.841095890410959</v>
+        <v>1.838356164383562</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005428509098065208</v>
+        <v>0.00543553660819635</v>
       </c>
     </row>
     <row r="17">
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>76.2</v>
+        <v>77.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05321909016563546</v>
+        <v>0.05322180628186696</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>1.013779527559055</v>
+        <v>0.9800000000000002</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.091340482027312</v>
+        <v>3.088599259645629</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.935135254281376</v>
+        <v>2.93252498307944</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.345205479452055</v>
+        <v>3.342465753424658</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003234842638052592</v>
+        <v>0.003237713655719568</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1467271949473812</v>
+        <v>0.1468635788601355</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.280918953414167</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.81397479457584</v>
+        <v>1.811229229250245</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.581871261594242</v>
+        <v>1.579289169728818</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.841095890410959</v>
+        <v>1.838356164383562</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005512755761492424</v>
+        <v>0.005521112313398058</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153.4</v>
+        <v>145</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01798953824230569</v>
+        <v>0.01796871250033176</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5058670143415906</v>
+        <v>0.5931034482758621</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.282899290457713</v>
+        <v>3.280170217273238</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.224885096683876</v>
+        <v>3.222270170972635</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.506849315068493</v>
+        <v>3.504109589041096</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003046087959221487</v>
+        <v>0.003048622277996557</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23070</v>
+        <v>23900</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.481792505018929</v>
+        <v>-0.4775707973417874</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01162361855223248</v>
+        <v>-0.05938533891213393</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.517588697445183</v>
+        <v>1.514737174517392</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.928534828506517</v>
+        <v>2.899411378250183</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.504109589041096</v>
+        <v>1.501369863013699</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006589400683356904</v>
+        <v>0.006601805361505095</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>426.2</v>
+        <v>432.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04776571807714202</v>
+        <v>0.04779760905021074</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5610176912247771</v>
+        <v>0.5372128927911275</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8684931506849316</v>
+        <v>0.8657534246575342</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8289001402706598</v>
+        <v>0.8262601643482534</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8410958904109589</v>
+        <v>0.8383561643835616</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01151419558359621</v>
+        <v>0.01155063291139241</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>180</v>
+        <v>176.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.100993841791344</v>
+        <v>0.1004645515360342</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2049444444444444</v>
+        <v>0.2329358319136854</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.920230333929174</v>
+        <v>1.917633828000093</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.744088169289769</v>
+        <v>1.742567559603305</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.106849315068493</v>
+        <v>2.104109589041096</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005207708587509919</v>
+        <v>0.005214759905664074</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9657</v>
+        <v>9539</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02438241311370935</v>
+        <v>0.02464677067458266</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6765547202029618</v>
+        <v>0.6954472613481497</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.407886323052187</v>
+        <v>4.405106411999713</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.302969542061924</v>
+        <v>4.299146338107895</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.432876712328767</v>
+        <v>4.43013698630137</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002268661046838345</v>
+        <v>0.002270092720747799</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2184356678474524</v>
+        <v>0.2089008923020419</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.06072467441860452</v>
+        <v>0.1016852549738219</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.964091953987516</v>
+        <v>2.967782181209422</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.432702876487542</v>
+        <v>2.454942501992898</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.345205479452055</v>
+        <v>3.342465753424658</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003373714498481486</v>
+        <v>0.003369519523135902</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1469943686646569</v>
+        <v>0.1470705664930828</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.986842105263158</v>
+        <v>0.9610389610389611</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.037279606145893</v>
+        <v>3.034494046288351</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.648033581613767</v>
+        <v>2.645429265581848</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.345205479452055</v>
+        <v>3.342465753424658</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003292419960205554</v>
+        <v>0.003295442287069743</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3687,7 +3687,7 @@
         <v>0.55865</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK26" s="10" t="n">
         <v>46377</v>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>56.27383300460225</v>
+        <v>56.65864939053991</v>
       </c>
       <c r="AZ26" s="12" t="n">
-        <v>-0.02843478260869559</v>
+        <v>-0.06891666666666663</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3698630136986302</v>
+        <v>0.3671232876712329</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006457800958928484</v>
+        <v>0.006367185002628019</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3424657534246575</v>
+        <v>0.3397260273972603</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02703703703703703</v>
+        <v>0.02723880597014925</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1194</v>
+        <v>1183</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05453571178101615</v>
+        <v>0.05473798095294582</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5428611055276382</v>
+        <v>0.557207235841082</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3643835616438357</v>
+        <v>0.3616438356164384</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3455393284201106</v>
+        <v>0.3428755218331064</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3424657534246575</v>
+        <v>0.3397260273972603</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02744360902255639</v>
+        <v>0.02765151515151515</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>509.4</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13000</v>
+        <v>13280</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.150476557710941</v>
+        <v>-2.165887353904286</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.02720747692307701</v>
+        <v>0.00436648855421673</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3424657534246575</v>
+        <v>0.3397260273972603</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>190</v>
+        <v>190.1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18180</v>
+        <v>18110</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1676599706402295</v>
+        <v>-0.1679904418740883</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.202915291529153</v>
+        <v>0.2082004417448922</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.770028907288571</v>
+        <v>2.767348842014341</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.328001549341867</v>
+        <v>3.32610222441164</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.841095890410959</v>
+        <v>2.838356164383562</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003610070629114283</v>
+        <v>0.00361356683630859</v>
       </c>
     </row>
     <row r="30">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05648301894514204</v>
+        <v>0.05570767316257446</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6333478863292414</v>
+        <v>0.6366277013620312</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.714483349837002</v>
+        <v>2.711915929217185</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.569358239706787</v>
+        <v>2.568813316562455</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.841095890410959</v>
+        <v>2.838356164383562</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003683942287065595</v>
+        <v>0.003687429942891546</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1153196085856532</v>
+        <v>0.1153752517536956</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.122758871611253</v>
+        <v>1.139171955670103</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.249961791613001</v>
+        <v>2.24720794751451</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.017324697147751</v>
+        <v>2.014755073668026</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.413698630136986</v>
+        <v>2.410958904109589</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004444519919083152</v>
+        <v>0.004449966462187155</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66280</v>
+        <v>67100</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2624756769417703</v>
+        <v>-0.2628614894897362</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1716656608328304</v>
+        <v>0.1573472429210134</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.712142160089762</v>
+        <v>1.709416465868562</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.321472128526104</v>
+        <v>2.318989499931656</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.715068493150685</v>
+        <v>1.712328767123288</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.0058406365038495</v>
+        <v>0.005849949500117254</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>125</v>
+        <v>126.1</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.06627550169396419</v>
+        <v>-0.06637612519156667</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.004623999999999961</v>
+        <v>-0.01330689928628059</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.740920921548781</v>
+        <v>2.738202142406131</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.935470715956755</v>
+        <v>2.932875022040296</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.841095890410959</v>
+        <v>2.838356164383562</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003648408796248457</v>
+        <v>0.003652031325639361</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1335</v>
+        <v>1312</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03321129192047901</v>
+        <v>0.03319335582365446</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3752808988764045</v>
+        <v>0.399390243902439</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.743704263061437</v>
+        <v>1.740965245002573</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.687655058260476</v>
+        <v>1.68503333397328</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.761643835616438</v>
+        <v>1.758904109589041</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005734917446633358</v>
+        <v>0.005743940052051538</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>94.2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>856</v>
+        <v>854.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.07039177318668359</v>
+        <v>0.06253074079059175</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8271028037383177</v>
+        <v>0.8734206832007489</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.112918959982039</v>
+        <v>3.116853670125165</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.908205236587824</v>
+        <v>2.933424465259258</v>
       </c>
       <c r="BC2" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003212418995982375</v>
+        <v>0.003208363644353707</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8824</v>
+        <v>8950</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.009322069896764811</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.185970705349048</v>
+        <v>0.169274357988827</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.818408453917869</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>94.7</v>
+        <v>91.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02416375588731291</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2997676874340023</v>
+        <v>0.3452240437158471</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.464831371132245</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5903</v>
+        <v>5871</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05325256976639808</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.753261053701508</v>
+        <v>1.768267756770567</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3671232876712329</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24820</v>
+        <v>24660</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1307823191010174</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.0298146655922642</v>
+        <v>0.03649635036496357</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.56050896627573</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24820</v>
+        <v>24660</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09025681128454807</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1893634165995166</v>
+        <v>0.197080291970803</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.016765882326986</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2102</v>
+        <v>2108</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03960538913520929</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.873721581351094</v>
+        <v>2.862695808349146</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9506849315068491</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12120</v>
+        <v>11910</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005492091648701787</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4693069306930693</v>
+        <v>0.4952141057934509</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.18810387176399</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.6</v>
+        <v>104.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03772045497864172</v>
+        <v>0.03808342390083946</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5794882430086787</v>
+        <v>0.5871614064015518</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.715894876557588</v>
+        <v>2.715814934463467</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.617173886789662</v>
+        <v>2.616181774927262</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.838356164383562</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003682027638961879</v>
+        <v>0.003682136022267507</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>159.4</v>
+        <v>161.5</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217</v>
+        <v>220.3</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,10 +2105,10 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-10.15800668000952</v>
+        <v>-10.38491084425846</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.008341013824884724</v>
+        <v>-0.01032682705401733</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>213</v>
+        <v>219.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217</v>
+        <v>220.3</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1158807357736761</v>
+        <v>-0.1223412701409858</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.01843317972350234</v>
+        <v>-0.001815705855651384</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.301999448481613</v>
+        <v>4.307841611011165</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.865858739370657</v>
+        <v>4.908333346952716</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.589041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002324500530452065</v>
+        <v>0.002321348114201612</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>245.6</v>
+        <v>243.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1812797160692919</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>3.114820846916722e-05</v>
+        <v>0.007001435014350132</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.231388815943629</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>82</v>
+        <v>81.2</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1881195698381118</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1710853658536584</v>
+        <v>0.1826231527093596</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.990684475677455</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>109.3</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17680</v>
+        <v>17920</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02324553264777342</v>
+        <v>-0.03607522453225612</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1598807194570135</v>
+        <v>0.172615</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.839744761339811</v>
+        <v>1.84004337875121</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.883528381832711</v>
+        <v>1.9089076508676</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.838356164383562</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00543553660819635</v>
+        <v>0.005434654484497395</v>
       </c>
     </row>
     <row r="17">
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>156.7</v>
+        <v>155.1</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2800,7 +2800,7 @@
         <v>0.1468635788601355</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.280918953414167</v>
+        <v>1.304448742746615</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.811229229250245</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01796871250033176</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5931034482758621</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.280170217273238</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>280</v>
+        <v>297.3</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23900</v>
+        <v>24360</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4775707973417874</v>
+        <v>-0.4977502775489129</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.05938533891213393</v>
+        <v>-0.02012824655172418</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.514737174517392</v>
+        <v>1.515271785353681</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>2.899411378250183</v>
+        <v>3.01696888543577</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.501369863013699</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006601805361505095</v>
+        <v>0.006599476144582134</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>432.8</v>
+        <v>441.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04779760905021074</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5372128927911275</v>
+        <v>0.5065800271739129</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8657534246575342</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>176.1</v>
+        <v>177.4</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.1004645515360342</v>
+        <v>0.09705733050804594</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2329358319136854</v>
+        <v>0.2316798196166852</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.917633828000093</v>
+        <v>1.918555071693733</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.742567559603305</v>
+        <v>1.748819335453738</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.104109589041096</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005214759905664074</v>
+        <v>0.005212255904216411</v>
       </c>
     </row>
     <row r="23">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9539</v>
+        <v>9479</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02464677067458266</v>
+        <v>0.02515271988724753</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6954472613481497</v>
+        <v>0.7024619065302247</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.405106411999713</v>
+        <v>4.40502943750212</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.299146338107895</v>
+        <v>4.296949471086232</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.43013698630137</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002270092720747799</v>
+        <v>0.002270132388870146</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1470705664930828</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9610389610389611</v>
+        <v>0.9661458333333335</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.034494046288351</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1183</v>
+        <v>1202</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05473798095294582</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.557207235841082</v>
+        <v>0.532592479201331</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3616438356164384</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13280</v>
+        <v>13370</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.165887353904286</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.00436648855421673</v>
+        <v>-0.002394392819745739</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18110</v>
+        <v>18080</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1679904418740883</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2082004417448922</v>
+        <v>0.2102051991150442</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.767348842014341</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>594.7</v>
+        <v>585</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05570767316257446</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6366277013620312</v>
+        <v>0.6637649470085472</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.711915929217185</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1153752517536956</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.139171955670103</v>
+        <v>1.122758871611253</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.24720794751451</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67100</v>
+        <v>67740</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2628614894897362</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1573472429210134</v>
+        <v>0.1464127546501328</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.709416465868562</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>139.8</v>
+        <v>141.8</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>126.1</v>
+        <v>127</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.06637612519156667</v>
+        <v>-0.07118086968030556</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01330689928628059</v>
+        <v>-0.006283464566929076</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.738202142406131</v>
+        <v>2.739200915885041</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.932875022040296</v>
+        <v>2.949121983461111</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.838356164383562</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003652031325639361</v>
+        <v>0.003650699713923314</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>854.8</v>
+        <v>830</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06253074079059175</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8734206832007489</v>
+        <v>0.929397590361446</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.116853670125165</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8950</v>
+        <v>8862</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.009322069896764811</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.169274357988827</v>
+        <v>0.1808852972241031</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.818408453917869</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.9</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02416375588731291</v>
+        <v>0.02815069132135843</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3452240437158471</v>
+        <v>0.3020452099031217</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.464831371132245</v>
+        <v>4.460748933191376</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.359489725609372</v>
+        <v>4.338613951091656</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.838356164383562</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002239726244681012</v>
+        <v>0.002241776022315977</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5871</v>
+        <v>5946</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05325256976639808</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.768267756770567</v>
+        <v>1.73335015136226</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3671232876712329</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24660</v>
+        <v>24400</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1307823191010174</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03649635036496357</v>
+        <v>0.04754098360655745</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.56050896627573</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24660</v>
+        <v>24400</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09025681128454807</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.197080291970803</v>
+        <v>0.2098360655737705</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.016765882326986</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2108</v>
+        <v>2123</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03960538913520929</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.862695808349146</v>
+        <v>2.835404033914272</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9506849315068491</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>231.3</v>
+        <v>229.7</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.160947414288893</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.427998270644184</v>
+        <v>2.451876360470179</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.730151529304168</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11910</v>
+        <v>11970</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005492091648701787</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4952141057934509</v>
+        <v>0.487719298245614</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.18810387176399</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03808342390083946</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5871614064015518</v>
+        <v>0.5810274492753622</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.715814934463467</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.3</v>
+        <v>219.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-10.38491084425846</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.01032682705401733</v>
+        <v>-0.005360401459853947</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219.9</v>
+        <v>218.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.3</v>
+        <v>219.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1223412701409858</v>
+        <v>-0.1208661905382414</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001815705855651384</v>
+        <v>-0.004105839416058243</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.307841611011165</v>
+        <v>4.306513997413078</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.908333346952716</v>
+        <v>4.898587622343521</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.589041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002321348114201612</v>
+        <v>0.002322063740186842</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.9</v>
+        <v>244.2</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1812797160692919</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.007001435014350132</v>
+        <v>0.005764332514332615</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.231388815943629</v>
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>155.1</v>
+        <v>155</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2800,7 +2800,7 @@
         <v>0.1468635788601355</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.304448742746615</v>
+        <v>1.305935483870968</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>1.811229229250245</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>147</v>
+        <v>145.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.01796871250033176</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5898141775636612</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.280170217273238</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>297.3</v>
+        <v>304.5</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24360</v>
+        <v>24400</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.4977502775489129</v>
+        <v>-0.5055849422771767</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.02012824655172418</v>
+        <v>0.001957000409835929</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.515271785353681</v>
+        <v>1.515479503793718</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.01696888543577</v>
+        <v>3.065196903131779</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.501369863013699</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006599476144582134</v>
+        <v>0.006598571590685907</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>441.6</v>
+        <v>437.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04779760905021074</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5065800271739129</v>
+        <v>0.5193097510847227</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8657534246575342</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>177.4</v>
+        <v>180.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09705733050804594</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2316798196166852</v>
+        <v>0.2078496406854613</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.918555071693733</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9479</v>
+        <v>9539</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02515271988724753</v>
+        <v>0.02489957542588311</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7024619065302247</v>
+        <v>0.6936003689065942</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.40502943750212</v>
+        <v>4.405067961284015</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.296949471086232</v>
+        <v>4.298048381426589</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.43013698630137</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002270132388870146</v>
+        <v>0.002270112535808674</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13370</v>
+        <v>13380</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.165887353904286</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.002394392819745739</v>
+        <v>-0.003139987443946279</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18080</v>
+        <v>18050</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1679904418740883</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2102051991150442</v>
+        <v>0.2122166204986149</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.767348842014341</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67740</v>
+        <v>67640</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2628614894897362</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1464127546501328</v>
+        <v>0.148107628622117</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.709416465868562</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>830</v>
+        <v>849.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06253074079059175</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.929397590361446</v>
+        <v>0.8844433984466935</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.116853670125165</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8862</v>
+        <v>8860</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.009322069896764811</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1808852972241031</v>
+        <v>0.1811518627539503</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.818408453917869</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02815069132135843</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3020452099031217</v>
+        <v>0.3048543689320389</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.460748933191376</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24400</v>
+        <v>24300</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1307823191010174</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04754098360655745</v>
+        <v>0.05185185185185182</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.56050896627573</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24400</v>
+        <v>24300</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09025681128454807</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2098360655737705</v>
+        <v>0.2148148148148148</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.016765882326986</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2123</v>
+        <v>2104</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03960538913520929</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.835404033914272</v>
+        <v>2.870039336501901</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9506849315068491</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11970</v>
+        <v>11960</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005492091648701787</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.487719298245614</v>
+        <v>0.4889632107023412</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.18810387176399</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.5</v>
+        <v>104.7</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1035</v>
+        <v>1022</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03808342390083946</v>
+        <v>0.03735796785993852</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5810274492753622</v>
+        <v>0.604202745596869</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.715814934463467</v>
+        <v>2.715974698054486</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.616181774927262</v>
+        <v>2.618165360658983</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.838356164383562</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003682136022267507</v>
+        <v>0.003681919425524555</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>219.2</v>
+        <v>219</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-10.38491084425846</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.005360401459853947</v>
+        <v>-0.004452054794520488</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>219.2</v>
+        <v>219</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1208661905382414</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.004105839416058243</v>
+        <v>-0.003196347031963365</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.306513997413078</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>244.2</v>
+        <v>244.5</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1812797160692919</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.005764332514332615</v>
+        <v>0.004530265848670778</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.231388815943629</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>111.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17920</v>
+        <v>17940</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03607522453225612</v>
+        <v>-0.03560859644981636</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.172615</v>
+        <v>0.1702619264214047</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.84004337875121</v>
+        <v>1.840032514552519</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.9089076508676</v>
+        <v>1.907972746105851</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.838356164383562</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005434654484497395</v>
+        <v>0.005434686572607613</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05322180628186696</v>
+        <v>0.05624426799672135</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9800000000000002</v>
+        <v>0.9620000000000002</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.088599259645629</v>
+        <v>3.086931589723232</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.93252498307944</v>
+        <v>2.922554643139435</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003237713655719568</v>
+        <v>0.003239462783461483</v>
       </c>
     </row>
     <row r="18">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110</v>
+        <v>107.2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145.3</v>
+        <v>146</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01796871250033176</v>
+        <v>0.02584407981813247</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5898141775636612</v>
+        <v>0.541917808219178</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.280170217273238</v>
+        <v>3.276124571923132</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.222270170972635</v>
+        <v>3.193589197789144</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.504109589041096</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003048622277996557</v>
+        <v>0.003052386983602964</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24400</v>
+        <v>24270</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5055849422771767</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.001957000409835929</v>
+        <v>0.007323889987638887</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.515479503793718</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>437.9</v>
+        <v>436.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04779760905021074</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5193097510847227</v>
+        <v>0.5227872281986725</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8657534246575342</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>180.9</v>
+        <v>177.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09705733050804594</v>
+        <v>0.09480377677949926</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2078496406854613</v>
+        <v>0.236169014084507</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.918555071693733</v>
+        <v>1.919163707241879</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.748819335453738</v>
+        <v>1.752975051736976</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.104109589041096</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005212255904216411</v>
+        <v>0.005210602911187537</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9539</v>
+        <v>9532</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02489957542588311</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6936003689065942</v>
+        <v>0.6948440955728075</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.405067961284015</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2089008923020419</v>
+        <v>0.2173397168100258</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1016852549738219</v>
+        <v>0.07799309895287965</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.967782181209422</v>
+        <v>2.962093552664248</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.454942501992898</v>
+        <v>2.433251385592065</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003369519523135902</v>
+        <v>0.003375990603337131</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18050</v>
+        <v>18070</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1679904418740883</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2122166204986149</v>
+        <v>0.210874930824571</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.767348842014341</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67640</v>
+        <v>67350</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2628614894897362</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.148107628622117</v>
+        <v>0.1530512249443208</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.709416465868562</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127</v>
+        <v>127.8</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07118086968030556</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.006283464566929076</v>
+        <v>-0.01250391236306714</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.739200915885041</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1312</v>
+        <v>1348</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03319335582365446</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.399390243902439</v>
+        <v>0.3620178041543027</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.740965245002573</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8860</v>
+        <v>8794</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.009322069896764811</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1811518627539503</v>
+        <v>0.1900165458267</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.818408453917869</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.7</v>
+        <v>93</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02815069132135843</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3048543689320389</v>
+        <v>0.3006451612903227</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.460748933191376</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5946</v>
+        <v>5876</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05325256976639808</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.73335015136226</v>
+        <v>1.765912185159973</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3671232876712329</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09025681128454807</v>
+        <v>-0.08287507062277596</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2148148148148148</v>
+        <v>0.1950617283950618</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.016765882326986</v>
+        <v>2.016516349501799</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.216851862529071</v>
+        <v>2.198736818626356</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.010958904109589</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004958433741680416</v>
+        <v>0.004959047320628272</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2104</v>
+        <v>2108</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03960538913520929</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.870039336501901</v>
+        <v>2.862695808349146</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9506849315068491</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>229.7</v>
+        <v>232.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.160947414288893</v>
+        <v>0.1617450355014498</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.451876360470179</v>
+        <v>2.401817010309278</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.730151529304168</v>
+        <v>1.730120178271133</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.490292762626053</v>
+        <v>1.489242583700263</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005779840569237193</v>
+        <v>0.005779945304142256</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11960</v>
+        <v>11840</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005492091648701787</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4889632107023412</v>
+        <v>0.5040540540540541</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.18810387176399</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1022</v>
+        <v>1031</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03735796785993852</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.604202745596869</v>
+        <v>0.590199035887488</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.715974698054486</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>219</v>
+        <v>221.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-10.38491084425846</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.004452054794520488</v>
+        <v>-0.01568848758465013</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>218.3</v>
+        <v>219.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>219</v>
+        <v>221.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1208661905382414</v>
+        <v>-0.1220657269288503</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003196347031963365</v>
+        <v>-0.008577878103837477</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.306513997413078</v>
+        <v>4.307593896322358</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.898587622343521</v>
+        <v>4.90651069043441</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.589041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002322063740186842</v>
+        <v>0.002321481606828716</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>217.4</v>
+        <v>212</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>244.5</v>
+        <v>243.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1812797160692919</v>
+        <v>-0.1749547409691311</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>0.004530265848670778</v>
+        <v>-0.01720558063192446</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.231388815943629</v>
+        <v>3.229195469878952</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.946877681385399</v>
+        <v>3.91396160941776</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003094644615547387</v>
+        <v>0.003096746571484214</v>
       </c>
     </row>
     <row r="15">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.9</v>
+        <v>110.9</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17940</v>
+        <v>17920</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03560859644981636</v>
+        <v>-0.03090660354989684</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1702619264214047</v>
+        <v>0.1610982455357144</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.840032514552519</v>
+        <v>1.839923054586535</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.907972746105851</v>
+        <v>1.898602406461934</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.838356164383562</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005434686572607613</v>
+        <v>0.005435009890806105</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05624426799672135</v>
+        <v>0.05590660479293472</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9620000000000002</v>
+        <v>0.9640000000000002</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.086931589723232</v>
+        <v>3.087118150544056</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.922554643139435</v>
+        <v>2.923665915651172</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003239462783461483</v>
+        <v>0.003239267016145028</v>
       </c>
     </row>
     <row r="18">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>107.2</v>
+        <v>109.5</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02584407981813247</v>
+        <v>0.01935539970890273</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.541917808219178</v>
+        <v>0.5858620689655174</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.276124571923132</v>
+        <v>3.279460367457296</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.193589197789144</v>
+        <v>3.217190362059996</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.504109589041096</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003052386983602964</v>
+        <v>0.003049282162160545</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24270</v>
+        <v>24260</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5055849422771767</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007323889987638887</v>
+        <v>0.007739110057707999</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.515479503793718</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>436.9</v>
+        <v>428.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04779760905021074</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5227872281986725</v>
+        <v>0.5540895585143657</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8657534246575342</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>177.5</v>
+        <v>177</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09480377677949926</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.236169014084507</v>
+        <v>0.2396610169491524</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.919163707241879</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9532</v>
+        <v>9616</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02489957542588311</v>
+        <v>0.02464677067458266</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6948440955728075</v>
+        <v>0.6818709885607321</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.405067961284015</v>
+        <v>4.405106411999713</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.298048381426589</v>
+        <v>4.299146338107895</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.43013698630137</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002270112535808674</v>
+        <v>0.002270092720747799</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1470705664930828</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9661458333333335</v>
+        <v>0.9764397905759161</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.034494046288351</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1202</v>
+        <v>1165</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05473798095294582</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.532592479201331</v>
+        <v>0.5812670901287553</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3616438356164384</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13380</v>
+        <v>13400</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.165887353904286</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.003139987443946279</v>
+        <v>-0.004627838208955293</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18070</v>
+        <v>18120</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1679904418740883</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.210874930824571</v>
+        <v>0.207533664459161</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.767348842014341</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67350</v>
+        <v>66750</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2628614894897362</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1530512249443208</v>
+        <v>0.1634157303370787</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.709416465868562</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>849.8</v>
+        <v>830</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06253074079059175</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8844433984466935</v>
+        <v>0.929397590361446</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.116853670125165</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>107.2</v>
+        <v>105.6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8794</v>
+        <v>8850</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.009322069896764811</v>
+        <v>0.01765215277603228</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1900165458267</v>
+        <v>0.1648374454237287</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.818408453917869</v>
+        <v>1.818056870419706</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.801613685217305</v>
+        <v>1.78652093002532</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.838356164383562</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005499314512344246</v>
+        <v>0.005500377992956544</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>108.4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02815069132135843</v>
+        <v>0.02730397275159773</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3006451612903227</v>
+        <v>0.3082758620689656</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.460748933191376</v>
+        <v>4.461618056381988</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.338613951091656</v>
+        <v>4.343035921910921</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.838356164383562</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002241776022315977</v>
+        <v>0.002241339324350232</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5876</v>
+        <v>5900</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05325256976639808</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.765912185159973</v>
+        <v>1.754661016949152</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3671232876712329</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24300</v>
+        <v>24590</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1307823191010174</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05185185185185182</v>
+        <v>0.03944692964619767</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.56050896627573</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24300</v>
+        <v>24590</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08287507062277596</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1950617283950618</v>
+        <v>0.1809678731191542</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.016516349501799</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03960538913520929</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.862695808349146</v>
+        <v>2.86820083800475</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9506849315068491</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>232.8</v>
+        <v>236</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1617450355014498</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.401817010309278</v>
+        <v>2.355690677966101</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.730120178271133</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11840</v>
+        <v>12130</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005492091648701787</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.5040540540540541</v>
+        <v>0.4680956306677659</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.18810387176399</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03735796785993852</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.590199035887488</v>
+        <v>0.5979485438596492</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.715974698054486</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221.5</v>
+        <v>227</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-10.38491084425846</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.01568848758465013</v>
+        <v>-0.03953744493392064</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219.6</v>
+        <v>226.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.5</v>
+        <v>227</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1220657269288503</v>
+        <v>-0.1284625187274389</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.008577878103837477</v>
+        <v>-0.001321585903083733</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.307593896322358</v>
+        <v>4.313311252823162</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.90651069043441</v>
+        <v>4.949082908660626</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.589041095890411</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002321481606828716</v>
+        <v>0.002318404449355415</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.7</v>
+        <v>243.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1749547409691311</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01720558063192446</v>
+        <v>-0.01599424815119144</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.229195469878952</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1881195698381118</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1826231527093596</v>
+        <v>0.1943905472636815</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.990684475677455</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.9</v>
+        <v>110.7</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17920</v>
+        <v>17910</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03090660354989684</v>
+        <v>-0.02995833563323633</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1610982455357144</v>
+        <v>0.1596514170854273</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.839923054586535</v>
+        <v>1.83990098237114</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.898602406461934</v>
+        <v>1.896723666577986</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.838356164383562</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005435009890806105</v>
+        <v>0.005435075091439255</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05590660479293472</v>
+        <v>0.0538902700550292</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9640000000000002</v>
+        <v>0.9759999999999998</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.087118150544056</v>
+        <v>3.088230866741559</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.923665915651172</v>
+        <v>2.930315379589097</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003239267016145028</v>
+        <v>0.003238099880321175</v>
       </c>
     </row>
     <row r="18">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>304.5</v>
+        <v>303.4</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24260</v>
+        <v>24180</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5055849422771767</v>
+        <v>-0.5044079534993969</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.007739110057707999</v>
+        <v>0.00742075318444968</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.515479503793718</v>
+        <v>1.515448293011296</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.065196903131779</v>
+        <v>3.057854345548807</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.501369863013699</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006598571590685907</v>
+        <v>0.006598707488811342</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>428.1</v>
+        <v>427.6</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04779760905021074</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5540895585143657</v>
+        <v>0.5559067820392891</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8657534246575342</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>177</v>
+        <v>187.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09480377677949926</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.2396610169491524</v>
+        <v>0.1677488025545502</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.919163707241879</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9616</v>
+        <v>9693</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02464677067458266</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6818709885607321</v>
+        <v>0.6685104122562673</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.405106411999713</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.2</v>
+        <v>35.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2173397168100258</v>
+        <v>0.2179521105034452</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.07799309895287965</v>
+        <v>0.1452560066852369</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.962093552664248</v>
+        <v>2.961679388238215</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.433251385592065</v>
+        <v>2.431687882222227</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.342465753424658</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003375990603337131</v>
+        <v>0.003376462705488389</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1470705664930828</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9764397905759161</v>
+        <v>0.9610389610389611</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.034494046288351</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1165</v>
+        <v>1174</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05473798095294582</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5812670901287553</v>
+        <v>0.569144940374787</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3616438356164384</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13400</v>
+        <v>13380</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.165887353904286</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.004627838208955293</v>
+        <v>-0.003139987443946279</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>190.1</v>
+        <v>190</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18120</v>
+        <v>17850</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1679904418740883</v>
+        <v>-0.1678327865112798</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.207533664459161</v>
+        <v>0.2251540616246499</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.767348842014341</v>
+        <v>2.76732038183724</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.32610222441164</v>
+        <v>3.325437889142157</v>
       </c>
       <c r="BC29" s="8" t="n">
         <v>2.838356164383562</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.00361356683630859</v>
+        <v>0.003613603999606631</v>
       </c>
     </row>
     <row r="30">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66750</v>
+        <v>66780</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2628614894897362</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1634157303370787</v>
+        <v>0.1628930817610064</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.709416465868562</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>141.8</v>
+        <v>142.6</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07118086968030556</v>
+        <v>-0.07307659247457939</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01250391236306714</v>
+        <v>-0.00693270735524254</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.739200915885041</v>
+        <v>2.739594209518104</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.949121983461111</v>
+        <v>2.955577761092381</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.838356164383562</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003650699713923314</v>
+        <v>0.00365017562281934</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03319335582365446</v>
+        <v>0.03608611352545368</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3620178041543027</v>
+        <v>0.3553412462908012</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.740965245002573</v>
+        <v>1.740851076421538</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.68503333397328</v>
+        <v>1.680218520155632</v>
       </c>
       <c r="BC34" s="8" t="n">
         <v>1.758904109589041</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005743940052051538</v>
+        <v>0.005744316751410936</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>830</v>
+        <v>833.4</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06253074079059175</v>
+        <v>0.06644846670539038</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.929397590361446</v>
+        <v>0.8990880729541635</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.116853670125165</v>
+        <v>3.112157045692779</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.933424465259258</v>
+        <v>2.918244193558883</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.342465753424658</v>
+        <v>3.33972602739726</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003208363644353707</v>
+        <v>0.003213205456273483</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105.6</v>
+        <v>108</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8850</v>
+        <v>8982</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.01765215277603228</v>
+        <v>0.005169290176581878</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1648374454237287</v>
+        <v>0.1738034468937875</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.818056870419706</v>
+        <v>1.815844098824776</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.78652093002532</v>
+        <v>1.80650574641589</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.838356164383562</v>
+        <v>1.835616438356164</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005500377992956544</v>
+        <v>0.005507080705040732</v>
       </c>
     </row>
     <row r="4">
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.8</v>
+        <v>92.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02730397275159773</v>
+        <v>0.02729434679463554</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3082758620689656</v>
+        <v>0.315362946912243</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.461618056381988</v>
+        <v>4.458888204441037</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.343035921910921</v>
+        <v>4.340419294969998</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.838356164383562</v>
+        <v>4.835616438356165</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002241339324350232</v>
+        <v>0.002242711532897379</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5900</v>
+        <v>5980</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05325256976639808</v>
+        <v>0.05356029229152386</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.754661016949152</v>
+        <v>1.717809364548495</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3671232876712329</v>
+        <v>0.3643835616438356</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3485614924753115</v>
+        <v>0.3458592396751124</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3397260273972603</v>
+        <v>0.336986301369863</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02723880597014925</v>
+        <v>0.02744360902255639</v>
       </c>
     </row>
     <row r="6">
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24590</v>
+        <v>24800</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1307823191010174</v>
+        <v>-0.1308377078692213</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03944692964619767</v>
+        <v>0.03064516129032269</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.56050896627573</v>
+        <v>6.557892698687392</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.54760183834568</v>
+        <v>7.545072718940109</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.013698630136986</v>
+        <v>7.010958904109589</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524271981244894</v>
+        <v>0.001524880088690925</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24590</v>
+        <v>24800</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08287507062277596</v>
+        <v>-0.09038136741862032</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1809678731191542</v>
+        <v>0.1903225806451614</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.016516349501799</v>
+        <v>2.014030353846835</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.198736818626356</v>
+        <v>2.214148085479822</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.010958904109589</v>
+        <v>2.008219178082192</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004959047320628272</v>
+        <v>0.0049651684647651</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2105</v>
+        <v>2168</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03960538913520929</v>
+        <v>0.03971209524919882</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.86820083800475</v>
+        <v>2.755794632841328</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9506849315068491</v>
+        <v>0.9479452054794522</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9144671059253279</v>
+        <v>0.9117381723372644</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9232876712328767</v>
+        <v>0.9205479452054794</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01051873198847262</v>
+        <v>0.01054913294797688</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83.09999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>236</v>
+        <v>233.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1617450355014498</v>
+        <v>0.1659392867435039</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.355690677966101</v>
+        <v>2.372656383890317</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.730120178271133</v>
+        <v>1.72721562837412</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.489242583700263</v>
+        <v>1.481394141197758</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.758904109589041</v>
+        <v>1.756164383561644</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005779945304142256</v>
+        <v>0.005789665074657357</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12130</v>
+        <v>12240</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005492091648701787</v>
+        <v>-0.005507243056394101</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4680956306677659</v>
+        <v>0.4549019607843137</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.18810387176399</v>
+        <v>4.185371824447336</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.211232345760886</v>
+        <v>4.208549328514288</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.347945205479452</v>
+        <v>4.345205479452055</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002387715373398343</v>
+        <v>0.002389273980770028</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.7</v>
+        <v>105</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1026</v>
+        <v>1083</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03735796785993852</v>
+        <v>0.03625624755656395</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5979485438596492</v>
+        <v>0.5181836565096953</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.715974698054486</v>
+        <v>2.713477487515666</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.618165360658983</v>
+        <v>2.618539086170914</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.838356164383562</v>
+        <v>2.835616438356164</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003681919425524555</v>
+        <v>0.003685307892182123</v>
       </c>
     </row>
     <row r="12">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>161.5</v>
+        <v>159.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>227</v>
+        <v>217.6</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-10.38491084425846</v>
+        <v>-11.02964726852432</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.03953744493392064</v>
+        <v>-0.009834558823529349</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.01095890410958904</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>226.7</v>
+        <v>217</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>227</v>
+        <v>217.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1284625187274389</v>
+        <v>-0.119743105139911</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.001321585903083733</v>
+        <v>-0.002757352941176405</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.313311252823162</v>
+        <v>4.302760972178555</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.949082908660626</v>
+        <v>4.888074148924956</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.589041095890411</v>
+        <v>4.586301369863014</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002318404449355415</v>
+        <v>0.002324089128970798</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>243.4</v>
+        <v>255.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1749547409691311</v>
+        <v>-0.175102522695012</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01599424815119144</v>
+        <v>-0.06332811888932333</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.229195469878952</v>
+        <v>3.226507228627327</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.91396160941776</v>
+        <v>3.91140392278639</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.342465753424658</v>
+        <v>3.33972602739726</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003096746571484214</v>
+        <v>0.003099326699557516</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1881195698381118</v>
+        <v>-0.1883956457286948</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1943905472636815</v>
+        <v>0.1569759036144578</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.990684475677455</v>
+        <v>1.988009228720242</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.451942923763434</v>
+        <v>2.449480733140184</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.104109589041096</v>
+        <v>2.101369863013699</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.00502339779215733</v>
+        <v>0.005030157735453463</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>110.7</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17910</v>
+        <v>18060</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.02995833563323633</v>
+        <v>-0.03616001815618996</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1596514170854273</v>
+        <v>0.16352496124031</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.83990098237114</v>
+        <v>1.837305626944649</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.896723666577986</v>
+        <v>1.906235123624892</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.838356164383562</v>
+        <v>1.835616438356164</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005435075091439255</v>
+        <v>0.005442752611948139</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>77.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0538902700550292</v>
+        <v>0.05322453336556376</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9759999999999998</v>
+        <v>0.9448669201520914</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.088230866741559</v>
+        <v>3.085858031217651</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.930315379589097</v>
+        <v>2.929914689089929</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.342465753424658</v>
+        <v>3.33972602739726</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003238099880321175</v>
+        <v>0.00324058978048776</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1468635788601355</v>
+        <v>0.1470004089045183</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.305935483870968</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.811229229250245</v>
+        <v>1.808483644895727</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.579289169728818</v>
+        <v>1.576707062051513</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.838356164383562</v>
+        <v>1.835616438356164</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005521112313398058</v>
+        <v>0.005529494296630246</v>
       </c>
     </row>
     <row r="19">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>109.5</v>
+        <v>108.6</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.01935539970890273</v>
+        <v>0.02185459229198599</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5858620689655174</v>
+        <v>0.540945945945946</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.279460367457296</v>
+        <v>3.275438592584997</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.217190362059996</v>
+        <v>3.205386184386858</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.504109589041096</v>
+        <v>3.501369863013699</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003049282162160545</v>
+        <v>0.003053026248954323</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>303.4</v>
+        <v>299.2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24180</v>
+        <v>24260</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5044079534993969</v>
+        <v>-0.5004837982713854</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.00742075318444968</v>
+        <v>-0.009801176586974436</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.515448293011296</v>
+        <v>1.512604522519984</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.057854345548807</v>
+        <v>3.028139061927319</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.501369863013699</v>
+        <v>1.498630136986301</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006598707488811342</v>
+        <v>0.006611113381665749</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>427.6</v>
+        <v>422.8</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04779760905021074</v>
+        <v>0.04782972622708263</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5559067820392891</v>
+        <v>0.5735708136234625</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8657534246575342</v>
+        <v>0.863013698630137</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8262601643482534</v>
+        <v>0.823620171320762</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8383561643835616</v>
+        <v>0.8356164383561644</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01155063291139241</v>
+        <v>0.01158730158730159</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>187.9</v>
+        <v>189.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09480377677949926</v>
+        <v>0.09596412305598499</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1677488025545502</v>
+        <v>0.1548523206751053</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.919163707241879</v>
+        <v>1.916110664819518</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.752975051736976</v>
+        <v>1.74833338474314</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.104109589041096</v>
+        <v>2.101369863013699</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005210602911187537</v>
+        <v>0.005218905245716546</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9693</v>
+        <v>9747</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02464677067458266</v>
+        <v>0.02465883378301262</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6685104122562673</v>
+        <v>0.6592665872576178</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.405106411999713</v>
+        <v>4.40236485170091</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.299146338107895</v>
+        <v>4.296420141567997</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.43013698630137</v>
+        <v>4.427397260273972</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002270092720747799</v>
+        <v>0.002271506414589052</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.6</v>
+        <v>63.1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35.9</v>
+        <v>38.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2179521105034452</v>
+        <v>0.2211662957858448</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1452560066852369</v>
+        <v>0.05404294418604638</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.961679388238215</v>
+        <v>2.956762918394088</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.431687882222227</v>
+        <v>2.421261484695131</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.342465753424658</v>
+        <v>3.33972602739726</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003376462705488389</v>
+        <v>0.003382077047094232</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.5</v>
+        <v>37.8</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1470705664930828</v>
+        <v>0.147146919742316</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9610389610389611</v>
+        <v>0.9973544973544974</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.034494046288351</v>
+        <v>3.031708389916165</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.645429265581848</v>
+        <v>2.642824853330189</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.342465753424658</v>
+        <v>3.33972602739726</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003295442287069743</v>
+        <v>0.00329847027282084</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>56.65864939053991</v>
+        <v>57.04929433512859</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>-0.06891666666666663</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3671232876712329</v>
+        <v>0.3643835616438357</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006367185002628019</v>
+        <v>0.006277140244637368</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3397260273972603</v>
+        <v>0.336986301369863</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02723880597014925</v>
+        <v>0.02744360902255639</v>
       </c>
     </row>
     <row r="27">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1174</v>
+        <v>1193</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05473798095294582</v>
+        <v>0.05494336998040791</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.569144940374787</v>
+        <v>0.5441543671416598</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3616438356164384</v>
+        <v>0.3589041095890412</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3428755218331064</v>
+        <v>0.3402117306028538</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3397260273972603</v>
+        <v>0.336986301369863</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02765151515151515</v>
+        <v>0.02786259541984732</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>509.4</v>
+        <v>578.2</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13380</v>
+        <v>13790</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.165887353904286</v>
+        <v>-2.248714603292159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.003139987443946279</v>
+        <v>0.09785546802030476</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3397260273972603</v>
+        <v>0.336986301369863</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>190</v>
+        <v>189.9</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17850</v>
+        <v>19100</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1678327865112798</v>
+        <v>-0.1678480254411474</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2251540616246499</v>
+        <v>0.1443712041884815</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.76732038183724</v>
+        <v>2.764583406900671</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.325437889142157</v>
+        <v>3.322209754253429</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.838356164383562</v>
+        <v>2.835616438356164</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003613603999606631</v>
+        <v>0.003617181516404613</v>
       </c>
     </row>
     <row r="30">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.8</v>
+        <v>100.2</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05570767316257446</v>
+        <v>0.05416132165759539</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6637649470085472</v>
+        <v>0.6704333435897436</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.711915929217185</v>
+        <v>2.709519655284417</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.568813316562455</v>
+        <v>2.570308357570819</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.838356164383562</v>
+        <v>2.835616438356164</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003687429942891546</v>
+        <v>0.003690691071569401</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>39.1</v>
+        <v>45</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1153752517536956</v>
+        <v>0.115431051259197</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>1.122758871611253</v>
+        <v>0.8444415973333332</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.24720794751451</v>
+        <v>2.244454063426789</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.014755073668026</v>
+        <v>2.012185388682744</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.410958904109589</v>
+        <v>2.408219178082192</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004449966462187155</v>
+        <v>0.004455426449999245</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66780</v>
+        <v>67480</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2628614894897362</v>
+        <v>-0.2632483331778747</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1628930817610064</v>
+        <v>0.1508298755186721</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.709416465868562</v>
+        <v>1.70669080955599</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.318989499931656</v>
+        <v>2.316507564777642</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.712328767123288</v>
+        <v>1.70958904109589</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005849949500117254</v>
+        <v>0.005859292113140039</v>
       </c>
     </row>
     <row r="33">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142.6</v>
+        <v>142.8</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.8</v>
+        <v>128.7</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07307659247457939</v>
+        <v>-0.07365459851120809</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.00693270735524254</v>
+        <v>-0.01249417249417228</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.739594209518104</v>
+        <v>2.736974311358057</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.955577761092381</v>
+        <v>2.954593726011141</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.838356164383562</v>
+        <v>2.835616438356164</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00365017562281934</v>
+        <v>0.003653669659412371</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101.5</v>
+        <v>102</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1348</v>
+        <v>1323</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03608611352545368</v>
+        <v>0.03317537202683044</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3553412462908012</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.740851076421538</v>
+        <v>1.738226228827561</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.680218520155632</v>
+        <v>1.682411598156466</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.758904109589041</v>
+        <v>1.756164383561644</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005744316751410936</v>
+        <v>0.005752991086059626</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02729434679463554</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.315362946912243</v>
+        <v>0.3283150984682714</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.458888204441037</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5980</v>
+        <v>6013</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05356029229152386</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.717809364548495</v>
+        <v>1.702893730251123</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3643835616438356</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24800</v>
+        <v>24400</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1308377078692213</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03064516129032269</v>
+        <v>0.04754098360655745</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.557892698687392</v>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24800</v>
+        <v>24400</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09038136741862032</v>
+        <v>-0.08299069514802647</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1903225806451614</v>
+        <v>0.1901639344262296</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.014030353846835</v>
+        <v>2.013780543692041</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.214148085479822</v>
+        <v>2.196030654255043</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.008219178082192</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.0049651684647651</v>
+        <v>0.004965784395585687</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2168</v>
+        <v>2153</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03971209524919882</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.755794632841328</v>
+        <v>2.781961339526242</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9479452054794522</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12240</v>
+        <v>12180</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005507243056394101</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4549019607843137</v>
+        <v>0.4620689655172414</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.185371824447336</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03625624755656395</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5181836565096953</v>
+        <v>0.526641504178273</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.713477487515666</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217.6</v>
+        <v>217.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-11.02964726852432</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.009834558823529349</v>
+        <v>-0.009379310344827529</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>217</v>
+        <v>216.8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.6</v>
+        <v>217.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.119743105139911</v>
+        <v>-0.1195562720343603</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002757352941176405</v>
+        <v>-0.003218390804597626</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.302760972178555</v>
+        <v>4.302592193849517</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.888074148924956</v>
+        <v>4.88684518633703</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.586301369863014</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002324089128970798</v>
+        <v>0.002324180296309474</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.7</v>
+        <v>257</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.175102522695012</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.06332811888932333</v>
+        <v>-0.06806614785992215</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.226507228627327</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1883956457286948</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1569759036144578</v>
+        <v>0.1710853658536584</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.988009228720242</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18060</v>
+        <v>18110</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03616001815618996</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.16352496124031</v>
+        <v>0.1603125786858088</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.837305626944649</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>148</v>
+        <v>151.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02185459229198599</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.540945945945946</v>
+        <v>0.5073364177131525</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.275438592584997</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24260</v>
+        <v>24270</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5004837982713854</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.009801176586974436</v>
+        <v>-0.01020916950968276</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.512604522519984</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>422.8</v>
+        <v>424.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04782972622708263</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5735708136234625</v>
+        <v>0.5657936926335609</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.863013698630137</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>95.2</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>189.6</v>
+        <v>187</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09596412305598499</v>
+        <v>0.09147959994628593</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1548523206751053</v>
+        <v>0.1807486631016042</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.916110664819518</v>
+        <v>1.917320776370782</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.74833338474314</v>
+        <v>1.756625388569001</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.101369863013699</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005218905245716546</v>
+        <v>0.005215611348523845</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9747</v>
+        <v>9720</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02465883378301262</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6592665872576178</v>
+        <v>0.6638756611111112</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.40236485170091</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.1</v>
+        <v>61.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2211662957858448</v>
+        <v>0.2293431381758461</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.05404294418604638</v>
+        <v>0.03232732093023238</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.956762918394088</v>
+        <v>2.951202886158705</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.421261484695131</v>
+        <v>2.400633960130798</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.33972602739726</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003382077047094232</v>
+        <v>0.003388448841284522</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.147146919742316</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9973544973544974</v>
+        <v>0.986842105263158</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.031708389916165</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13790</v>
+        <v>13760</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.248714603292159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.09785546802030476</v>
+        <v>0.100249048255814</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19100</v>
+        <v>18680</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1678480254411474</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1443712041884815</v>
+        <v>0.1701011777301926</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.764583406900671</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67480</v>
+        <v>67340</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2632483331778747</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1508298755186721</v>
+        <v>0.1532224532224533</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70669080955599</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1323</v>
+        <v>1386</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03317537202683044</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3877551020408163</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.738226228827561</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>833.4</v>
+        <v>833.5</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06644846670539038</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8990880729541635</v>
+        <v>0.8988602279544089</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.112157045692779</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8982</v>
+        <v>8996</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.005169290176581878</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1738034468937875</v>
+        <v>0.1719767185415739</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.815844098824776</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02729434679463554</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3283150984682714</v>
+        <v>0.3297699890470978</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.458888204441037</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6013</v>
+        <v>6020</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05356029229152386</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.702893730251123</v>
+        <v>1.699750830564784</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3643835616438356</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.5</v>
+        <v>319</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24400</v>
+        <v>24910</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1308377078692213</v>
+        <v>-0.1306325863478283</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04754098360655745</v>
+        <v>0.02448815736651944</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.557892698687392</v>
+        <v>6.557435359569471</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.545072718940109</v>
+        <v>7.542766449022967</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.010958904109589</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524880088690925</v>
+        <v>0.001524986439310711</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24400</v>
+        <v>24910</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08299069514802647</v>
+        <v>-0.08670867701654249</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1901639344262296</v>
+        <v>0.1754315535929345</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.013780543692041</v>
+        <v>2.013906403410764</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.196030654255043</v>
+        <v>2.205108438818752</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.008219178082192</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004965784395585687</v>
+        <v>0.004965474057316635</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2153</v>
+        <v>2198</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03971209524919882</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.781961339526242</v>
+        <v>2.704532649681529</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9479452054794522</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12180</v>
+        <v>12350</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005507243056394101</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4620689655172414</v>
+        <v>0.4419433198380567</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.185371824447336</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>104.4</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03625624755656395</v>
+        <v>0.0384315839579336</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.526641504178273</v>
+        <v>0.5235764324324326</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.713477487515666</v>
+        <v>2.712998514290174</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.618539086170914</v>
+        <v>2.612592448266747</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.835616438356164</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003685307892182123</v>
+        <v>0.003685958524240618</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>217.5</v>
+        <v>220.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-11.02964726852432</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.009379310344827529</v>
+        <v>-0.02418478260869572</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>216.8</v>
+        <v>222.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>217.5</v>
+        <v>220.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1195562720343603</v>
+        <v>-0.1244351492119388</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003218390804597626</v>
+        <v>0.005887681159420177</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.302592193849517</v>
+        <v>4.306980060234666</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.88684518633703</v>
+        <v>4.919087439791722</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.586301369863014</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002324180296309474</v>
+        <v>0.00232181246723839</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>257</v>
+        <v>256.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.175102522695012</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.06806614785992215</v>
+        <v>-0.0669770159719516</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.226507228627327</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18110</v>
+        <v>18010</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03616001815618996</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1603125786858088</v>
+        <v>0.1667551804553027</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.837305626944649</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>151.3</v>
+        <v>149.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02185459229198599</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5073364177131525</v>
+        <v>0.5275284661754855</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.275438592584997</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24270</v>
+        <v>24210</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5004837982713854</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.01020916950968276</v>
+        <v>-0.007756156299050021</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.512604522519984</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>424.9</v>
+        <v>422.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04782972622708263</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5657936926335609</v>
+        <v>0.5750609375000002</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.863013698630137</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>187</v>
+        <v>190.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09147959994628593</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1807486631016042</v>
+        <v>0.1584470094438615</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.917320776370782</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9720</v>
+        <v>9771</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02465883378301262</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6638756611111112</v>
+        <v>0.6551910168867054</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.40236485170091</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.7</v>
+        <v>34</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3482,7 +3482,7 @@
         <v>0.2293431381758461</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.03232732093023238</v>
+        <v>0.1750313917647057</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>2.951202886158705</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>38.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.147146919742316</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.986842105263158</v>
+        <v>0.9712793733681464</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.031708389916165</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13760</v>
+        <v>13800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.248714603292159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.100249048255814</v>
+        <v>0.09705992057971025</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18680</v>
+        <v>18760</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1678480254411474</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1701011777301926</v>
+        <v>0.1651114072494668</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.764583406900671</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67340</v>
+        <v>67970</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2632483331778747</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1532224532224533</v>
+        <v>0.1425334706488157</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70669080955599</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.7</v>
+        <v>127.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07365459851120809</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01249417249417228</v>
+        <v>-0.00319999999999987</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.736974311358057</v>
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1386</v>
+        <v>1361</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03317537202683044</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.349008082292432</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.738226228827561</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24910</v>
+        <v>24550</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1306325863478283</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02448815736651944</v>
+        <v>0.03951120162932797</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.557435359569471</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24910</v>
+        <v>24550</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08670867701654249</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1754315535929345</v>
+        <v>0.1926680244399186</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.013906403410764</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2198</v>
+        <v>2167</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03971209524919882</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.704532649681529</v>
+        <v>2.757527809875404</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9479452054794522</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>233.4</v>
+        <v>239.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1659392867435039</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.372656383890317</v>
+        <v>2.28812865497076</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.72721562837412</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12350</v>
+        <v>12410</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005507243056394101</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4419433198380567</v>
+        <v>0.4349717969379532</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.185371824447336</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.0384315839579336</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5235764324324326</v>
+        <v>0.5307092808988765</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.712998514290174</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.8</v>
+        <v>221.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-11.02964726852432</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.02418478260869572</v>
+        <v>-0.028146143437077</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222.1</v>
+        <v>224.6</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.8</v>
+        <v>221.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1244351492119388</v>
+        <v>-0.1266857680197274</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.005887681159420177</v>
+        <v>0.01308073973838519</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.306980060234666</v>
+        <v>4.308990490875175</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.919087439791722</v>
+        <v>4.934066494146531</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.586301369863014</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00232181246723839</v>
+        <v>0.002320729187306458</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>256.7</v>
+        <v>253.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.175102522695012</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.0669770159719516</v>
+        <v>-0.05594402837997625</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.226507228627327</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>111.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18010</v>
+        <v>17820</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03616001815618996</v>
+        <v>-0.03428712017357381</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1667551804553027</v>
+        <v>0.1749839191919191</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.837305626944649</v>
+        <v>1.837262022761881</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.906235123624892</v>
+        <v>1.902493029907714</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.835616438356164</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005442752611948139</v>
+        <v>0.005442881786108769</v>
       </c>
     </row>
     <row r="17">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>149.3</v>
+        <v>149.7</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02185459229198599</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5275284661754855</v>
+        <v>0.5234468937875754</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.275438592584997</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>299.2</v>
+        <v>300.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24210</v>
+        <v>24020</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5004837982713854</v>
+        <v>-0.5020162473779319</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.007756156299050021</v>
+        <v>0.004772144379683763</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.512604522519984</v>
+        <v>1.512645151034606</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.028139061927319</v>
+        <v>3.037539162813991</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.498630136986301</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006611113381665749</v>
+        <v>0.006610935812117129</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>422.4</v>
+        <v>421.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04782972622708263</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5750609375000002</v>
+        <v>0.5795482905982907</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.863013698630137</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>190.6</v>
+        <v>192.6</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09147959994628593</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1584470094438615</v>
+        <v>0.1464174454828659</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.917320776370782</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9771</v>
+        <v>9700</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02465883378301262</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6551910168867054</v>
+        <v>0.6673063325773196</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.40236485170091</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>61.8</v>
+        <v>63.8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2293431381758461</v>
+        <v>0.2168575123797575</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1750313917647057</v>
+        <v>0.2130582976470587</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.951202886158705</v>
+        <v>2.959679815532269</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.400633960130798</v>
+        <v>2.432232028336783</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.33972602739726</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003388448841284522</v>
+        <v>0.003378743858548632</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13800</v>
+        <v>13730</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.248714603292159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.09705992057971025</v>
+        <v>0.1026530884195194</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18760</v>
+        <v>18640</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1678480254411474</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1651114072494668</v>
+        <v>0.1726121244635193</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.764583406900671</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67970</v>
+        <v>67900</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2632483331778747</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1425334706488157</v>
+        <v>0.1437113402061856</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70669080955599</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8996</v>
+        <v>8956</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.005169290176581878</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1719767185415739</v>
+        <v>0.1772110942384992</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.815844098824776</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.3</v>
+        <v>91.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02729434679463554</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3297699890470978</v>
+        <v>0.3225272331154687</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.458888204441037</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6020</v>
+        <v>6050</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05356029229152386</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.699750830564784</v>
+        <v>1.686363636363637</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3643835616438356</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24550</v>
+        <v>24470</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1306325863478283</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.03951120162932797</v>
+        <v>0.04290968532897432</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.557435359569471</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24550</v>
+        <v>24470</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08670867701654249</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1926680244399186</v>
+        <v>0.1965672251736821</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.013906403410764</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03971209524919882</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.757527809875404</v>
+        <v>2.750604681713496</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9479452054794522</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>239.4</v>
+        <v>234.9</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1659392867435039</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.28812865497076</v>
+        <v>2.351119625372498</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.72721562837412</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12410</v>
+        <v>12490</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005507243056394101</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4349717969379532</v>
+        <v>0.4257806244995996</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.185371824447336</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.4</v>
+        <v>104.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0384315839579336</v>
+        <v>0.03806782307406642</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5307092808988765</v>
+        <v>0.5221985209302324</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.712998514290174</v>
+        <v>2.713078644738709</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.612592448266747</v>
+        <v>2.613585147745332</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.835616438356164</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003685958524240618</v>
+        <v>0.003685849659902903</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221.7</v>
+        <v>220.9</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-11.02964726852432</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.028146143437077</v>
+        <v>-0.02462652784065189</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224.6</v>
+        <v>223.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.7</v>
+        <v>220.9</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1266857680197274</v>
+        <v>-0.1255194152077193</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01308073973838519</v>
+        <v>0.01086464463558179</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.308990490875175</v>
+        <v>4.307949690395195</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.934066494146531</v>
+        <v>4.926295409312583</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.586301369863014</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002320729187306458</v>
+        <v>0.002321289875389106</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>253.7</v>
+        <v>250.3</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.175102522695012</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.05594402837997625</v>
+        <v>-0.04312025569316824</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.226507228627327</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17820</v>
+        <v>17970</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03428712017357381</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1749839191919191</v>
+        <v>0.1651760400667779</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.837262022761881</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>149.7</v>
+        <v>149.1</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02185459229198599</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5234468937875754</v>
+        <v>0.5295774647887326</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.275438592584997</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24020</v>
+        <v>24220</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5020162473779319</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.004772144379683763</v>
+        <v>-0.003524900578034562</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.512645151034606</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>421.2</v>
+        <v>422.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,16 +3126,16 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04782972622708263</v>
+        <v>0.03582333696837507</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5795482905982907</v>
+        <v>0.5917243012790145</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.863013698630137</v>
+        <v>0.8630136986301371</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.823620171320762</v>
+        <v>0.8331668807115183</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.8356164383561644</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>192.6</v>
+        <v>189.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09147959994628593</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1464174454828659</v>
+        <v>0.1627172195892574</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.917320776370782</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9700</v>
+        <v>9778</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02465883378301262</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6673063325773196</v>
+        <v>0.6540060775209655</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.40236485170091</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>63.8</v>
+        <v>64.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2168575123797575</v>
+        <v>0.2138189046689852</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2130582976470587</v>
+        <v>0.2225650241176469</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.959679815532269</v>
+        <v>2.961731433466556</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.432232028336783</v>
+        <v>2.440010962157683</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.33972602739726</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003378743858548632</v>
+        <v>0.003376403372366383</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.3</v>
+        <v>37.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.147146919742316</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9712793733681464</v>
+        <v>1.007978723404255</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.031708389916165</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13730</v>
+        <v>13740</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.248714603292159</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1026530884195194</v>
+        <v>0.1018505752547307</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18640</v>
+        <v>18780</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1678480254411474</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1726121244635193</v>
+        <v>0.1638706070287539</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.764583406900671</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67900</v>
+        <v>68790</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2632483331778747</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1437113402061856</v>
+        <v>0.1289140863497602</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70669080955599</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.5</v>
+        <v>127.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07365459851120809</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.00319999999999987</v>
+        <v>-0.003981191222570346</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.736974311358057</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8956</v>
+        <v>8888</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.005169290176581878</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1772110942384992</v>
+        <v>0.1862176597659766</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.815844098824776</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.4</v>
+        <v>109.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02729434679463554</v>
+        <v>0.02436035339449663</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3225272331154687</v>
+        <v>0.3366956521739133</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.458888204441037</v>
+        <v>4.461890933293359</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.340419294969998</v>
+        <v>4.355782531516053</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.835616438356165</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002242711532897379</v>
+        <v>0.00224120225023495</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6050</v>
+        <v>6027</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05356029229152386</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.686363636363637</v>
+        <v>1.696615231458437</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3643835616438356</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24470</v>
+        <v>24420</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1306325863478283</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04290968532897432</v>
+        <v>0.04504504504504503</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.557435359569471</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24470</v>
+        <v>24420</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08670867701654249</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1965672251736821</v>
+        <v>0.1990171990171989</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.013906403410764</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2171</v>
+        <v>2134</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.03971209524919882</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.750604681713496</v>
+        <v>2.815633910028116</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9479452054794522</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12490</v>
+        <v>12350</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005507243056394101</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4257806244995996</v>
+        <v>0.4419433198380567</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.185371824447336</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03806782307406642</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5221985209302324</v>
+        <v>0.519371782729805</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.713078644738709</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.9</v>
+        <v>220.6</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-11.02964726852432</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.02462652784065189</v>
+        <v>-0.02330009066183136</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223.3</v>
+        <v>220</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.9</v>
+        <v>220.6</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1255194152077193</v>
+        <v>-0.1225197724832084</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01086464463558179</v>
+        <v>-0.002719854941069744</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.307949690395195</v>
+        <v>4.305262290308657</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.926295409312583</v>
+        <v>4.906392366802671</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.586301369863014</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002321289875389106</v>
+        <v>0.00232273885438071</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>250.3</v>
+        <v>249</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.175102522695012</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.04312025569316824</v>
+        <v>-0.03812449799196782</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.226507228627327</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.1883956457286948</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1710853658536584</v>
+        <v>0.1855432098765433</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.988009228720242</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17970</v>
+        <v>17760</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03428712017357381</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1651760400667779</v>
+        <v>0.1789534594594595</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.837262022761881</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>149.1</v>
+        <v>147.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02185459229198599</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5295774647887326</v>
+        <v>0.5461694915254238</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.275438592584997</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24220</v>
+        <v>23980</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5020162473779319</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.003524900578034562</v>
+        <v>0.006448161301084276</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.512645151034606</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>422.2</v>
+        <v>421.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,16 +3126,16 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03582333696837507</v>
+        <v>0.04782972622708263</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5917243012790145</v>
+        <v>0.5787986236355009</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8630136986301371</v>
+        <v>0.863013698630137</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8331668807115183</v>
+        <v>0.823620171320762</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.8356164383561644</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>189.9</v>
+        <v>188.3</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09147959994628593</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1627172195892574</v>
+        <v>0.1725969198088155</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.917320776370782</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9778</v>
+        <v>9705</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02465883378301262</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6540060775209655</v>
+        <v>0.6664473391035548</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.40236485170091</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>64.3</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2138189046689852</v>
+        <v>0.2096183147756585</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2225650241176469</v>
+        <v>0.2358744411764706</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.961731433466556</v>
+        <v>2.964560191799732</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.440010962157683</v>
+        <v>2.450822838565861</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.33972602739726</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003376403372366383</v>
+        <v>0.00337318163674362</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.6</v>
+        <v>38.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.147146919742316</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.007978723404255</v>
+        <v>0.9816272965879265</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.031708389916165</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>578.2</v>
+        <v>550</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13740</v>
+        <v>13720</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,10 +3940,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.248714603292159</v>
+        <v>-2.223447467661278</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.1018505752547307</v>
+        <v>0.04963892128279879</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18780</v>
+        <v>18420</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1678480254411474</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1638706070287539</v>
+        <v>0.1866172638436481</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.764583406900671</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68790</v>
+        <v>67270</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2632483331778747</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1289140863497602</v>
+        <v>0.1544224765868887</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70669080955599</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.6</v>
+        <v>128.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07365459851120809</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.003981191222570346</v>
+        <v>-0.008642745709828259</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.736974311358057</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>833.5</v>
+        <v>825</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06644846670539038</v>
+        <v>0.06646675917688198</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.8988602279544089</v>
+        <v>0.9184242424242421</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.112157045692779</v>
+        <v>3.109408163694451</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.918244193558883</v>
+        <v>2.915616578705507</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.33972602739726</v>
+        <v>3.336986301369863</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003213205456273483</v>
+        <v>0.003216046100592492</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>108</v>
+        <v>106.9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8888</v>
+        <v>8800</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.005169290176581878</v>
+        <v>0.01076448679770347</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1862176597659766</v>
+        <v>0.1858771713636365</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.815844098824776</v>
+        <v>1.812868103989441</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.80650574641589</v>
+        <v>1.793561336660092</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.835616438356164</v>
+        <v>1.832876712328767</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005507080705040732</v>
+        <v>0.005516121100036875</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.8</v>
+        <v>109.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02436035339449663</v>
+        <v>0.02414143583457899</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3366956521739133</v>
+        <v>0.3452240437158471</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.461890933293359</v>
+        <v>4.459374702331707</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.355782531516053</v>
+        <v>4.354256693752202</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.835616438356165</v>
+        <v>4.832876712328767</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.00224120225023495</v>
+        <v>0.002242466863071907</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6027</v>
+        <v>6004</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05356029229152386</v>
+        <v>0.05387268346426118</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.696615231458437</v>
+        <v>1.706945369753498</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3643835616438356</v>
+        <v>0.3616438356164383</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3458592396751124</v>
+        <v>0.3431570447652678</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.336986301369863</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02744360902255639</v>
+        <v>0.02765151515151516</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24420</v>
+        <v>24290</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1306325863478283</v>
+        <v>-0.1260751538440652</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04504504504504503</v>
+        <v>0.01440922190201732</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.557435359569471</v>
+        <v>6.544438748394072</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.542766449022967</v>
+        <v>7.48856011724645</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.010958904109589</v>
+        <v>7.008219178082192</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001524986439310711</v>
+        <v>0.001528014912272482</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>122</v>
+        <v>121.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24420</v>
+        <v>24290</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08670867701654249</v>
+        <v>-0.08348093745684698</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1990171990171989</v>
+        <v>0.1965417867435157</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.013906403410764</v>
+        <v>2.011057435081197</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.205108438818752</v>
+        <v>2.194234159735777</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.008219178082192</v>
+        <v>2.005479452054795</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004965474057316635</v>
+        <v>0.004972508405557421</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2134</v>
+        <v>2147</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.03971209524919882</v>
+        <v>0.04095686526192585</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.815633910028116</v>
+        <v>2.788604382859804</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9479452054794522</v>
+        <v>0.9452054794520547</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9117381723372644</v>
+        <v>0.9080159908587776</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9205479452054794</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01054913294797688</v>
+        <v>0.01057971014492754</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>82.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>234.9</v>
+        <v>238.8</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1659392867435039</v>
+        <v>0.1859847789189014</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.351119625372498</v>
+        <v>2.200611390284757</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.72721562837412</v>
+        <v>1.723688950794738</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.481394141197758</v>
+        <v>1.453382017571918</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.756164383561644</v>
+        <v>1.753424657534246</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005789665074657357</v>
+        <v>0.005801510762942071</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.3</v>
+        <v>114.7</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12350</v>
+        <v>12420</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005507243056394101</v>
+        <v>-0.01256885548586711</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4419433198380567</v>
+        <v>0.4776167471819646</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.185371824447336</v>
+        <v>4.186185589752733</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.208549328514288</v>
+        <v>4.23947088666375</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.345205479452055</v>
+        <v>4.342465753424658</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002389273980770028</v>
+        <v>0.002388809522558859</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03806782307406642</v>
+        <v>0.03805219881218559</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.519371782729805</v>
+        <v>0.5067803038674032</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.713078644738709</v>
+        <v>2.710342360149007</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.613585147745332</v>
+        <v>2.610988506406881</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.835616438356164</v>
+        <v>2.832876712328767</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003685849659902903</v>
+        <v>0.003689570788928019</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>220.6</v>
+        <v>222.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-11.02964726852432</v>
+        <v>-12.03393274060977</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.02330009066183136</v>
+        <v>-0.03033303330333026</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.01095890410958904</v>
+        <v>0.00821917808219178</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220.6</v>
+        <v>222.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1225197724832084</v>
+        <v>-0.1271318303512</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.002719854941069744</v>
+        <v>0.01260126012601259</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.305262290308657</v>
+        <v>4.306648197717667</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.906392366802671</v>
+        <v>4.933904508684805</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.586301369863014</v>
+        <v>4.583561643835616</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00232273885438071</v>
+        <v>0.002321991381905668</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>249</v>
+        <v>253.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.175102522695012</v>
+        <v>-0.1822738726340063</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03812449799196782</v>
+        <v>-0.02999015360378099</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.226507228627327</v>
+        <v>3.226252219131402</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.91140392278639</v>
+        <v>3.945394565688632</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.33972602739726</v>
+        <v>3.336986301369863</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003099326699557516</v>
+        <v>0.003099571676603847</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1883956457286948</v>
+        <v>-0.188672375834369</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1855432098765433</v>
+        <v>0.1782699386503066</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.988009228720242</v>
+        <v>1.985334123052143</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.449480733140184</v>
+        <v>2.447019014166884</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.101369863013699</v>
+        <v>2.098630136986301</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005030157735453463</v>
+        <v>0.005036935538400233</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17760</v>
+        <v>17810</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03428712017357381</v>
+        <v>-0.03436963993104377</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1789534594594595</v>
+        <v>0.1756436518809656</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.837262022761881</v>
+        <v>1.834524217849841</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.902493029907714</v>
+        <v>1.899820359540929</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.835616438356164</v>
+        <v>1.832876712328767</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005442881786108769</v>
+        <v>0.005451004627085559</v>
       </c>
     </row>
     <row r="17">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>98.3</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05322453336556376</v>
+        <v>0.05557842750018602</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9448669201520914</v>
+        <v>0.9508962868117801</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.085858031217651</v>
+        <v>3.081819957538019</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.929914689089929</v>
+        <v>2.919555645748052</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.33972602739726</v>
+        <v>3.336986301369863</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00324058978048776</v>
+        <v>0.003244835888462713</v>
       </c>
     </row>
     <row r="18">
@@ -2783,7 +2783,7 @@
         <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>155</v>
+        <v>154.6</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>46924</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1470004089045183</v>
+        <v>0.147137687192455</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.305935483870968</v>
+        <v>1.311901681759379</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.808483644895727</v>
+        <v>1.805738041422573</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.576707062051513</v>
+        <v>1.574124938604362</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.835616438356164</v>
+        <v>1.832876712328767</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005529494296630246</v>
+        <v>0.005537901827732406</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>147.5</v>
+        <v>147.6</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02185459229198599</v>
+        <v>0.02183643278691482</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5461694915254238</v>
+        <v>0.5451219512195122</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.275438592584997</v>
+        <v>3.272708194651608</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.205386184386858</v>
+        <v>3.202771098820345</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.501369863013699</v>
+        <v>3.498630136986301</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003053026248954323</v>
+        <v>0.003055573367751639</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>300.6</v>
+        <v>299</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23980</v>
+        <v>24070</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5020162473779319</v>
+        <v>-0.5009009739470281</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.006448161301084276</v>
+        <v>-0.00265202243456597</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.512645151034606</v>
+        <v>1.509875856383582</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.037539162813991</v>
+        <v>3.025202970889652</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.498630136986301</v>
+        <v>1.495890410958904</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006610935812117129</v>
+        <v>0.006623061066723562</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>421.4</v>
+        <v>423</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04782972622708263</v>
+        <v>0.04786207176186421</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5787986236355009</v>
+        <v>0.5728268085106383</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.863013698630137</v>
+        <v>0.8602739726027396</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.823620171320762</v>
+        <v>0.8209801612117557</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8356164383561644</v>
+        <v>0.8328767123287671</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01158730158730159</v>
+        <v>0.01162420382165605</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>188.3</v>
+        <v>184.8</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09147959994628593</v>
+        <v>0.09150934465167805</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1725969198088155</v>
+        <v>0.1948051948051945</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.917320776370782</v>
+        <v>1.914573031085914</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.756625388569001</v>
+        <v>1.754060137430057</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.101369863013699</v>
+        <v>2.098630136986301</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005215611348523845</v>
+        <v>0.005223096657915507</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9705</v>
+        <v>9654</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02465883378301262</v>
+        <v>0.02467091211414712</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6664473391035548</v>
+        <v>0.6752508210068364</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.40236485170091</v>
+        <v>4.399623289038703</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.296420141567997</v>
+        <v>4.293693943122873</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.427397260273972</v>
+        <v>4.424657534246576</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002271506414589052</v>
+        <v>0.002272921871496174</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>65.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>34</v>
+        <v>38.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.2096183147756585</v>
+        <v>0.207958428086079</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2358744411764706</v>
+        <v>0.09079246046511602</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.964560191799732</v>
+        <v>2.962935885883404</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.450822838565861</v>
+        <v>2.452845906773429</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.33972602739726</v>
+        <v>3.336986301369863</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00337318163674362</v>
+        <v>0.003375030842767792</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.147146919742316</v>
+        <v>0.1486712577160273</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9816272965879265</v>
+        <v>0.9481865284974094</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.031708389916165</v>
+        <v>3.028051063568724</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.642824853330189</v>
+        <v>2.636133744296502</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.33972602739726</v>
+        <v>3.336986301369863</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00329847027282084</v>
+        <v>0.0033024542156216</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>57.04929433512859</v>
+        <v>57.44590023089727</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>-0.06891666666666663</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3643835616438357</v>
+        <v>0.3616438356164384</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006277140244637368</v>
+        <v>0.00618766815444236</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.336986301369863</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02744360902255639</v>
+        <v>0.02765151515151515</v>
       </c>
     </row>
     <row r="27">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1193</v>
+        <v>1155</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.05494336998040791</v>
+        <v>0.0494812987334202</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5441543671416598</v>
+        <v>0.5981798510822509</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3589041095890412</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3402117306028538</v>
+        <v>0.3393718249114923</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.336986301369863</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02786259541984732</v>
+        <v>0.02807692307692308</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>550</v>
+        <v>526.9</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13720</v>
+        <v>13880</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.223447467661278</v>
+        <v>-2.217433328235412</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.04963892128279879</v>
+        <v>-0.006037314985590791</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.336986301369863</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18420</v>
+        <v>18780</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1678480254411474</v>
+        <v>-0.1680213376217799</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1866172638436481</v>
+        <v>0.1638706070287539</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.764583406900671</v>
+        <v>2.761874966937765</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.322209754253429</v>
+        <v>3.319646394587711</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.835616438356164</v>
+        <v>2.832876712328767</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003617181516404613</v>
+        <v>0.003620728714988688</v>
       </c>
     </row>
     <row r="30">
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>585</v>
+        <v>584.8</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05416132165759539</v>
+        <v>0.05415947468692567</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6704333435897436</v>
+        <v>0.6710046272229824</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.709519655284417</v>
+        <v>2.706780339323255</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.570308357570819</v>
+        <v>2.567714282629904</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.835616438356164</v>
+        <v>2.832876712328767</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003690691071569401</v>
+        <v>0.003694426124914215</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>45</v>
+        <v>43.1</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.115431051259197</v>
+        <v>0.1154870076848439</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>0.8444415973333332</v>
+        <v>0.9257510877030162</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.244454063426789</v>
+        <v>2.241700139199299</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.012185388682744</v>
+        <v>2.009615642096874</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.408219178082192</v>
+        <v>2.405479452054795</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004455426449999245</v>
+        <v>0.004460899932660864</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67270</v>
+        <v>67860</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2632483331778747</v>
+        <v>-0.2636362120860116</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1544224765868887</v>
+        <v>0.1443854995579132</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.70669080955599</v>
+        <v>1.70396519130371</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.316507564777642</v>
+        <v>2.314026326757316</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.70958904109589</v>
+        <v>1.706849315068493</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005859292113140039</v>
+        <v>0.005868664483896506</v>
       </c>
     </row>
     <row r="33">
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.2</v>
+        <v>131.2</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07365459851120809</v>
+        <v>-0.07376116795628866</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.008642745709828259</v>
+        <v>-0.03131097560975593</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.736974311358057</v>
+        <v>2.7342566740445</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.954593726011141</v>
+        <v>2.951999613330251</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.835616438356164</v>
+        <v>2.832876712328767</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003653669659412371</v>
+        <v>0.00365730112133476</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1361</v>
+        <v>1500</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03317537202683044</v>
+        <v>0.03315734030314918</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.349008082292432</v>
+        <v>0.224</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.738226228827561</v>
+        <v>1.735487214545365</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.682411598156466</v>
+        <v>1.679789850823823</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.756164383561644</v>
+        <v>1.753424657534246</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005752991086059626</v>
+        <v>0.005762070683199842</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106.9</v>
+        <v>107</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8800</v>
+        <v>8969</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.01076448679770347</v>
+        <v>0.0102466506679319</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1858771713636365</v>
+        <v>0.1646204972683687</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.812868103989441</v>
+        <v>1.812889965790071</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.793561336660092</v>
+        <v>1.79450232731924</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.832876712328767</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005516121100036875</v>
+        <v>0.005516054580644074</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.9</v>
+        <v>108.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.5</v>
+        <v>91.3</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02414143583457899</v>
+        <v>0.02644112986316511</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3452240437158471</v>
+        <v>0.3346768893756846</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.459374702331707</v>
+        <v>4.457023101226119</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.354256693752202</v>
+        <v>4.34221015853124</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.832876712328767</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002242466863071907</v>
+        <v>0.002243650026684631</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6004</v>
+        <v>6061</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05387268346426118</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.706945369753498</v>
+        <v>1.681488203266788</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3616438356164383</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2147</v>
+        <v>2143</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04095686526192585</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.788604382859804</v>
+        <v>2.795675972935137</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9452054794520547</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>80.2</v>
+        <v>81.8</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1859847789189014</v>
+        <v>0.1726416890860324</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.200611390284757</v>
+        <v>2.264463986599665</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.723688950794738</v>
+        <v>1.724212632676073</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.453382017571918</v>
+        <v>1.470366138884198</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.753424657534246</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005801510762942071</v>
+        <v>0.005799748714565123</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12420</v>
+        <v>12460</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01256885548586711</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4776167471819646</v>
+        <v>0.4728731942215088</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.186185589752733</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03805219881218559</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.5067803038674032</v>
+        <v>0.4768622833935017</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.710342360149007</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>222.2</v>
+        <v>225</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-12.03393274060977</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.03033303330333026</v>
+        <v>-0.04239999999999999</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>224.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>222.2</v>
+        <v>225</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1271318303512</v>
+        <v>-0.1270425742335022</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01260126012601259</v>
+        <v>-0.0004444444444444695</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.306648197717667</v>
+        <v>4.306568699389187</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.933904508684805</v>
+        <v>4.933308970489387</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.583561643835616</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002321991381905668</v>
+        <v>0.002322034245365302</v>
       </c>
     </row>
     <row r="14">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>218</v>
+        <v>219.4</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>253.9</v>
+        <v>255.1</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1822738726340063</v>
+        <v>-0.1838759597162673</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02999015360378099</v>
+        <v>-0.02835299882399056</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.226252219131402</v>
+        <v>3.226803649680857</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.945394565688632</v>
+        <v>3.953815217303279</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003099571676603847</v>
+        <v>0.003099041988808039</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.5</v>
+        <v>80</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.188672375834369</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1782699386503066</v>
+        <v>0.2003625</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.985334123052143</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17810</v>
+        <v>17960</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03436963993104377</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1756436518809656</v>
+        <v>0.1658248017817372</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.834524217849841</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>147.6</v>
+        <v>148.2</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02183643278691482</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5451219512195122</v>
+        <v>0.5388663967611338</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.272708194651608</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>299</v>
+        <v>300.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24070</v>
+        <v>24340</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5009009739470281</v>
+        <v>-0.502654188043852</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.00265202243456597</v>
+        <v>-0.008437678389482284</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.509875856383582</v>
+        <v>1.509922339169825</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.025202970889652</v>
+        <v>3.035960699520192</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.495890410958904</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006623061066723562</v>
+        <v>0.006622857176547325</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>423</v>
+        <v>438.4</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04786207176186421</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5728268085106383</v>
+        <v>0.5175769616788322</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8602739726027396</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>184.8</v>
+        <v>185</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09150934465167805</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1948051948051945</v>
+        <v>0.1935135135135133</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.914573031085914</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9654</v>
+        <v>9544</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02467091211414712</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6752508210068364</v>
+        <v>0.6945590345766974</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.399623289038703</v>
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.6</v>
+        <v>37.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1486712577160273</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9481865284974094</v>
+        <v>0.9946949602122015</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.028051063568724</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>526.9</v>
+        <v>526.8</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13880</v>
+        <v>13800</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,10 +3940,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.217433328235412</v>
+        <v>-2.21732998357862</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.006037314985590791</v>
+        <v>-0.0004649495652173652</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18780</v>
+        <v>18240</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1680213376217799</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1638706070287539</v>
+        <v>0.1983273026315788</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.761874966937765</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>584.8</v>
+        <v>584.7</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05415947468692567</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6710046272229824</v>
+        <v>0.6712904155977424</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.706780339323255</v>
@@ -4288,7 +4288,7 @@
         <v>0.9284102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>47133</v>
@@ -4308,7 +4308,7 @@
         <v>0.1154870076848439</v>
       </c>
       <c r="AZ31" s="12" t="n">
-        <v>0.9257510877030162</v>
+        <v>1.044331819704433</v>
       </c>
       <c r="BA31" s="8" t="n">
         <v>2.241700139199299</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67860</v>
+        <v>67810</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2636362120860116</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1443854995579132</v>
+        <v>0.1452293172098511</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70396519130371</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>131.2</v>
+        <v>128.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07376116795628866</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.03131097560975593</v>
+        <v>-0.01095719844357967</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.7342566740445</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06646675917688198</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9184242424242421</v>
+        <v>0.9419631901840488</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.109408163694451</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8969</v>
+        <v>8958</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.0102466506679319</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1646204972683687</v>
+        <v>0.1660505961152041</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.812889965790071</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.8</v>
+        <v>108.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02644112986316511</v>
+        <v>0.02623084941207249</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3346768893756846</v>
+        <v>0.3359036144578316</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.457023101226119</v>
+        <v>4.457238478776186</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.34221015853124</v>
+        <v>4.343309774140718</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.832876712328767</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002243650026684631</v>
+        <v>0.002243541611609186</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6061</v>
+        <v>6103</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05387268346426118</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.681488203266788</v>
+        <v>1.663034573160741</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3616438356164383</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>319.9</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24290</v>
+        <v>24510</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1260751538440652</v>
+        <v>-0.1310570115203887</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.01440922190201732</v>
+        <v>0.04414524683802523</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.544438748394072</v>
+        <v>6.55564152377696</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.48856011724645</v>
+        <v>7.544386237867411</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.008219178082192</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001528014912272482</v>
+        <v>0.001525403724979552</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24290</v>
+        <v>24510</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08348093745684698</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1965417867435157</v>
+        <v>0.1858017135862913</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.011057435081197</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2143</v>
+        <v>2164</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04095686526192585</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.795675972935137</v>
+        <v>2.758841779112754</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9452054794520547</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12460</v>
+        <v>12550</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01256885548586711</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4728731942215088</v>
+        <v>0.4623107569721117</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.186185589752733</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03805219881218559</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4768622833935017</v>
+        <v>0.4636524239713773</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.710342360149007</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>225</v>
+        <v>225.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-12.03393274060977</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.04239999999999999</v>
+        <v>-0.04579273693534103</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>225</v>
+        <v>225.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1270425742335022</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.0004444444444444695</v>
+        <v>-0.003985828166519045</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.306568699389187</v>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219.4</v>
+        <v>222.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.1</v>
+        <v>252.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1838759597162673</v>
+        <v>-0.187151998778349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02835299882399056</v>
+        <v>-0.006552907436708888</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.226803649680857</v>
+        <v>3.227927090833218</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.953815217303279</v>
+        <v>3.971132470009006</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003099041988808039</v>
+        <v>0.003097963404563366</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17960</v>
+        <v>17850</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03436963993104377</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1658248017817372</v>
+        <v>0.1730091563025209</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.834524217849841</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05557842750018602</v>
+        <v>0.05625431736545893</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9508962868117801</v>
+        <v>0.9469270166453267</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.081819957538019</v>
+        <v>3.081446584364265</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.919555645748052</v>
+        <v>2.917333954241343</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003244835888462713</v>
+        <v>0.00324522905921574</v>
       </c>
     </row>
     <row r="18">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>148.2</v>
+        <v>148</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02183643278691482</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5388663967611338</v>
+        <v>0.540945945945946</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.272708194651608</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24340</v>
+        <v>24280</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.502654188043852</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.008437678389482284</v>
+        <v>-0.005987359637561696</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.509922339169825</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>438.4</v>
+        <v>436.9</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04786207176186421</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5175769616788322</v>
+        <v>0.5227872281986725</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8602739726027396</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>185</v>
+        <v>184.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09150934465167805</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1935135135135133</v>
+        <v>0.1941590048674957</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.914573031085914</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.8</v>
+        <v>89</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9544</v>
+        <v>9534</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02467091211414712</v>
+        <v>0.03188960438286072</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6945590345766974</v>
+        <v>0.644596311097126</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.399623289038703</v>
+        <v>4.398516865951005</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.293693943122873</v>
+        <v>4.262584725409278</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.424657534246576</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002272921871496174</v>
+        <v>0.002273493612678895</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65.3</v>
+        <v>72.7</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.207958428086079</v>
+        <v>0.1672098188519774</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.09079246046511602</v>
+        <v>0.2144044697674417</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.962935885883404</v>
+        <v>2.989887511165108</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.452845906773429</v>
+        <v>2.561568162702612</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003375030842767792</v>
+        <v>0.003344607435114899</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1155</v>
+        <v>1173</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0494812987334202</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5981798510822509</v>
+        <v>0.5736553520886616</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3561643835616438</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13800</v>
+        <v>13700</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.21732998357862</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.0004649495652173652</v>
+        <v>0.006830926715328367</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18240</v>
+        <v>18370</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1680213376217799</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1983273026315788</v>
+        <v>0.1898470332063145</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.761874966937765</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05415947468692567</v>
+        <v>0.05726244278091448</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6712904155977424</v>
+        <v>0.657946779545066</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.706780339323255</v>
+        <v>2.706090894588981</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.567714282629904</v>
+        <v>2.559526173530914</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.832876712328767</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003694426124914215</v>
+        <v>0.003695367372912603</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67810</v>
+        <v>68140</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2636362120860116</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1452293172098511</v>
+        <v>0.1396830055767537</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70396519130371</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.5</v>
+        <v>128.4</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07376116795628866</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01095719844357967</v>
+        <v>-0.01018691588785037</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.7342566740445</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8958</v>
+        <v>8874</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.0102466506679319</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1660505961152041</v>
+        <v>0.1770882623394183</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.812889965790071</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.02623084941207249</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3359036144578316</v>
+        <v>0.3388364434687159</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.457238478776186</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6103</v>
+        <v>6142</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05387268346426118</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.663034573160741</v>
+        <v>1.646125040703354</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3616438356164383</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24510</v>
+        <v>24360</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1310570115203887</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.04414524683802523</v>
+        <v>0.05057471264367819</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.55564152377696</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24510</v>
+        <v>24360</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.08348093745684698</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.1858017135862913</v>
+        <v>0.193103448275862</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.011057435081197</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2164</v>
+        <v>2147</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04095686526192585</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.758841779112754</v>
+        <v>2.788604382859804</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9452054794520547</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12550</v>
+        <v>12470</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.01256885548586711</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4623107569721117</v>
+        <v>0.4716920609462711</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.186185589752733</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.5</v>
+        <v>104.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03805219881218559</v>
+        <v>0.0376886121435597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4636524239713773</v>
+        <v>0.4663646445837062</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.710342360149007</v>
+        <v>2.710422437036049</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.610988506406881</v>
+        <v>2.611980516425937</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.832876712328767</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003689570788928019</v>
+        <v>0.003689461784021898</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>225.8</v>
+        <v>224</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-12.03393274060977</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.04579273693534103</v>
+        <v>-0.03812499999999996</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224.9</v>
+        <v>224.5</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>225.8</v>
+        <v>224</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1270425742335022</v>
+        <v>-0.126685048214102</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.003985828166519045</v>
+        <v>0.002232142857142794</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.306568699389187</v>
+        <v>4.306250123240901</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.933308970489387</v>
+        <v>4.930924535798651</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.583561643835616</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002322034245365302</v>
+        <v>0.002322206029331608</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>252.8</v>
+        <v>255.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.187151998778349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.006552907436708888</v>
+        <v>-0.01743573943661969</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.227927090833218</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80</v>
+        <v>80.3</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.188672375834369</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.2003625</v>
+        <v>0.1958779576587795</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.985334123052143</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17850</v>
+        <v>17970</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03436963993104377</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1730091563025209</v>
+        <v>0.1651760400667779</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.834524217849841</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2670,7 +2670,7 @@
         <v>0.05625431736545893</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9469270166453267</v>
+        <v>0.9394770408163264</v>
       </c>
       <c r="BA17" s="8" t="n">
         <v>3.081446584364265</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24280</v>
+        <v>24300</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.502654188043852</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.005987359637561696</v>
+        <v>-0.006805477037036933</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.509922339169825</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>436.9</v>
+        <v>435.7</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.04786207176186421</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5227872281986725</v>
+        <v>0.5269812715170989</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8602739726027396</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>89</v>
+        <v>91.8</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9534</v>
+        <v>9555</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.03188960438286072</v>
+        <v>0.02467091211414712</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.644596311097126</v>
+        <v>0.6926082078492934</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.398516865951005</v>
+        <v>4.399623289038703</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.262584725409278</v>
+        <v>4.293693943122873</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.424657534246576</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002273493612678895</v>
+        <v>0.002272921871496174</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.7</v>
+        <v>37.1</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1486712577160273</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9946949602122015</v>
+        <v>1.026954177897574</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.028051063568724</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0494812987334202</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5736553520886616</v>
+        <v>0.5382481066666667</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3561643835616438</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13700</v>
+        <v>13630</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.21732998357862</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.006830926715328367</v>
+        <v>0.01200173851797492</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18370</v>
+        <v>18430</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1680213376217799</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1898470332063145</v>
+        <v>0.1859734129137276</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.761874966937765</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>584.7</v>
+        <v>585</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4194,7 +4194,7 @@
         <v>0.05726244278091448</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.657946779545066</v>
+        <v>0.6570965504273505</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>2.706090894588981</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68140</v>
+        <v>68160</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2636362120860116</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1396830055767537</v>
+        <v>0.1393485915492958</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70396519130371</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>815</v>
+        <v>803.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06646675917688198</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9419631901840488</v>
+        <v>0.9687772110959072</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.109408163694451</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>107.5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8874</v>
+        <v>8917</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.0102466506679319</v>
+        <v>0.007668711080856917</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1770882623394183</v>
+        <v>0.1768859369743188</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.812889965790071</v>
+        <v>1.812998815113519</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.79450232731924</v>
+        <v>1.799201260470656</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.832876712328767</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005516054580644074</v>
+        <v>0.005515723406236125</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.9</v>
+        <v>108.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02623084941207249</v>
+        <v>0.02644112986316511</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3388364434687159</v>
+        <v>0.3332166301969366</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.457238478776186</v>
+        <v>4.457023101226119</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.343309774140718</v>
+        <v>4.34221015853124</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.832876712328767</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002243541611609186</v>
+        <v>0.002243650026684631</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6142</v>
+        <v>6073</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05387268346426118</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.646125040703354</v>
+        <v>1.676189692079697</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3616438356164383</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>319.9</v>
+        <v>312.3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24360</v>
+        <v>24400</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1310570115203887</v>
+        <v>-0.1279012142265995</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05057471264367819</v>
+        <v>0.02393442622950825</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.55564152377696</v>
+        <v>6.548570476334864</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.544386237867411</v>
+        <v>7.508977862556495</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7.008219178082192</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001525403724979552</v>
+        <v>0.001527050832870757</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>121.1</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24360</v>
+        <v>24400</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.08348093745684698</v>
+        <v>-0.09050624537826668</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.193103448275862</v>
+        <v>0.2098360655737705</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.011057435081197</v>
+        <v>2.011294835780449</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.194234159735777</v>
+        <v>2.21144436183288</v>
       </c>
       <c r="BC7" s="8" t="n">
         <v>2.005479452054795</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004972508405557421</v>
+        <v>0.004971921481675594</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2147</v>
+        <v>2135</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04095686526192585</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.788604382859804</v>
+        <v>2.809898646370023</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9452054794520547</v>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>81.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>238.8</v>
+        <v>230.5</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1726416890860324</v>
+        <v>0.180096024505521</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.264463986599665</v>
+        <v>2.344802603036876</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.724212632676073</v>
+        <v>1.723919998153532</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.470366138884198</v>
+        <v>1.460830273431251</v>
       </c>
       <c r="BC9" s="8" t="n">
         <v>1.753424657534246</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005799748714565123</v>
+        <v>0.00580073321889117</v>
       </c>
     </row>
     <row r="10">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>114.7</v>
+        <v>111.5</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12470</v>
+        <v>12600</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.01256885548586711</v>
+        <v>-0.005944340409847748</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4716920609462711</v>
+        <v>0.4158730158730159</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.186185589752733</v>
+        <v>4.182853518343765</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.23947088666375</v>
+        <v>4.207866509274088</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.342465753424658</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002388809522558859</v>
+        <v>0.002390712454104676</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.0376886121435597</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4663646445837062</v>
+        <v>0.4624368821428568</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.710422437036049</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>224</v>
+        <v>224.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-12.03393274060977</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.03812499999999996</v>
+        <v>-0.0402672605790646</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224.5</v>
+        <v>224.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>224</v>
+        <v>224.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.126685048214102</v>
+        <v>-0.1265955410670211</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002232142857142794</v>
+        <v>-0.0004454342984409054</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.306250123240901</v>
+        <v>4.306170333151533</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.930924535798651</v>
+        <v>4.930327855679025</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.583561643835616</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002322206029331608</v>
+        <v>0.00232224905805836</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.6</v>
+        <v>257</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.187151998778349</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01743573943661969</v>
+        <v>-0.02278822957198445</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.227927090833218</v>
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.3</v>
+        <v>81.2</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2431,7 +2431,7 @@
         <v>-0.188672375834369</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1958779576587795</v>
+        <v>0.1826231527093596</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1.985334123052143</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17970</v>
+        <v>17810</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03436963993104377</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1651760400667779</v>
+        <v>0.1756436518809656</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.834524217849841</v>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2653,7 +2653,7 @@
         <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>47473</v>
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05625431736545893</v>
+        <v>0.05591614146391322</v>
       </c>
       <c r="AZ17" s="12" t="n">
-        <v>0.9394770408163264</v>
+        <v>0.9389808917197453</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.081446584364265</v>
+        <v>3.081633430294816</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.917333954241343</v>
+        <v>2.91844523374978</v>
       </c>
       <c r="BC17" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00324522905921574</v>
+        <v>0.00324503229413737</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>85.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.147137687192455</v>
+        <v>0.155363847147625</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.311901681759379</v>
+        <v>1.282018111254851</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.805738041422573</v>
+        <v>1.805385978773531</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.574124938604362</v>
+        <v>1.562612490628548</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.832876712328767</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005537901827732406</v>
+        <v>0.0055389817565734</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>148</v>
+        <v>147.8</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.02183643278691482</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.540945945945946</v>
+        <v>0.5430311231393774</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.272708194651608</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24300</v>
+        <v>24270</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.502654188043852</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.006805477037036933</v>
+        <v>-0.005577795302842969</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.509922339169825</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>99.7</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>435.7</v>
+        <v>431</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,16 +3126,16 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.04786207176186421</v>
+        <v>0.03940725901244674</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5269812715170989</v>
+        <v>0.5545473828306264</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.8602739726027396</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8209801612117557</v>
+        <v>0.8276582303457224</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.8328767123287671</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>184.9</v>
+        <v>185.1</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09150934465167805</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1941590048674957</v>
+        <v>0.192868719611021</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.914573031085914</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9555</v>
+        <v>9515</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02467091211414712</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6926082078492934</v>
+        <v>0.6997237441933788</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.399623289038703</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>72.7</v>
+        <v>68.3</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38.7</v>
+        <v>36.9</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1672098188519774</v>
+        <v>0.1907187133278092</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.2144044697674417</v>
+        <v>0.1965593609756098</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.989887511165108</v>
+        <v>2.974440256259328</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.561568162702612</v>
+        <v>2.49802092044593</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003344607435114899</v>
+        <v>0.00336197709096906</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.1</v>
+        <v>37.7</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1486712577160273</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.026954177897574</v>
+        <v>0.9946949602122015</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.028051063568724</v>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1200</v>
+        <v>1179</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.0494812987334202</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5382481066666667</v>
+        <v>0.5656469279050043</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3561643835616438</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>526.8</v>
+        <v>526.9</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13630</v>
+        <v>13650</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,10 +3940,10 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.21732998357862</v>
+        <v>-2.217433328235412</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01200173851797492</v>
+        <v>0.01071077421245414</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18430</v>
+        <v>18240</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.1680213376217799</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1859734129137276</v>
+        <v>0.1983273026315788</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.761874966937765</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4177,7 +4177,7 @@
         <v>9.75253</v>
       </c>
       <c r="AJ30" t="n">
-        <v>585</v>
+        <v>585.5</v>
       </c>
       <c r="AK30" s="10" t="n">
         <v>47289</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05726244278091448</v>
+        <v>0.05493197870644382</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6570965504273505</v>
+        <v>0.6656754910333049</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.706090894588981</v>
+        <v>2.706608794983437</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.559526173530914</v>
+        <v>2.565671388881658</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.832876712328767</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003695367372912603</v>
+        <v>0.003694660276924577</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68160</v>
+        <v>68600</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2636362120860116</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1393485915492958</v>
+        <v>0.1320408163265305</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.70396519130371</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142.8</v>
+        <v>118.1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.4</v>
+        <v>127.9</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07376116795628866</v>
+        <v>-0.007373657737312838</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01018691588785037</v>
+        <v>-0.1781939014855356</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.7342566740445</v>
+        <v>2.72023260955336</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.951999613330251</v>
+        <v>2.740439673757401</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.832876712328767</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00365730112133476</v>
+        <v>0.003676156209906592</v>
       </c>
     </row>
     <row r="34">
@@ -4618,7 +4618,7 @@
         <v>18</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="AK34" s="10" t="n">
         <v>46895</v>
@@ -4635,7 +4635,7 @@
         <v>0.03315734030314918</v>
       </c>
       <c r="AZ34" s="12" t="n">
-        <v>0.224</v>
+        <v>0.2248165443629087</v>
       </c>
       <c r="BA34" s="8" t="n">
         <v>1.735487214545365</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222.3</v>
+        <v>220.6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.187151998778349</v>
+        <v>-0.185238462398414</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02278822957198445</v>
+        <v>-0.03026128404669259</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.227927090833218</v>
+        <v>3.22727156599563</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.971132470009006</v>
+        <v>3.96100136918067</v>
       </c>
       <c r="BC14" s="8" t="n">
         <v>3.336986301369863</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003097963404563366</v>
+        <v>0.003098592664269624</v>
       </c>
     </row>
     <row r="15">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>118.1</v>
+        <v>142.8</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.007373657737312838</v>
+        <v>-0.07376116795628866</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.1781939014855356</v>
+        <v>-0.00631743549648156</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.72023260955336</v>
+        <v>2.7342566740445</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.740439673757401</v>
+        <v>2.951999613330251</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.832876712328767</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003676156209906592</v>
+        <v>0.00365730112133476</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06646675917688198</v>
+        <v>0.06648508946720762</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.9687772110959072</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.109408163694451</v>
+        <v>3.106659262590386</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.915616578705507</v>
+        <v>2.912988932777677</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.336986301369863</v>
+        <v>3.334246575342466</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003216046100592492</v>
+        <v>0.003218891791712563</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.007668711080856917</v>
+        <v>0.007612002289986083</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1768859369743188</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.812998815113519</v>
+        <v>1.810261483801777</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.799201260470656</v>
+        <v>1.796585868059948</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.832876712328767</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005515723406236125</v>
+        <v>0.005524063838003523</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02644112986316511</v>
+        <v>0.02643107504630946</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3332166301969366</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.457023101226119</v>
+        <v>4.454293675346718</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.34221015853124</v>
+        <v>4.339593552490364</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.832876712328767</v>
+        <v>4.83013698630137</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002243650026684631</v>
+        <v>0.002245024852166177</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05387268346426118</v>
+        <v>0.05418985019958541</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.676189692079697</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3616438356164383</v>
+        <v>0.3589041095890412</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3431570447652678</v>
+        <v>0.3404549090669876</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3342465753424658</v>
+        <v>0.3315068493150685</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02765151515151516</v>
+        <v>0.02786259541984732</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1279012142265995</v>
+        <v>-0.1279557826547837</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02393442622950825</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.548570476334864</v>
+        <v>6.545953765207117</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.508977862556495</v>
+        <v>7.506447075740162</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.008219178082192</v>
+        <v>7.005479452054795</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001527050832870757</v>
+        <v>0.001527661263535306</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09050624537826668</v>
+        <v>-0.09063144641071647</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2098360655737705</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.011294835780449</v>
+        <v>2.008559328166498</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.21144436183288</v>
+        <v>2.208740691811589</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.005479452054795</v>
+        <v>2.002739726027397</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004971921481675594</v>
+        <v>0.004978692866955761</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04095686526192585</v>
+        <v>0.04106810450865155</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.809898646370023</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9452054794520547</v>
+        <v>0.9424657534246577</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9080159908587776</v>
+        <v>0.9052873191898133</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9178082191780822</v>
+        <v>0.9150684931506849</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01057971014492754</v>
+        <v>0.01061046511627907</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.180096024505521</v>
+        <v>0.1803031844321807</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.344802603036876</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.723919998153532</v>
+        <v>1.721172142228207</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.460830273431251</v>
+        <v>1.458245783735835</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.753424657534246</v>
+        <v>1.750684931506849</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.00580073321889117</v>
+        <v>0.005809994104979023</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005944340409847748</v>
+        <v>-0.005959778636974543</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4158730158730159</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.182853518343765</v>
+        <v>4.180121609295536</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.207866509274088</v>
+        <v>4.205183572515571</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.342465753424658</v>
+        <v>4.33972602739726</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002390712454104676</v>
+        <v>0.002392274898836082</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.0376886121435597</v>
+        <v>0.03767265455284374</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4624368821428568</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.710422437036049</v>
+        <v>2.707686225199445</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.611980516425937</v>
+        <v>2.609383810317568</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.832876712328767</v>
+        <v>2.83013698630137</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003689461784021898</v>
+        <v>0.003693190114472519</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-12.03393274060977</v>
+        <v>-13.2390750440674</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>-0.0402672605790646</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.00821917808219178</v>
+        <v>0.005479452054794521</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1265955410670211</v>
+        <v>-0.1266842989933002</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.0004454342984409054</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.306170333151533</v>
+        <v>4.303509729386136</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.930327855679025</v>
+        <v>4.927782386627584</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.583561643835616</v>
+        <v>4.580821917808219</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00232224905805836</v>
+        <v>0.002323684766346845</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.185238462398414</v>
+        <v>-0.1853926717815834</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.03026128404669259</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.22727156599563</v>
+        <v>3.224584738379798</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.96100136918067</v>
+        <v>3.958452897093514</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.336986301369863</v>
+        <v>3.334246575342466</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003098592664269624</v>
+        <v>0.003101174511240951</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.188672375834369</v>
+        <v>-0.1889497624545266</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1826231527093596</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.985334123052143</v>
+        <v>1.982659159124967</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.447019014166884</v>
+        <v>2.444557768856833</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.098630136986301</v>
+        <v>2.095890410958904</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005036935538400233</v>
+        <v>0.005043731270690739</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03436963993104377</v>
+        <v>-0.03445239738884485</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1756436518809656</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.834524217849841</v>
+        <v>1.831786418479212</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.899820359540929</v>
+        <v>1.897147705121389</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.832876712328767</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005451004627085559</v>
+        <v>0.005459151732494126</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.05591614146391322</v>
+        <v>0.0559209319582244</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9389808917197453</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.081633430294816</v>
+        <v>3.078891057910262</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.91844523374978</v>
+        <v>2.915834855362136</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.336986301369863</v>
+        <v>3.334246575342466</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.00324503229413737</v>
+        <v>0.003247922648743314</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.155363847147625</v>
+        <v>0.1555138107794581</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.282018111254851</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.805385978773531</v>
+        <v>1.802639837038992</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.562612490628548</v>
+        <v>1.56003313869785</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.832876712328767</v>
+        <v>1.83013698630137</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.0055389817565734</v>
+        <v>0.005547419842016781</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02183643278691482</v>
+        <v>0.02181824753328845</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5430311231393774</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.272708194651608</v>
+        <v>3.269977809760783</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.202771098820345</v>
+        <v>3.200156013708548</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.498630136986301</v>
+        <v>3.495890410958904</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003055573367751639</v>
+        <v>0.003058124727987545</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.502654188043852</v>
+        <v>-0.5032936189085672</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.005577795302842969</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.509922339169825</v>
+        <v>1.507199567397699</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.035960699520192</v>
+        <v>3.034387366004577</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.495890410958904</v>
+        <v>1.493150684931507</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006622857176547325</v>
+        <v>0.006634821437260498</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03940725901244674</v>
+        <v>0.03941449826781709</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5545473828306264</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8602739726027396</v>
+        <v>0.8575342465753427</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8276582303457224</v>
+        <v>0.8250166300397218</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8328767123287671</v>
+        <v>0.8301369863013699</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01162420382165605</v>
+        <v>0.01166134185303514</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09150934465167805</v>
+        <v>0.09153919564616342</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.192868719611021</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.914573031085914</v>
+        <v>1.911825257049606</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.754060137430057</v>
+        <v>1.751494829205702</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.098630136986301</v>
+        <v>2.095890410958904</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005223096657915507</v>
+        <v>0.005230603562290177</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02467091211414712</v>
+        <v>0.02468300569672978</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.6997237441933788</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.399623289038703</v>
+        <v>4.396881724008534</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.293693943122873</v>
+        <v>4.290967742769277</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.424657534246576</v>
+        <v>4.421917808219178</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002272921871496174</v>
+        <v>0.002274339094771745</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1907187133278092</v>
+        <v>0.1908262736231878</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.1965593609756098</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.974440256259328</v>
+        <v>2.971629211931984</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.49802092044593</v>
+        <v>2.495434705929485</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.336986301369863</v>
+        <v>3.334246575342466</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00336197709096906</v>
+        <v>0.00336515738903326</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1486712577160273</v>
+        <v>0.1487491011745581</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.9946949602122015</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.028051063568724</v>
+        <v>3.025264446007242</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.636133744296502</v>
+        <v>2.633529325867597</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.336986301369863</v>
+        <v>3.334246575342466</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.0033024542156216</v>
+        <v>0.003305496156938626</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>57.44590023089727</v>
+        <v>57.84860351307263</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>-0.06891666666666663</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3616438356164384</v>
+        <v>0.3589041095890412</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.00618766815444236</v>
+        <v>0.00609877020292103</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3342465753424658</v>
+        <v>0.3315068493150685</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02765151515151515</v>
+        <v>0.02786259541984732</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0494812987334202</v>
+        <v>0.04965004070834822</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5656469279050043</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342466</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3393718249114923</v>
+        <v>0.3367071345948224</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3342465753424658</v>
+        <v>0.3315068493150685</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02807692307692308</v>
+        <v>0.02829457364341085</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.217433328235412</v>
+        <v>-2.234374562016596</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.01071077421245414</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3342465753424658</v>
+        <v>0.3315068493150685</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1680213376217799</v>
+        <v>-0.168194954259744</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.1983273026315788</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.761874966937765</v>
+        <v>2.759166578135818</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.319646394587711</v>
+        <v>3.317083242360387</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.832876712328767</v>
+        <v>2.83013698630137</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003620728714988688</v>
+        <v>0.003624282810339172</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05493197870644382</v>
+        <v>0.05493080269858694</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6656754910333049</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.706608794983437</v>
+        <v>2.703869330152649</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.565671388881658</v>
+        <v>2.563077429567856</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.832876712328767</v>
+        <v>2.83013698630137</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003694660276924577</v>
+        <v>0.003698403576120834</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1154870076848439</v>
+        <v>0.1155431216162661</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.044331819704433</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.241700139199299</v>
+        <v>2.238946174680727</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.009615642096874</v>
+        <v>2.007045833814839</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.405479452054795</v>
+        <v>2.402739726027397</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004460899932660864</v>
+        <v>0.004466386960564605</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2636362120860116</v>
+        <v>-0.2640251303150951</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1320408163265305</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.70396519130371</v>
+        <v>1.701239611264184</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.314026326757316</v>
+        <v>2.31154578958999</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.706849315068493</v>
+        <v>1.704109589041096</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005868664483896506</v>
+        <v>0.005878066754258704</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07376116795628866</v>
+        <v>-0.07386793428558842</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.00631743549648156</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.7342566740445</v>
+        <v>2.731539076145678</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.951999613330251</v>
+        <v>2.949405573209031</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.832876712328767</v>
+        <v>2.83013698630137</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.00365730112133476</v>
+        <v>0.003660939756392004</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03315734030314918</v>
+        <v>0.03313926042432644</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2248165443629087</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.735487214545365</v>
+        <v>1.732748202165002</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.679789850823823</v>
+        <v>1.677168091989201</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.753424657534246</v>
+        <v>1.750684931506849</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005762070683199842</v>
+        <v>0.005771178978864549</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06648508946720762</v>
+        <v>0.06650345767668067</v>
       </c>
       <c r="AZ2" s="12" t="n">
         <v>0.9687772110959072</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.106659262590386</v>
+        <v>3.103910342329284</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.912988932777677</v>
+        <v>2.910361255734681</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.334246575342466</v>
+        <v>3.331506849315069</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003218891791712563</v>
+        <v>0.003221742543148217</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.007612002289986083</v>
+        <v>0.007555133275366017</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1768859369743188</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.810261483801777</v>
+        <v>1.807524159268066</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.796585868059948</v>
+        <v>1.793970473250586</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.83013698630137</v>
+        <v>1.827397260273973</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005524063838003523</v>
+        <v>0.005532429510679057</v>
       </c>
     </row>
     <row r="4">
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02643107504630946</v>
+        <v>0.02642101103098185</v>
       </c>
       <c r="AZ4" s="12" t="n">
         <v>0.3332166301969366</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.454293675346718</v>
+        <v>4.451564258728596</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.339593552490364</v>
+        <v>4.33697694307451</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.83013698630137</v>
+        <v>4.827397260273973</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002245024852166177</v>
+        <v>0.002246401358891331</v>
       </c>
     </row>
     <row r="5">
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.05418985019958541</v>
+        <v>0.0545119027021635</v>
       </c>
       <c r="AZ5" s="12" t="n">
         <v>1.676189692079697</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3589041095890412</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3404549090669876</v>
+        <v>0.3377528339404994</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3315068493150685</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02786259541984732</v>
+        <v>0.02807692307692308</v>
       </c>
     </row>
     <row r="6">
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1279557826547837</v>
+        <v>-0.1280103921746371</v>
       </c>
       <c r="AZ6" s="12" t="n">
         <v>0.02393442622950825</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.545953765207117</v>
+        <v>6.543337120369132</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.506447075740162</v>
+        <v>7.503916401810598</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.005479452054795</v>
+        <v>7.002739726027397</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001527661263535306</v>
+        <v>0.001528272166945277</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09063144641071647</v>
+        <v>-0.09075697176964102</v>
       </c>
       <c r="AZ7" s="12" t="n">
         <v>0.2098360655737705</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.008559328166498</v>
+        <v>2.005823831043847</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.208740691811589</v>
+        <v>2.206037075640537</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2.002739726027397</v>
+        <v>2</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004978692866955761</v>
+        <v>0.004985482695554533</v>
       </c>
     </row>
     <row r="8">
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04106810450865155</v>
+        <v>0.04117999249205764</v>
       </c>
       <c r="AZ8" s="12" t="n">
         <v>2.809898646370023</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9424657534246577</v>
+        <v>0.9397260273972602</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9052873191898133</v>
+        <v>0.9025586682164646</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9150684931506849</v>
+        <v>0.9123287671232877</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01061046511627907</v>
+        <v>0.01064139941690962</v>
       </c>
     </row>
     <row r="9">
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1803031844321807</v>
+        <v>0.1805110582193112</v>
       </c>
       <c r="AZ9" s="12" t="n">
         <v>2.344802603036876</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.721172142228207</v>
+        <v>1.718424258427423</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.458245783735835</v>
+        <v>1.455661297251635</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.750684931506849</v>
+        <v>1.747945205479452</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005809994104979023</v>
+        <v>0.005819284702807487</v>
       </c>
     </row>
     <row r="10">
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005959778636974543</v>
+        <v>-0.005975236283513869</v>
       </c>
       <c r="AZ10" s="3" t="n">
         <v>0.4158730158730159</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.180121609295536</v>
+        <v>4.177389709837716</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.205183572515571</v>
+        <v>4.20250064416824</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.33972602739726</v>
+        <v>4.336986301369863</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002392274898836082</v>
+        <v>0.002393839381671786</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03767265455284374</v>
+        <v>0.03765667274661461</v>
       </c>
       <c r="AZ11" s="12" t="n">
         <v>0.4624368821428568</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.707686225199445</v>
+        <v>2.704950018667484</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.609383810317568</v>
+        <v>2.606787090288394</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.83013698630137</v>
+        <v>2.827397260273973</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003693190114472519</v>
+        <v>0.003696925980512651</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-13.2390750440674</v>
+        <v>-14.7120264560872</v>
       </c>
       <c r="AZ12" s="12" t="n">
         <v>-0.0402672605790646</v>
@@ -2113,7 +2113,7 @@
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.005479452054794521</v>
+        <v>0.00273972602739726</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1266842989933002</v>
+        <v>-0.1267731584330202</v>
       </c>
       <c r="AZ13" s="12" t="n">
         <v>-0.0004454342984409054</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.303509729386136</v>
+        <v>4.300849202663533</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.927782386627584</v>
+        <v>4.925237060905944</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.580821917808219</v>
+        <v>4.578082191780822</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002323684766346845</v>
+        <v>0.002325122209308562</v>
       </c>
     </row>
     <row r="14">
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.1853926717815834</v>
+        <v>-0.185547111025413</v>
       </c>
       <c r="AZ14" s="12" t="n">
         <v>-0.03026128404669259</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.224584738379798</v>
+        <v>3.221897977220474</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.958452897093514</v>
+        <v>3.955904658005339</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.334246575342466</v>
+        <v>3.331506849315069</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.003101174511240951</v>
+        <v>0.00310376060033626</v>
       </c>
     </row>
     <row r="15">
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1889497624545266</v>
+        <v>-0.1892278078991016</v>
       </c>
       <c r="AZ15" s="12" t="n">
         <v>0.1826231527093596</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.982659159124967</v>
+        <v>1.979984337392363</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.444557768856833</v>
+        <v>2.442096999234477</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.095890410958904</v>
+        <v>2.093150684931507</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005043731270690739</v>
+        <v>0.005050545002376125</v>
       </c>
     </row>
     <row r="16">
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03445239738884485</v>
+        <v>-0.03453539358387062</v>
       </c>
       <c r="AZ16" s="12" t="n">
         <v>0.1756436518809656</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.831786418479212</v>
+        <v>1.8290486246742</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.897147705121389</v>
+        <v>1.894475066738856</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.83013698630137</v>
+        <v>1.827397260273973</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005459151732494126</v>
+        <v>0.00546732321114823</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0559209319582244</v>
+        <v>0.0559257372756963</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9389808917197453</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.078891057910262</v>
+        <v>3.076148677324301</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.915834855362136</v>
+        <v>2.913224451996794</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.334246575342466</v>
+        <v>3.331506849315069</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003247922648743314</v>
+        <v>0.003250818165491992</v>
       </c>
     </row>
     <row r="18">
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1555138107794581</v>
+        <v>0.1556642678215366</v>
       </c>
       <c r="AZ18" s="12" t="n">
         <v>1.282018111254851</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.802639837038992</v>
+        <v>1.799893674282776</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.56003313869785</v>
+        <v>1.557453773037071</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.83013698630137</v>
+        <v>1.827397260273973</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005547419842016781</v>
+        <v>0.005555883740735302</v>
       </c>
     </row>
     <row r="19">
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02181824753328845</v>
+        <v>0.02180003646611907</v>
       </c>
       <c r="AZ19" s="12" t="n">
         <v>0.5430311231393774</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.269977809760783</v>
+        <v>3.26724743794512</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.200156013708548</v>
+        <v>3.197540929089071</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.495890410958904</v>
+        <v>3.493150684931507</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003058124727987545</v>
+        <v>0.003060680340234448</v>
       </c>
     </row>
     <row r="20">
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5032936189085672</v>
+        <v>-0.5039345446397384</v>
       </c>
       <c r="AZ20" s="12" t="n">
         <v>-0.005577795302842969</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.507199567397699</v>
+        <v>1.504476835846099</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.034387366004577</v>
+        <v>3.032819196719697</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.493150684931507</v>
+        <v>1.49041095890411</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006634821437260498</v>
+        <v>0.006646828825633679</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03941449826781709</v>
+        <v>0.03942180735890902</v>
       </c>
       <c r="AZ21" s="12" t="n">
         <v>0.5545473828306264</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8575342465753427</v>
+        <v>0.8547945205479451</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8250166300397218</v>
+        <v>0.8223750112766177</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8301369863013699</v>
+        <v>0.8273972602739726</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01166134185303514</v>
+        <v>0.01169871794871795</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09153919564616342</v>
+        <v>0.09156915338633578</v>
       </c>
       <c r="AZ22" s="12" t="n">
         <v>0.192868719611021</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.911825257049606</v>
+        <v>1.909077454137735</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.751494829205702</v>
+        <v>1.748929463804719</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.095890410958904</v>
+        <v>2.093150684931507</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005230603562290177</v>
+        <v>0.005238132155573887</v>
       </c>
     </row>
     <row r="23">
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02468300569672978</v>
+        <v>0.02469511455957676</v>
       </c>
       <c r="AZ23" s="12" t="n">
         <v>0.6997237441933788</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.396881724008534</v>
+        <v>4.394140156605835</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.290967742769277</v>
+        <v>4.288241540503954</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.421917808219178</v>
+        <v>4.419178082191781</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002274339094771745</v>
+        <v>0.00227575808772661</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1908262736231878</v>
+        <v>0.1909340624221614</v>
       </c>
       <c r="AZ24" s="12" t="n">
         <v>0.1965593609756098</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.971629211931984</v>
+        <v>2.96881801027789</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.495434705929485</v>
+        <v>2.492848348161114</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.334246575342466</v>
+        <v>3.331506849315069</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00336515738903326</v>
+        <v>0.00336834388816712</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1487491011745581</v>
+        <v>0.1488271038556464</v>
       </c>
       <c r="AZ25" s="12" t="n">
         <v>0.9946949602122015</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.025264446007242</v>
+        <v>3.022477729377995</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.633529325867597</v>
+        <v>2.630924809515792</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.334246575342466</v>
+        <v>3.331506849315069</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003305496156938626</v>
+        <v>0.003308543815824222</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>57.84860351307263</v>
+        <v>58.25754481506694</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>-0.06891666666666663</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3589041095890412</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.00609877020292103</v>
+        <v>0.006010447862346885</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3315068493150685</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02786259541984732</v>
+        <v>0.02807692307692308</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.04965004070834822</v>
+        <v>0.0498214515833668</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5656469279050043</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3534246575342466</v>
+        <v>0.3506849315068493</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3367071345948224</v>
+        <v>0.3340424516739847</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3315068493150685</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.02829457364341085</v>
+        <v>0.028515625</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3940,7 +3940,7 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.234374562016596</v>
+        <v>-2.251576429420905</v>
       </c>
       <c r="AZ28" s="12" t="n">
         <v>0.01071077421245414</v>
@@ -3948,7 +3948,7 @@
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3315068493150685</v>
+        <v>0.3287671232876712</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.168194954259744</v>
+        <v>-0.1683688761538659</v>
       </c>
       <c r="AZ29" s="12" t="n">
         <v>0.1983273026315788</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.759166578135818</v>
+        <v>2.756458240618498</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.317083242360387</v>
+        <v>3.314520298218769</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.83013698630137</v>
+        <v>2.827397260273973</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003624282810339172</v>
+        <v>0.003627843822424891</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05493080269858694</v>
+        <v>0.05492963303701845</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6656754910333049</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.703869330152649</v>
+        <v>2.701129863912174</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.563077429567856</v>
+        <v>2.560483447730953</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.83013698630137</v>
+        <v>2.827397260273973</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003698403576120834</v>
+        <v>0.003702154470098868</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1155431216162661</v>
+        <v>0.1155993936420554</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.044331819704433</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.238946174680727</v>
+        <v>2.236192169718992</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.007045833814839</v>
+        <v>2.004475963740514</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.402739726027397</v>
+        <v>2.4</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004466386960564605</v>
+        <v>0.004471887584355792</v>
       </c>
     </row>
     <row r="32">
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2640251303150951</v>
+        <v>-0.2644150919873296</v>
       </c>
       <c r="AZ32" s="12" t="n">
         <v>0.1320408163265305</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.701239611264184</v>
+        <v>1.69851406959067</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.31154578958999</v>
+        <v>2.309065957021257</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.704109589041096</v>
+        <v>1.701369863013699</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005878066754258704</v>
+        <v>0.005887499066999151</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07386793428558842</v>
+        <v>-0.0739748980539135</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.00631743549648156</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.731539076145678</v>
+        <v>2.72882151776872</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.949405573209031</v>
+        <v>2.946811605899203</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.83013698630137</v>
+        <v>2.827397260273973</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003660939756392004</v>
+        <v>0.003664585585713468</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03313926042432644</v>
+        <v>0.03312113216063943</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2248165443629087</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.732748202165002</v>
+        <v>1.730009191695549</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.677168091989201</v>
+        <v>1.67454632166652</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.750684931506849</v>
+        <v>1.747945205479452</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005771178978864549</v>
+        <v>0.005780316109302974</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>803.9</v>
+        <v>805</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -943,22 +943,22 @@
         <v>1082</v>
       </c>
       <c r="AY2" s="11" t="n">
-        <v>0.06650345767668067</v>
+        <v>0.06652186390597495</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9687772110959072</v>
+        <v>0.9660869565217389</v>
       </c>
       <c r="BA2" s="8" t="n">
-        <v>3.103910342329284</v>
+        <v>3.101161402859654</v>
       </c>
       <c r="BB2" s="8" t="n">
-        <v>2.910361255734681</v>
+        <v>2.90773354753565</v>
       </c>
       <c r="BC2" s="8" t="n">
-        <v>3.331506849315069</v>
+        <v>3.328767123287671</v>
       </c>
       <c r="BD2" s="11" t="n">
-        <v>0.003221742543148217</v>
+        <v>0.003224598368462461</v>
       </c>
       <c r="BE2" s="1" t="n"/>
       <c r="BF2" s="1" t="n"/>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.007555133275366017</v>
+        <v>0.007498103318900832</v>
       </c>
       <c r="AZ3" s="12" t="n">
         <v>0.1768859369743188</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.807524159268066</v>
+        <v>1.804786841542811</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.793970473250586</v>
+        <v>1.791355076101366</v>
       </c>
       <c r="BC3" s="8" t="n">
-        <v>1.827397260273973</v>
+        <v>1.824657534246575</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005532429510679057</v>
+        <v>0.005540820538923898</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>108.8</v>
+        <v>109.2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>91.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02642101103098185</v>
+        <v>0.0255700540446938</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.3332166301969366</v>
+        <v>0.2874105263157896</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.451564258728596</v>
+        <v>4.449695653906621</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.33697694307451</v>
+        <v>4.33875349261388</v>
       </c>
       <c r="BC4" s="8" t="n">
-        <v>4.827397260273973</v>
+        <v>4.824657534246575</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002246401358891331</v>
+        <v>0.002247344712490724</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6073</v>
+        <v>6064</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1272,22 +1272,22 @@
         <v>2101</v>
       </c>
       <c r="AY5" s="11" t="n">
-        <v>0.0545119027021635</v>
+        <v>0.05483895459386028</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.676189692079697</v>
+        <v>1.680161609498681</v>
       </c>
       <c r="BA5" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342465</v>
       </c>
       <c r="BB5" s="8" t="n">
-        <v>0.3377528339404994</v>
+        <v>0.3350508207865</v>
       </c>
       <c r="BC5" s="8" t="n">
-        <v>0.3287671232876712</v>
+        <v>0.326027397260274</v>
       </c>
       <c r="BD5" s="11" t="n">
-        <v>0.02807692307692308</v>
+        <v>0.02829457364341086</v>
       </c>
     </row>
     <row r="6">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>312.3</v>
+        <v>322</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24400</v>
+        <v>24360</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1280103921746371</v>
+        <v>-0.132080850909001</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.02393442622950825</v>
+        <v>0.05747126436781613</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.543337120369132</v>
+        <v>6.549697612364303</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.503916401810598</v>
+        <v>7.546437498497438</v>
       </c>
       <c r="BC6" s="8" t="n">
-        <v>7.002739726027397</v>
+        <v>7</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001528272166945277</v>
+        <v>0.001526788043026953</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24400</v>
+        <v>24360</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-        <v>-0.09075697176964102</v>
+        <v>-0.09088282271519445</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2098360655737705</v>
+        <v>0.2118226600985222</v>
       </c>
       <c r="BA7" s="8" t="n">
-        <v>2.005823831043847</v>
+        <v>2.003088344451551</v>
       </c>
       <c r="BB7" s="8" t="n">
-        <v>2.206037075640537</v>
+        <v>2.203333513545559</v>
       </c>
       <c r="BC7" s="8" t="n">
-        <v>2</v>
+        <v>1.997260273972603</v>
       </c>
       <c r="BD7" s="11" t="n">
-        <v>0.004985482695554533</v>
+        <v>0.004992291042828676</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2135</v>
+        <v>2092</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,22 +1617,22 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04117999249205764</v>
+        <v>0.04129253490281405</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.809898646370023</v>
+        <v>2.888209182600382</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9397260273972602</v>
+        <v>0.9369863013698631</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.9025586682164646</v>
+        <v>0.8998300381144226</v>
       </c>
       <c r="BC8" s="8" t="n">
-        <v>0.9123287671232877</v>
+        <v>0.9095890410958904</v>
       </c>
       <c r="BD8" s="11" t="n">
-        <v>0.01064139941690962</v>
+        <v>0.01067251461988304</v>
       </c>
     </row>
     <row r="9">
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>230.5</v>
+        <v>214.4</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1729,22 +1729,22 @@
         <v>1975</v>
       </c>
       <c r="AY9" s="11" t="n">
-        <v>0.1805110582193112</v>
+        <v>0.1807196494824911</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.344802603036876</v>
+        <v>2.595974813432836</v>
       </c>
       <c r="BA9" s="8" t="n">
-        <v>1.718424258427423</v>
+        <v>1.715676346610731</v>
       </c>
       <c r="BB9" s="8" t="n">
-        <v>1.455661297251635</v>
+        <v>1.453076814096141</v>
       </c>
       <c r="BC9" s="8" t="n">
-        <v>1.747945205479452</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="BD9" s="11" t="n">
-        <v>0.005819284702807487</v>
+        <v>0.005828605156068457</v>
       </c>
     </row>
     <row r="10">
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12600</v>
+        <v>12480</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005975236283513869</v>
+        <v>-0.005990713387202561</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4158730158730159</v>
+        <v>0.4294871794871795</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.177389709837716</v>
+        <v>4.174657819988498</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.20250064416824</v>
+        <v>4.199817724252991</v>
       </c>
       <c r="BC10" s="4" t="n">
-        <v>4.336986301369863</v>
+        <v>4.334246575342465</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002393839381671786</v>
+        <v>0.002395405906591777</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.6</v>
+        <v>104.3</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1120</v>
+        <v>1098</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03765667274661461</v>
+        <v>0.03873567801644592</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4624368821428568</v>
+        <v>0.4874604863387977</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.704950018667484</v>
+        <v>2.701972612160273</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.606787090288394</v>
+        <v>2.601212868051205</v>
       </c>
       <c r="BC11" s="8" t="n">
-        <v>2.827397260273973</v>
+        <v>2.824657534246575</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003696925980512651</v>
+        <v>0.003700999764022342</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>224.5</v>
+        <v>221.8</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2105,15 +2105,15 @@
         <v>1006</v>
       </c>
       <c r="AY12" s="11" t="n">
-        <v>-14.7120264560872</v>
+        <v>-16.55321539245412</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.0402672605790646</v>
+        <v>-0.02858431018935981</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
       <c r="BC12" s="8" t="n">
-        <v>0.00273972602739726</v>
+        <v>0</v>
       </c>
       <c r="BD12" s="11" t="n"/>
       <c r="BE12" s="1" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>224.5</v>
+        <v>221.8</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1267731584330202</v>
+        <v>-0.126862119559157</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.0004454342984409054</v>
+        <v>0.01172227231740308</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.300849202663533</v>
+        <v>4.298188753092063</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.925237060905944</v>
+        <v>4.922691878769397</v>
       </c>
       <c r="BC13" s="8" t="n">
-        <v>4.578082191780822</v>
+        <v>4.575342465753424</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002325122209308562</v>
+        <v>0.002326561390028794</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>257</v>
+        <v>253.4</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2319,22 +2319,22 @@
         <v>1769</v>
       </c>
       <c r="AY14" s="11" t="n">
-        <v>-0.185547111025413</v>
+        <v>-0.1857017806377094</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03026128404669259</v>
+        <v>-0.01648441199684303</v>
       </c>
       <c r="BA14" s="8" t="n">
-        <v>3.221897977220474</v>
+        <v>3.219211282636755</v>
       </c>
       <c r="BB14" s="8" t="n">
-        <v>3.955904658005339</v>
+        <v>3.953356652502381</v>
       </c>
       <c r="BC14" s="8" t="n">
-        <v>3.331506849315069</v>
+        <v>3.328767123287671</v>
       </c>
       <c r="BD14" s="11" t="n">
-        <v>0.00310376060033626</v>
+        <v>0.003106350941901929</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2414,7 @@
         <v>0.545</v>
       </c>
       <c r="AJ15" t="n">
-        <v>81.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AK15" s="10" t="n">
         <v>47021</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1892278078991016</v>
+        <v>-0.1895065144886296</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1826231527093596</v>
+        <v>0.1943905472636815</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.979984337392363</v>
+        <v>1.977309658309824</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.442096999234477</v>
+        <v>2.43963670733549</v>
       </c>
       <c r="BC15" s="8" t="n">
-        <v>2.093150684931507</v>
+        <v>2.09041095890411</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005050545002376125</v>
+        <v>0.005057376803867865</v>
       </c>
     </row>
     <row r="16">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.6</v>
+        <v>111.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17810</v>
+        <v>17790</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03453539358387062</v>
+        <v>-0.03272513463858011</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1756436518809656</v>
+        <v>0.1727468285553684</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.8290486246742</v>
+        <v>1.826266756005275</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.894475066738856</v>
+        <v>1.888053563061307</v>
       </c>
       <c r="BC16" s="8" t="n">
-        <v>1.827397260273973</v>
+        <v>1.824657534246575</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.00546732321114823</v>
+        <v>0.005475651334678907</v>
       </c>
     </row>
     <row r="17">
@@ -2667,22 +2667,22 @@
         <v>486</v>
       </c>
       <c r="AY17" s="11" t="n">
-        <v>0.0559257372756963</v>
+        <v>0.05593055745445944</v>
       </c>
       <c r="AZ17" s="12" t="n">
         <v>0.9389808917197453</v>
       </c>
       <c r="BA17" s="8" t="n">
-        <v>3.076148677324301</v>
+        <v>3.073406288515751</v>
       </c>
       <c r="BB17" s="8" t="n">
-        <v>2.913224451996794</v>
+        <v>2.910614023638862</v>
       </c>
       <c r="BC17" s="8" t="n">
-        <v>3.331506849315069</v>
+        <v>3.328767123287671</v>
       </c>
       <c r="BD17" s="11" t="n">
-        <v>0.003250818165491992</v>
+        <v>0.00325371885824745</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.1556642678215366</v>
+        <v>0.163474657029748</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.282018111254851</v>
+        <v>1.254851228978008</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.799893674282776</v>
+        <v>1.79681993065786</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.557453773037071</v>
+        <v>1.544356741937971</v>
       </c>
       <c r="BC18" s="8" t="n">
-        <v>1.827397260273973</v>
+        <v>1.824657534246575</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005555883740735302</v>
+        <v>0.005565387955341053</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>147.8</v>
+        <v>150</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.02180003646611907</v>
+        <v>0.0217817995202038</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5430311231393774</v>
+        <v>0.5204</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.26724743794512</v>
+        <v>3.264517079237326</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.197540929089071</v>
+        <v>3.194925844999626</v>
       </c>
       <c r="BC19" s="8" t="n">
-        <v>3.493150684931507</v>
+        <v>3.49041095890411</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003060680340234448</v>
+        <v>0.003063240215099825</v>
       </c>
     </row>
     <row r="20">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>300.6</v>
+        <v>301.9</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24270</v>
+        <v>24350</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5039345446397384</v>
+        <v>-0.5059921600355936</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.005577795302842969</v>
+        <v>-0.004558458234086293</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.504476835846099</v>
+        <v>1.501791672507348</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.032819196719697</v>
+        <v>3.040015868200701</v>
       </c>
       <c r="BC20" s="8" t="n">
-        <v>1.49041095890411</v>
+        <v>1.487671232876712</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006646828825633679</v>
+        <v>0.006658713177776707</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>431</v>
+        <v>422.5</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3126,22 +3126,22 @@
         <v>473</v>
       </c>
       <c r="AY21" s="11" t="n">
-        <v>0.03942180735890902</v>
+        <v>0.03942918695244019</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5545473828306264</v>
+        <v>0.5858223005917158</v>
       </c>
       <c r="BA21" s="8" t="n">
-        <v>0.8547945205479451</v>
+        <v>0.852054794520548</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.8223750112766177</v>
+        <v>0.8197333740634458</v>
       </c>
       <c r="BC21" s="8" t="n">
-        <v>0.8273972602739726</v>
+        <v>0.8246575342465754</v>
       </c>
       <c r="BD21" s="11" t="n">
-        <v>0.01169871794871795</v>
+        <v>0.01173633440514469</v>
       </c>
       <c r="BE21" s="1" t="n"/>
       <c r="BF21" s="1" t="n"/>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>96.8</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>185.1</v>
+        <v>205</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.09156915338633578</v>
+        <v>0.08714793797107284</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.192868719611021</v>
+        <v>0.08604878048780473</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.909077454137735</v>
+        <v>1.907528683401057</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.748929463804719</v>
+        <v>1.75461739545866</v>
       </c>
       <c r="BC22" s="8" t="n">
-        <v>2.093150684931507</v>
+        <v>2.09041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005238132155573887</v>
+        <v>0.005242385127425895</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9515</v>
+        <v>9526</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02469511455957676</v>
+        <v>0.02470723873157624</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6997237441933788</v>
+        <v>0.6977610146966198</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.394140156605835</v>
+        <v>4.391398586826026</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.288241540503954</v>
+        <v>4.285515336323646</v>
       </c>
       <c r="BC23" s="8" t="n">
-        <v>4.419178082191781</v>
+        <v>4.416438356164384</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.00227575808772661</v>
+        <v>0.002277178853679895</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3465,7 +3465,7 @@
         <v>0.6464574</v>
       </c>
       <c r="AJ24" t="n">
-        <v>36.9</v>
+        <v>38.7</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>47473</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1909340624221614</v>
+        <v>0.1910420804002134</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1965593609756098</v>
+        <v>0.1409054372093022</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.96881801027789</v>
+        <v>2.966006650812791</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.492848348161114</v>
+        <v>2.490261846849403</v>
       </c>
       <c r="BC24" s="8" t="n">
-        <v>3.331506849315069</v>
+        <v>3.328767123287671</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.00336834388816712</v>
+        <v>0.003371536607060421</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37.7</v>
+        <v>38.4</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1488271038556464</v>
+        <v>0.1489052662133557</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9946949602122015</v>
+        <v>0.9583333333333335</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.022477729377995</v>
+        <v>3.019690913388293</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.630924809515792</v>
+        <v>2.628320195050378</v>
       </c>
       <c r="BC25" s="8" t="n">
-        <v>3.331506849315069</v>
+        <v>3.328767123287671</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.003308543815824222</v>
+        <v>0.00331159720872867</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3701,22 +3701,22 @@
         <v>1502</v>
       </c>
       <c r="AY26" s="11" t="n">
-        <v>58.25754481506694</v>
+        <v>58.67286913119789</v>
       </c>
       <c r="AZ26" s="12" t="n">
         <v>-0.06891666666666663</v>
       </c>
       <c r="BA26" s="8" t="n">
-        <v>0.3561643835616438</v>
+        <v>0.3534246575342466</v>
       </c>
       <c r="BB26" s="8" t="n">
-        <v>0.006010447862346885</v>
+        <v>0.005922702606392202</v>
       </c>
       <c r="BC26" s="8" t="n">
-        <v>0.3287671232876712</v>
+        <v>0.326027397260274</v>
       </c>
       <c r="BD26" s="11" t="n">
-        <v>0.02807692307692308</v>
+        <v>0.02829457364341085</v>
       </c>
     </row>
     <row r="27">
@@ -3810,22 +3810,22 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0498214515833668</v>
+        <v>0.0499955943960718</v>
       </c>
       <c r="AZ27" s="12" t="n">
         <v>0.5656469279050043</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.3506849315068493</v>
+        <v>0.347945205479452</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3340424516739847</v>
+        <v>0.3313777765701774</v>
       </c>
       <c r="BC27" s="8" t="n">
-        <v>0.3287671232876712</v>
+        <v>0.326027397260274</v>
       </c>
       <c r="BD27" s="11" t="n">
-        <v>0.028515625</v>
+        <v>0.02874015748031496</v>
       </c>
     </row>
     <row r="28" customFormat="1" s="1">
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13650</v>
+        <v>14000</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3940,15 +3940,15 @@
         <v>1688</v>
       </c>
       <c r="AY28" s="11" t="n">
-        <v>-2.251576429420905</v>
+        <v>-2.269044991695447</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>0.01071077421245414</v>
+        <v>-0.01455699514285713</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
       <c r="BC28" s="8" t="n">
-        <v>0.3287671232876712</v>
+        <v>0.326027397260274</v>
       </c>
       <c r="BD28" s="11" t="n"/>
     </row>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18240</v>
+        <v>17790</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4061,22 +4061,22 @@
         <v>1831</v>
       </c>
       <c r="AY29" s="11" t="n">
-        <v>-0.1683688761538659</v>
+        <v>-0.168543104105735</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.1983273026315788</v>
+        <v>0.2286391231028666</v>
       </c>
       <c r="BA29" s="8" t="n">
-        <v>2.756458240618498</v>
+        <v>2.75374995450986</v>
       </c>
       <c r="BB29" s="8" t="n">
-        <v>3.314520298218769</v>
+        <v>3.311957562812794</v>
       </c>
       <c r="BC29" s="8" t="n">
-        <v>2.827397260273973</v>
+        <v>2.824657534246575</v>
       </c>
       <c r="BD29" s="11" t="n">
-        <v>0.003627843822424891</v>
+        <v>0.003631411771291304</v>
       </c>
     </row>
     <row r="30">
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05492963303701845</v>
+        <v>0.05492846973842921</v>
       </c>
       <c r="AZ30" s="12" t="n">
         <v>0.6656754910333049</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.701129863912174</v>
+        <v>2.698390396258306</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.560483447730953</v>
+        <v>2.557889443373706</v>
       </c>
       <c r="BC30" s="8" t="n">
-        <v>2.827397260273973</v>
+        <v>2.824657534246575</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003702154470098868</v>
+        <v>0.003705912982000823</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4305,22 +4305,22 @@
         <v>1369</v>
       </c>
       <c r="AY31" s="11" t="n">
-        <v>0.1155993936420554</v>
+        <v>0.1156558243537848</v>
       </c>
       <c r="AZ31" s="12" t="n">
         <v>1.044331819704433</v>
       </c>
       <c r="BA31" s="8" t="n">
-        <v>2.236192169718992</v>
+        <v>2.233438124161235</v>
       </c>
       <c r="BB31" s="8" t="n">
-        <v>2.004475963740514</v>
+        <v>2.001906031777226</v>
       </c>
       <c r="BC31" s="8" t="n">
-        <v>2.4</v>
+        <v>2.397260273972603</v>
       </c>
       <c r="BD31" s="11" t="n">
-        <v>0.004471887584355792</v>
+        <v>0.004477401854934077</v>
       </c>
     </row>
     <row r="32">
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>68600</v>
+        <v>66770</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4414,22 +4414,22 @@
         <v>1621</v>
       </c>
       <c r="AY32" s="11" t="n">
-        <v>-0.2644150919873296</v>
+        <v>-0.2648061012463095</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1320408163265305</v>
+        <v>0.1630672457690581</v>
       </c>
       <c r="BA32" s="8" t="n">
-        <v>1.69851406959067</v>
+        <v>1.695788566437233</v>
       </c>
       <c r="BB32" s="8" t="n">
-        <v>2.309065957021257</v>
+        <v>2.306586832823224</v>
       </c>
       <c r="BC32" s="8" t="n">
-        <v>1.701369863013699</v>
+        <v>1.698630136986301</v>
       </c>
       <c r="BD32" s="11" t="n">
-        <v>0.005887499066999151</v>
+        <v>0.005896961565797971</v>
       </c>
     </row>
     <row r="33">
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.0739748980539135</v>
+        <v>-0.07408205981814089</v>
       </c>
       <c r="AZ33" s="12" t="n">
         <v>-0.00631743549648156</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.72882151776872</v>
+        <v>2.726103999021137</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.946811605899203</v>
+        <v>2.944217711653479</v>
       </c>
       <c r="BC33" s="8" t="n">
-        <v>2.827397260273973</v>
+        <v>2.824657534246575</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003664585585713468</v>
+        <v>0.003668238630511053</v>
       </c>
     </row>
     <row r="34">
@@ -4632,22 +4632,22 @@
         <v>634</v>
       </c>
       <c r="AY34" s="11" t="n">
-        <v>0.03312113216063943</v>
+        <v>0.03310295528091618</v>
       </c>
       <c r="AZ34" s="12" t="n">
         <v>0.2248165443629087</v>
       </c>
       <c r="BA34" s="8" t="n">
-        <v>1.730009191695549</v>
+        <v>1.727270183146141</v>
       </c>
       <c r="BB34" s="8" t="n">
-        <v>1.67454632166652</v>
+        <v>1.671924539869766</v>
       </c>
       <c r="BC34" s="8" t="n">
-        <v>1.747945205479452</v>
+        <v>1.745205479452055</v>
       </c>
       <c r="BD34" s="11" t="n">
-        <v>0.005780316109302974</v>
+        <v>0.005789482211627989</v>
       </c>
     </row>
     <row r="35">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>805</v>
+        <v>831.8</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06652186390597495</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9660869565217389</v>
+        <v>0.9027410435200769</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.101161402859654</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>107.5</v>
+        <v>106.4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8917</v>
+        <v>8762</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1054,22 +1054,22 @@
         <v>1036</v>
       </c>
       <c r="AY3" s="11" t="n">
-        <v>0.007498103318900832</v>
+        <v>0.01321730232303311</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1768859369743188</v>
+        <v>0.1854494918968272</v>
       </c>
       <c r="BA3" s="8" t="n">
-        <v>1.804786841542811</v>
+        <v>1.804545387505134</v>
       </c>
       <c r="BB3" s="8" t="n">
-        <v>1.791355076101366</v>
+        <v>1.78100530198981</v>
       </c>
       <c r="BC3" s="8" t="n">
         <v>1.824657534246575</v>
       </c>
       <c r="BD3" s="11" t="n">
-        <v>0.005540820538923898</v>
+        <v>0.005541561918719846</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>109.2</v>
+        <v>110.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0255700540446938</v>
+        <v>0.0224512240634912</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2874105263157896</v>
+        <v>0.2821509824198554</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.449695653906621</v>
+        <v>4.452878500375547</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.33875349261388</v>
+        <v>4.355101148667643</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.824657534246575</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002247344712490724</v>
+        <v>0.002245738346365529</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6064</v>
+        <v>6031</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05483895459386028</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.680161609498681</v>
+        <v>1.69482672856906</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3534246575342465</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24360</v>
+        <v>24290</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.132080850909001</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.05747126436781613</v>
+        <v>0.06051873198847257</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.549697612364303</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24360</v>
+        <v>24290</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09088282271519445</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2118226600985222</v>
+        <v>0.2153149444215727</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.003088344451551</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2092</v>
+        <v>2066</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04129253490281405</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.888209182600382</v>
+        <v>2.93714114714424</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9369863013698631</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>214.4</v>
+        <v>212.2</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1807196494824911</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.595974813432836</v>
+        <v>2.633256361922714</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.715676346610731</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.3</v>
+        <v>104.6</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03873567801644592</v>
+        <v>0.03764066664944925</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4874604863387977</v>
+        <v>0.4917388961748632</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.701972612160273</v>
+        <v>2.702213817456645</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.601212868051205</v>
+        <v>2.604190356361145</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.824657534246575</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003700999764022342</v>
+        <v>0.003700669404988876</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>221.8</v>
+        <v>226.4</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-16.55321539245412</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.02858431018935981</v>
+        <v>-0.04832155477031796</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224.4</v>
+        <v>225.9</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>221.8</v>
+        <v>226.4</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.126862119559157</v>
+        <v>-0.1282012735093229</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.01172227231740308</v>
+        <v>-0.00220848056537104</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.298188753092063</v>
+        <v>4.299380491763697</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.922691878769397</v>
+        <v>4.931620523317745</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.575342465753424</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.002326561390028794</v>
+        <v>0.00232591649405233</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>253.4</v>
+        <v>255.9</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1857017806377094</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.01648441199684303</v>
+        <v>-0.02609280969128569</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.219211282636755</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17790</v>
+        <v>17860</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03272513463858011</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1727468285553684</v>
+        <v>0.1681503964165736</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.826266756005275</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>150</v>
+        <v>148.5</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0217817995202038</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5204</v>
+        <v>0.5357575757575759</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.264517079237326</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>301.9</v>
+        <v>304.9</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24350</v>
+        <v>24400</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3015,22 +3015,22 @@
         <v>224</v>
       </c>
       <c r="AY20" s="11" t="n">
-        <v>-0.5059921600355936</v>
+        <v>-0.5092196071828929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.004558458234086293</v>
+        <v>0.003273200081967076</v>
       </c>
       <c r="BA20" s="8" t="n">
-        <v>1.501791672507348</v>
+        <v>1.501877268294256</v>
       </c>
       <c r="BB20" s="8" t="n">
-        <v>3.040015868200701</v>
+        <v>3.06018188638995</v>
       </c>
       <c r="BC20" s="8" t="n">
         <v>1.487671232876712</v>
       </c>
       <c r="BD20" s="11" t="n">
-        <v>0.006658713177776707</v>
+        <v>0.006658333680858899</v>
       </c>
       <c r="BE20" s="1" t="n"/>
       <c r="BF20" s="1" t="n"/>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>422.5</v>
+        <v>420.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03942918695244019</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5858223005917158</v>
+        <v>0.5945024321751546</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.852054794520548</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>205</v>
+        <v>201.9</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08714793797107284</v>
+        <v>0.08549297373773526</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.08604878048780473</v>
+        <v>0.106141654284299</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.907528683401057</v>
+        <v>1.90797394281616</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.75461739545866</v>
+        <v>1.757702711097551</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.09041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005242385127425895</v>
+        <v>0.005241161724273891</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9526</v>
+        <v>9361</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02470723873157624</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.6977610146966198</v>
+        <v>0.7276862969768187</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.391398586826026</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3479,22 +3479,22 @@
         <v>544</v>
       </c>
       <c r="AY24" s="11" t="n">
-        <v>0.1910420804002134</v>
+        <v>0.1899266058766849</v>
       </c>
       <c r="AZ24" s="12" t="n">
-        <v>0.1409054372093022</v>
+        <v>0.1442463023255811</v>
       </c>
       <c r="BA24" s="8" t="n">
-        <v>2.966006650812791</v>
+        <v>2.966746109665541</v>
       </c>
       <c r="BB24" s="8" t="n">
-        <v>2.490261846849403</v>
+        <v>2.493217728735273</v>
       </c>
       <c r="BC24" s="8" t="n">
         <v>3.328767123287671</v>
       </c>
       <c r="BD24" s="11" t="n">
-        <v>0.003371536607060421</v>
+        <v>0.003370696254533004</v>
       </c>
     </row>
     <row r="25" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38.4</v>
+        <v>37</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1489052662133557</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>0.9583333333333335</v>
+        <v>1.032432432432433</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.019690913388293</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14000</v>
+        <v>14130</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.269044991695447</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.01455699514285713</v>
+        <v>-0.02362334975230007</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17790</v>
+        <v>17940</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.168543104105735</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2286391231028666</v>
+        <v>0.2183662207357859</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.75374995450986</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66770</v>
+        <v>66600</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2648061012463095</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1630672457690581</v>
+        <v>0.166036036036036</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.695788566437233</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>127.9</v>
+        <v>128.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07408205981814089</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.00631743549648156</v>
+        <v>-0.01095719844357967</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.726103999021137</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8762</v>
+        <v>8810</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.01321730232303311</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1854494918968272</v>
+        <v>0.1789907432463109</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.804545387505134</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.0224512240634912</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2821509824198554</v>
+        <v>0.280826446280992</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.452878500375547</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6031</v>
+        <v>6045</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05483895459386028</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.69482672856906</v>
+        <v>1.688585607940447</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3534246575342465</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24290</v>
+        <v>23650</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.132080850909001</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.06051873198847257</v>
+        <v>0.08921775898520079</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.549697612364303</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24290</v>
+        <v>23650</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09088282271519445</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2153149444215727</v>
+        <v>0.2482029598308668</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.003088344451551</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.5</v>
+        <v>96.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04129253490281405</v>
+        <v>0.04474896679915365</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.93714114714424</v>
+        <v>2.926802008716707</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9369863013698631</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8998300381144226</v>
+        <v>0.8968530538398635</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.9095890410958904</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12480</v>
+        <v>12470</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005990713387202561</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4294871794871795</v>
+        <v>0.4306335204490779</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.174657819988498</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03764066664944925</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4917388961748632</v>
+        <v>0.4876742125340596</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.702213817456645</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>226.4</v>
+        <v>224.2</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-16.55321539245412</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.04832155477031796</v>
+        <v>-0.03898305084745757</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225.9</v>
+        <v>224.3</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>226.4</v>
+        <v>224.2</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2210,22 +2210,22 @@
         <v>1006</v>
       </c>
       <c r="AY13" s="11" t="n">
-        <v>-0.1282012735093229</v>
+        <v>-0.1267724410223861</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>-0.00220848056537104</v>
+        <v>0.00044603033006263</v>
       </c>
       <c r="BA13" s="8" t="n">
-        <v>4.299380491763697</v>
+        <v>4.298108837270917</v>
       </c>
       <c r="BB13" s="8" t="n">
-        <v>4.931620523317745</v>
+        <v>4.922094811463804</v>
       </c>
       <c r="BC13" s="8" t="n">
         <v>4.575342465753424</v>
       </c>
       <c r="BD13" s="11" t="n">
-        <v>0.00232591649405233</v>
+        <v>0.002326604648371236</v>
       </c>
     </row>
     <row r="14">
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.9</v>
+        <v>255.7</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1857017806377094</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02609280969128569</v>
+        <v>-0.02533105201407893</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.219211282636755</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17860</v>
+        <v>17830</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03272513463858011</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1681503964165736</v>
+        <v>0.1701158766124511</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.826266756005275</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.45</v>
@@ -2797,22 +2797,22 @@
         <v>2386</v>
       </c>
       <c r="AY18" s="11" t="n">
-        <v>0.163474657029748</v>
+        <v>0.1603937173913823</v>
       </c>
       <c r="AZ18" s="12" t="n">
-        <v>1.254851228978008</v>
+        <v>1.265717981888745</v>
       </c>
       <c r="BA18" s="8" t="n">
-        <v>1.79681993065786</v>
+        <v>1.796951661407982</v>
       </c>
       <c r="BB18" s="8" t="n">
-        <v>1.544356741937971</v>
+        <v>1.548570657076299</v>
       </c>
       <c r="BC18" s="8" t="n">
         <v>1.824657534246575</v>
       </c>
       <c r="BD18" s="11" t="n">
-        <v>0.005565387955341053</v>
+        <v>0.005564979968445344</v>
       </c>
     </row>
     <row r="19">
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>148.5</v>
+        <v>153</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0217817995202038</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.5357575757575759</v>
+        <v>0.4905882352941178</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.264517079237326</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24400</v>
+        <v>24460</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5092196071828929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.003273200081967076</v>
+        <v>0.0008121865085852775</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.501877268294256</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>420.2</v>
+        <v>419.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03942918695244019</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5945024321751546</v>
+        <v>0.5983061116412214</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.852054794520548</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08549297373773526</v>
+        <v>0.08494303029199295</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.106141654284299</v>
+        <v>0.1072808320950966</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.90797394281616</v>
+        <v>1.908121836529253</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.757702711097551</v>
+        <v>1.758729982362039</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.09041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005241161724273891</v>
+        <v>0.005240755495041834</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9361</v>
+        <v>9307</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02470723873157624</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7276862969768187</v>
+        <v>0.7377104787794133</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.391398586826026</v>
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3810,16 +3810,16 @@
         <v>1484</v>
       </c>
       <c r="AY27" s="11" t="n">
-        <v>0.0499955943960718</v>
+        <v>0.05579759844606474</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5656469279050043</v>
+        <v>0.5624903816793894</v>
       </c>
       <c r="BA27" s="8" t="n">
-        <v>0.347945205479452</v>
+        <v>0.3479452054794521</v>
       </c>
       <c r="BB27" s="8" t="n">
-        <v>0.3313777765701774</v>
+        <v>0.3295567313200579</v>
       </c>
       <c r="BC27" s="8" t="n">
         <v>0.326027397260274</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14130</v>
+        <v>14040</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.269044991695447</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.02362334975230007</v>
+        <v>-0.01736452507122499</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17940</v>
+        <v>17620</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.168543104105735</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2183662207357859</v>
+        <v>0.240493189557321</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.75374995450986</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66600</v>
+        <v>67420</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2648061012463095</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.166036036036036</v>
+        <v>0.1518540492435478</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.695788566437233</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>142.8</v>
+        <v>144</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.5</v>
+        <v>128.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4523,22 +4523,22 @@
         <v>1949</v>
       </c>
       <c r="AY33" s="11" t="n">
-        <v>-0.07408205981814089</v>
+        <v>-0.07690367754397723</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.01095719844357967</v>
+        <v>-0.003421461897356148</v>
       </c>
       <c r="BA33" s="8" t="n">
-        <v>2.726103999021137</v>
+        <v>2.72668822057858</v>
       </c>
       <c r="BB33" s="8" t="n">
-        <v>2.944217711653479</v>
+        <v>2.953850160862798</v>
       </c>
       <c r="BC33" s="8" t="n">
         <v>2.824657534246575</v>
       </c>
       <c r="BD33" s="11" t="n">
-        <v>0.003668238630511053</v>
+        <v>0.003667452671900304</v>
       </c>
     </row>
     <row r="34">

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>831.8</v>
+        <v>831.7</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06652186390597495</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9027410435200769</v>
+        <v>0.9029698208488635</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.101161402859654</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8810</v>
+        <v>8847</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.01321730232303311</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1789907432463109</v>
+        <v>0.174059957951848</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.804545387505134</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110.7</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.0224512240634912</v>
+        <v>0.02389995896165496</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.280826446280992</v>
+        <v>0.2714138286893706</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.452878500375547</v>
+        <v>4.45140196154347</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.355101148667643</v>
+        <v>4.347496962552546</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.824657534246575</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002245738346365529</v>
+        <v>0.002246483262215354</v>
       </c>
     </row>
     <row r="5">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23650</v>
+        <v>23930</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.132080850909001</v>
+        <v>-0.1227550938052214</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.08921775898520079</v>
+        <v>0.002925198495612236</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.549697612364303</v>
+        <v>6.528631539873046</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.546437498497438</v>
+        <v>7.442199428882708</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001526788043026953</v>
+        <v>0.001531714562068004</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23650</v>
+        <v>23930</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09088282271519445</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2482029598308668</v>
+        <v>0.2335979941496029</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.003088344451551</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2065</v>
+        <v>2058</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1620,7 +1620,7 @@
         <v>0.04474896679915365</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.926802008716707</v>
+        <v>2.940158478134111</v>
       </c>
       <c r="BA8" s="8" t="n">
         <v>0.9369863013698631</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>212.2</v>
+        <v>215</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1807196494824911</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.633256361922714</v>
+        <v>2.585939534883721</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.715676346610731</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12470</v>
+        <v>12480</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1862,7 +1862,7 @@
         <v>-0.005990713387202561</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4306335204490779</v>
+        <v>0.4294871794871795</v>
       </c>
       <c r="BA10" s="4" t="n">
         <v>4.174657819988498</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>104.6</v>
+        <v>104.5</v>
       </c>
       <c r="F11" t="n">
         <v>1.93</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1101</v>
+        <v>1111</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1996,22 +1996,22 @@
         <v>126</v>
       </c>
       <c r="AY11" s="11" t="n">
-        <v>0.03764066664944925</v>
+        <v>0.03800518468499123</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4876742125340596</v>
+        <v>0.4728743564356435</v>
       </c>
       <c r="BA11" s="8" t="n">
-        <v>2.702213817456645</v>
+        <v>2.70213353735</v>
       </c>
       <c r="BB11" s="8" t="n">
-        <v>2.604190356361145</v>
+        <v>2.603198497674201</v>
       </c>
       <c r="BC11" s="8" t="n">
         <v>2.824657534246575</v>
       </c>
       <c r="BD11" s="11" t="n">
-        <v>0.003700669404988876</v>
+        <v>0.0037007793514924</v>
       </c>
     </row>
     <row r="12">
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>224.2</v>
+        <v>223.7</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-16.55321539245412</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.03898305084745757</v>
+        <v>-0.0368350469378631</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>224.2</v>
+        <v>223.7</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1267724410223861</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.00044603033006263</v>
+        <v>0.002682163611980481</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.298108837270917</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>255.7</v>
+        <v>257.6</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1857017806377094</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.02533105201407893</v>
+        <v>-0.03251999223602497</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.219211282636755</v>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>176.2</v>
+        <v>171.5</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         <v>1532</v>
       </c>
       <c r="AY15" s="11" t="n">
-        <v>-0.1895065144886296</v>
+        <v>-0.1787324544724126</v>
       </c>
       <c r="AZ15" s="12" t="n">
-        <v>0.1943905472636815</v>
+        <v>0.162531094527363</v>
       </c>
       <c r="BA15" s="8" t="n">
-        <v>1.977309658309824</v>
+        <v>1.974786632512631</v>
       </c>
       <c r="BB15" s="8" t="n">
-        <v>2.43963670733549</v>
+        <v>2.404559443833879</v>
       </c>
       <c r="BC15" s="8" t="n">
         <v>2.09041095890411</v>
       </c>
       <c r="BD15" s="11" t="n">
-        <v>0.005057376803867865</v>
+        <v>0.005063838206802344</v>
       </c>
     </row>
     <row r="16">
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17830</v>
+        <v>17770</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2540,7 +2540,7 @@
         <v>-0.03272513463858011</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1701158766124511</v>
+        <v>0.1740667462014633</v>
       </c>
       <c r="BA16" s="8" t="n">
         <v>1.826266756005275</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>153</v>
+        <v>152.3</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2909,7 +2909,7 @@
         <v>0.0217817995202038</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4905882352941178</v>
+        <v>0.4974392646093235</v>
       </c>
       <c r="BA19" s="8" t="n">
         <v>3.264517079237326</v>
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24460</v>
+        <v>24490</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5092196071828929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>0.0008121865085852775</v>
+        <v>-0.0004137982033484144</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.501877268294256</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>419.2</v>
+        <v>417.2</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03942918695244019</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.5983061116412214</v>
+        <v>0.6059681735378715</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.852054794520548</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>97.2</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
         <v>1.75</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>201.9</v>
+        <v>201.7</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3261,22 +3261,22 @@
         <v>345</v>
       </c>
       <c r="AY22" s="11" t="n">
-        <v>0.08494303029199295</v>
+        <v>0.09159921833146163</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.1072808320950966</v>
+        <v>0.09469509172037682</v>
       </c>
       <c r="BA22" s="8" t="n">
-        <v>1.908121836529253</v>
+        <v>1.90632962222545</v>
       </c>
       <c r="BB22" s="8" t="n">
-        <v>1.758729982362039</v>
+        <v>1.746364041135285</v>
       </c>
       <c r="BC22" s="8" t="n">
         <v>2.09041095890411</v>
       </c>
       <c r="BD22" s="11" t="n">
-        <v>0.005240755495041834</v>
+        <v>0.005245682532240147</v>
       </c>
     </row>
     <row r="23">
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9307</v>
+        <v>9358</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3373,7 +3373,7 @@
         <v>0.02470723873157624</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.7377104787794133</v>
+        <v>0.728240160931823</v>
       </c>
       <c r="BA23" s="8" t="n">
         <v>4.391398586826026</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3588,22 +3588,22 @@
         <v>494</v>
       </c>
       <c r="AY25" s="11" t="n">
-        <v>0.1489052662133557</v>
+        <v>0.1503644689107819</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.032432432432433</v>
+        <v>1.024324324324324</v>
       </c>
       <c r="BA25" s="8" t="n">
-        <v>3.019690913388293</v>
+        <v>3.018811215239059</v>
       </c>
       <c r="BB25" s="8" t="n">
-        <v>2.628320195050378</v>
+        <v>2.624221537455349</v>
       </c>
       <c r="BC25" s="8" t="n">
         <v>3.328767123287671</v>
       </c>
       <c r="BD25" s="11" t="n">
-        <v>0.00331159720872867</v>
+        <v>0.003312562226322623</v>
       </c>
       <c r="BF25" s="16" t="n"/>
     </row>
@@ -3796,7 +3796,7 @@
         <v>18.60784</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="AK27" s="10" t="n">
         <v>46377</v>
@@ -3813,7 +3813,7 @@
         <v>0.05579759844606474</v>
       </c>
       <c r="AZ27" s="12" t="n">
-        <v>0.5624903816793894</v>
+        <v>0.545449798657718</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>0.3479452054794521</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14040</v>
+        <v>13810</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.269044991695447</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.01736452507122499</v>
+        <v>-0.0009991261404779239</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17620</v>
+        <v>17630</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.168543104105735</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.240493189557321</v>
+        <v>0.2397895632444695</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.75374995450986</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="F30" t="n">
         <v>0.1</v>
@@ -4191,22 +4191,22 @@
         <v>1974</v>
       </c>
       <c r="AY30" s="11" t="n">
-        <v>0.05492846973842921</v>
+        <v>0.05376751651355594</v>
       </c>
       <c r="AZ30" s="12" t="n">
-        <v>0.6656754910333049</v>
+        <v>0.6706725175064048</v>
       </c>
       <c r="BA30" s="8" t="n">
-        <v>2.698390396258306</v>
+        <v>2.698648175815709</v>
       </c>
       <c r="BB30" s="8" t="n">
-        <v>2.557889443373706</v>
+        <v>2.560952139371619</v>
       </c>
       <c r="BC30" s="8" t="n">
         <v>2.824657534246575</v>
       </c>
       <c r="BD30" s="11" t="n">
-        <v>0.003705912982000823</v>
+        <v>0.003705558986760971</v>
       </c>
       <c r="BE30" s="1" t="n"/>
       <c r="BF30" s="1" t="n"/>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>67420</v>
+        <v>66980</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2648061012463095</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1518540492435478</v>
+        <v>0.1594207226037623</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.695788566437233</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.6</v>
+        <v>128.5</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07690367754397723</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.003421461897356148</v>
+        <v>-0.002645914396887217</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.72668822057858</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>831.7</v>
+        <v>806</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06652186390597495</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9029698208488635</v>
+        <v>0.9636476426799006</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.101161402859654</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8847</v>
+        <v>8870</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.01321730232303311</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.174059957951848</v>
+        <v>0.1710156085682075</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.804545387505134</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>110.7</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1163,22 +1163,22 @@
         <v>1978</v>
       </c>
       <c r="AY4" s="11" t="n">
-        <v>0.02389995896165496</v>
+        <v>0.0224512240634912</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2714138286893706</v>
+        <v>0.2781855670103093</v>
       </c>
       <c r="BA4" s="8" t="n">
-        <v>4.45140196154347</v>
+        <v>4.452878500375547</v>
       </c>
       <c r="BB4" s="8" t="n">
-        <v>4.347496962552546</v>
+        <v>4.355101148667643</v>
       </c>
       <c r="BC4" s="8" t="n">
         <v>4.824657534246575</v>
       </c>
       <c r="BD4" s="11" t="n">
-        <v>0.002246483262215354</v>
+        <v>0.002245738346365529</v>
       </c>
     </row>
     <row r="5">
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6045</v>
+        <v>6010</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05483895459386028</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.688585607940447</v>
+        <v>1.704242928452579</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3534246575342465</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23930</v>
+        <v>23810</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1402,7 +1402,7 @@
         <v>-0.1227550938052214</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.002925198495612236</v>
+        <v>0.007979840403191885</v>
       </c>
       <c r="BA6" s="8" t="n">
         <v>6.528631539873046</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23930</v>
+        <v>23810</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1511,7 +1511,7 @@
         <v>-0.09088282271519445</v>
       </c>
       <c r="AZ7" s="12" t="n">
-        <v>0.2335979941496029</v>
+        <v>0.239815203695926</v>
       </c>
       <c r="BA7" s="8" t="n">
         <v>2.003088344451551</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>84.29154</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2058</v>
+        <v>2041</v>
       </c>
       <c r="AK8" s="10" t="n">
         <v>46590</v>
@@ -1617,16 +1617,16 @@
         <v>1581</v>
       </c>
       <c r="AY8" s="11" t="n">
-        <v>0.04474896679915365</v>
+        <v>0.04359443040271956</v>
       </c>
       <c r="AZ8" s="12" t="n">
-        <v>2.940158478134111</v>
+        <v>2.977106958353748</v>
       </c>
       <c r="BA8" s="8" t="n">
-        <v>0.9369863013698631</v>
+        <v>0.9369863013698632</v>
       </c>
       <c r="BB8" s="8" t="n">
-        <v>0.8968530538398635</v>
+        <v>0.8978452491436576</v>
       </c>
       <c r="BC8" s="8" t="n">
         <v>0.9095890410958904</v>
@@ -1712,7 +1712,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>46895</v>
@@ -1732,7 +1732,7 @@
         <v>0.1807196494824911</v>
       </c>
       <c r="AZ9" s="12" t="n">
-        <v>2.585939534883721</v>
+        <v>2.536591743119266</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>1.715676346610731</v>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111.5</v>
+        <v>110.1</v>
       </c>
       <c r="F10" t="n">
         <v>-1.15</v>
@@ -1845,7 +1845,7 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12480</v>
+        <v>12440</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>47840</v>
@@ -1859,22 +1859,22 @@
         <v>1884</v>
       </c>
       <c r="AY10" s="2" t="n">
-        <v>-0.005990713387202561</v>
+        <v>-0.003011835643982028</v>
       </c>
       <c r="AZ10" s="3" t="n">
-        <v>0.4294871794871795</v>
+        <v>0.4160771704180064</v>
       </c>
       <c r="BA10" s="4" t="n">
-        <v>4.174657819988498</v>
+        <v>4.173145106675152</v>
       </c>
       <c r="BB10" s="4" t="n">
-        <v>4.199817724252991</v>
+        <v>4.185751903454843</v>
       </c>
       <c r="BC10" s="4" t="n">
         <v>4.334246575342465</v>
       </c>
       <c r="BD10" s="2" t="n">
-        <v>0.002395405906591777</v>
+        <v>0.00239627421150645</v>
       </c>
       <c r="BE10" s="1" t="n">
         <v>3.73</v>
@@ -1982,7 +1982,7 @@
         <v>15.65898</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AK11" s="10" t="n">
         <v>47289</v>
@@ -1999,7 +1999,7 @@
         <v>0.03800518468499123</v>
       </c>
       <c r="AZ11" s="12" t="n">
-        <v>0.4728743564356435</v>
+        <v>0.4742012702702703</v>
       </c>
       <c r="BA11" s="8" t="n">
         <v>2.70213353735</v>
@@ -2091,7 +2091,7 @@
         <v>1.35</v>
       </c>
       <c r="AJ12" t="n">
-        <v>223.7</v>
+        <v>223.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>46258</v>
@@ -2108,7 +2108,7 @@
         <v>-16.55321539245412</v>
       </c>
       <c r="AZ12" s="12" t="n">
-        <v>-0.0368350469378631</v>
+        <v>-0.0359731543624161</v>
       </c>
       <c r="BA12" s="8" t="n"/>
       <c r="BB12" s="8" t="n"/>
@@ -2196,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>223.7</v>
+        <v>223.5</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>47928</v>
@@ -2213,7 +2213,7 @@
         <v>-0.1267724410223861</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>0.002682163611980481</v>
+        <v>0.003579418344519025</v>
       </c>
       <c r="BA13" s="8" t="n">
         <v>4.298108837270917</v>
@@ -2305,7 +2305,7 @@
         <v>1.12975</v>
       </c>
       <c r="AJ14" t="n">
-        <v>257.6</v>
+        <v>258.8</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>47473</v>
@@ -2322,7 +2322,7 @@
         <v>-0.1857017806377094</v>
       </c>
       <c r="AZ14" s="12" t="n">
-        <v>-0.03251999223602497</v>
+        <v>-0.03700598918083464</v>
       </c>
       <c r="BA14" s="8" t="n">
         <v>3.219211282636755</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111.2</v>
+        <v>111.6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>187.6184</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17770</v>
+        <v>17810</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>46924</v>
@@ -2537,22 +2537,22 @@
         <v>767</v>
       </c>
       <c r="AY16" s="11" t="n">
-        <v>-0.03272513463858011</v>
+        <v>-0.03461862955904856</v>
       </c>
       <c r="AZ16" s="12" t="n">
-        <v>0.1740667462014633</v>
+        <v>0.1756436518809656</v>
       </c>
       <c r="BA16" s="8" t="n">
-        <v>1.826266756005275</v>
+        <v>1.82631083645915</v>
       </c>
       <c r="BB16" s="8" t="n">
-        <v>1.888053563061307</v>
+        <v>1.891802444483631</v>
       </c>
       <c r="BC16" s="8" t="n">
         <v>1.824657534246575</v>
       </c>
       <c r="BD16" s="11" t="n">
-        <v>0.005475651334678907</v>
+        <v>0.00547551917251282</v>
       </c>
     </row>
     <row r="17">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>108.6</v>
+        <v>107</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>2.1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>152.3</v>
+        <v>150.9</v>
       </c>
       <c r="AK19" s="10" t="n">
         <v>47532</v>
@@ -2906,22 +2906,22 @@
         <v>1238</v>
       </c>
       <c r="AY19" s="11" t="n">
-        <v>0.0217817995202038</v>
+        <v>0.02634205663916618</v>
       </c>
       <c r="AZ19" s="12" t="n">
-        <v>0.4974392646093235</v>
+        <v>0.4890656063618291</v>
       </c>
       <c r="BA19" s="8" t="n">
-        <v>3.264517079237326</v>
+        <v>3.262168967740881</v>
       </c>
       <c r="BB19" s="8" t="n">
-        <v>3.194925844999626</v>
+        <v>3.178442261659916</v>
       </c>
       <c r="BC19" s="8" t="n">
         <v>3.49041095890411</v>
       </c>
       <c r="BD19" s="11" t="n">
-        <v>0.003063240215099825</v>
+        <v>0.003065445137541482</v>
       </c>
     </row>
     <row r="20">
@@ -3001,7 +3001,7 @@
         <v>80.28818</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24490</v>
+        <v>24520</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>46801</v>
@@ -3018,7 +3018,7 @@
         <v>-0.5092196071828929</v>
       </c>
       <c r="AZ20" s="12" t="n">
-        <v>-0.0004137982033484144</v>
+        <v>-0.001636782952691762</v>
       </c>
       <c r="BA20" s="8" t="n">
         <v>1.501877268294256</v>
@@ -3112,7 +3112,7 @@
         <v>6.72026</v>
       </c>
       <c r="AJ21" t="n">
-        <v>417.2</v>
+        <v>415.1</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>46559</v>
@@ -3129,7 +3129,7 @@
         <v>0.03942918695244019</v>
       </c>
       <c r="AZ21" s="12" t="n">
-        <v>0.6059681735378715</v>
+        <v>0.6140928017345215</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.852054794520548</v>
@@ -3244,7 +3244,7 @@
         <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>201.7</v>
+        <v>199.5</v>
       </c>
       <c r="AK22" s="10" t="n">
         <v>47021</v>
@@ -3264,7 +3264,7 @@
         <v>0.09159921833146163</v>
       </c>
       <c r="AZ22" s="12" t="n">
-        <v>0.09469509172037682</v>
+        <v>0.1067669172932331</v>
       </c>
       <c r="BA22" s="8" t="n">
         <v>1.90632962222545</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>91.8</v>
+        <v>91.5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>176.17507</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9358</v>
+        <v>9354</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>47870</v>
@@ -3370,22 +3370,22 @@
         <v>445</v>
       </c>
       <c r="AY23" s="11" t="n">
-        <v>0.02470723873157624</v>
+        <v>0.02546903264876205</v>
       </c>
       <c r="AZ23" s="12" t="n">
-        <v>0.728240160931823</v>
+        <v>0.7233289400256575</v>
       </c>
       <c r="BA23" s="8" t="n">
-        <v>4.391398586826026</v>
+        <v>4.391282640462611</v>
       </c>
       <c r="BB23" s="8" t="n">
-        <v>4.285515336323646</v>
+        <v>4.282218673264109</v>
       </c>
       <c r="BC23" s="8" t="n">
         <v>4.416438356164384</v>
       </c>
       <c r="BD23" s="11" t="n">
-        <v>0.002277178853679895</v>
+        <v>0.00227723897975889</v>
       </c>
     </row>
     <row r="24" customFormat="1" s="1">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>47473</v>
@@ -3591,7 +3591,7 @@
         <v>0.1503644689107819</v>
       </c>
       <c r="AZ25" s="12" t="n">
-        <v>1.024324324324324</v>
+        <v>1.008042895442359</v>
       </c>
       <c r="BA25" s="8" t="n">
         <v>3.018811215239059</v>
@@ -3923,7 +3923,7 @@
         <v>26.18372</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13810</v>
+        <v>13780</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>46377</v>
@@ -3943,7 +3943,7 @@
         <v>-2.269044991695447</v>
       </c>
       <c r="AZ28" s="12" t="n">
-        <v>-0.0009991261404779239</v>
+        <v>0.001175766908563247</v>
       </c>
       <c r="BA28" s="8" t="n"/>
       <c r="BB28" s="8" t="n"/>
@@ -4047,7 +4047,7 @@
         <v>115.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17630</v>
+        <v>17490</v>
       </c>
       <c r="AK29" s="10" t="n">
         <v>47289</v>
@@ -4064,7 +4064,7 @@
         <v>-0.168543104105735</v>
       </c>
       <c r="AZ29" s="12" t="n">
-        <v>0.2397895632444695</v>
+        <v>0.2497135506003429</v>
       </c>
       <c r="BA29" s="8" t="n">
         <v>2.75374995450986</v>
@@ -4400,7 +4400,7 @@
         <v>430</v>
       </c>
       <c r="AJ32" t="n">
-        <v>66980</v>
+        <v>66600</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>46878</v>
@@ -4417,7 +4417,7 @@
         <v>-0.2648061012463095</v>
       </c>
       <c r="AZ32" s="12" t="n">
-        <v>0.1594207226037623</v>
+        <v>0.166036036036036</v>
       </c>
       <c r="BA32" s="8" t="n">
         <v>1.695788566437233</v>
@@ -4509,7 +4509,7 @@
         <v>0.89</v>
       </c>
       <c r="AJ33" t="n">
-        <v>128.5</v>
+        <v>128.6</v>
       </c>
       <c r="AK33" s="10" t="n">
         <v>47289</v>
@@ -4526,7 +4526,7 @@
         <v>-0.07690367754397723</v>
       </c>
       <c r="AZ33" s="12" t="n">
-        <v>-0.002645914396887217</v>
+        <v>-0.003421461897356148</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>2.72668822057858</v>

--- a/ytm_computed.xlsx
+++ b/ytm_computed.xlsx
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>806</v>
+        <v>832.9</v>
       </c>
       <c r="AK2" s="10" t="n">
         <v>47473</v>
@@ -946,7 +946,7 @@
         <v>0.06652186390597495</v>
       </c>
       <c r="AZ2" s="12" t="n">
-        <v>0.9636476426799006</v>
+        <v>0.9002281186216832</v>
       </c>
       <c r="BA2" s="8" t="n">
         <v>3.101161402859654</v>
@@ -1040,7 +1040,7 @@
         <v>97.62132</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8870</v>
+        <v>8862</v>
       </c>
       <c r="AK3" s="10" t="n">
         <v>46924</v>
@@ -1057,7 +1057,7 @@
         <v>0.01321730232303311</v>
       </c>
       <c r="AZ3" s="12" t="n">
-        <v>0.1710156085682075</v>
+        <v>0.172072720379147</v>
       </c>
       <c r="BA3" s="8" t="n">
         <v>1.804545387505134</v>
@@ -1149,7 +1149,7 @@
         <v>1.12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AK4" s="10" t="n">
         <v>48019</v>
@@ -1166,7 +1166,7 @@
         <v>0.0224512240634912</v>
       </c>
       <c r="AZ4" s="12" t="n">
-        <v>0.2781855670103093</v>
+        <v>0.2768692070030898</v>
       </c>
       <c r="BA4" s="8" t="n">
         <v>4.452878500375547</v>
@@ -1258,7 +1258,7 @@
         <v>165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6010</v>
+        <v>6070</v>
       </c>
       <c r="AK5" s="10" t="n">
         <v>46377</v>
@@ -1275,7 +1275,7 @@
         <v>0.05483895459386028</v>
       </c>
       <c r="AZ5" s="12" t="n">
-        <v>1.704242928452579</v>
+        <v>1.677512355848435</v>
       </c>
       <c r="BA5" s="8" t="n">
         <v>0.3534246575342465</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>300</v>
+        <v>307.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23810</v>
+        <v>24010</v>
       </c>
       <c r="AK6" s="10" t="n">
         <v>48813</v>
@@ -1399,22 +1399,22 @@
         <v>720</v>
       </c>
       <c r="AY6" s="11" t="n">
-        <v>-0.1227550938052214</v>
+        <v>-0.1260228373785039</v>
       </c>
       <c r="AZ6" s="12" t="n">
-        <v>0.007979840403191885</v>
+        <v>0.02457309454393997</v>
       </c>
       <c r="BA6" s="8" t="n">
-        <v>6.528631539873046</v>
+        <v>6.536100761162104</v>
       </c>
       <c r="BB6" s="8" t="n">
-        <v>7.442199428882708</v>
+        <v>7.478571569944755</v>
       </c>
       <c r="BC6" s="8" t="n">
         <v>7</v>
       </c>
       <c r="BD6" s="11" t="n">
-        <v>0.001531714562068004</v>
+        <v>0.001529964173658489</v>
       </c>
     </row>
     <row r="7">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23810</v>
+        <v>24010</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>46987</v>
@@ -1508,22 +1508,22 @@
         <v>720</v>
       </c>
       <c r="AY7" s="11" t="n">
-     